--- a/reports/file_approval/report.xlsx
+++ b/reports/file_approval/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="213">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cc57-75e5-7003-92f0-f32c0437136e</t>
+    <t>01a0cce0-bc30-7871-9658-56d600af9884</t>
   </si>
   <si>
     <t>Recording</t>
@@ -183,7 +183,7 @@
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T03:35:56.284466Z</t>
+    <t>2026-09-23T06:06:28.037095Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cc57-75ee-7b10-b3be-fcd4fd79ebdf</t>
+    <t>01a0cce0-bc37-7fd3-bc0c-f454386957f0</t>
   </si>
   <si>
     <t>Fresh input</t>
@@ -357,9 +357,9 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0c7ac8f62ac0da58006ab34997d8b887d2b4b1a2b5d19b9956", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0mYutBTuVmr3WROenirVHao2b3cnCdY4JrexNIFLURMXlxfOWAQZgqbfAgEJGNFOWGADxjH8Io_J0m28TKcMmYj0InEHwozndBYw9YbaR5r0RBGorXX5dL-lQebJbG5Sx0V8Fsn7HJKtvq-qWSZslk8Yj9xnCzrOHp5ciqA2dENNbRSr8c-295MkZ8anddSW6mo64qo5NwVL6ml4lFjOzRZM-1ex1SXsGnBEUwqjfGMByYZH16tEw3d-8RS4QM_BuaIFQC3T7bUibFsFgHLYtr4lmyFYBRrG662T_A7GhooAdPI6x8kBqevjmSpSITdJUznGQlshj6grntaM8DhZzUhz7ziZpyclEHd6WbqxJVIMrYrercab2scmSPO0HA8hsOwNVMggCCgJUFMcOw6nOFmMkoL0SKDwPpgpvaRe6Y3KQPJqKHYN3xBXsUJluHYsLioMFVSaX4-Y1pGLMSExFBLK-S051sFNJNDQo2kcaqKzYxutVZjnhcneIUjHQt3g4WW31nD2mzY1pUDWulXfFraj2T_x94Cow3Gy4UfcMwnbSi_FAg52bJw-RZ92PycNfChn3cZeZBurQCdgza2CxEooM9gu6xBhAr_5amh7eh5jrR4PfS0rUWM7usyASoSAMD6S0sBWVnN_dDMSKM2MIQiHzYh5DOqSPJPM2gKzgdNhP1m7cMU2e5ovbp4O3McC6iVrwy99gwKaBdw5oJqXqzeyTo0Fj2Sz3jW1ryKdYJPRWkIZn76T1VsEDzSlgZrktNXXyB4PsJ-w_-NYyG6x-voNwbLS92kOMjS4S6jxXTswVTvVgKnQZ15hLYpVU_eYIQNKjq3aIuDlIOyIIxDuQTzzwLTV9L6WwPo-C4Ui-qkyPu_vNV1OfBUfvpdJ2VDdp0HrLeFTrWghkXYO3Kycmgi2jm7CLGR0XtVntWL9ndKsfMz3iyrOSx-nLPE8lviz6MZXdSyEhCu3DmhaUuR4czrAMV7NlpflaT7f5kAEAt48RaNfCcVW0YFin5xjgsdsMIS4s999tff6YArGiHPPqUcNLIwNlv-C8dY8l6FbAyC6RwMQvW_0922Dvht_-_XS3EP59MY9nZhUOB_fQPP7z7IY7LmBl5C5PVmVO-lz6chBRU_pK3skDNY0zMiKWA31x8SimHA6yLs213nO9zW7NQuYr3vLV0DqQ3yt_gIImFxNTsP0Jh8WI5v1sZFwqAXvaY7_Um0Tf9jX1RVofeEyACKwSkfUvc_5VGC4yhln41FNQA="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/source.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_XCU0lXdpIwD2ku5VcUwWzYxW", "id": "fc_0c7ac8f62ac0da58006ab34998670c87d29ceef5e11e38fdb6", "index": 1}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_lVnz2mNu8T1B7JT12UR7J2gr", "id": "fc_0c7ac8f62ac0da58006ab34998672487d2bcf9dadbd863051c", "index": 2}]
-{"name": "read_file", "args": {"file_path": "/source.txt", "offset": 0, "limit": 100}, "id": "call_XCU0lXdpIwD2ku5VcUwWzYxW", "type": "tool_call"}
-{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_lVnz2mNu8T1B7JT12UR7J2gr", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0be63b89bf4dc92a006ab36cbc7a7087d2a1d7d74fa055e1af", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2y9XDRLSkVTrLY5v91PlOqHPv504476Ch61y59qcC5WeZzNEU4hsksRNaapJYk7EZvEJldQ3O6ppVx3kZh0TS_aHmegwEvu7_maiQIvHUk_yL23q7FdTFAhi7mSxJdUFBoaa00u_D1AWIVjUJrZMkfjI7Xb0KzAhufCbkgcdywGkh7HK9WFn6fJeM6hb_iU_kySbeqEZEwh1ZIdhS2uLFy5I2TJ25C5Dw8CYTsG2WlDzIqp6-ZFAS84fb1utr_qrGy-xnwcF_Zo33gCUsRa7EUntxJSRryYo34k69LgqnnP0paIlzNwYQmtsRDCwvmiMaHel0_Y3hkdeSq2BUn81E6CHtYaBQdl9mgGmMdF289Ves4JzL8gpBvuAmjTQK8J6vvo3K3RdrUYf_9w7z50A-F0JxagnR04Fcq8EYFU5BIuHUgzvrfqDpb3QuGQCJeZG23sHr8GFjVNUWgfbQavZOpya-zLWHVyyiNOk-TIe_D0-m1bnzEgLsWKkK5UDDle7-0lfMYIoAWLoXnqKpThPowSTIslrByIJk7-Hc_nUOemXP8qWaCWA0rjHW1o_4m9wH-e7by9a4kYCRp9lRaOB_zOhYCx_lk68Eyjnf2ULn1N1GxvMDsyf6bBkrZkS05nHBGGmXbkmMqUuxSIGtY1-CI5WYpl5O3cDpU4c0YMAUztzZmtEI6p1zNVqiV0og_AQzzsbXHzu4pQlp00sWbc8DbbpIsQN6fXklLR0AKCC0jQUACyCdQ-yQcRw2Z77L5ZKyfI-U_6F65Gv1_KBh9-u2h7AfsBn52R2gM9X6AzAxSOMD4T80l-WYtAyc0T-vuelwkPSsHdWCwjXCKHWrq70dA5qR1Y2kgA0b03pus9_Y64UjSF0wyz4wZt0Eo1yeIAVWhlJGfePTB5vtVQU-dBP2-HrY7QdSbLUNysuh2d-271UozfvH9P4r7wtEEFIIl8J-v1Cke2YZxF3qWqwuO_UhBywqV0iASV-d1fEceKBbHzXuGGcbuHxa9K_gV4HqNhiqOc2W-bJ2Kx4bMgerhzOE4J4ZkKEUuh-W3SSmKxIdzzvTAVCO777QdoRQRa1kVz-XhQO3t_KYcBTEfYAWyAJWna0-7k_0IpDQNcNG_ulC6VK0rK2Zdap4mxeasP4DuyA_ZH-_0JJdsFBwWaUEvDg60qqNVIVnEfTdDTenRjMMFCnXV8V1MPODnKpODVB648terbMOXu5t3_OTJvaHEI7wxtO1dWXtBW0ksHEytfPFkUJVvSJOxMTg2MZMmZhEDYpW6Sg9djqACu5HAlt26UTzZqmdVC74wPLKgmiaezq5EkbB4="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/source.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_ymjhEvEzLR32bCmpdnAVgwsg", "id": "fc_0be63b89bf4dc92a006ab36cbda66487d2b5060e5c92d6d6d1", "index": 1}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_J0P3mDBwugsB5VQBS6x7sN9t", "id": "fc_0be63b89bf4dc92a006ab36cbda67c87d2a2812f7792d543b7", "index": 2}]
+{"name": "read_file", "args": {"file_path": "/source.txt", "offset": 0, "limit": 100}, "id": "call_ymjhEvEzLR32bCmpdnAVgwsg", "type": "tool_call"}
+{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_J0P3mDBwugsB5VQBS6x7sN9t", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -371,7 +371,7 @@
     <t>Tool · read_file</t>
   </si>
   <si>
-    <t>01a0cc57-7c37-7a33-bb56-fbd2be72e9dc</t>
+    <t>01a0cce0-c65d-7f22-a15a-af95c767fec7</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -388,111 +388,10 @@
 We prepare clear, practical reports.</t>
   </si>
   <si>
-    <t>01a0cc57-7c37-7a33-bb56-fbe0c49ae93b</t>
+    <t>01a0cce0-c65d-7f22-a15a-afa233874ea3</t>
   </si>
   <si>
     <t>{'file_path': '/target.txt', 'offset': 0, 'limit': 100}</t>
-  </si>
-  <si>
-    <t>@@ lines 1-8 of 8 @@
-Project summary
-We prepare clear, practical reports.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>01a0cc57-7c3c-7b93-9042-b3ef499cd007</t>
-  </si>
-  <si>
-    <t>Conversation history · cache read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Tool result</t>
-  </si>
-  <si>
-    <t>@@ lines 1-2 of 2 @@
-Project summary
-We prepare clear, practical reports.
-@@ lines 1-8 of 8 @@
-Project summary
-We prepare clear, practical reports.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0c7ac8f62ac0da58006ab34999403c87d2bba9d0982e4a543f", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0maql7MvfjDzgK9w89idVuwdtayjGcqBHTh4WIWu3WRd_FH3zPxsoMjs5RAojRyLvkefRCNwMkc4sOu6oTtKJm4hbwjI3Q-X-qI00EZKoPzkFX4n-w6ZBc9Jp9NUP6YSDOsBz3-6_OGQRZqVoQMLBH68_Y8Er5fGua7aeXjesflaBTS5ZYv1rwTUAXDVVFOwYhefPpgGsRyqvcsVa2f_PgJ1quDVAoT-mZOytXFCMSlfyeNl_jOwUPImuqkqboDOx-cVuUJbP61pPHb62GPgjgfbZvNd7dC6bD8dGUXXJPV2vCTvkQZqVA5Q8sdby9wG8XocTL5xN7hYe7O0OTvxpYiAAWCXAGBW9VACGZHof4HrZlOy-hUFhV5b_sGRF7s--SlvJHsbD-etm_36QfIF5NXtcMfGOnRrvXDUFFemNTebFRtDQhENdi5ae3ElLlgwPYeJ4RjmGr65vUsX-VHeIomZiKqW8kV2rfwI28A0odLbWyN-6iK-UZTHw-VIsLlgvpB4Dzugm8bD9VRG78g_9QE9ZOOTkjYqPHmddUDDYMDbNuv3X7GbkxGBbEne3uPO_UsxtKzgb5zeyy4lGsL1NbMEqDnImYIz-1daEAZ8FOi-GnA32XRlQ86XSTeVAaLE7tMJFeIfm_UtEFnRc-30vzDCJJvwU3cyVAyc_6_XaXFPxQizAtdGVPcwNQUWJqOmZmGlS1seeOBQHIZdioA9CvBuDJzchDjdCwyVrUEcKyfztAy7grt5HNiEVMYF_QaGUnSoe1t9SI_bWXllX8F_IhjJQnruygG87BT0lWqMshJNA1jgd4f5evWUudDXPc5jCnyWRTDNjZtHK1-PFjRMg2dRG025Df233mKwu33JTfebuTTg5OkOWFIG_hA9De9ZqI9jfkTwFB2H3Mxpod83gzwN_kW4kcjaoqbo0zez87GEsaLzzPSzo_bVlNwoIOzD1VkTjYCV3Orf06BPguE9Rrx2MKeP14jdwh76ZKiW3oVTtFm7qZ6ljBABH9JVMvqthhd359gWpDKSshjP_Uc2ChMnuyJtso3c65Dbp98tQ7sZwT4d5gpZA9KMu2Wtm9ry9VaMAHzMw2va0KlMONzg5XgTZT2sEz38Iqn2lVKrfJuKWEnQVhi9uBaV-u7g7AI2585PKJDtdl72CZre-x56uZ0Jy5Z6SIVrIn22MxKP4eiWH39TTj3ttpek4GiE1GkuEadntCCQUNElScDO-rD1JgkWoI_jhB3ZnL_-aPvhKb_nbpBgs5R_dSUssA1FuGpyyQV3R9_ApuRYCoQYL7HrDxMGTHBTwNGkkriqJQOs23x2hNouJSlvRXv9-G9eVtEQvY2mhjdMDTgll6FOxS3vVdnre6V0nnmjv-RwnY4puZ5-HL0BGBqMf0bfJW6Lms6LMpBJiH89DUYyacSaJ02IAgmCl1kfEaiOFQjK7HYXm1WUT-5_5rA9c3KWyWp1QWrAVi4WOHIUI3-JULYTtId0ynUyYbuTb35zuOLq33QLO9bjPp_V-qPRolIyUoNnStl4KRpKmOSQIm5B5oziasDc0mvOYMHexk7HunzzL22FU8iBawKGl13DopHlrX8YjRcEwrccthTKu7yqAyHTMqAIv16wXoqi7x5ParF6Nxq_zcR-yoADS7gFEQulQPCUqRMN43H23pfm8fcMlysAy1bL5vp9CNvLUm9ThJ7e3KENXom_QNTv3ozW6DWpgEgFpLlqxMzGl_WkAmsHbUUTPrtPHVR4tx1zPVCiUGQqAzLbbRvgOs4TTOuSYB8DbPitJpsPRB3o20xlFkkJz20uXWGipwdf0gtQZeocLx2i_i0DUtvp6UM-QXiUPIrnpdJwTa37nL2L9AFb0l7OTOeyHOAkW7ZUdwyao2g0PnJJsL5rnzhtWwDZvn5sAEtAmLS_hokQHN641DT_ZmBs6x4lBYVipuWQS0AThpJlelp9kW9EKBByAxyG81kzrbu9KREATHOat8C9p5-z0gWJV7cyKxD4VXdz5EybB63XbStlaRYz1KYpwpFl61XPgdusw7lMzjMd4B6CMpIbaU-V1w_FHWT7S63HXnnti3uYhHZVovwyFvayUKMsRLzFPVYXA92-b34aRsR"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\",\"new_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"replace_all\":false}", "call_id": "call_OZuTdbsQh8MZlZcVQTCRVpox", "id": "fc_0c7ac8f62ac0da58006ab3499ad7ac87d2b0300f32fe9a5255", "index": 1}]
-{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n", "new_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n", "replace_all": false}, "id": "call_OZuTdbsQh8MZlZcVQTCRVpox", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>Tool · edit_file</t>
-  </si>
-  <si>
-    <t>01a0cc57-87e3-72b1-a81a-d5a39dd01599</t>
-  </si>
-  <si>
-    <t>{'file_path': '/target.txt', 'old_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n', 'new_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n', 'replace_all': False}</t>
-  </si>
-  <si>
-    <t>Successfully replaced 1 instance(s) of the string in '/target.txt'</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>01a0cc57-87e8-7163-b9dc-0c2a536de31a</t>
-  </si>
-  <si>
-    <t>[{"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_pCGM0nC6caxfEnTXIJUyMyqS", "id": "fc_0c7ac8f62ac0da58006ab3499c69b487d283a4587527a0a9cd", "index": 0}]
-{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_pCGM0nC6caxfEnTXIJUyMyqS", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cc57-8c69-7053-9762-7b6ef74f9164</t>
-  </si>
-  <si>
-    <t>@@ lines 1-10 of 10 @@
-Project summary
-We prepare clear, practical reports.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>01a0cc57-8c6e-7aa0-a78b-0b6f76f60e23</t>
-  </si>
-  <si>
-    <t>[{"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"new_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\",\"replace_all\":false}", "call_id": "call_Tuz68iAXuvQBqICzMDLainX8", "id": "fc_0c7ac8f62ac0da58006ab3499d879887d2b6d897fdc2c7a1a6", "index": 0}]
-{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n", "new_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n", "replace_all": false}, "id": "call_Tuz68iAXuvQBqICzMDLainX8", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cc57-92b6-74f2-8a93-db61a0d31cb6</t>
-  </si>
-  <si>
-    <t>{'file_path': '/target.txt', 'old_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n', 'new_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n', 'replace_all': False}</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>01a0cc57-92bb-7a61-9a3c-c399b0a58f7e</t>
-  </si>
-  <si>
-    <t>[{"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_KZcTCr84afM2p4rG6wqkMOns", "id": "fc_0c7ac8f62ac0da58006ab3499f0c6c87d298a6e7a31c16919a", "index": 0}]
-{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_KZcTCr84afM2p4rG6wqkMOns", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cc57-968e-7ba2-838a-6a340f914d1f</t>
   </si>
   <si>
     <t>@@ lines 1-11 of 11 @@
@@ -506,13 +405,148 @@
 Next step: request a quote.</t>
   </si>
   <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>01a0cce0-c663-7853-b277-58aa59dc1391</t>
+  </si>
+  <si>
+    <t>Conversation history · cache read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Tool result</t>
+  </si>
+  <si>
+    <t>@@ lines 1-2 of 2 @@
+Project summary
+We prepare clear, practical reports.
+@@ lines 1-11 of 11 @@
+Project summary
+We prepare clear, practical reports.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0be63b89bf4dc92a006ab36cbf2ce887d2a2d601fa43cd44fb", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2zEUa9kR18wRU5tKGaIOa8m_QT6fADG0bwGziTXXbMC33Hch_pup4QXlAnN29_eZ41zESludwXHUfdlVbVC615AF0GDtm2uXBZLSSd62NCqZSXia5r1GVZsJlw4PrxC0f6R800g10CNoyfVdp1pjf06gJLSNFej0wiVWe2vPWUpScGAJs4g8nb3-Uu5AqF_mTKyB2VLDvuaftJh_UNGTUQcHjZNCRXWB63cyb2lt6PBkcSgInjHDlrO5AdCOLlPghIou0qqaGpQ_zuQhY6TRwmctjGqAkXGQjM8BK09oeTBiCumNcmjKJ_i4WVI9BeFL4zwl-iBgJUMh49M_HIilL_PnQGRM0YgLXhbYAlkbTkRjIfrZC_XYy98k4CnYkC10v2jgpozAMS6lh2T46XDLyooe1CvsMSR2A7EPNzBIJFkM_dV4ay7X7CnvUmA04A2zJAAOzvLtpbN-ufwHbdcbjEj7IjkTq2jbhWLQh3Fba4KPpGV8s8GjXHgci-eTipVAsRcUzldQ3le6o6BSJbeqKfmMd7OEAEY_516FK8c1proyAcYqEvKvgRxcRsWu1CalUVCMpXdWjYEiZgFFmb1cVhlRm8qpUTUDTuRlj8kiULK5VPD5mPSF4SL-aWxfjp8PNOWBLAc4bvBZzyU15H9UjKHkQ0xGzJGOnf9uNMi37ukJY8Dm-lwloLIuRMhDkdn7z09NHCKj4lQe9Yz6DauWWDD0GWOBwU3VFP2N1qtELC5HqaI79aw4DShALT6aMUN58lVwkCdY5Yw42GJfRBcffyMsZWWwod-kJhspQoPdHpgZ1iMz_k3S4l9JLOkHyW1sRrfRJg084q5BEP3qlGjqel8izuSmzwZ-aYO29R2ELaoi-6zSbos4PRuK5zGUHMmLg_8IGJo7swHtMTuUH0cgN3OY9v2-fE5JeR0KTtRHys-qslQZKTzJGYXxxOnWmaFEzziO-yD0y7B1PCc2bf35r5wTIuhmm20Ca7IU0kiDvi2tKN7-2xlCijpdXkr4BXA0usJMy-Ch-Z9Lj7PMJXMk-rNLVJCQ8emD3qG16YgUpXs81xXidfvo2R5Skr5-U2438Bse9khOouEjJFZjpIPqaNzNUZPdMW_Ob0F-PKXx1Yp2HCbQPi4RnwwT0o68VtDuZytdWtO_rmZbx7du7Tz9LeAIrsGxJuTfZY7f0V1Y1D3gSjsbj8VHRKxcPjyDyo601yYlON-wTsIRwuNvPH-hY1S1qEMrvcXe8F_yTkIkVXcYZQvqs4U9HeYTQrdNp_a9LhsW3XZQv0bJfyznOuYp4tGachYlByHbFceVhlLuJZ51nbTeDO4E3agL5TuuQxaKGNwiLD0bflvkQ0BR-c9Dvky3EUobRAxs2cJU_vMbCCTi9eccO5uBDwhBH5pEhlW4mJ9_hOZlKu1Hq1Z1-FNpeRjb3jIR-r_cid5486b4gLDgDKdJF8JVppKivCZjRkt-qR_q3tBiDSJmzdImzglQmmWkIAooRs8_vV7dA_txiXAwvE7cU-ckkVu5G6ZoJq3shpWDtx50kmLf-Wnt3S3PZmYZk9_pTltJe_6wQ6f-FQA0zWJbNQQR_N8g0f41f2T5f81PSC5AVEn0SVpALqhNZvxaRtlXc0lFVZm7kpkvt95NhlQ2D6KsnBP2UUHP-_XgL1WXFImTdIToHILfEt2QL_MXu7K_p5OpGbWbHEHwxF99_JDmqWadUd0LyEisuRbMWwkJZ_JRl7l0HwVvKiknDTA6U-ZwgDQ7P6dOlQKcxZ6BLUQu8xF6KwBO4n5M2iOajnA1i6ajPTYw6_PAKYrZ5a7vTaw21LX7mlxgB_KInABuR0UXAFyhU5RsDWBaxrkbww8rixOSCzWEKKaExyNKxBmRBpW2jhX_oiA84E37B2dLQeJLqVGVewUP9JDTywp4Rk2DKb42_c1An78EcGoJK2FTYQ64cIXryTgTFE0bInni4S5_WKV279Z-rdK_H8IGWFX3BdQvfGyGQjwwv4AKD19XYLdJEgWSzdOefnRNYXmTkCU3rWpowM0ndLM8_bohuwOTtsJiAvqdAYaGI2Uei2IN4gUsdy2kqdaXn2XI9HRyf-wd-IRvF5c8Ktq9LwAdCXmHHurvjECAI3iUgz4XxZ_Il4xdpGS-ILF60i1cth_gS5h4tWS4rtKpF0c4pkC6vM0u-gUeRf7GNYMUXuZJf3MuuXEAHIfRJZ4LV1RqoFYc57dEm-KIo71yQ5Swl1LhKio5ALS1dsUbWAbr-lLjAkhvZPTw8kp1iZStLWOiLmmsltDZY-WjEKZVO-F40slNeM5mD6ukgoZ2azghvsWuKBdXTRc-JudB6Y5EhqpxnqrJkX0JXT2XVsSE1G_KI7HjSt8OPlrcOryizwwj7UTpVr5MkxZIDx_BOIH_hVpK9NH-iw65JcftMz1HUdogaWiei8XjwQFLw9eme9nk5e61NWYkH6xlU1v0Bej5TF9Su6X_Wll8c8qr2G9w8tws1hYQTwud6rxEPNM92EU3XFXQrAo4sT04DLppbicysJxuWMXltsbXJvU5OqmrE2MtouPllc9oq-atIzrh7VbeID2t1YbBjrrTRIfcuDMKH6zsirb1XYkUj4b8D5OOptQdoZd-AfvEnzVGGWD_Yym0xOjdBXE0MkFt6GTvaUwlfqbwTo2Aeh8SUhSEg-TcOVw_QvnntOw6oybvzVFuImVac7tvwkgPc-Qz5OZTYThKJ8ySjsSypM2xPnySaezD58DsLWY6eloY4aGbmAFjBcz8X98sJebmaY7NVvzqbs02g35O_iB0xPaCOZytXzlabES9510ltgjEZVye-RaaELc5-KbftVDz6zPmCEbO2u_BEEXV10uSY1oJX9sIU1QHbwZw31LYL8VF4K8A4VjQthkvA4YeFmMKimsQu_1wlZgtntxm1eKr7A="}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\",\"new_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"replace_all\":false}", "call_id": "call_vHsVsy2o9mAHYkwuQzWden0t", "id": "fc_0be63b89bf4dc92a006ab36cc477f887d2bc267f66d01c1675", "index": 1}]
+{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.", "new_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n", "replace_all": false}, "id": "call_vHsVsy2o9mAHYkwuQzWden0t", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>Tool · edit_file</t>
+  </si>
+  <si>
+    <t>01a0cce0-e58a-74d1-86cc-653d85029ab5</t>
+  </si>
+  <si>
+    <t>{'file_path': '/target.txt', 'old_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.', 'new_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n', 'replace_all': False}</t>
+  </si>
+  <si>
+    <t>Successfully replaced 1 instance(s) of the string in '/target.txt'</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>01a0cce0-e591-7600-87a9-e502f1a6ebc2</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0be63b89bf4dc92a006ab36cc6da6c87d286f8aad93fedeb65", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2zHKTg4fQx-VMPwtLLOp-eUM7GxOcfLqwxVg5QnA32DWcbP2C0QkLEZm73G--WX5pwdGN1a6Edn8Fb7DzGKlU4W4gfC2ASBJ8Ishmkr5j71KaaquofSr0R-VxHhGATy3rb13Gw9zoM01IyQB1fslFz0TQ7yI-aJfGVuDXvCixSpcZfrnopqu5FecI0MNU1Llrvh5NkYkTcxrWYJoHzxFDayjCH8FKIwYOUXjh583kkKhcGm09t_DpXhQbThotYnb7y2bweI8G8A_NJ4XxvSldJybYeXe1NHikP4onvyjNwiymcHoKUBcf_nkAS6nQ9J5SNl1wMwXPoxBnNpdfUq-xUxnPuoyWEtnfqtIYWj9gF3HtKXyTIp2si4wK0ZzhwyprYNXGnblyLp4TRt43LRL9CcwyQC2cNoTSPglzQvIHACFpi9W9mXLVMWhIeRhkbA9rmlaVHX57_DTueY2HkEj1nHG81uWQjaXfI4UeAbym9NvocYH90UM86zeXKqr7Szi9ppWTkTNFKp4zVYeSK_kd125K_FjChSegIYUD6Tq-_-1vCPf58Hem-7lJ76HHZIpoyNUXciThIKGOsKzTpeFIXMbk6KWibaNy1MBB7QhNwFi2gc-OV1I9iXwOd-Xl3jMY4JKBWulXTLZd38C0pyPf2zz51T8LzwI1IC_0BVVZeug1pmly4YVBJfbrIR6CjlUHVoDLqS5J4Xvz6xBlN3vCXEcK4aWbXz6meMdW7UvBVMq5DkSDigUu0i7z65IXuZ8pXv92njkQqys7QFZuuSe3BZ5HE3O5PcvWIbfSumaG1lOo7TofE8RoC_eFiBuqr4SUplNkdKtdNAPv7e4frCfU67qnIFGo80dkhoml8t5EcwoVXpAsJsknV435aqADHl5Zy2LXZgu65dA5mdf_Ozm-75elzoPiv9Xr4u0Cfj5sc0xSzaSNm3HJ49iVqF4qDITMtCa-I979ZHSg_3mWYDtOaPrWCWt8Ke6msa1o3c_g68uCGstMS4W5BwFzAkOb3AXRGceHyiqG-SQxTf_kj1N5SlVE7_5m4Hls5D6QOOcuDzkbqF9KjlcdX3mAe221ll7VxmK8u5fhV8oh9QSmclSOwzOom6qjL4TjLPAxAYvN3ii-h473A48gNr_5RSDjlpuLRjWqz1EQuW1b4B7hY75TkcmU4TqFLf9fP54lqM6OZuatZxpo6iWzITFDgV5ZxX1tHB3AtB3iFcyszeegx5Z7QYEGKanMrt3yYiEq2lnvmv-o6x9t6kphUqa6QGGy-1g1e589RTxzO9W-xAyT4oGGe33hrKtq5vRVTXuGBzWbhBkzA="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_Uh7wTF1aLj2DBW5qc2Gn9of2", "id": "fc_0be63b89bf4dc92a006ab36cc7781887d290a36597813ef5ed", "index": 1}]
+{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_Uh7wTF1aLj2DBW5qc2Gn9of2", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0cce0-ecaa-7e70-8bbb-da40a697a8fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@@ lines 1-14 of 14 @@
+Project summary
+We prepare clear, practical reports.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>01a0cce0-ecaf-7a30-a098-7ddc12630e0d</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0be63b89bf4dc92a006ab36cc8dcb887d2b2bf0dd6103ef5d0", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2zMUtdm2ObzIhhK3EZf8KUrdJC2w9KYfD_xQrJL0WbghAibhIVGPBM3GnZ19bXAPsquUt2507UQeWS022V0ExhbktCwJHdokmWchO5upBdsRp0eM9IKDM2XvDKY_6eNX8dNZjbINsNzrETAsBZxO_lC1U01rWHwv-vWMCCcoUaeY8wrCWNK8TDnfhAkYSSXvc816tYZ8PheQeJFpj4iTdcacrcSL9hbMEauWlIoHd3Vby9FO-ypTr5GpqUUsuvfUnJMzt3WLCz7mhkC4jrvnuUwr4cXvBh3cgTIpS4reRV9xd9kp7OaO0hPBAFAZU5juUKu7gtXogjDzfVA1Wor1y3dhAfyPrm4VE2H0HP4uliCAFpyw3B6ytx9lWTF38NsngaeNsSy3z9UaQjZv1BI9acoyz0QlIhGF9hcSdYAYFkHOJAIZv2DY7cJbC81YnHO4nEiPBiwtpQInhhWn6yy-G58lgex-x96Ul-9XX8Rf_anG4HgFAKCZnZ9sIlGi0vLKG_uEon8Xxy0-WvUgj9NAnnru8NeSZMMmm7fOB0yTKstP-iFIrpUuXd2vG5jookyfvCn6QLNcgx3zpb6SuUarsaTWlCG91IlmYhejZXqta7B5h94qIxvAu4aB_PRiWKuB43fmAGSmmBGUzPo7tKWkESRXNSwrAEAD2uOuqioC171ZW3l3N5h3Y8JZ4ia9RTsGSq0QDAkdKzPQSGf2wbmQ9TDzoZZl2WI2Unsip43YZnFD8DkhUx8EVzFoAU4P4pj6_w419G26kOJNtO1WvwIQ3P95y36D29CcizCz-zabbB4m-eHvHa9FlSUh5c6ck4JAvLjlcDq5ykA0RCAcA6-2nb2Ww111eMUGSETv-nD_9nUWGjE2ZMscfqhrEsBI-cx3DPctofCAXEH4vHB15SMRhWyQsghhCN9rsdlsWs7AtmS-rRv0dvIAIhITqWXS862aOMb9NW1JRKg4ltbRi6yjnTswUnzYIMzg7UA2inrbANHZOXOQ-X4zEUSf1RNM5RsKrwUUjBDPdbP-Zac8o7469wZT87PbgeN6xjKy0Mu5xD62DQOBvblK1f8wfFBFCA_wyvSNadi4mj17K69DP6zO-Ib-WJxmIjrse3iBDZ2WIxMBFqEJuoj653OK-Ows6_JXk2PdySO3vd1x7yz3p74Uf97mQjYD-CFAP6ZHVg_dXlp-gZwjtev96D3IaEH9REpnmeTSoFOeHVgjXronmUidzRr_fVX3ceZU67Y8j98BEsBw0UhdMeZUusBjmVHSLqsqsBwSnHgxfidpn0O4xx1r2ygVcOpqp2QSJNgE5MIc-4Bip-tgXCZEgkZq6T9YTG0uHOcny4_nQ8Aq_kz_kfGSZawfDupAiRyH8XS2mMtazTyOVrsjjEOB6O7nf9P2dBaDQphjO4PFD91M3t_yIvSaicwYGeR4udT_n7klYjiTWU5QmSljz-7TWynQuev1iTN0_UOXThrHtNYiSLNfxkqmobgLlzYH_K6l185yX-_gRauPE89snDmDBnXsSOeh02-2JLWn-NUBtxfNVyKGL5Qz6gNepy6tRNeGTRx3cw5zBA5Y6_Z8eNYuZDQ2D7lrGKiFjyxUooTsLITxHqsXbwHz1GB0ruw1kqUTZXLH5_Zpa5zsTGnhXCOjys-gGxE_OiX75sN9jjaxE9yPqkPwFP9RFM-wjuWeQ9uIDTq_FvbRre85nhNqfKqRbRwYlN2inqvGmzoi3Gu-MrW1aEJY2fqXSjZVIzBrtpKnUp1XlRgU9Jx_4CTcd-8ERQNLGaFU394W87k3k_cO8cmRtLpGxjsybnCCbRkq03WZRJkl0LLAV838woFd9QuOyhgREvFJQfDHJlBtxiXCb0u2Kh9tDKvgafCKy64tB1FtAdxwV-FIr95haY2WyP49fx9m11dwPXO02jRqC-amRJgCGftNcePyzYjoYTEr1no3kx7ZLOE3hALcqdaNh6OxmXaO8JwGtEBu7j4_k10XFWFlITFTGs7WgJBvxwD2GLzjvH635TiJYvgQvC_st5EAjj37d2RouFoBZTWrRgVGPvzstqeCAqvn42_t9Fj2I9uVExH89HJm0D1HKRjm36ov4HolODDpGvy7KbJ3WtwHIpQa_g0-78M8c0fZlrITo5a25n8c4KWWp0La4XYAJlSMVF5CCSVg_IssWGkG8U-DPfeRRxEWbV9xQxtNAkDBCjokHGpGVG4wtOd3BSSTx_OtCFS9nAhXuln_t26DX9f0B__iIsKDcqezb6jhZeB-y1KkFOSL6mDOy4vi-z1208nfe9D74Khr5_KyhYKswu_nLLtKre_qSksZg2YoXGdVmNl4xB6WEOEhZ9V6cSE9S2fVZLm4noOLXHnlk-1_GPEBmZ4np0s5VrphTnoxBGKQQD5c86wbWT6g7-X6_rFZ9AYhkIc0HKqLYRPdY9M"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Next step: request a quote.\\n\\nReviewed by the project team.\\n\",\"new_string\":\"Next step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"replace_all\":false}", "call_id": "call_xmGfNb5cXbcibuRLSEUUxD04", "id": "fc_0be63b89bf4dc92a006ab36cccc4e087d2821a22465e980e87", "index": 1}]
+{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Next step: request a quote.\n\nReviewed by the project team.\n", "new_string": "Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "replace_all": false}, "id": "call_xmGfNb5cXbcibuRLSEUUxD04", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>01a0cce1-0357-7193-a5f9-000e06bf8228</t>
+  </si>
+  <si>
+    <t>{'file_path': '/target.txt', 'old_string': 'Next step: request a quote.\n\nReviewed by the project team.\n', 'new_string': 'Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'replace_all': False}</t>
+  </si>
+  <si>
+    <t>Error: String 'Next step: request a quote.
+Reviewed by the project team.
+' appears 3 times in file. Use replace_all=True to replace all instances, or provide a more specific string with surrounding context.</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>01a0cce1-035b-7d43-8fa7-46141fd220ff</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0be63b89bf4dc92a006ab36ccea80087d2a3ed827cee0d2b27", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2zQTUuKw10VnA2dZ6EEBYCmAeQO01hfOeMSGetZt4szW5jOtJHkNhID2sHs_wrUgWiuAxmSEo745KfGJuH_3Z5Az-Sl_avtXJOEWsc6b-dtpXSr93-hwiW4LquyD7KRLHVj0kiJxXJtYTzWo2SxZIaQzcf-fFIXPi98vJWelKelFHRKlRuSoRZ0zLh-N2KTxlxWM04DxWyJ5NFUuJlnUO4rSYqOyeN33DlJ-jy-v8lDQlm_vvsXRcmv0bU24wMs6hgQ1ezKzMmlWwP5b0BgYc8Hbmct6GTFwXsk1nmFbEqObQjUJ25tl6NXQnGQh7d9tBB3_2KOYFggLWhmtCJmcIZZgatXEhEFL_YWfBjU4-l73nXTy8K2paTypIycqiykqJfrM62RLH8ceorx7ofpGibvic0iLhBI-Fc5z_a2L4kD97TRyeWb-rOtEswTeWu-ukkDf3ybe0vyz8iTufMDag8DkDUO5jbPd5JM2qhQXCQZ-vslfEZort5P1o4LHTjiRY3ogoCrhTwmro-VTaN-xjRbV3MV-GzwdVyQY2wdak5pXt5flg4zOQmMQVk6Eknt2IrckxiMPuhR4DYw97Mz86yIIi5aS-fR9YJEfHFbw77ebzGeN4JoV4KRZLMYX4OevnxvDQCAaKYBxRgQzy7_r4QpnTRJfM6Wp7yL6R3hcejxdtl7uy0zfnrC4RbDVMHWCoFm6q9qN35gLgdCAeY9LIZnDWCCbAaOosfMJ1LAjGTWuG0VuWkKGfTsNXZEyKyqmRolldjv-y51hnb2vRHJ0AKeYklA-uXk_yH4hn6uA7JTbs0hf1Eh4ZB8L3pEcZIBkov7GmDrmplm2NztUsQ9TdIbzhI6WEEH2EgpnKqAz2xtZbjlnV_gE1SzZAW_yq6YlIiSJwkaxKveZiOpxuKqqJV7rRjSBUloh0IcVMKVwOt54prT6NqAdMRBRtUh-5A0UwVpXY-VJxym_x97ATgtlQgqbpSU834Sou1epmFM6u7WbeC6pv8mOvX2uSMpFEaZAYfzrRE2nCxnJgdMf9mJsT0WlNF-9QXCImgZkPrujUQD3UXahEjoXd5B3XIb70_uQaIteS74Fn_uqxgq7NoGntSkiihDCbx9-Bj3gnWuca6E2GXy1rxAZOQsCuR5yDt845e3RdMSfB-e6sEtmT0xRTUQUwL72zYuP1XYMAVJLkVxa8WlPk3CYQ-yuois-m_WwFzp0lpUlfSbfpJDjP4HGVUlI2BCJe4HItCWVycVRK0DpR_P1hL6DqWKDIdjygZaUxd7WMW_UfV7T0D-X-PnQ54bcDG22XRn76nL-NnKWigeI8YWSxikFpARtLJ8xDuF_r1mmex73B5Tf6waeaIrjIkhBnPbjY7xWJloBqnUvWJ3qMm83K7ir_Kl-lvzWmLnSurGs_Oy249uOLVaaVNxlI_dqYMEW8vfj21TEMZLAYyqXtMOPnmUZGCIDbbb3fkVcCoR2a39PpQtJwRmMNrfpPuD2KbgHE9_T5emfPwM04_aJdpsHGc-mAFjlAVpmypK10_H38OXb68NF85OaCT71-c6wglqyo04afH1cm50wTFXZFCdiYp22GpN79yfwEDeDQEEN-DlxLiW5fbDZ3FzL8Uvv0N1TD9mM9u9xwLA_1pKriDsDHlzKS3C04e7NKNGZyIDvzDBT0nT0o2J8eOWtxogacCZE338HZx1ZWz45PWkuhOVChI6X7U7A9Ra-6MmSfIbRHksI-mIHUhlBJJgipe3DubpiE8aL2jiN9d3indqpCQLFLiivgUhZhQIeUMdGneGxNU0CAM3doTnnThAI5P6bX4Bar-xD6iSVNFY79fpjUbX8yDVZBtBo1M1jtlx85MB"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"new_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"replace_all\":false}", "call_id": "call_Y6Wa99qdOi8UzJbYBOnvPG3c", "id": "fc_0be63b89bf4dc92a006ab36cd07f8087d2b28e7018839137a9", "index": 1}]
+{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n", "new_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "replace_all": false}, "id": "call_Y6Wa99qdOi8UzJbYBOnvPG3c", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0cce1-14c8-7592-bebd-2358da5aa44e</t>
+  </si>
+  <si>
+    <t>{'file_path': '/target.txt', 'old_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n', 'new_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'replace_all': False}</t>
+  </si>
+  <si>
     <t>R6</t>
   </si>
   <si>
-    <t>01a0cc57-9693-7031-81c4-5a30e2f559ae</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Appended both sentences as separate changes to `/target.txt`.", "phase": "final_answer", "index": 0, "id": "msg_0c7ac8f62ac0da58006ab3499ff69087d28285a1da4bd51619"}]</t>
+    <t>01a0cce1-14cd-7082-99be-5e5b03bda314</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0be63b89bf4dc92a006ab36cd3142087d28a43c44455603cad", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2zTPxmham_cuR4Gc1XV7ptAqvLLmmk3vSPepJfPd2SxnkfS7sBlVQ9EKaZFPaxEoUoEo3XGV3VTicCn6EFZzvIxl5f9kKKiN28FNfCh1AgkYA-38z4eqfxMQHlEqD-9Z9oCrdtD9wnnccpun9GT4vKcuSxZzuzpXWLV8jVuEc-2xQnwmnlDnJOKi1UUz7vJd6yzOXJxaZEdv3jPsTh_8tL_6Fs6iOdIHA3k6RCOpXnBuZa-oawlKKT28WSDMdJP44kUaWo8svfL0lmKWHBt5xEKVJOPZrzCp9BGKEh9uHA_8ATNKf0xnd3gZG_fyemu1knJyWPwU1yGdOY0z8l9WYKHYpaEv3UnRWGJ7qgMOfzy6reanBFfi2qwTt2fN3Igs6cZOA3lTTK8t8o1tQvcCkKtfRbFqq5LdhnVPeaYOyM90ZQ3sqMz2Lhnfr1zn5H9ro6D63FGnrP7aHSPNCveMtaN8h5yGB6OtrlTn8cwHykD2l-WkTJ_uRnWVGjJtz5OSWgBNR1eJzF7iGN1nzhKGRD3HzGrC_vy9Gs03y6bduiDUrtM1aap5WkfzKcJT-gg3bzq90aAVk1DcZQldKwZPd-_lUciz9tS_3LF4HUS7NZ-GIirUAazEK-QeNh-pVdtf4R5ryj7tIveDVIE9wgf9kZm2wSaUuhJvzs61XU-HMR7zSCSZJbnp9QK5Z7KvDNVp_E2-djKeZJP56PzsHMMkwu5fcI1DPONPRMmdk3c6HwZ2RvdO3O-zqekUvCdgdijeUYDI460WGX3minKDvf8sFPYTNBkxuKif6-pDanwLvUbwW_-XfJAaVTuD-ObhvMR9POIDKFp2PCN_k3UQSF6bAAz08eWS2azeGFqlTBKemeWkRvTa81rSA7Oyvywq1boz5dh95mtVEUgbm2h40A21ItQywAcHblBctgbn62XKbj2Yax6VZbSqnODhz2u3c5LeevT_9ECeJogIpVSDGjUq8XYnXEsROAlmaP8FCIOK9z-qtusGqvwBaQ3PoLRps7qSJx7AR-OZTWz_HOguSYdg2ri8IcRhw89UnubF6kmv72G5c8FjEF83er3yZdqdYjY_QnI-xlwqVVPj5eX0pU_EJYs1GdrDkTPu6fFPRGoIVedOhuCvXZhScoeE80AbKWjhtV6oIBBriYOj1qOkLy3FZewHpjKwJmheyXcAmurQHmjQuo="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_pXwFpExgHp1ByUyFdXXe1MBe", "id": "fc_0be63b89bf4dc92a006ab36cd3518087d2a6c907e70bbb2395", "index": 1}]
+{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_pXwFpExgHp1ByUyFdXXe1MBe", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0cce1-1adc-71f1-98d8-be3a39d72496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@@ lines 1-16 of 16 @@
+Project summary
+We prepare clear, practical reports.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>01a0cce1-1ae1-7f00-9d83-5c140d10485c</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "Appended both sentences to `/target.txt` as separate changes.", "phase": "final_answer", "index": 0, "id": "msg_0be63b89bf4dc92a006ab36cd461e887d2ae549e26ba5ed228"}]</t>
   </si>
   <si>
     <t>file_editor</t>
@@ -533,7 +567,7 @@
     <t>Execute the RestrictedToolApproval.before_model workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc57-75e8-7df2-8bb3-296a28f46985</t>
+    <t>01a0cce0-bc32-7003-b125-44ac8cc900ae</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -545,7 +579,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cc57-75eb-7912-a835-9ec72ea0599b</t>
+    <t>01a0cce0-bc35-7bf0-b538-86ea9a24066b</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -566,7 +600,7 @@
     <t>Execute the RestrictedToolApproval.after_model workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc57-7c34-7150-bf7d-d7280b292ba3</t>
+    <t>01a0cce0-c659-7871-908f-b1521d183f16</t>
   </si>
   <si>
     <t xml:space="preserve">    tools</t>
@@ -575,7 +609,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cc57-7c35-7640-8b69-5448ec8257ac</t>
+    <t>01a0cce0-c65b-7c10-be9a-fed7be5c68fd</t>
   </si>
   <si>
     <t xml:space="preserve">        read_file</t>
@@ -596,28 +630,28 @@
 - Always read a file before editing it.</t>
   </si>
   <si>
-    <t>01a0cc57-7c35-7640-8b69-54578f674979</t>
-  </si>
-  <si>
-    <t>01a0cc57-7c3b-7ce3-bd03-fc4eec844954</t>
-  </si>
-  <si>
-    <t>01a0cc57-7c3b-7ce3-bd03-fc524db75d12</t>
+    <t>01a0cce0-c65b-7c10-be9a-fee10c60ceb3</t>
+  </si>
+  <si>
+    <t>01a0cce0-c661-7ee1-b643-c7ac6b487d9e</t>
+  </si>
+  <si>
+    <t>01a0cce0-c662-7382-bf27-7180d5126953</t>
   </si>
   <si>
     <t>interrupted</t>
   </si>
   <si>
-    <t>01a0cc57-87cb-7f72-b1cd-cc4a198b192c</t>
-  </si>
-  <si>
-    <t>01a0cc57-87df-7a31-ae7e-3641d8cb6c9c</t>
-  </si>
-  <si>
-    <t>01a0cc57-87e0-7031-855b-7ee6cb048698</t>
-  </si>
-  <si>
-    <t>01a0cc57-87e2-7182-8898-af57b2214c7a</t>
+    <t>01a0cce0-e56c-7f50-ba17-fee13d85162c</t>
+  </si>
+  <si>
+    <t>01a0cce0-e585-7b82-b6b0-024d4e55b3b5</t>
+  </si>
+  <si>
+    <t>01a0cce0-e586-7a33-bf42-42a9b7d08b28</t>
+  </si>
+  <si>
+    <t>01a0cce0-e588-77a1-9782-a7b399473d65</t>
   </si>
   <si>
     <t xml:space="preserve">        edit_file</t>
@@ -631,55 +665,73 @@
 - Only use emojis if the user explicitly requests it.</t>
   </si>
   <si>
-    <t>01a0cc57-87e6-7d01-80aa-367bdbd62242</t>
-  </si>
-  <si>
-    <t>01a0cc57-87e7-7191-9e7b-6421b6ae91cf</t>
-  </si>
-  <si>
-    <t>01a0cc57-8c65-7433-be92-cbd286f0c872</t>
-  </si>
-  <si>
-    <t>01a0cc57-8c66-7c02-9a5b-8362ce3c6dfe</t>
-  </si>
-  <si>
-    <t>01a0cc57-8c6c-7640-a186-0b2b65733d8f</t>
-  </si>
-  <si>
-    <t>01a0cc57-8c6d-7b03-bc09-2aebc1662a4e</t>
-  </si>
-  <si>
-    <t>01a0cc57-92a1-7d41-9764-53d982f1da3e</t>
-  </si>
-  <si>
-    <t>01a0cc57-92b3-7af0-b05e-d2222f02600f</t>
-  </si>
-  <si>
-    <t>01a0cc57-92b4-7ed3-b124-b6b5f371d13b</t>
-  </si>
-  <si>
-    <t>01a0cc57-92b5-7ab3-adff-d6196c310b56</t>
-  </si>
-  <si>
-    <t>01a0cc57-92b9-7141-8169-03127ace808e</t>
-  </si>
-  <si>
-    <t>01a0cc57-92ba-75d1-8e10-b5634612f431</t>
-  </si>
-  <si>
-    <t>01a0cc57-9686-7282-bd18-52e08da6eb58</t>
-  </si>
-  <si>
-    <t>01a0cc57-9688-7311-8f1e-66881c706a42</t>
-  </si>
-  <si>
-    <t>01a0cc57-9691-7be1-83bb-93fcdd39c038</t>
-  </si>
-  <si>
-    <t>01a0cc57-9692-7ec3-836e-809be5634652</t>
-  </si>
-  <si>
-    <t>01a0cc57-99d2-77d0-8ccc-d5776187f2d6</t>
+    <t>01a0cce0-e58d-7513-9f48-f3743a84eeac</t>
+  </si>
+  <si>
+    <t>01a0cce0-e58f-7db2-9f40-40440aea8692</t>
+  </si>
+  <si>
+    <t>01a0cce0-eca7-72f3-a473-f53c33ec2c02</t>
+  </si>
+  <si>
+    <t>01a0cce0-eca8-7a50-8090-394c247047b4</t>
+  </si>
+  <si>
+    <t>01a0cce0-ecad-7533-9010-89499336d0a7</t>
+  </si>
+  <si>
+    <t>01a0cce0-ecae-75e0-9431-19509224642d</t>
+  </si>
+  <si>
+    <t>01a0cce1-033e-73c2-ae91-e2eba3d7d098</t>
+  </si>
+  <si>
+    <t>01a0cce1-0354-7b42-83a4-6040ba11231f</t>
+  </si>
+  <si>
+    <t>01a0cce1-0355-7433-a6aa-8217870285aa</t>
+  </si>
+  <si>
+    <t>01a0cce1-0356-7382-a298-74112364b53d</t>
+  </si>
+  <si>
+    <t>01a0cce1-035a-7c42-9e0d-feff1a0b125e</t>
+  </si>
+  <si>
+    <t>01a0cce1-035a-7c42-9e0d-ff01117ffb9e</t>
+  </si>
+  <si>
+    <t>01a0cce1-14b1-7e42-ad43-69840d5b7301</t>
+  </si>
+  <si>
+    <t>01a0cce1-14c4-7e92-b732-3a51284bf8f0</t>
+  </si>
+  <si>
+    <t>01a0cce1-14c5-77a3-8025-ecb3efc1d856</t>
+  </si>
+  <si>
+    <t>01a0cce1-14c6-7450-b467-0e072dadf26f</t>
+  </si>
+  <si>
+    <t>01a0cce1-14cb-78c1-a853-6e1b4c45ab41</t>
+  </si>
+  <si>
+    <t>01a0cce1-14cc-7d42-b663-8794ca39c99b</t>
+  </si>
+  <si>
+    <t>01a0cce1-1ad1-7440-a89d-62cbbf18f362</t>
+  </si>
+  <si>
+    <t>01a0cce1-1ad3-79a1-b434-3a4744ad4bd6</t>
+  </si>
+  <si>
+    <t>01a0cce1-1adf-7821-9e77-3d628f439c18</t>
+  </si>
+  <si>
+    <t>01a0cce1-1ae1-7f00-9d83-5c06f29af53d</t>
+  </si>
+  <si>
+    <t>01a0cce1-1eef-7630-9396-4c6640f589be</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1138,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1146,20 +1198,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E51,'Turns'!E66,'Turns'!E81,'Turns'!E96)=6,SUM('Turns'!E17,'Turns'!E36,'Turns'!E51,'Turns'!E66,'Turns'!E81,'Turns'!E96),"Unknown")</f>
-        <v>0.0012182123628</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E115)=7,SUM('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E115),"Unknown")</f>
+        <v>0.0020831410467</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F51,'Turns'!F66,'Turns'!F81,'Turns'!F96)=6,SUM('Turns'!F17,'Turns'!F36,'Turns'!F51,'Turns'!F66,'Turns'!F81,'Turns'!F96),"Unknown")</f>
-        <v>0.00139644</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F115)=7,SUM('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F115),"Unknown")</f>
+        <v>0.00238791</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>122.0</v>
+        <v>208.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>140.0</v>
+        <v>239.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1170,20 +1222,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E51,'Turns'!E66,'Turns'!E81,'Turns'!E96)=6,SUM('Turns'!E17,'Turns'!E36,'Turns'!E51,'Turns'!E66,'Turns'!E81,'Turns'!E96),"Unknown")</f>
-        <v>0.0012182123628</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E115)=7,SUM('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E115),"Unknown")</f>
+        <v>0.0020831410467</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F51,'Turns'!F66,'Turns'!F81,'Turns'!F96)=6,SUM('Turns'!F17,'Turns'!F36,'Turns'!F51,'Turns'!F66,'Turns'!F81,'Turns'!F96),"Unknown")</f>
-        <v>0.00139644</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F115)=7,SUM('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F115),"Unknown")</f>
+        <v>0.00238791</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>122.0</v>
+        <v>208.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>140.0</v>
+        <v>239.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1308,7 +1360,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1322,23 +1374,23 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.570266e-05</v>
+        <v>2.8264788e-05</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>1.8e-05</v>
+        <v>3.24e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1371,7 +1423,7 @@
         <v>9.0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="346" customHeight="1">
+    <row r="14" spans="1:13" ht="359" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1419,19 +1471,19 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.00024600834</v>
+        <v>0.000258570468</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.000282</v>
+        <v>0.0002964</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>111</v>
@@ -1498,7 +1550,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="125" customHeight="1">
+    <row r="23" spans="1:13" ht="164" customHeight="1">
       <c r="B23">
         <v>1</v>
       </c>
@@ -1520,7 +1572,7 @@
         <v>94</v>
       </c>
       <c r="D24" s="4">
-        <v>1063</v>
+        <v>1088</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>95</v>
@@ -1589,7 +1641,7 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="164" customHeight="1">
+    <row r="27" spans="1:13" ht="203" customHeight="1">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -1614,19 +1666,19 @@
         <v>103</v>
       </c>
       <c r="D28" s="5">
-        <v>1060</v>
+        <v>1085</v>
       </c>
       <c r="E28" s="2">
         <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00023117805</v>
+        <v>0.0002366303625</v>
       </c>
       <c r="F28" s="2">
         <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!D17),D28*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.000265</v>
+        <v>0.00027125</v>
       </c>
       <c r="G28" s="5">
         <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="H28" s="5">
         <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1655,7 +1707,7 @@
         <v>105</v>
       </c>
       <c r="D30" s="4">
-        <v>261</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1">
@@ -1669,23 +1721,23 @@
         <v>106</v>
       </c>
       <c r="D31" s="5">
-        <v>131</v>
+        <v>267</v>
       </c>
       <c r="E31" s="2">
         <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000137136564</v>
+        <v>0.000279507348</v>
       </c>
       <c r="F31" s="2">
         <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!F17),D31*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.0001572</v>
+        <v>0.0003204</v>
       </c>
       <c r="G31" s="5">
         <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>28.0</v>
       </c>
       <c r="H31" s="5">
         <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="24" customHeight="1">
@@ -1699,23 +1751,23 @@
         <v>107</v>
       </c>
       <c r="D32" s="5">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="E32" s="2">
         <f>IF(AND(ISNUMBER(F32),ISNUMBER('Reference data'!$B$3)),F32*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00013608972</v>
+        <v>0.00016749504</v>
       </c>
       <c r="F32" s="2">
         <f>IF(D32=0,0,IF(ISNUMBER('Reference data'!E17),D32*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.000156</v>
+        <v>0.000192</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="H32" s="5">
         <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="409" customHeight="1">
@@ -1766,19 +1818,19 @@
       </c>
       <c r="E36" s="2">
         <f>IF(COUNT('Turns'!E25,'Turns'!E26,'Turns'!E28,'Turns'!E31,'Turns'!E32)=5,SUM('Turns'!E25,'Turns'!E26,'Turns'!E28,'Turns'!E31,'Turns'!E32),"Unknown")</f>
-        <v>0.000504927756</v>
+        <v>0.0006841561725</v>
       </c>
       <c r="F36" s="2">
         <f>IF(COUNT('Turns'!F25,'Turns'!F26,'Turns'!F28,'Turns'!F31,'Turns'!F32)=5,SUM('Turns'!F25,'Turns'!F26,'Turns'!F28,'Turns'!F31,'Turns'!F32),"Unknown")</f>
-        <v>0.0005788</v>
+        <v>0.00078425</v>
       </c>
       <c r="G36" s="5">
         <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>50.0</v>
+        <v>68.0</v>
       </c>
       <c r="H36" s="5">
         <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
+        <v>78.0</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>111</v>
@@ -1798,7 +1850,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="86" customHeight="1">
+    <row r="38" spans="1:13" ht="99" customHeight="1">
       <c r="B38">
         <v>1</v>
       </c>
@@ -1831,7 +1883,7 @@
         <v>94</v>
       </c>
       <c r="D40" s="4">
-        <v>1350</v>
+        <v>1541</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>95</v>
@@ -1851,15 +1903,15 @@
         <v>123</v>
       </c>
       <c r="D41" s="5">
-        <v>1060</v>
+        <v>1085</v>
       </c>
       <c r="E41" s="2">
         <f>IF(AND(ISNUMBER(F41),ISNUMBER('Reference data'!$B$3)),F41*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.8494244e-05</v>
+        <v>1.8930429e-05</v>
       </c>
       <c r="F41" s="2">
         <f>IF(D41=0,0,IF(ISNUMBER('Reference data'!C17),D41*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>2.12e-05</v>
+        <v>2.17e-05</v>
       </c>
       <c r="G41" s="5">
         <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1925,23 +1977,23 @@
         <v>103</v>
       </c>
       <c r="D44" s="5">
-        <v>287</v>
+        <v>453</v>
       </c>
       <c r="E44" s="2">
         <f>IF(AND(ISNUMBER(F44),ISNUMBER('Reference data'!$B$3)),F44*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.25925475e-05</v>
+        <v>9.87959025e-05</v>
       </c>
       <c r="F44" s="2">
         <f>IF(D44=0,0,IF(ISNUMBER('Reference data'!D17),D44*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>7.175e-05</v>
+        <v>0.00011325</v>
       </c>
       <c r="G44" s="5">
         <f>IF(ISNUMBER(E44),ROUND(E44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H44" s="5">
         <f>IF(ISNUMBER(F44),ROUND(F44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="24" customHeight="1">
@@ -1966,7 +2018,7 @@
         <v>105</v>
       </c>
       <c r="D46" s="4">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="24" customHeight="1">
@@ -1977,18 +2029,18 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D47" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E47" s="2">
         <f>IF(AND(ISNUMBER(F47),ISNUMBER('Reference data'!$B$3)),F47*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>2.9311632e-05</v>
       </c>
       <c r="F47" s="2">
-        <f>IF(D47=0,0,IF(ISNUMBER('Reference data'!E17),D47*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.48e-05</v>
+        <f>IF(D47=0,0,IF(ISNUMBER('Reference data'!F17),D47*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>3.36e-05</v>
       </c>
       <c r="G47" s="5">
         <f>IF(ISNUMBER(E47),ROUND(E47*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1999,7 +2051,7 @@
         <v>3.0</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="73" customHeight="1">
+    <row r="48" spans="1:13" ht="24" customHeight="1">
       <c r="A48" t="s">
         <v>131</v>
       </c>
@@ -2007,13 +2059,29 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>108</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="24" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="D48" s="5">
+        <v>31</v>
+      </c>
+      <c r="E48" s="2">
+        <f>IF(AND(ISNUMBER(F48),ISNUMBER('Reference data'!$B$3)),F48*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.2452164e-05</v>
+      </c>
+      <c r="F48" s="2">
+        <f>IF(D48=0,0,IF(ISNUMBER('Reference data'!E17),D48*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>3.72e-05</v>
+      </c>
+      <c r="G48" s="5">
+        <f>IF(ISNUMBER(E48),ROUND(E48*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H48" s="5">
+        <f>IF(ISNUMBER(F48),ROUND(F48*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="294" customHeight="1">
       <c r="A49" t="s">
         <v>131</v>
       </c>
@@ -2021,7 +2089,10 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="24" customHeight="1">
@@ -2032,123 +2103,104 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="24" customHeight="1">
+      <c r="A51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A51" s="4" t="s">
+    <row r="52" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A52" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B51" s="4">
-        <v>1</v>
-      </c>
-      <c r="C51" s="4" t="s">
+      <c r="B52" s="4">
+        <v>1</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E51" s="2">
-        <f>IF(COUNT('Turns'!E41,'Turns'!E42,'Turns'!E44,'Turns'!E47)=4,SUM('Turns'!E41,'Turns'!E42,'Turns'!E44,'Turns'!E47),"Unknown")</f>
-        <v>0.0001119686895</v>
-      </c>
-      <c r="F51" s="2">
-        <f>IF(COUNT('Turns'!F41,'Turns'!F42,'Turns'!F44,'Turns'!F47)=4,SUM('Turns'!F41,'Turns'!F42,'Turns'!F44,'Turns'!F47),"Unknown")</f>
-        <v>0.00012835</v>
-      </c>
-      <c r="G51" s="5">
-        <f>IF(ISNUMBER(E51),ROUND(E51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="H51" s="5">
-        <f>IF(ISNUMBER(F51),ROUND(F51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B52" s="4">
-        <v>1</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>112</v>
+      <c r="E52" s="2">
+        <f>IF(COUNT('Turns'!E41,'Turns'!E42,'Turns'!E44,'Turns'!E47,'Turns'!E48)=5,SUM('Turns'!E41,'Turns'!E42,'Turns'!E44,'Turns'!E47,'Turns'!E48),"Unknown")</f>
+        <v>0.0001800135495</v>
+      </c>
+      <c r="F52" s="2">
+        <f>IF(COUNT('Turns'!F41,'Turns'!F42,'Turns'!F44,'Turns'!F47,'Turns'!F48)=5,SUM('Turns'!F41,'Turns'!F42,'Turns'!F44,'Turns'!F47,'Turns'!F48),"Unknown")</f>
+        <v>0.00020635</v>
+      </c>
+      <c r="G52" s="5">
+        <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>18.0</v>
+      </c>
+      <c r="H52" s="5">
+        <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>21.0</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="M52" s="4" t="s">
+    </row>
+    <row r="53" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B53" s="4">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M53" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="24" customHeight="1">
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="C53" t="s">
+    <row r="54" spans="1:13" ht="24" customHeight="1">
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
         <v>114</v>
       </c>
-      <c r="I53" s="6" t="s">
+      <c r="I54" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="151" customHeight="1">
-      <c r="B54">
-        <v>1</v>
-      </c>
-      <c r="C54" t="s">
+    <row r="55" spans="1:13" ht="190" customHeight="1">
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
         <v>116</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="I55" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A55" s="4" t="s">
+    <row r="56" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A56" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B55" s="4">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4" t="s">
+      <c r="B56" s="4">
+        <v>1</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D55" s="4">
-        <v>1443</v>
-      </c>
-      <c r="J55" s="4" t="s">
+      <c r="D56" s="4">
+        <v>1677</v>
+      </c>
+      <c r="J56" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M55" s="4" t="s">
+      <c r="M56" s="4" t="s">
         <v>137</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="24" customHeight="1">
-      <c r="A56" t="s">
-        <v>136</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>123</v>
-      </c>
-      <c r="D56" s="5">
-        <v>1347</v>
-      </c>
-      <c r="E56" s="2">
-        <f>IF(AND(ISNUMBER(F56),ISNUMBER('Reference data'!$B$3)),F56*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.35016478e-05</v>
-      </c>
-      <c r="F56" s="2">
-        <f>IF(D56=0,0,IF(ISNUMBER('Reference data'!C17),D56*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>2.694e-05</v>
-      </c>
-      <c r="G56" s="5">
-        <f>IF(ISNUMBER(E56),ROUND(E56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H56" s="5">
-        <f>IF(ISNUMBER(F56),ROUND(F56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="24" customHeight="1">
@@ -2159,29 +2211,29 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="D57" s="5">
-        <v>3</v>
+        <v>1538</v>
       </c>
       <c r="E57" s="2">
         <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>2.68341012e-05</v>
       </c>
       <c r="F57" s="2">
-        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!B17),D57*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!C17),D57*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>3.076e-05</v>
       </c>
       <c r="G57" s="5">
         <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H57" s="5">
         <f>IF(ISNUMBER(F57),ROUND(F57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="151" customHeight="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="24" customHeight="1">
       <c r="A58" t="s">
         <v>136</v>
       </c>
@@ -2189,13 +2241,29 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>124</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="24" customHeight="1">
+        <v>97</v>
+      </c>
+      <c r="D58" s="5">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2">
+        <f>IF(AND(ISNUMBER(F58),ISNUMBER('Reference data'!$B$3)),F58*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="F58" s="2">
+        <f>IF(D58=0,0,IF(ISNUMBER('Reference data'!B17),D58*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G58" s="5">
+        <f>IF(ISNUMBER(E58),ROUND(E58*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H58" s="5">
+        <f>IF(ISNUMBER(F58),ROUND(F58*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="190" customHeight="1">
       <c r="A59" t="s">
         <v>136</v>
       </c>
@@ -2203,26 +2271,10 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" s="5">
-        <v>93</v>
-      </c>
-      <c r="E59" s="2">
-        <f>IF(AND(ISNUMBER(F59),ISNUMBER('Reference data'!$B$3)),F59*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.02826025e-05</v>
-      </c>
-      <c r="F59" s="2">
-        <f>IF(D59=0,0,IF(ISNUMBER('Reference data'!D17),D59*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>2.325e-05</v>
-      </c>
-      <c r="G59" s="5">
-        <f>IF(ISNUMBER(E59),ROUND(E59*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H59" s="5">
-        <f>IF(ISNUMBER(F59),ROUND(F59*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>124</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="24" customHeight="1">
@@ -2233,54 +2285,54 @@
         <v>1</v>
       </c>
       <c r="C60" t="s">
+        <v>103</v>
+      </c>
+      <c r="D60" s="5">
+        <v>136</v>
+      </c>
+      <c r="E60" s="2">
+        <f>IF(AND(ISNUMBER(F60),ISNUMBER('Reference data'!$B$3)),F60*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.966058e-05</v>
+      </c>
+      <c r="F60" s="2">
+        <f>IF(D60=0,0,IF(ISNUMBER('Reference data'!D17),D60*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>3.4e-05</v>
+      </c>
+      <c r="G60" s="5">
+        <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H60" s="5">
+        <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="24" customHeight="1">
+      <c r="A61" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A61" s="4" t="s">
+    <row r="62" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A62" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B61" s="4">
-        <v>1</v>
-      </c>
-      <c r="C61" s="4" t="s">
+      <c r="B62" s="4">
+        <v>1</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D61" s="4">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="24" customHeight="1">
-      <c r="A62" t="s">
-        <v>136</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62" t="s">
-        <v>107</v>
-      </c>
-      <c r="D62" s="5">
-        <v>144</v>
-      </c>
-      <c r="E62" s="2">
-        <f>IF(AND(ISNUMBER(F62),ISNUMBER('Reference data'!$B$3)),F62*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000150745536</v>
-      </c>
-      <c r="F62" s="2">
-        <f>IF(D62=0,0,IF(ISNUMBER('Reference data'!E17),D62*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001728</v>
-      </c>
-      <c r="G62" s="5">
-        <f>IF(ISNUMBER(E62),ROUND(E62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
-      </c>
-      <c r="H62" s="5">
-        <f>IF(ISNUMBER(F62),ROUND(F62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="229" customHeight="1">
+      <c r="D62" s="4">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="24" customHeight="1">
       <c r="A63" t="s">
         <v>136</v>
       </c>
@@ -2288,10 +2340,26 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>108</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>138</v>
+        <v>106</v>
+      </c>
+      <c r="D63" s="5">
+        <v>191</v>
+      </c>
+      <c r="E63" s="2">
+        <f>IF(AND(ISNUMBER(F63),ISNUMBER('Reference data'!$B$3)),F63*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000199947204</v>
+      </c>
+      <c r="F63" s="2">
+        <f>IF(D63=0,0,IF(ISNUMBER('Reference data'!F17),D63*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>0.0002292</v>
+      </c>
+      <c r="G63" s="5">
+        <f>IF(ISNUMBER(E63),ROUND(E63*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>20.0</v>
+      </c>
+      <c r="H63" s="5">
+        <f>IF(ISNUMBER(F63),ROUND(F63*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>23.0</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="24" customHeight="1">
@@ -2302,10 +2370,29 @@
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="24" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="D64" s="5">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2">
+        <f>IF(AND(ISNUMBER(F64),ISNUMBER('Reference data'!$B$3)),F64*'Reference data'!$B$3,"Unknown")</f>
+        <v>8.0606988e-05</v>
+      </c>
+      <c r="F64" s="2">
+        <f>IF(D64=0,0,IF(ISNUMBER('Reference data'!E17),D64*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>9.24e-05</v>
+      </c>
+      <c r="G64" s="5">
+        <f>IF(ISNUMBER(E64),ROUND(E64*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="H64" s="5">
+        <f>IF(ISNUMBER(F64),ROUND(F64*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="409" customHeight="1">
       <c r="A65" t="s">
         <v>136</v>
       </c>
@@ -2313,603 +2400,969 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
+        <v>108</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="24" customHeight="1">
+      <c r="A66" t="s">
+        <v>136</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="24" customHeight="1">
+      <c r="A67" t="s">
+        <v>136</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="66" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A66" s="4" t="s">
+    <row r="68" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A68" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B66" s="4">
-        <v>1</v>
-      </c>
-      <c r="C66" s="4" t="s">
+      <c r="B68" s="4">
+        <v>1</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E66" s="2">
-        <f>IF(COUNT('Turns'!E56,'Turns'!E57,'Turns'!E59,'Turns'!E62)=4,SUM('Turns'!E56,'Turns'!E57,'Turns'!E59,'Turns'!E62),"Unknown")</f>
-        <v>0.0001950532083</v>
-      </c>
-      <c r="F66" s="2">
-        <f>IF(COUNT('Turns'!F56,'Turns'!F57,'Turns'!F59,'Turns'!F62)=4,SUM('Turns'!F56,'Turns'!F57,'Turns'!F59,'Turns'!F62),"Unknown")</f>
-        <v>0.00022359</v>
-      </c>
-      <c r="G66" s="5">
-        <f>IF(ISNUMBER(E66),ROUND(E66*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
-      </c>
-      <c r="H66" s="5">
-        <f>IF(ISNUMBER(F66),ROUND(F66*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
-      </c>
-      <c r="K66" s="4" t="s">
+      <c r="E68" s="2">
+        <f>IF(COUNT('Turns'!E57,'Turns'!E58,'Turns'!E60,'Turns'!E63,'Turns'!E64)=5,SUM('Turns'!E57,'Turns'!E58,'Turns'!E60,'Turns'!E63,'Turns'!E64),"Unknown")</f>
+        <v>0.0003375722952</v>
+      </c>
+      <c r="F68" s="2">
+        <f>IF(COUNT('Turns'!F57,'Turns'!F58,'Turns'!F60,'Turns'!F63,'Turns'!F64)=5,SUM('Turns'!F57,'Turns'!F58,'Turns'!F60,'Turns'!F63,'Turns'!F64),"Unknown")</f>
+        <v>0.00038696</v>
+      </c>
+      <c r="G68" s="5">
+        <f>IF(ISNUMBER(E68),ROUND(E68*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>34.0</v>
+      </c>
+      <c r="H68" s="5">
+        <f>IF(ISNUMBER(F68),ROUND(F68*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>39.0</v>
+      </c>
+      <c r="K68" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="67" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B67" s="4">
-        <v>1</v>
-      </c>
-      <c r="C67" s="4" t="s">
+    <row r="69" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B69" s="4">
+        <v>1</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K67" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M67" s="4" t="s">
+      <c r="K69" s="4" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" ht="99" customHeight="1">
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="M69" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="47" customHeight="1">
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
         <v>114</v>
       </c>
-      <c r="I68" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="24" customHeight="1">
-      <c r="B69">
-        <v>1</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="I70" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="73" customHeight="1">
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
         <v>116</v>
       </c>
-      <c r="I69" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A70" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B70" s="4">
-        <v>1</v>
-      </c>
-      <c r="C70" s="4" t="s">
+      <c r="I71" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A72" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="4">
+        <v>1</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D70" s="4">
-        <v>1613</v>
-      </c>
-      <c r="J70" s="4" t="s">
+      <c r="D72" s="4">
+        <v>2000</v>
+      </c>
+      <c r="J72" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M70" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="24" customHeight="1">
-      <c r="A71" t="s">
-        <v>141</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
-      </c>
-      <c r="C71" t="s">
-        <v>123</v>
-      </c>
-      <c r="D71" s="5">
-        <v>1440</v>
-      </c>
-      <c r="E71" s="2">
-        <f>IF(AND(ISNUMBER(F71),ISNUMBER('Reference data'!$B$3)),F71*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.5124256e-05</v>
-      </c>
-      <c r="F71" s="2">
-        <f>IF(D71=0,0,IF(ISNUMBER('Reference data'!C17),D71*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>2.88e-05</v>
-      </c>
-      <c r="G71" s="5">
-        <f>IF(ISNUMBER(E71),ROUND(E71*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H71" s="5">
-        <f>IF(ISNUMBER(F71),ROUND(F71*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="24" customHeight="1">
-      <c r="A72" t="s">
-        <v>141</v>
-      </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72" t="s">
-        <v>97</v>
-      </c>
-      <c r="D72" s="5">
-        <v>3</v>
-      </c>
-      <c r="E72" s="2">
-        <f>IF(AND(ISNUMBER(F72),ISNUMBER('Reference data'!$B$3)),F72*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F72" s="2">
-        <f>IF(D72=0,0,IF(ISNUMBER('Reference data'!B17),D72*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G72" s="5">
-        <f>IF(ISNUMBER(E72),ROUND(E72*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H72" s="5">
-        <f>IF(ISNUMBER(F72),ROUND(F72*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+      <c r="M72" s="4" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="24" customHeight="1">
       <c r="A73" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>124</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>130</v>
+        <v>123</v>
+      </c>
+      <c r="D73" s="5">
+        <v>1674</v>
+      </c>
+      <c r="E73" s="2">
+        <f>IF(AND(ISNUMBER(F73),ISNUMBER('Reference data'!$B$3)),F73*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.92069476e-05</v>
+      </c>
+      <c r="F73" s="2">
+        <f>IF(D73=0,0,IF(ISNUMBER('Reference data'!C17),D73*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>3.348e-05</v>
+      </c>
+      <c r="G73" s="5">
+        <f>IF(ISNUMBER(E73),ROUND(E73*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H73" s="5">
+        <f>IF(ISNUMBER(F73),ROUND(F73*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="24" customHeight="1">
       <c r="A74" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D74" s="5">
-        <v>170</v>
+        <v>3</v>
       </c>
       <c r="E74" s="2">
         <f>IF(AND(ISNUMBER(F74),ISNUMBER('Reference data'!$B$3)),F74*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.7075725e-05</v>
+        <v>5.23422e-07</v>
       </c>
       <c r="F74" s="2">
-        <f>IF(D74=0,0,IF(ISNUMBER('Reference data'!D17),D74*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.25e-05</v>
+        <f>IF(D74=0,0,IF(ISNUMBER('Reference data'!B17),D74*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G74" s="5">
         <f>IF(ISNUMBER(E74),ROUND(E74*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" s="5">
         <f>IF(ISNUMBER(F74),ROUND(F74*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="24" customHeight="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="73" customHeight="1">
       <c r="A75" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A76" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B76" s="4">
-        <v>1</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D76" s="4">
-        <v>29</v>
+        <v>124</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="24" customHeight="1">
+      <c r="A76" t="s">
+        <v>143</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>103</v>
+      </c>
+      <c r="D76" s="5">
+        <v>323</v>
+      </c>
+      <c r="E76" s="2">
+        <f>IF(AND(ISNUMBER(F76),ISNUMBER('Reference data'!$B$3)),F76*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.04438775e-05</v>
+      </c>
+      <c r="F76" s="2">
+        <f>IF(D76=0,0,IF(ISNUMBER('Reference data'!D17),D76*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>8.075e-05</v>
+      </c>
+      <c r="G76" s="5">
+        <f>IF(ISNUMBER(E76),ROUND(E76*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="H76" s="5">
+        <f>IF(ISNUMBER(F76),ROUND(F76*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="24" customHeight="1">
       <c r="A77" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
-      </c>
-      <c r="D77" s="5">
-        <v>29</v>
-      </c>
-      <c r="E77" s="2">
-        <f>IF(AND(ISNUMBER(F77),ISNUMBER('Reference data'!$B$3)),F77*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.0358476e-05</v>
-      </c>
-      <c r="F77" s="2">
-        <f>IF(D77=0,0,IF(ISNUMBER('Reference data'!E17),D77*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.48e-05</v>
-      </c>
-      <c r="G77" s="5">
-        <f>IF(ISNUMBER(E77),ROUND(E77*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H77" s="5">
-        <f>IF(ISNUMBER(F77),ROUND(F77*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="73" customHeight="1">
-      <c r="A78" t="s">
-        <v>141</v>
-      </c>
-      <c r="B78">
-        <v>1</v>
-      </c>
-      <c r="C78" t="s">
-        <v>108</v>
-      </c>
-      <c r="I78" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A78" s="4" t="s">
         <v>143</v>
+      </c>
+      <c r="B78" s="4">
+        <v>1</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D78" s="4">
+        <v>281</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="24" customHeight="1">
       <c r="A79" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>103</v>
+        <v>106</v>
+      </c>
+      <c r="D79" s="5">
+        <v>102</v>
+      </c>
+      <c r="E79" s="2">
+        <f>IF(AND(ISNUMBER(F79),ISNUMBER('Reference data'!$B$3)),F79*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000106778088</v>
+      </c>
+      <c r="F79" s="2">
+        <f>IF(D79=0,0,IF(ISNUMBER('Reference data'!F17),D79*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>0.0001224</v>
+      </c>
+      <c r="G79" s="5">
+        <f>IF(ISNUMBER(E79),ROUND(E79*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+      <c r="H79" s="5">
+        <f>IF(ISNUMBER(F79),ROUND(F79*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="24" customHeight="1">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80" t="s">
+        <v>107</v>
+      </c>
+      <c r="D80" s="5">
+        <v>179</v>
+      </c>
+      <c r="E80" s="2">
+        <f>IF(AND(ISNUMBER(F80),ISNUMBER('Reference data'!$B$3)),F80*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000187385076</v>
+      </c>
+      <c r="F80" s="2">
+        <f>IF(D80=0,0,IF(ISNUMBER('Reference data'!E17),D80*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.0002148</v>
+      </c>
+      <c r="G80" s="5">
+        <f>IF(ISNUMBER(E80),ROUND(E80*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>19.0</v>
+      </c>
+      <c r="H80" s="5">
+        <f>IF(ISNUMBER(F80),ROUND(F80*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="409" customHeight="1">
+      <c r="A81" t="s">
+        <v>143</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>108</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="24" customHeight="1">
+      <c r="A82" t="s">
+        <v>143</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="24" customHeight="1">
+      <c r="A83" t="s">
+        <v>143</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="81" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A81" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B81" s="4">
-        <v>1</v>
-      </c>
-      <c r="C81" s="4" t="s">
+    <row r="84" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A84" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B84" s="4">
+        <v>1</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E81" s="2">
-        <f>IF(COUNT('Turns'!E71,'Turns'!E72,'Turns'!E74,'Turns'!E77)=4,SUM('Turns'!E71,'Turns'!E72,'Turns'!E74,'Turns'!E77),"Unknown")</f>
-        <v>9.3081879e-05</v>
-      </c>
-      <c r="F81" s="2">
-        <f>IF(COUNT('Turns'!F71,'Turns'!F72,'Turns'!F74,'Turns'!F77)=4,SUM('Turns'!F71,'Turns'!F72,'Turns'!F74,'Turns'!F77),"Unknown")</f>
-        <v>0.0001067</v>
-      </c>
-      <c r="G81" s="5">
-        <f>IF(ISNUMBER(E81),ROUND(E81*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="H81" s="5">
-        <f>IF(ISNUMBER(F81),ROUND(F81*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="K81" s="4" t="s">
+      <c r="E84" s="2">
+        <f>IF(COUNT('Turns'!E73,'Turns'!E74,'Turns'!E76,'Turns'!E79,'Turns'!E80)=5,SUM('Turns'!E73,'Turns'!E74,'Turns'!E76,'Turns'!E79,'Turns'!E80),"Unknown")</f>
+        <v>0.0003943374111</v>
+      </c>
+      <c r="F84" s="2">
+        <f>IF(COUNT('Turns'!F73,'Turns'!F74,'Turns'!F76,'Turns'!F79,'Turns'!F80)=5,SUM('Turns'!F73,'Turns'!F74,'Turns'!F76,'Turns'!F79,'Turns'!F80),"Unknown")</f>
+        <v>0.00045203</v>
+      </c>
+      <c r="G84" s="5">
+        <f>IF(ISNUMBER(E84),ROUND(E84*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>39.0</v>
+      </c>
+      <c r="H84" s="5">
+        <f>IF(ISNUMBER(F84),ROUND(F84*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>45.0</v>
+      </c>
+      <c r="K84" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="82" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B82" s="4">
-        <v>1</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K82" s="4" t="s">
+    <row r="85" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B85" s="4">
+        <v>1</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="K85" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="M82" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="24" customHeight="1">
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="M85" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="112" customHeight="1">
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
         <v>114</v>
       </c>
-      <c r="I83" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="164" customHeight="1">
-      <c r="B84">
-        <v>1</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="I86" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="24" customHeight="1">
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
         <v>116</v>
       </c>
-      <c r="I84" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A85" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B85" s="4">
-        <v>1</v>
-      </c>
-      <c r="C85" s="4" t="s">
+      <c r="I87" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A88" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B88" s="4">
+        <v>1</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D85" s="4">
-        <v>1713</v>
-      </c>
-      <c r="J85" s="4" t="s">
+      <c r="D88" s="4">
+        <v>2307</v>
+      </c>
+      <c r="J88" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M85" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="24" customHeight="1">
-      <c r="A86" t="s">
-        <v>146</v>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86" t="s">
-        <v>123</v>
-      </c>
-      <c r="D86" s="5">
-        <v>1610</v>
-      </c>
-      <c r="E86" s="2">
-        <f>IF(AND(ISNUMBER(F86),ISNUMBER('Reference data'!$B$3)),F86*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.8090314e-05</v>
-      </c>
-      <c r="F86" s="2">
-        <f>IF(D86=0,0,IF(ISNUMBER('Reference data'!C17),D86*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.22e-05</v>
-      </c>
-      <c r="G86" s="5">
-        <f>IF(ISNUMBER(E86),ROUND(E86*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H86" s="5">
-        <f>IF(ISNUMBER(F86),ROUND(F86*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="24" customHeight="1">
-      <c r="A87" t="s">
-        <v>146</v>
-      </c>
-      <c r="B87">
-        <v>1</v>
-      </c>
-      <c r="C87" t="s">
-        <v>97</v>
-      </c>
-      <c r="D87" s="5">
-        <v>3</v>
-      </c>
-      <c r="E87" s="2">
-        <f>IF(AND(ISNUMBER(F87),ISNUMBER('Reference data'!$B$3)),F87*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F87" s="2">
-        <f>IF(D87=0,0,IF(ISNUMBER('Reference data'!B17),D87*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G87" s="5">
-        <f>IF(ISNUMBER(E87),ROUND(E87*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H87" s="5">
-        <f>IF(ISNUMBER(F87),ROUND(F87*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="164" customHeight="1">
-      <c r="A88" t="s">
-        <v>146</v>
-      </c>
-      <c r="B88">
-        <v>1</v>
-      </c>
-      <c r="C88" t="s">
-        <v>124</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>145</v>
+      <c r="M88" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="24" customHeight="1">
       <c r="A89" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="D89" s="5">
-        <v>100</v>
+        <v>1997</v>
       </c>
       <c r="E89" s="2">
         <f>IF(AND(ISNUMBER(F89),ISNUMBER('Reference data'!$B$3)),F89*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.180925e-05</v>
+        <v>3.48424578e-05</v>
       </c>
       <c r="F89" s="2">
-        <f>IF(D89=0,0,IF(ISNUMBER('Reference data'!D17),D89*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>2.5e-05</v>
+        <f>IF(D89=0,0,IF(ISNUMBER('Reference data'!C17),D89*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>3.994e-05</v>
       </c>
       <c r="G89" s="5">
         <f>IF(ISNUMBER(E89),ROUND(E89*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H89" s="5">
         <f>IF(ISNUMBER(F89),ROUND(F89*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="24" customHeight="1">
       <c r="A90" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A91" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B91" s="4">
-        <v>1</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D91" s="4">
-        <v>16</v>
+        <v>97</v>
+      </c>
+      <c r="D90" s="5">
+        <v>3</v>
+      </c>
+      <c r="E90" s="2">
+        <f>IF(AND(ISNUMBER(F90),ISNUMBER('Reference data'!$B$3)),F90*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="F90" s="2">
+        <f>IF(D90=0,0,IF(ISNUMBER('Reference data'!B17),D90*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G90" s="5">
+        <f>IF(ISNUMBER(E90),ROUND(E90*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H90" s="5">
+        <f>IF(ISNUMBER(F90),ROUND(F90*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="24" customHeight="1">
+      <c r="A91" t="s">
+        <v>148</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>124</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="24" customHeight="1">
       <c r="A92" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D92" s="5">
-        <v>16</v>
+        <v>307</v>
       </c>
       <c r="E92" s="2">
         <f>IF(AND(ISNUMBER(F92),ISNUMBER('Reference data'!$B$3)),F92*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>6.69543975e-05</v>
       </c>
       <c r="F92" s="2">
-        <f>IF(D92=0,0,IF(ISNUMBER('Reference data'!E17),D92*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>1.92e-05</v>
+        <f>IF(D92=0,0,IF(ISNUMBER('Reference data'!D17),D92*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>7.675e-05</v>
       </c>
       <c r="G92" s="5">
         <f>IF(ISNUMBER(E92),ROUND(E92*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H92" s="5">
         <f>IF(ISNUMBER(F92),ROUND(F92*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="47" customHeight="1">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="24" customHeight="1">
       <c r="A93" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>108</v>
-      </c>
-      <c r="I93" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A94" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" ht="24" customHeight="1">
-      <c r="A94" t="s">
-        <v>146</v>
-      </c>
-      <c r="B94">
-        <v>1</v>
-      </c>
-      <c r="C94" t="s">
-        <v>103</v>
+      <c r="B94" s="4">
+        <v>1</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D94" s="4">
+        <v>39</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="24" customHeight="1">
       <c r="A95" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A96" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B96" s="4">
-        <v>1</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
+      </c>
+      <c r="D95" s="5">
+        <v>8</v>
+      </c>
+      <c r="E95" s="2">
+        <f>IF(AND(ISNUMBER(F95),ISNUMBER('Reference data'!$B$3)),F95*'Reference data'!$B$3,"Unknown")</f>
+        <v>8.374752e-06</v>
+      </c>
+      <c r="F95" s="2">
+        <f>IF(D95=0,0,IF(ISNUMBER('Reference data'!F17),D95*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>9.6e-06</v>
+      </c>
+      <c r="G95" s="5">
+        <f>IF(ISNUMBER(E95),ROUND(E95*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H95" s="5">
+        <f>IF(ISNUMBER(F95),ROUND(F95*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="24" customHeight="1">
+      <c r="A96" t="s">
+        <v>148</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" t="s">
+        <v>107</v>
+      </c>
+      <c r="D96" s="5">
+        <v>31</v>
       </c>
       <c r="E96" s="2">
-        <f>IF(COUNT('Turns'!E86,'Turns'!E87,'Turns'!E89,'Turns'!E92)=4,SUM('Turns'!E86,'Turns'!E87,'Turns'!E89,'Turns'!E92),"Unknown")</f>
-        <v>6.717249e-05</v>
+        <f>IF(AND(ISNUMBER(F96),ISNUMBER('Reference data'!$B$3)),F96*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.2452164e-05</v>
       </c>
       <c r="F96" s="2">
-        <f>IF(COUNT('Turns'!F86,'Turns'!F87,'Turns'!F89,'Turns'!F92)=4,SUM('Turns'!F86,'Turns'!F87,'Turns'!F89,'Turns'!F92),"Unknown")</f>
-        <v>7.7e-05</v>
+        <f>IF(D96=0,0,IF(ISNUMBER('Reference data'!E17),D96*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>3.72e-05</v>
       </c>
       <c r="G96" s="5">
         <f>IF(ISNUMBER(E96),ROUND(E96*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H96" s="5">
         <f>IF(ISNUMBER(F96),ROUND(F96*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="K96" s="4" t="s">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="281" customHeight="1">
+      <c r="A97" t="s">
+        <v>148</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97" t="s">
+        <v>108</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="24" customHeight="1">
+      <c r="A98" t="s">
+        <v>148</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="24" customHeight="1">
+      <c r="A99" t="s">
+        <v>148</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A100" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B100" s="4">
+        <v>1</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E100" s="2">
+        <f>IF(COUNT('Turns'!E89,'Turns'!E90,'Turns'!E92,'Turns'!E95,'Turns'!E96)=5,SUM('Turns'!E89,'Turns'!E90,'Turns'!E92,'Turns'!E95,'Turns'!E96),"Unknown")</f>
+        <v>0.0001431471933</v>
+      </c>
+      <c r="F100" s="2">
+        <f>IF(COUNT('Turns'!F89,'Turns'!F90,'Turns'!F92,'Turns'!F95,'Turns'!F96)=5,SUM('Turns'!F89,'Turns'!F90,'Turns'!F92,'Turns'!F95,'Turns'!F96),"Unknown")</f>
+        <v>0.00016409</v>
+      </c>
+      <c r="G100" s="5">
+        <f>IF(ISNUMBER(E100),ROUND(E100*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>14.0</v>
+      </c>
+      <c r="H100" s="5">
+        <f>IF(ISNUMBER(F100),ROUND(F100*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+      <c r="K100" s="4" t="s">
         <v>111</v>
       </c>
     </row>
+    <row r="101" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B101" s="4">
+        <v>1</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M101" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="24" customHeight="1">
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>114</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="216" customHeight="1">
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>116</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A104" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B104" s="4">
+        <v>1</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D104" s="4">
+        <v>2430</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M104" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="24" customHeight="1">
+      <c r="A105" t="s">
+        <v>153</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105" t="s">
+        <v>123</v>
+      </c>
+      <c r="D105" s="5">
+        <v>2304</v>
+      </c>
+      <c r="E105" s="2">
+        <f>IF(AND(ISNUMBER(F105),ISNUMBER('Reference data'!$B$3)),F105*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.01988096e-05</v>
+      </c>
+      <c r="F105" s="2">
+        <f>IF(D105=0,0,IF(ISNUMBER('Reference data'!C17),D105*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.608e-05</v>
+      </c>
+      <c r="G105" s="5">
+        <f>IF(ISNUMBER(E105),ROUND(E105*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H105" s="5">
+        <f>IF(ISNUMBER(F105),ROUND(F105*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="24" customHeight="1">
+      <c r="A106" t="s">
+        <v>153</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>97</v>
+      </c>
+      <c r="D106" s="5">
+        <v>3</v>
+      </c>
+      <c r="E106" s="2">
+        <f>IF(AND(ISNUMBER(F106),ISNUMBER('Reference data'!$B$3)),F106*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="F106" s="2">
+        <f>IF(D106=0,0,IF(ISNUMBER('Reference data'!B17),D106*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G106" s="5">
+        <f>IF(ISNUMBER(E106),ROUND(E106*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H106" s="5">
+        <f>IF(ISNUMBER(F106),ROUND(F106*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="216" customHeight="1">
+      <c r="A107" t="s">
+        <v>153</v>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107" t="s">
+        <v>124</v>
+      </c>
+      <c r="I107" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="24" customHeight="1">
+      <c r="A108" t="s">
+        <v>153</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>103</v>
+      </c>
+      <c r="D108" s="5">
+        <v>123</v>
+      </c>
+      <c r="E108" s="2">
+        <f>IF(AND(ISNUMBER(F108),ISNUMBER('Reference data'!$B$3)),F108*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.68253775e-05</v>
+      </c>
+      <c r="F108" s="2">
+        <f>IF(D108=0,0,IF(ISNUMBER('Reference data'!D17),D108*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>3.075e-05</v>
+      </c>
+      <c r="G108" s="5">
+        <f>IF(ISNUMBER(E108),ROUND(E108*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H108" s="5">
+        <f>IF(ISNUMBER(F108),ROUND(F108*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="24" customHeight="1">
+      <c r="A109" t="s">
+        <v>153</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A110" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B110" s="4">
+        <v>1</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D110" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="24" customHeight="1">
+      <c r="A111" t="s">
+        <v>153</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>107</v>
+      </c>
+      <c r="D111" s="5">
+        <v>17</v>
+      </c>
+      <c r="E111" s="2">
+        <f>IF(AND(ISNUMBER(F111),ISNUMBER('Reference data'!$B$3)),F111*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.7796348e-05</v>
+      </c>
+      <c r="F111" s="2">
+        <f>IF(D111=0,0,IF(ISNUMBER('Reference data'!E17),D111*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.04e-05</v>
+      </c>
+      <c r="G111" s="5">
+        <f>IF(ISNUMBER(E111),ROUND(E111*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H111" s="5">
+        <f>IF(ISNUMBER(F111),ROUND(F111*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="47" customHeight="1">
+      <c r="A112" t="s">
+        <v>153</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112" t="s">
+        <v>108</v>
+      </c>
+      <c r="I112" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="24" customHeight="1">
+      <c r="A113" t="s">
+        <v>153</v>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="24" customHeight="1">
+      <c r="A114" t="s">
+        <v>153</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A115" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B115" s="4">
+        <v>1</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E115" s="2">
+        <f>IF(COUNT('Turns'!E105,'Turns'!E106,'Turns'!E108,'Turns'!E111)=4,SUM('Turns'!E105,'Turns'!E106,'Turns'!E108,'Turns'!E111),"Unknown")</f>
+        <v>8.53439571e-05</v>
+      </c>
+      <c r="F115" s="2">
+        <f>IF(COUNT('Turns'!F105,'Turns'!F106,'Turns'!F108,'Turns'!F111)=4,SUM('Turns'!F105,'Turns'!F106,'Turns'!F108,'Turns'!F111),"Unknown")</f>
+        <v>9.783e-05</v>
+      </c>
+      <c r="G115" s="5">
+        <f>IF(ISNUMBER(E115),ROUND(E115*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="H115" s="5">
+        <f>IF(ISNUMBER(F115),ROUND(F115*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="K115" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE96">
+  <conditionalFormatting sqref="A2:AE115">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2923,7 +3376,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE42"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -3030,13 +3483,13 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
@@ -3045,7 +3498,7 @@
         <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
@@ -3076,72 +3529,72 @@
       </c>
       <c r="P2" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>1060.0</v>
+        <v>1085.0</v>
       </c>
       <c r="Q2" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.00023117805</v>
+        <v>0.0002366303625</v>
       </c>
       <c r="R2" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.000265</v>
+        <v>0.00027125</v>
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D13,'Turns'!D32)=2,SUM('Turns'!D13,'Turns'!D32),"Unknown")</f>
-        <v>202.0</v>
+        <v>232.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E13,'Turns'!E32)=2,SUM('Turns'!E13,'Turns'!E32),"Unknown")</f>
-        <v>0.000211462488</v>
+        <v>0.000242867808</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F13,'Turns'!F32)=2,SUM('Turns'!F13,'Turns'!F32),"Unknown")</f>
-        <v>0.0002424</v>
+        <v>0.0002784</v>
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D12,'Turns'!D31)=2,SUM('Turns'!D12,'Turns'!D31),"Unknown")</f>
-        <v>146.0</v>
+        <v>294.0</v>
       </c>
       <c r="W2" s="2">
         <f>IF(COUNT('Turns'!E12,'Turns'!E31)=2,SUM('Turns'!E12,'Turns'!E31),"Unknown")</f>
-        <v>0.000152839224</v>
+        <v>0.000307772136</v>
       </c>
       <c r="X2" s="2">
         <f>IF(COUNT('Turns'!F12,'Turns'!F31)=2,SUM('Turns'!F12,'Turns'!F31),"Unknown")</f>
-        <v>0.0001752</v>
+        <v>0.0003528</v>
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E36)=2,SUM('Turns'!E17,'Turns'!E36),"Unknown")</f>
-        <v>0.000750936096</v>
+        <v>0.0009427266405</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F36)=2,SUM('Turns'!F17,'Turns'!F36),"Unknown")</f>
-        <v>0.0008608</v>
+        <v>0.00108065</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>75.0</v>
+        <v>94.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>86.0</v>
+        <v>108.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>4580.84</v>
+        <v>10557.352</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
@@ -3150,30 +3603,30 @@
         <v>111</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>1.822</v>
+        <v>1.358</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
@@ -3182,10 +3635,10 @@
         <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
@@ -3234,48 +3687,48 @@
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>15.0</v>
+        <v>27.0</v>
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>1.570266e-05</v>
+        <v>2.8264788e-05</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.8e-05</v>
+        <v>3.24e-05</v>
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.00024600834</v>
+        <v>0.000258570468</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.000282</v>
+        <v>0.0002964</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>1607.581</v>
+        <v>2595.144</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>95</v>
@@ -3287,13 +3740,13 @@
         <v>888</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H5" t="s">
         <v>96</v>
       </c>
       <c r="I5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="J5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -3339,51 +3792,51 @@
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>15.0</v>
+        <v>27.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>1.570266e-05</v>
+        <v>2.8264788e-05</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.8e-05</v>
+        <v>3.24e-05</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.00024600834</v>
+        <v>0.000258570468</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.000282</v>
+        <v>0.0002964</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>1603.962</v>
+        <v>2590.657</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
@@ -3392,30 +3845,30 @@
         <v>111</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H6" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>0.556</v>
+        <v>0.482</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
@@ -3424,30 +3877,30 @@
         <v>111</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
       </c>
       <c r="AD7" s="1">
-        <v>4.253</v>
+        <v>5.189</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>47</v>
@@ -3456,30 +3909,30 @@
         <v>111</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H8" t="s">
         <v>113</v>
       </c>
       <c r="I8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AD8" s="1">
-        <v>2.134</v>
+        <v>2.67</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
@@ -3488,30 +3941,30 @@
         <v>111</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
       </c>
       <c r="AD9" s="1">
-        <v>3.139</v>
+        <v>3.745</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
@@ -3520,30 +3973,30 @@
         <v>111</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H10" t="s">
         <v>118</v>
       </c>
       <c r="I10" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AD10" s="1">
-        <v>0.928</v>
+        <v>1.107</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
@@ -3552,30 +4005,30 @@
         <v>111</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H11" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.291</v>
+        <v>0.308</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B12" s="1">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
@@ -3584,10 +4037,10 @@
         <v>111</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H12" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -3618,72 +4071,72 @@
       </c>
       <c r="P12" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>1060.0</v>
+        <v>1085.0</v>
       </c>
       <c r="Q12" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.00023117805</v>
+        <v>0.0002366303625</v>
       </c>
       <c r="R12" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.000265</v>
+        <v>0.00027125</v>
       </c>
       <c r="S12" s="2">
         <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>130.0</v>
+        <v>160.0</v>
       </c>
       <c r="T12" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.00013608972</v>
+        <v>0.00016749504</v>
       </c>
       <c r="U12" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.000156</v>
+        <v>0.000192</v>
       </c>
       <c r="V12" s="2">
         <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>131.0</v>
+        <v>267.0</v>
       </c>
       <c r="W12" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.000137136564</v>
+        <v>0.000279507348</v>
       </c>
       <c r="X12" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0001572</v>
+        <v>0.0003204</v>
       </c>
       <c r="Y12" s="2">
         <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000504927756</v>
+        <v>0.0006841561725</v>
       </c>
       <c r="Z12" s="2">
         <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.0005788</v>
+        <v>0.00078425</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>50.0</v>
+        <v>68.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
+        <v>78.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>2958.588</v>
+        <v>7938.058</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>95</v>
@@ -3692,16 +4145,16 @@
         <v>111</v>
       </c>
       <c r="F13" s="1">
-        <v>1063</v>
+        <v>1088</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H13" t="s">
         <v>122</v>
       </c>
       <c r="I13" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="J13" s="2">
         <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
@@ -3729,107 +4182,107 @@
       </c>
       <c r="P13" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>1060.0</v>
+        <v>1085.0</v>
       </c>
       <c r="Q13" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.00023117805</v>
+        <v>0.0002366303625</v>
       </c>
       <c r="R13" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.000265</v>
+        <v>0.00027125</v>
       </c>
       <c r="S13" s="2">
         <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>130.0</v>
+        <v>160.0</v>
       </c>
       <c r="T13" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.00013608972</v>
+        <v>0.00016749504</v>
       </c>
       <c r="U13" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.000156</v>
+        <v>0.000192</v>
       </c>
       <c r="V13" s="2">
         <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>131.0</v>
+        <v>267.0</v>
       </c>
       <c r="W13" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.000137136564</v>
+        <v>0.000279507348</v>
       </c>
       <c r="X13" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0001572</v>
+        <v>0.0003204</v>
       </c>
       <c r="Y13" s="2">
         <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.000504927756</v>
+        <v>0.0006841561725</v>
       </c>
       <c r="Z13" s="2">
         <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.0005788</v>
+        <v>0.00078425</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>50.0</v>
+        <v>68.0</v>
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
+        <v>78.0</v>
       </c>
       <c r="AC13" s="1" t="s">
         <v>121</v>
       </c>
       <c r="AD13" s="1">
-        <v>2957.011</v>
+        <v>7932.653</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H14" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
       </c>
       <c r="AD14" s="1">
-        <v>0.305</v>
+        <v>0.577</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
@@ -3838,100 +4291,103 @@
         <v>111</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H15" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="J15" s="2">
-        <f>IF(COUNT('Turns'!D42,'Turns'!D57)=2,SUM('Turns'!D42,'Turns'!D57),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D42,'Turns'!D58)=2,SUM('Turns'!D42,'Turns'!D58),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K15" s="2">
-        <f>IF(COUNT('Turns'!E42,'Turns'!E57)=2,SUM('Turns'!E42,'Turns'!E57),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E42,'Turns'!E58)=2,SUM('Turns'!E42,'Turns'!E58),"Unknown")</f>
         <v>1.046844e-06</v>
       </c>
       <c r="L15" s="2">
-        <f>IF(COUNT('Turns'!F42,'Turns'!F57)=2,SUM('Turns'!F42,'Turns'!F57),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F42,'Turns'!F58)=2,SUM('Turns'!F42,'Turns'!F58),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M15" s="2">
-        <f>IF(COUNT('Turns'!D41,'Turns'!D56)=2,SUM('Turns'!D41,'Turns'!D56),"Unknown")</f>
-        <v>2407.0</v>
+        <f>IF(COUNT('Turns'!D41,'Turns'!D57)=2,SUM('Turns'!D41,'Turns'!D57),"Unknown")</f>
+        <v>2623.0</v>
       </c>
       <c r="N15" s="2">
-        <f>IF(COUNT('Turns'!E41,'Turns'!E56)=2,SUM('Turns'!E41,'Turns'!E56),"Unknown")</f>
-        <v>4.19958918e-05</v>
+        <f>IF(COUNT('Turns'!E41,'Turns'!E57)=2,SUM('Turns'!E41,'Turns'!E57),"Unknown")</f>
+        <v>4.57645302e-05</v>
       </c>
       <c r="O15" s="2">
-        <f>IF(COUNT('Turns'!F41,'Turns'!F56)=2,SUM('Turns'!F41,'Turns'!F56),"Unknown")</f>
-        <v>4.814e-05</v>
+        <f>IF(COUNT('Turns'!F41,'Turns'!F57)=2,SUM('Turns'!F41,'Turns'!F57),"Unknown")</f>
+        <v>5.246e-05</v>
       </c>
       <c r="P15" s="2">
-        <f>IF(COUNT('Turns'!D44,'Turns'!D59)=2,SUM('Turns'!D44,'Turns'!D59),"Unknown")</f>
-        <v>380.0</v>
+        <f>IF(COUNT('Turns'!D44,'Turns'!D60)=2,SUM('Turns'!D44,'Turns'!D60),"Unknown")</f>
+        <v>589.0</v>
       </c>
       <c r="Q15" s="2">
-        <f>IF(COUNT('Turns'!E44,'Turns'!E59)=2,SUM('Turns'!E44,'Turns'!E59),"Unknown")</f>
-        <v>8.287515e-05</v>
+        <f>IF(COUNT('Turns'!E44,'Turns'!E60)=2,SUM('Turns'!E44,'Turns'!E60),"Unknown")</f>
+        <v>0.0001284564825</v>
       </c>
       <c r="R15" s="2">
-        <f>IF(COUNT('Turns'!F44,'Turns'!F59)=2,SUM('Turns'!F44,'Turns'!F59),"Unknown")</f>
-        <v>9.5e-05</v>
+        <f>IF(COUNT('Turns'!F44,'Turns'!F60)=2,SUM('Turns'!F44,'Turns'!F60),"Unknown")</f>
+        <v>0.00014725</v>
       </c>
       <c r="S15" s="2">
-        <f>IF(COUNT('Turns'!D47,'Turns'!D62)=2,SUM('Turns'!D47,'Turns'!D62),"Unknown")</f>
-        <v>173.0</v>
+        <f>IF(COUNT('Turns'!D48,'Turns'!D64)=2,SUM('Turns'!D48,'Turns'!D64),"Unknown")</f>
+        <v>108.0</v>
       </c>
       <c r="T15" s="2">
-        <f>IF(COUNT('Turns'!E47,'Turns'!E62)=2,SUM('Turns'!E47,'Turns'!E62),"Unknown")</f>
-        <v>0.000181104012</v>
+        <f>IF(COUNT('Turns'!E48,'Turns'!E64)=2,SUM('Turns'!E48,'Turns'!E64),"Unknown")</f>
+        <v>0.000113059152</v>
       </c>
       <c r="U15" s="2">
-        <f>IF(COUNT('Turns'!F47,'Turns'!F62)=2,SUM('Turns'!F47,'Turns'!F62),"Unknown")</f>
-        <v>0.0002076</v>
+        <f>IF(COUNT('Turns'!F48,'Turns'!F64)=2,SUM('Turns'!F48,'Turns'!F64),"Unknown")</f>
+        <v>0.0001296</v>
       </c>
       <c r="V15" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D47,'Turns'!D63)=2,SUM('Turns'!D47,'Turns'!D63),"Unknown")</f>
+        <v>219.0</v>
       </c>
       <c r="W15" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E47,'Turns'!E63)=2,SUM('Turns'!E47,'Turns'!E63),"Unknown")</f>
+        <v>0.000229258836</v>
       </c>
       <c r="X15" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F47,'Turns'!F63)=2,SUM('Turns'!F47,'Turns'!F63),"Unknown")</f>
+        <v>0.0002628</v>
       </c>
       <c r="Y15" s="2">
-        <f>IF(COUNT('Turns'!E51,'Turns'!E66)=2,SUM('Turns'!E51,'Turns'!E66),"Unknown")</f>
-        <v>0.0003070218978</v>
+        <f>IF(COUNT('Turns'!E52,'Turns'!E68)=2,SUM('Turns'!E52,'Turns'!E68),"Unknown")</f>
+        <v>0.0005175858447</v>
       </c>
       <c r="Z15" s="2">
-        <f>IF(COUNT('Turns'!F51,'Turns'!F66)=2,SUM('Turns'!F51,'Turns'!F66),"Unknown")</f>
-        <v>0.00035194</v>
+        <f>IF(COUNT('Turns'!F52,'Turns'!F68)=2,SUM('Turns'!F52,'Turns'!F68),"Unknown")</f>
+        <v>0.00059331</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>31.0</v>
+        <v>52.0</v>
       </c>
       <c r="AB15" s="5">
         <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
+        <v>59.0</v>
       </c>
       <c r="AD15" s="1">
-        <v>2754.788</v>
+        <v>7610.67</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
@@ -3940,30 +4396,30 @@
         <v>111</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H16" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I16" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AD16" s="1">
-        <v>0.467</v>
+        <v>0.704</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>47</v>
@@ -3972,30 +4428,30 @@
         <v>111</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="I17" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AD17" s="1">
-        <v>3.697</v>
+        <v>4.354</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="54" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>47</v>
@@ -4004,30 +4460,30 @@
         <v>111</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H18" t="s">
         <v>128</v>
       </c>
       <c r="I18" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AD18" s="1">
-        <v>1.828</v>
+        <v>1.554</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="54" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>47</v>
@@ -4036,30 +4492,30 @@
         <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H19" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="I19" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.307</v>
+        <v>0.673</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="54" customHeight="1">
       <c r="A20" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>47</v>
@@ -4068,13 +4524,13 @@
         <v>111</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H20" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="I20" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="J20" s="2">
         <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
@@ -4090,81 +4546,84 @@
       </c>
       <c r="M20" s="2">
         <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>1060.0</v>
+        <v>1085.0</v>
       </c>
       <c r="N20" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.8494244e-05</v>
+        <v>1.8930429e-05</v>
       </c>
       <c r="O20" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>2.12e-05</v>
+        <v>2.17e-05</v>
       </c>
       <c r="P20" s="2">
         <f>IF(COUNT('Turns'!D44)=1,SUM('Turns'!D44),"Unknown")</f>
-        <v>287.0</v>
+        <v>453.0</v>
       </c>
       <c r="Q20" s="2">
         <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>6.25925475e-05</v>
+        <v>9.87959025e-05</v>
       </c>
       <c r="R20" s="2">
         <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>7.175e-05</v>
+        <v>0.00011325</v>
       </c>
       <c r="S20" s="2">
+        <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
+        <v>31.0</v>
+      </c>
+      <c r="T20" s="2">
+        <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
+        <v>3.2452164e-05</v>
+      </c>
+      <c r="U20" s="2">
+        <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
+        <v>3.72e-05</v>
+      </c>
+      <c r="V20" s="2">
         <f>IF(COUNT('Turns'!D47)=1,SUM('Turns'!D47),"Unknown")</f>
-        <v>29.0</v>
-      </c>
-      <c r="T20" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="W20" s="2">
         <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>3.0358476e-05</v>
-      </c>
-      <c r="U20" s="2">
+        <v>2.9311632e-05</v>
+      </c>
+      <c r="X20" s="2">
         <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>3.48e-05</v>
-      </c>
-      <c r="V20" s="2">
-        <v>0</v>
-      </c>
-      <c r="W20" s="2">
-        <v>0</v>
-      </c>
-      <c r="X20" s="2">
-        <v>0</v>
+        <v>3.36e-05</v>
       </c>
       <c r="Y20" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>0.0001119686895</v>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>0.0001800135495</v>
       </c>
       <c r="Z20" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
-        <v>0.00012835</v>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <v>0.00020635</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>21.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>1149.281</v>
+        <v>1814.838</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="54" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>95</v>
@@ -4173,16 +4632,16 @@
         <v>111</v>
       </c>
       <c r="F21" s="1">
-        <v>1350</v>
+        <v>1541</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H21" t="s">
         <v>132</v>
       </c>
       <c r="I21" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J21" s="2">
         <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
@@ -4198,84 +4657,87 @@
       </c>
       <c r="M21" s="2">
         <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>1060.0</v>
+        <v>1085.0</v>
       </c>
       <c r="N21" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.8494244e-05</v>
+        <v>1.8930429e-05</v>
       </c>
       <c r="O21" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>2.12e-05</v>
+        <v>2.17e-05</v>
       </c>
       <c r="P21" s="2">
         <f>IF(COUNT('Turns'!D44)=1,SUM('Turns'!D44),"Unknown")</f>
-        <v>287.0</v>
+        <v>453.0</v>
       </c>
       <c r="Q21" s="2">
         <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>6.25925475e-05</v>
+        <v>9.87959025e-05</v>
       </c>
       <c r="R21" s="2">
         <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>7.175e-05</v>
+        <v>0.00011325</v>
       </c>
       <c r="S21" s="2">
+        <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
+        <v>31.0</v>
+      </c>
+      <c r="T21" s="2">
+        <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
+        <v>3.2452164e-05</v>
+      </c>
+      <c r="U21" s="2">
+        <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
+        <v>3.72e-05</v>
+      </c>
+      <c r="V21" s="2">
         <f>IF(COUNT('Turns'!D47)=1,SUM('Turns'!D47),"Unknown")</f>
-        <v>29.0</v>
-      </c>
-      <c r="T21" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="W21" s="2">
         <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>3.0358476e-05</v>
-      </c>
-      <c r="U21" s="2">
+        <v>2.9311632e-05</v>
+      </c>
+      <c r="X21" s="2">
         <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>3.48e-05</v>
-      </c>
-      <c r="V21" s="2">
-        <v>0</v>
-      </c>
-      <c r="W21" s="2">
-        <v>0</v>
-      </c>
-      <c r="X21" s="2">
-        <v>0</v>
+        <v>3.36e-05</v>
       </c>
       <c r="Y21" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>0.0001119686895</v>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>0.0001800135495</v>
       </c>
       <c r="Z21" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
-        <v>0.00012835</v>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <v>0.00020635</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB21" s="5">
         <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>21.0</v>
       </c>
       <c r="AC21" s="1" t="s">
         <v>131</v>
       </c>
       <c r="AD21" s="1">
-        <v>1147.722</v>
+        <v>1812.529</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:31" ht="54" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>47</v>
@@ -4284,30 +4746,30 @@
         <v>111</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H22" t="s">
+        <v>192</v>
+      </c>
+      <c r="I22" t="s">
         <v>185</v>
       </c>
-      <c r="I22" t="s">
-        <v>178</v>
-      </c>
       <c r="AD22" s="1">
-        <v>0.446</v>
+        <v>0.36</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="54" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B23" s="1">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>47</v>
@@ -4316,30 +4778,30 @@
         <v>111</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H23" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I23" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AD23" s="1">
-        <v>4.872</v>
+        <v>4.091</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="54" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>47</v>
@@ -4348,30 +4810,30 @@
         <v>111</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H24" t="s">
         <v>134</v>
       </c>
       <c r="I24" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="AD24" s="1">
-        <v>1.343</v>
+        <v>1.111</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="54" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>47</v>
@@ -4380,30 +4842,30 @@
         <v>111</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H25" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="I25" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AD25" s="1">
-        <v>0.284</v>
+        <v>0.32</v>
       </c>
       <c r="AE25" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="54" customHeight="1">
       <c r="A26" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>47</v>
@@ -4412,103 +4874,106 @@
         <v>111</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H26" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="I26" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="J26" s="2">
+        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K26" s="2">
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="L26" s="2">
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M26" s="2">
         <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K26" s="2">
+        <v>1538.0</v>
+      </c>
+      <c r="N26" s="2">
         <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L26" s="2">
+        <v>2.68341012e-05</v>
+      </c>
+      <c r="O26" s="2">
         <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M26" s="2">
-        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>1347.0</v>
-      </c>
-      <c r="N26" s="2">
-        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>2.35016478e-05</v>
-      </c>
-      <c r="O26" s="2">
-        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>2.694e-05</v>
+        <v>3.076e-05</v>
       </c>
       <c r="P26" s="2">
-        <f>IF(COUNT('Turns'!D59)=1,SUM('Turns'!D59),"Unknown")</f>
-        <v>93.0</v>
+        <f>IF(COUNT('Turns'!D60)=1,SUM('Turns'!D60),"Unknown")</f>
+        <v>136.0</v>
       </c>
       <c r="Q26" s="2">
-        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>2.02826025e-05</v>
+        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
+        <v>2.966058e-05</v>
       </c>
       <c r="R26" s="2">
-        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
-        <v>2.325e-05</v>
+        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
+        <v>3.4e-05</v>
       </c>
       <c r="S26" s="2">
-        <f>IF(COUNT('Turns'!D62)=1,SUM('Turns'!D62),"Unknown")</f>
-        <v>144.0</v>
+        <f>IF(COUNT('Turns'!D64)=1,SUM('Turns'!D64),"Unknown")</f>
+        <v>77.0</v>
       </c>
       <c r="T26" s="2">
-        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
-        <v>0.000150745536</v>
+        <f>IF(COUNT('Turns'!E64)=1,SUM('Turns'!E64),"Unknown")</f>
+        <v>8.0606988e-05</v>
       </c>
       <c r="U26" s="2">
-        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
-        <v>0.0001728</v>
+        <f>IF(COUNT('Turns'!F64)=1,SUM('Turns'!F64),"Unknown")</f>
+        <v>9.24e-05</v>
       </c>
       <c r="V26" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
+        <v>191.0</v>
       </c>
       <c r="W26" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
+        <v>0.000199947204</v>
       </c>
       <c r="X26" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
+        <v>0.0002292</v>
       </c>
       <c r="Y26" s="2">
-        <f>IF(COUNT('Turns'!E66)=1,SUM('Turns'!E66),"Unknown")</f>
-        <v>0.0001950532083</v>
+        <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
+        <v>0.0003375722952</v>
       </c>
       <c r="Z26" s="2">
-        <f>IF(COUNT('Turns'!F66)=1,SUM('Turns'!F66),"Unknown")</f>
-        <v>0.00022359</v>
+        <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
+        <v>0.00038696</v>
       </c>
       <c r="AA26" s="5">
         <f>IF(ISNUMBER(Y26),ROUND(Y26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>34.0</v>
       </c>
       <c r="AB26" s="5">
         <f>IF(ISNUMBER(Z26),ROUND(Z26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>39.0</v>
       </c>
       <c r="AD26" s="1">
-        <v>1587.349</v>
+        <v>5774.887</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="54" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B27" s="1">
         <v>2</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>95</v>
@@ -4517,141 +4982,144 @@
         <v>111</v>
       </c>
       <c r="F27" s="1">
-        <v>1443</v>
+        <v>1677</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H27" t="s">
         <v>137</v>
       </c>
       <c r="I27" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="J27" s="2">
+        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K27" s="2">
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="L27" s="2">
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M27" s="2">
         <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K27" s="2">
+        <v>1538.0</v>
+      </c>
+      <c r="N27" s="2">
         <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L27" s="2">
+        <v>2.68341012e-05</v>
+      </c>
+      <c r="O27" s="2">
         <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M27" s="2">
-        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>1347.0</v>
-      </c>
-      <c r="N27" s="2">
-        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>2.35016478e-05</v>
-      </c>
-      <c r="O27" s="2">
-        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>2.694e-05</v>
+        <v>3.076e-05</v>
       </c>
       <c r="P27" s="2">
-        <f>IF(COUNT('Turns'!D59)=1,SUM('Turns'!D59),"Unknown")</f>
-        <v>93.0</v>
+        <f>IF(COUNT('Turns'!D60)=1,SUM('Turns'!D60),"Unknown")</f>
+        <v>136.0</v>
       </c>
       <c r="Q27" s="2">
-        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>2.02826025e-05</v>
+        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
+        <v>2.966058e-05</v>
       </c>
       <c r="R27" s="2">
-        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
-        <v>2.325e-05</v>
+        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
+        <v>3.4e-05</v>
       </c>
       <c r="S27" s="2">
-        <f>IF(COUNT('Turns'!D62)=1,SUM('Turns'!D62),"Unknown")</f>
-        <v>144.0</v>
+        <f>IF(COUNT('Turns'!D64)=1,SUM('Turns'!D64),"Unknown")</f>
+        <v>77.0</v>
       </c>
       <c r="T27" s="2">
-        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
-        <v>0.000150745536</v>
+        <f>IF(COUNT('Turns'!E64)=1,SUM('Turns'!E64),"Unknown")</f>
+        <v>8.0606988e-05</v>
       </c>
       <c r="U27" s="2">
-        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
-        <v>0.0001728</v>
+        <f>IF(COUNT('Turns'!F64)=1,SUM('Turns'!F64),"Unknown")</f>
+        <v>9.24e-05</v>
       </c>
       <c r="V27" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
+        <v>191.0</v>
       </c>
       <c r="W27" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
+        <v>0.000199947204</v>
       </c>
       <c r="X27" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
+        <v>0.0002292</v>
       </c>
       <c r="Y27" s="2">
-        <f>IF(COUNT('Turns'!E66)=1,SUM('Turns'!E66),"Unknown")</f>
-        <v>0.0001950532083</v>
+        <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
+        <v>0.0003375722952</v>
       </c>
       <c r="Z27" s="2">
-        <f>IF(COUNT('Turns'!F66)=1,SUM('Turns'!F66),"Unknown")</f>
-        <v>0.00022359</v>
+        <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
+        <v>0.00038696</v>
       </c>
       <c r="AA27" s="5">
         <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>34.0</v>
       </c>
       <c r="AB27" s="5">
         <f>IF(ISNUMBER(Z27),ROUND(Z27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>39.0</v>
       </c>
       <c r="AC27" s="1" t="s">
         <v>136</v>
       </c>
       <c r="AD27" s="1">
-        <v>1585.396</v>
+        <v>5772.727</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="54" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B28" s="1">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H28" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I28" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AD28" s="1">
-        <v>0.301</v>
+        <v>0.599</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="54" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B29" s="1">
         <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>47</v>
@@ -4660,100 +5128,103 @@
         <v>111</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H29" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="J29" s="2">
-        <f>IF(COUNT('Turns'!D72,'Turns'!D87)=2,SUM('Turns'!D72,'Turns'!D87),"Unknown")</f>
-        <v>6.0</v>
+        <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
+        <v>3.0</v>
       </c>
       <c r="K29" s="2">
-        <f>IF(COUNT('Turns'!E72,'Turns'!E87)=2,SUM('Turns'!E72,'Turns'!E87),"Unknown")</f>
-        <v>1.046844e-06</v>
+        <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
+        <v>5.23422e-07</v>
       </c>
       <c r="L29" s="2">
-        <f>IF(COUNT('Turns'!F72,'Turns'!F87)=2,SUM('Turns'!F72,'Turns'!F87),"Unknown")</f>
-        <v>1.2e-06</v>
+        <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
+        <v>6e-07</v>
       </c>
       <c r="M29" s="2">
-        <f>IF(COUNT('Turns'!D71,'Turns'!D86)=2,SUM('Turns'!D71,'Turns'!D86),"Unknown")</f>
-        <v>3050.0</v>
+        <f>IF(COUNT('Turns'!D73)=1,SUM('Turns'!D73),"Unknown")</f>
+        <v>1674.0</v>
       </c>
       <c r="N29" s="2">
-        <f>IF(COUNT('Turns'!E71,'Turns'!E86)=2,SUM('Turns'!E71,'Turns'!E86),"Unknown")</f>
-        <v>5.321457e-05</v>
+        <f>IF(COUNT('Turns'!E73)=1,SUM('Turns'!E73),"Unknown")</f>
+        <v>2.92069476e-05</v>
       </c>
       <c r="O29" s="2">
-        <f>IF(COUNT('Turns'!F71,'Turns'!F86)=2,SUM('Turns'!F71,'Turns'!F86),"Unknown")</f>
-        <v>6.1e-05</v>
+        <f>IF(COUNT('Turns'!F73)=1,SUM('Turns'!F73),"Unknown")</f>
+        <v>3.348e-05</v>
       </c>
       <c r="P29" s="2">
-        <f>IF(COUNT('Turns'!D74,'Turns'!D89)=2,SUM('Turns'!D74,'Turns'!D89),"Unknown")</f>
-        <v>270.0</v>
+        <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
+        <v>323.0</v>
       </c>
       <c r="Q29" s="2">
-        <f>IF(COUNT('Turns'!E74,'Turns'!E89)=2,SUM('Turns'!E74,'Turns'!E89),"Unknown")</f>
-        <v>5.8884975e-05</v>
+        <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
+        <v>7.04438775e-05</v>
       </c>
       <c r="R29" s="2">
-        <f>IF(COUNT('Turns'!F74,'Turns'!F89)=2,SUM('Turns'!F74,'Turns'!F89),"Unknown")</f>
-        <v>6.75e-05</v>
+        <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
+        <v>8.075e-05</v>
       </c>
       <c r="S29" s="2">
-        <f>IF(COUNT('Turns'!D77,'Turns'!D92)=2,SUM('Turns'!D77,'Turns'!D92),"Unknown")</f>
-        <v>45.0</v>
+        <f>IF(COUNT('Turns'!D80)=1,SUM('Turns'!D80),"Unknown")</f>
+        <v>179.0</v>
       </c>
       <c r="T29" s="2">
-        <f>IF(COUNT('Turns'!E77,'Turns'!E92)=2,SUM('Turns'!E77,'Turns'!E92),"Unknown")</f>
-        <v>4.710798e-05</v>
+        <f>IF(COUNT('Turns'!E80)=1,SUM('Turns'!E80),"Unknown")</f>
+        <v>0.000187385076</v>
       </c>
       <c r="U29" s="2">
-        <f>IF(COUNT('Turns'!F77,'Turns'!F92)=2,SUM('Turns'!F77,'Turns'!F92),"Unknown")</f>
-        <v>5.4e-05</v>
+        <f>IF(COUNT('Turns'!F80)=1,SUM('Turns'!F80),"Unknown")</f>
+        <v>0.0002148</v>
       </c>
       <c r="V29" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D79)=1,SUM('Turns'!D79),"Unknown")</f>
+        <v>102.0</v>
       </c>
       <c r="W29" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E79)=1,SUM('Turns'!E79),"Unknown")</f>
+        <v>0.000106778088</v>
       </c>
       <c r="X29" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F79)=1,SUM('Turns'!F79),"Unknown")</f>
+        <v>0.0001224</v>
       </c>
       <c r="Y29" s="2">
-        <f>IF(COUNT('Turns'!E81,'Turns'!E96)=2,SUM('Turns'!E81,'Turns'!E96),"Unknown")</f>
-        <v>0.000160254369</v>
+        <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
+        <v>0.0003943374111</v>
       </c>
       <c r="Z29" s="2">
-        <f>IF(COUNT('Turns'!F81,'Turns'!F96)=2,SUM('Turns'!F81,'Turns'!F96),"Unknown")</f>
-        <v>0.0001837</v>
+        <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
+        <v>0.00045203</v>
       </c>
       <c r="AA29" s="5">
         <f>IF(ISNUMBER(Y29),ROUND(Y29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>39.0</v>
       </c>
       <c r="AB29" s="5">
         <f>IF(ISNUMBER(Z29),ROUND(Z29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>45.0</v>
       </c>
       <c r="AD29" s="1">
-        <v>1824.85</v>
+        <v>4446.082</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="54" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>47</v>
@@ -4762,30 +5233,30 @@
         <v>111</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H30" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="I30" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AD30" s="1">
-        <v>0.402</v>
+        <v>0.395</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="54" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B31" s="1">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>47</v>
@@ -4794,62 +5265,62 @@
         <v>111</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H31" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="I31" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AD31" s="1">
-        <v>3.253</v>
+        <v>3.047</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="54" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B32" s="1">
         <v>2</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I32" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="AD32" s="1">
-        <v>1.243</v>
+        <v>0.93</v>
       </c>
       <c r="AE32" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="54" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B33" s="1">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>47</v>
@@ -4858,30 +5329,30 @@
         <v>111</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H33" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I33" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AD33" s="1">
-        <v>0.286</v>
+        <v>0.297</v>
       </c>
       <c r="AE33" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="54" customHeight="1">
       <c r="A34" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B34" s="1">
-        <v>1</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>47</v>
@@ -4890,103 +5361,106 @@
         <v>111</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H34" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="I34" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="J34" s="2">
-        <f>IF(COUNT('Turns'!D72)=1,SUM('Turns'!D72),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K34" s="2">
-        <f>IF(COUNT('Turns'!E72)=1,SUM('Turns'!E72),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L34" s="2">
-        <f>IF(COUNT('Turns'!F72)=1,SUM('Turns'!F72),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M34" s="2">
-        <f>IF(COUNT('Turns'!D71)=1,SUM('Turns'!D71),"Unknown")</f>
-        <v>1440.0</v>
+        <f>IF(COUNT('Turns'!D73)=1,SUM('Turns'!D73),"Unknown")</f>
+        <v>1674.0</v>
       </c>
       <c r="N34" s="2">
-        <f>IF(COUNT('Turns'!E71)=1,SUM('Turns'!E71),"Unknown")</f>
-        <v>2.5124256e-05</v>
+        <f>IF(COUNT('Turns'!E73)=1,SUM('Turns'!E73),"Unknown")</f>
+        <v>2.92069476e-05</v>
       </c>
       <c r="O34" s="2">
-        <f>IF(COUNT('Turns'!F71)=1,SUM('Turns'!F71),"Unknown")</f>
-        <v>2.88e-05</v>
+        <f>IF(COUNT('Turns'!F73)=1,SUM('Turns'!F73),"Unknown")</f>
+        <v>3.348e-05</v>
       </c>
       <c r="P34" s="2">
-        <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
-        <v>170.0</v>
+        <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
+        <v>323.0</v>
       </c>
       <c r="Q34" s="2">
-        <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
-        <v>3.7075725e-05</v>
+        <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
+        <v>7.04438775e-05</v>
       </c>
       <c r="R34" s="2">
-        <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
-        <v>4.25e-05</v>
+        <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
+        <v>8.075e-05</v>
       </c>
       <c r="S34" s="2">
-        <f>IF(COUNT('Turns'!D77)=1,SUM('Turns'!D77),"Unknown")</f>
-        <v>29.0</v>
+        <f>IF(COUNT('Turns'!D80)=1,SUM('Turns'!D80),"Unknown")</f>
+        <v>179.0</v>
       </c>
       <c r="T34" s="2">
-        <f>IF(COUNT('Turns'!E77)=1,SUM('Turns'!E77),"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <f>IF(COUNT('Turns'!E80)=1,SUM('Turns'!E80),"Unknown")</f>
+        <v>0.000187385076</v>
       </c>
       <c r="U34" s="2">
-        <f>IF(COUNT('Turns'!F77)=1,SUM('Turns'!F77),"Unknown")</f>
-        <v>3.48e-05</v>
+        <f>IF(COUNT('Turns'!F80)=1,SUM('Turns'!F80),"Unknown")</f>
+        <v>0.0002148</v>
       </c>
       <c r="V34" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D79)=1,SUM('Turns'!D79),"Unknown")</f>
+        <v>102.0</v>
       </c>
       <c r="W34" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E79)=1,SUM('Turns'!E79),"Unknown")</f>
+        <v>0.000106778088</v>
       </c>
       <c r="X34" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F79)=1,SUM('Turns'!F79),"Unknown")</f>
+        <v>0.0001224</v>
       </c>
       <c r="Y34" s="2">
-        <f>IF(COUNT('Turns'!E81)=1,SUM('Turns'!E81),"Unknown")</f>
-        <v>9.3081879e-05</v>
+        <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
+        <v>0.0003943374111</v>
       </c>
       <c r="Z34" s="2">
-        <f>IF(COUNT('Turns'!F81)=1,SUM('Turns'!F81),"Unknown")</f>
-        <v>0.0001067</v>
+        <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
+        <v>0.00045203</v>
       </c>
       <c r="AA34" s="5">
         <f>IF(ISNUMBER(Y34),ROUND(Y34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>39.0</v>
       </c>
       <c r="AB34" s="5">
         <f>IF(ISNUMBER(Z34),ROUND(Z34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>45.0</v>
       </c>
       <c r="AD34" s="1">
-        <v>971.492</v>
+        <v>4437.396</v>
       </c>
       <c r="AE34" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="54" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B35" s="1">
         <v>2</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>95</v>
@@ -4995,141 +5469,144 @@
         <v>111</v>
       </c>
       <c r="F35" s="1">
-        <v>1613</v>
+        <v>2000</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H35" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I35" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="J35" s="2">
-        <f>IF(COUNT('Turns'!D72)=1,SUM('Turns'!D72),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K35" s="2">
-        <f>IF(COUNT('Turns'!E72)=1,SUM('Turns'!E72),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L35" s="2">
-        <f>IF(COUNT('Turns'!F72)=1,SUM('Turns'!F72),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M35" s="2">
-        <f>IF(COUNT('Turns'!D71)=1,SUM('Turns'!D71),"Unknown")</f>
-        <v>1440.0</v>
+        <f>IF(COUNT('Turns'!D73)=1,SUM('Turns'!D73),"Unknown")</f>
+        <v>1674.0</v>
       </c>
       <c r="N35" s="2">
-        <f>IF(COUNT('Turns'!E71)=1,SUM('Turns'!E71),"Unknown")</f>
-        <v>2.5124256e-05</v>
+        <f>IF(COUNT('Turns'!E73)=1,SUM('Turns'!E73),"Unknown")</f>
+        <v>2.92069476e-05</v>
       </c>
       <c r="O35" s="2">
-        <f>IF(COUNT('Turns'!F71)=1,SUM('Turns'!F71),"Unknown")</f>
-        <v>2.88e-05</v>
+        <f>IF(COUNT('Turns'!F73)=1,SUM('Turns'!F73),"Unknown")</f>
+        <v>3.348e-05</v>
       </c>
       <c r="P35" s="2">
-        <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
-        <v>170.0</v>
+        <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
+        <v>323.0</v>
       </c>
       <c r="Q35" s="2">
-        <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
-        <v>3.7075725e-05</v>
+        <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
+        <v>7.04438775e-05</v>
       </c>
       <c r="R35" s="2">
-        <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
-        <v>4.25e-05</v>
+        <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
+        <v>8.075e-05</v>
       </c>
       <c r="S35" s="2">
-        <f>IF(COUNT('Turns'!D77)=1,SUM('Turns'!D77),"Unknown")</f>
-        <v>29.0</v>
+        <f>IF(COUNT('Turns'!D80)=1,SUM('Turns'!D80),"Unknown")</f>
+        <v>179.0</v>
       </c>
       <c r="T35" s="2">
-        <f>IF(COUNT('Turns'!E77)=1,SUM('Turns'!E77),"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <f>IF(COUNT('Turns'!E80)=1,SUM('Turns'!E80),"Unknown")</f>
+        <v>0.000187385076</v>
       </c>
       <c r="U35" s="2">
-        <f>IF(COUNT('Turns'!F77)=1,SUM('Turns'!F77),"Unknown")</f>
-        <v>3.48e-05</v>
+        <f>IF(COUNT('Turns'!F80)=1,SUM('Turns'!F80),"Unknown")</f>
+        <v>0.0002148</v>
       </c>
       <c r="V35" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D79)=1,SUM('Turns'!D79),"Unknown")</f>
+        <v>102.0</v>
       </c>
       <c r="W35" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E79)=1,SUM('Turns'!E79),"Unknown")</f>
+        <v>0.000106778088</v>
       </c>
       <c r="X35" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F79)=1,SUM('Turns'!F79),"Unknown")</f>
+        <v>0.0001224</v>
       </c>
       <c r="Y35" s="2">
-        <f>IF(COUNT('Turns'!E81)=1,SUM('Turns'!E81),"Unknown")</f>
-        <v>9.3081879e-05</v>
+        <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
+        <v>0.0003943374111</v>
       </c>
       <c r="Z35" s="2">
-        <f>IF(COUNT('Turns'!F81)=1,SUM('Turns'!F81),"Unknown")</f>
-        <v>0.0001067</v>
+        <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
+        <v>0.00045203</v>
       </c>
       <c r="AA35" s="5">
         <f>IF(ISNUMBER(Y35),ROUND(Y35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>39.0</v>
       </c>
       <c r="AB35" s="5">
         <f>IF(ISNUMBER(Z35),ROUND(Z35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>45.0</v>
       </c>
       <c r="AC35" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AD35" s="1">
-        <v>969.059</v>
+        <v>4435.348</v>
       </c>
       <c r="AE35" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="54" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H36" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I36" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AD36" s="1">
-        <v>0.451</v>
+        <v>0.344</v>
       </c>
       <c r="AE36" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="54" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>47</v>
@@ -5138,30 +5615,103 @@
         <v>111</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="H37" t="s">
-        <v>196</v>
-      </c>
-      <c r="I37" t="s">
-        <v>190</v>
+        <v>203</v>
+      </c>
+      <c r="J37" s="2">
+        <f>IF(COUNT('Turns'!D90,'Turns'!D106)=2,SUM('Turns'!D90,'Turns'!D106),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="K37" s="2">
+        <f>IF(COUNT('Turns'!E90,'Turns'!E106)=2,SUM('Turns'!E90,'Turns'!E106),"Unknown")</f>
+        <v>1.046844e-06</v>
+      </c>
+      <c r="L37" s="2">
+        <f>IF(COUNT('Turns'!F90,'Turns'!F106)=2,SUM('Turns'!F90,'Turns'!F106),"Unknown")</f>
+        <v>1.2e-06</v>
+      </c>
+      <c r="M37" s="2">
+        <f>IF(COUNT('Turns'!D89,'Turns'!D105)=2,SUM('Turns'!D89,'Turns'!D105),"Unknown")</f>
+        <v>4301.0</v>
+      </c>
+      <c r="N37" s="2">
+        <f>IF(COUNT('Turns'!E89,'Turns'!E105)=2,SUM('Turns'!E89,'Turns'!E105),"Unknown")</f>
+        <v>7.50412674e-05</v>
+      </c>
+      <c r="O37" s="2">
+        <f>IF(COUNT('Turns'!F89,'Turns'!F105)=2,SUM('Turns'!F89,'Turns'!F105),"Unknown")</f>
+        <v>8.602e-05</v>
+      </c>
+      <c r="P37" s="2">
+        <f>IF(COUNT('Turns'!D92,'Turns'!D108)=2,SUM('Turns'!D92,'Turns'!D108),"Unknown")</f>
+        <v>430.0</v>
+      </c>
+      <c r="Q37" s="2">
+        <f>IF(COUNT('Turns'!E92,'Turns'!E108)=2,SUM('Turns'!E92,'Turns'!E108),"Unknown")</f>
+        <v>9.3779775e-05</v>
+      </c>
+      <c r="R37" s="2">
+        <f>IF(COUNT('Turns'!F92,'Turns'!F108)=2,SUM('Turns'!F92,'Turns'!F108),"Unknown")</f>
+        <v>0.0001075</v>
+      </c>
+      <c r="S37" s="2">
+        <f>IF(COUNT('Turns'!D96,'Turns'!D111)=2,SUM('Turns'!D96,'Turns'!D111),"Unknown")</f>
+        <v>48.0</v>
+      </c>
+      <c r="T37" s="2">
+        <f>IF(COUNT('Turns'!E96,'Turns'!E111)=2,SUM('Turns'!E96,'Turns'!E111),"Unknown")</f>
+        <v>5.0248512e-05</v>
+      </c>
+      <c r="U37" s="2">
+        <f>IF(COUNT('Turns'!F96,'Turns'!F111)=2,SUM('Turns'!F96,'Turns'!F111),"Unknown")</f>
+        <v>5.76e-05</v>
+      </c>
+      <c r="V37" s="2">
+        <f>IF(COUNT('Turns'!D95)=1,SUM('Turns'!D95),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="W37" s="2">
+        <f>IF(COUNT('Turns'!E95)=1,SUM('Turns'!E95),"Unknown")</f>
+        <v>8.374752e-06</v>
+      </c>
+      <c r="X37" s="2">
+        <f>IF(COUNT('Turns'!F95)=1,SUM('Turns'!F95),"Unknown")</f>
+        <v>9.6e-06</v>
+      </c>
+      <c r="Y37" s="2">
+        <f>IF(COUNT('Turns'!E100,'Turns'!E115)=2,SUM('Turns'!E100,'Turns'!E115),"Unknown")</f>
+        <v>0.0002284911504</v>
+      </c>
+      <c r="Z37" s="2">
+        <f>IF(COUNT('Turns'!F100,'Turns'!F115)=2,SUM('Turns'!F100,'Turns'!F115),"Unknown")</f>
+        <v>0.00026192</v>
+      </c>
+      <c r="AA37" s="5">
+        <f>IF(ISNUMBER(Y37),ROUND(Y37*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>23.0</v>
+      </c>
+      <c r="AB37" s="5">
+        <f>IF(ISNUMBER(Z37),ROUND(Z37*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>26.0</v>
       </c>
       <c r="AD37" s="1">
-        <v>8.542999999999999</v>
+        <v>2603.93</v>
       </c>
       <c r="AE37" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="54" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B38" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>47</v>
@@ -5173,27 +5723,27 @@
         <v>172</v>
       </c>
       <c r="H38" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="I38" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="AD38" s="1">
-        <v>1.109</v>
+        <v>0.426</v>
       </c>
       <c r="AE38" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="54" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="B39" s="1">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>47</v>
@@ -5202,30 +5752,30 @@
         <v>111</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="H39" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="I39" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AD39" s="1">
-        <v>0.447</v>
+        <v>3.827</v>
       </c>
       <c r="AE39" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:31" ht="54" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="B40" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>47</v>
@@ -5234,92 +5784,19 @@
         <v>111</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="H40" t="s">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="I40" t="s">
-        <v>190</v>
-      </c>
-      <c r="J40" s="2">
-        <f>IF(COUNT('Turns'!D87)=1,SUM('Turns'!D87),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K40" s="2">
-        <f>IF(COUNT('Turns'!E87)=1,SUM('Turns'!E87),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L40" s="2">
-        <f>IF(COUNT('Turns'!F87)=1,SUM('Turns'!F87),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M40" s="2">
-        <f>IF(COUNT('Turns'!D86)=1,SUM('Turns'!D86),"Unknown")</f>
-        <v>1610.0</v>
-      </c>
-      <c r="N40" s="2">
-        <f>IF(COUNT('Turns'!E86)=1,SUM('Turns'!E86),"Unknown")</f>
-        <v>2.8090314e-05</v>
-      </c>
-      <c r="O40" s="2">
-        <f>IF(COUNT('Turns'!F86)=1,SUM('Turns'!F86),"Unknown")</f>
-        <v>3.22e-05</v>
-      </c>
-      <c r="P40" s="2">
-        <f>IF(COUNT('Turns'!D89)=1,SUM('Turns'!D89),"Unknown")</f>
-        <v>100.0</v>
-      </c>
-      <c r="Q40" s="2">
-        <f>IF(COUNT('Turns'!E89)=1,SUM('Turns'!E89),"Unknown")</f>
-        <v>2.180925e-05</v>
-      </c>
-      <c r="R40" s="2">
-        <f>IF(COUNT('Turns'!F89)=1,SUM('Turns'!F89),"Unknown")</f>
-        <v>2.5e-05</v>
-      </c>
-      <c r="S40" s="2">
-        <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
-        <v>16.0</v>
-      </c>
-      <c r="T40" s="2">
-        <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
-        <v>1.6749504e-05</v>
-      </c>
-      <c r="U40" s="2">
-        <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
-        <v>1.92e-05</v>
-      </c>
-      <c r="V40" s="2">
-        <v>0</v>
-      </c>
-      <c r="W40" s="2">
-        <v>0</v>
-      </c>
-      <c r="X40" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="2">
-        <f>IF(COUNT('Turns'!E96)=1,SUM('Turns'!E96),"Unknown")</f>
-        <v>6.717249e-05</v>
-      </c>
-      <c r="Z40" s="2">
-        <f>IF(COUNT('Turns'!F96)=1,SUM('Turns'!F96),"Unknown")</f>
-        <v>7.7e-05</v>
-      </c>
-      <c r="AA40" s="5">
-        <f>IF(ISNUMBER(Y40),ROUND(Y40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="AB40" s="5">
-        <f>IF(ISNUMBER(Z40),ROUND(Z40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>205</v>
       </c>
       <c r="AD40" s="1">
-        <v>829.708</v>
+        <v>1.289</v>
       </c>
       <c r="AE40" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:31" ht="54" customHeight="1">
@@ -5327,107 +5804,28 @@
         <v>160</v>
       </c>
       <c r="B41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="1">
-        <v>1713</v>
-      </c>
       <c r="G41" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H41" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="I41" t="s">
-        <v>198</v>
-      </c>
-      <c r="J41" s="2">
-        <f>IF(COUNT('Turns'!D87)=1,SUM('Turns'!D87),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K41" s="2">
-        <f>IF(COUNT('Turns'!E87)=1,SUM('Turns'!E87),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L41" s="2">
-        <f>IF(COUNT('Turns'!F87)=1,SUM('Turns'!F87),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M41" s="2">
-        <f>IF(COUNT('Turns'!D86)=1,SUM('Turns'!D86),"Unknown")</f>
-        <v>1610.0</v>
-      </c>
-      <c r="N41" s="2">
-        <f>IF(COUNT('Turns'!E86)=1,SUM('Turns'!E86),"Unknown")</f>
-        <v>2.8090314e-05</v>
-      </c>
-      <c r="O41" s="2">
-        <f>IF(COUNT('Turns'!F86)=1,SUM('Turns'!F86),"Unknown")</f>
-        <v>3.22e-05</v>
-      </c>
-      <c r="P41" s="2">
-        <f>IF(COUNT('Turns'!D89)=1,SUM('Turns'!D89),"Unknown")</f>
-        <v>100.0</v>
-      </c>
-      <c r="Q41" s="2">
-        <f>IF(COUNT('Turns'!E89)=1,SUM('Turns'!E89),"Unknown")</f>
-        <v>2.180925e-05</v>
-      </c>
-      <c r="R41" s="2">
-        <f>IF(COUNT('Turns'!F89)=1,SUM('Turns'!F89),"Unknown")</f>
-        <v>2.5e-05</v>
-      </c>
-      <c r="S41" s="2">
-        <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
-        <v>16.0</v>
-      </c>
-      <c r="T41" s="2">
-        <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
-        <v>1.6749504e-05</v>
-      </c>
-      <c r="U41" s="2">
-        <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
-        <v>1.92e-05</v>
-      </c>
-      <c r="V41" s="2">
-        <v>0</v>
-      </c>
-      <c r="W41" s="2">
-        <v>0</v>
-      </c>
-      <c r="X41" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="2">
-        <f>IF(COUNT('Turns'!E96)=1,SUM('Turns'!E96),"Unknown")</f>
-        <v>6.717249e-05</v>
-      </c>
-      <c r="Z41" s="2">
-        <f>IF(COUNT('Turns'!F96)=1,SUM('Turns'!F96),"Unknown")</f>
-        <v>7.7e-05</v>
-      </c>
-      <c r="AA41" s="5">
-        <f>IF(ISNUMBER(Y41),ROUND(Y41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="AB41" s="5">
-        <f>IF(ISNUMBER(Z41),ROUND(Z41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="AC41" s="1" t="s">
-        <v>146</v>
+        <v>203</v>
       </c>
       <c r="AD41" s="1">
-        <v>827.098</v>
+        <v>0.323</v>
       </c>
       <c r="AE41" s="1" t="s">
         <v>163</v>
@@ -5441,7 +5839,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>47</v>
@@ -5453,20 +5851,586 @@
         <v>165</v>
       </c>
       <c r="H42" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I42" t="s">
-        <v>190</v>
+        <v>203</v>
+      </c>
+      <c r="J42" s="2">
+        <f>IF(COUNT('Turns'!D90)=1,SUM('Turns'!D90),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K42" s="2">
+        <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="L42" s="2">
+        <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M42" s="2">
+        <f>IF(COUNT('Turns'!D89)=1,SUM('Turns'!D89),"Unknown")</f>
+        <v>1997.0</v>
+      </c>
+      <c r="N42" s="2">
+        <f>IF(COUNT('Turns'!E89)=1,SUM('Turns'!E89),"Unknown")</f>
+        <v>3.48424578e-05</v>
+      </c>
+      <c r="O42" s="2">
+        <f>IF(COUNT('Turns'!F89)=1,SUM('Turns'!F89),"Unknown")</f>
+        <v>3.994e-05</v>
+      </c>
+      <c r="P42" s="2">
+        <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
+        <v>307.0</v>
+      </c>
+      <c r="Q42" s="2">
+        <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
+        <v>6.69543975e-05</v>
+      </c>
+      <c r="R42" s="2">
+        <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
+        <v>7.675e-05</v>
+      </c>
+      <c r="S42" s="2">
+        <f>IF(COUNT('Turns'!D96)=1,SUM('Turns'!D96),"Unknown")</f>
+        <v>31.0</v>
+      </c>
+      <c r="T42" s="2">
+        <f>IF(COUNT('Turns'!E96)=1,SUM('Turns'!E96),"Unknown")</f>
+        <v>3.2452164e-05</v>
+      </c>
+      <c r="U42" s="2">
+        <f>IF(COUNT('Turns'!F96)=1,SUM('Turns'!F96),"Unknown")</f>
+        <v>3.72e-05</v>
+      </c>
+      <c r="V42" s="2">
+        <f>IF(COUNT('Turns'!D95)=1,SUM('Turns'!D95),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="W42" s="2">
+        <f>IF(COUNT('Turns'!E95)=1,SUM('Turns'!E95),"Unknown")</f>
+        <v>8.374752e-06</v>
+      </c>
+      <c r="X42" s="2">
+        <f>IF(COUNT('Turns'!F95)=1,SUM('Turns'!F95),"Unknown")</f>
+        <v>9.6e-06</v>
+      </c>
+      <c r="Y42" s="2">
+        <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
+        <v>0.0001431471933</v>
+      </c>
+      <c r="Z42" s="2">
+        <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
+        <v>0.00016409</v>
+      </c>
+      <c r="AA42" s="5">
+        <f>IF(ISNUMBER(Y42),ROUND(Y42*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>14.0</v>
+      </c>
+      <c r="AB42" s="5">
+        <f>IF(ISNUMBER(Z42),ROUND(Z42*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>16.0</v>
       </c>
       <c r="AD42" s="1">
-        <v>0.704</v>
+        <v>1539.551</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" ht="54" customHeight="1">
+      <c r="A43" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F43" s="1">
+        <v>2307</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H43" t="s">
+        <v>149</v>
+      </c>
+      <c r="I43" t="s">
+        <v>207</v>
+      </c>
+      <c r="J43" s="2">
+        <f>IF(COUNT('Turns'!D90)=1,SUM('Turns'!D90),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K43" s="2">
+        <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="L43" s="2">
+        <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M43" s="2">
+        <f>IF(COUNT('Turns'!D89)=1,SUM('Turns'!D89),"Unknown")</f>
+        <v>1997.0</v>
+      </c>
+      <c r="N43" s="2">
+        <f>IF(COUNT('Turns'!E89)=1,SUM('Turns'!E89),"Unknown")</f>
+        <v>3.48424578e-05</v>
+      </c>
+      <c r="O43" s="2">
+        <f>IF(COUNT('Turns'!F89)=1,SUM('Turns'!F89),"Unknown")</f>
+        <v>3.994e-05</v>
+      </c>
+      <c r="P43" s="2">
+        <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
+        <v>307.0</v>
+      </c>
+      <c r="Q43" s="2">
+        <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
+        <v>6.69543975e-05</v>
+      </c>
+      <c r="R43" s="2">
+        <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
+        <v>7.675e-05</v>
+      </c>
+      <c r="S43" s="2">
+        <f>IF(COUNT('Turns'!D96)=1,SUM('Turns'!D96),"Unknown")</f>
+        <v>31.0</v>
+      </c>
+      <c r="T43" s="2">
+        <f>IF(COUNT('Turns'!E96)=1,SUM('Turns'!E96),"Unknown")</f>
+        <v>3.2452164e-05</v>
+      </c>
+      <c r="U43" s="2">
+        <f>IF(COUNT('Turns'!F96)=1,SUM('Turns'!F96),"Unknown")</f>
+        <v>3.72e-05</v>
+      </c>
+      <c r="V43" s="2">
+        <f>IF(COUNT('Turns'!D95)=1,SUM('Turns'!D95),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="W43" s="2">
+        <f>IF(COUNT('Turns'!E95)=1,SUM('Turns'!E95),"Unknown")</f>
+        <v>8.374752e-06</v>
+      </c>
+      <c r="X43" s="2">
+        <f>IF(COUNT('Turns'!F95)=1,SUM('Turns'!F95),"Unknown")</f>
+        <v>9.6e-06</v>
+      </c>
+      <c r="Y43" s="2">
+        <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
+        <v>0.0001431471933</v>
+      </c>
+      <c r="Z43" s="2">
+        <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
+        <v>0.00016409</v>
+      </c>
+      <c r="AA43" s="5">
+        <f>IF(ISNUMBER(Y43),ROUND(Y43*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>14.0</v>
+      </c>
+      <c r="AB43" s="5">
+        <f>IF(ISNUMBER(Z43),ROUND(Z43*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+      <c r="AC43" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>1537.501</v>
+      </c>
+      <c r="AE43" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" ht="54" customHeight="1">
+      <c r="A44" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H44" t="s">
+        <v>208</v>
+      </c>
+      <c r="I44" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD44" s="1">
+        <v>0.536</v>
+      </c>
+      <c r="AE44" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" ht="54" customHeight="1">
+      <c r="A45" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H45" t="s">
+        <v>209</v>
+      </c>
+      <c r="I45" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD45" s="1">
+        <v>11.007</v>
+      </c>
+      <c r="AE45" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" ht="54" customHeight="1">
+      <c r="A46" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B46" s="1">
+        <v>2</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H46" t="s">
+        <v>151</v>
+      </c>
+      <c r="I46" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD46" s="1">
+        <v>1.052</v>
+      </c>
+      <c r="AE46" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" ht="54" customHeight="1">
+      <c r="A47" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" t="s">
+        <v>210</v>
+      </c>
+      <c r="I47" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD47" s="1">
+        <v>0.367</v>
+      </c>
+      <c r="AE47" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31" ht="54" customHeight="1">
+      <c r="A48" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H48" t="s">
+        <v>211</v>
+      </c>
+      <c r="I48" t="s">
+        <v>203</v>
+      </c>
+      <c r="J48" s="2">
+        <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K48" s="2">
+        <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="L48" s="2">
+        <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M48" s="2">
+        <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
+        <v>2304.0</v>
+      </c>
+      <c r="N48" s="2">
+        <f>IF(COUNT('Turns'!E105)=1,SUM('Turns'!E105),"Unknown")</f>
+        <v>4.01988096e-05</v>
+      </c>
+      <c r="O48" s="2">
+        <f>IF(COUNT('Turns'!F105)=1,SUM('Turns'!F105),"Unknown")</f>
+        <v>4.608e-05</v>
+      </c>
+      <c r="P48" s="2">
+        <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
+        <v>123.0</v>
+      </c>
+      <c r="Q48" s="2">
+        <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
+        <v>2.68253775e-05</v>
+      </c>
+      <c r="R48" s="2">
+        <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
+        <v>3.075e-05</v>
+      </c>
+      <c r="S48" s="2">
+        <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
+        <v>17.0</v>
+      </c>
+      <c r="T48" s="2">
+        <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
+        <v>1.7796348e-05</v>
+      </c>
+      <c r="U48" s="2">
+        <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
+        <v>2.04e-05</v>
+      </c>
+      <c r="V48" s="2">
+        <v>0</v>
+      </c>
+      <c r="W48" s="2">
+        <v>0</v>
+      </c>
+      <c r="X48" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="2">
+        <f>IF(COUNT('Turns'!E115)=1,SUM('Turns'!E115),"Unknown")</f>
+        <v>8.53439571e-05</v>
+      </c>
+      <c r="Z48" s="2">
+        <f>IF(COUNT('Turns'!F115)=1,SUM('Turns'!F115),"Unknown")</f>
+        <v>9.783e-05</v>
+      </c>
+      <c r="AA48" s="5">
+        <f>IF(ISNUMBER(Y48),ROUND(Y48*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="AB48" s="5">
+        <f>IF(ISNUMBER(Z48),ROUND(Z48*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="AD48" s="1">
+        <v>1038.006</v>
+      </c>
+      <c r="AE48" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31" ht="54" customHeight="1">
+      <c r="A49" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B49" s="1">
+        <v>2</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F49" s="1">
+        <v>2430</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H49" t="s">
+        <v>154</v>
+      </c>
+      <c r="I49" t="s">
+        <v>211</v>
+      </c>
+      <c r="J49" s="2">
+        <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K49" s="2">
+        <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="L49" s="2">
+        <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M49" s="2">
+        <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
+        <v>2304.0</v>
+      </c>
+      <c r="N49" s="2">
+        <f>IF(COUNT('Turns'!E105)=1,SUM('Turns'!E105),"Unknown")</f>
+        <v>4.01988096e-05</v>
+      </c>
+      <c r="O49" s="2">
+        <f>IF(COUNT('Turns'!F105)=1,SUM('Turns'!F105),"Unknown")</f>
+        <v>4.608e-05</v>
+      </c>
+      <c r="P49" s="2">
+        <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
+        <v>123.0</v>
+      </c>
+      <c r="Q49" s="2">
+        <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
+        <v>2.68253775e-05</v>
+      </c>
+      <c r="R49" s="2">
+        <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
+        <v>3.075e-05</v>
+      </c>
+      <c r="S49" s="2">
+        <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
+        <v>17.0</v>
+      </c>
+      <c r="T49" s="2">
+        <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
+        <v>1.7796348e-05</v>
+      </c>
+      <c r="U49" s="2">
+        <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
+        <v>2.04e-05</v>
+      </c>
+      <c r="V49" s="2">
+        <v>0</v>
+      </c>
+      <c r="W49" s="2">
+        <v>0</v>
+      </c>
+      <c r="X49" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="2">
+        <f>IF(COUNT('Turns'!E115)=1,SUM('Turns'!E115),"Unknown")</f>
+        <v>8.53439571e-05</v>
+      </c>
+      <c r="Z49" s="2">
+        <f>IF(COUNT('Turns'!F115)=1,SUM('Turns'!F115),"Unknown")</f>
+        <v>9.783e-05</v>
+      </c>
+      <c r="AA49" s="5">
+        <f>IF(ISNUMBER(Y49),ROUND(Y49*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="AB49" s="5">
+        <f>IF(ISNUMBER(Z49),ROUND(Z49*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="AC49" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD49" s="1">
+        <v>1036.489</v>
+      </c>
+      <c r="AE49" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" ht="54" customHeight="1">
+      <c r="A50" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H50" t="s">
+        <v>212</v>
+      </c>
+      <c r="I50" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD50" s="1">
+        <v>0.365</v>
+      </c>
+      <c r="AE50" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE42">
+  <conditionalFormatting sqref="A2:AE50">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>

--- a/reports/file_approval/report.xlsx
+++ b/reports/file_approval/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="233">
   <si>
     <t>Request</t>
   </si>
@@ -75,13 +75,13 @@
     <t>Parent ID</t>
   </si>
   <si>
-    <t>Fresh input tokens</t>
-  </si>
-  <si>
-    <t>Fresh input EUR</t>
-  </si>
-  <si>
-    <t>Fresh input USD</t>
+    <t>Input at standard rate tokens</t>
+  </si>
+  <si>
+    <t>Input at standard rate EUR</t>
+  </si>
+  <si>
+    <t>Input at standard rate USD</t>
   </si>
   <si>
     <t>Cache read tokens</t>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cce0-bc30-7871-9658-56d600af9884</t>
+    <t>01a0d130-9561-7081-adf9-e8f52d82f0d8</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T06:06:28.037095Z</t>
+    <t>2026-09-24T02:09:35.117183Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,10 +306,10 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cce0-bc37-7fd3-bc0c-f454386957f0</t>
-  </si>
-  <si>
-    <t>Fresh input</t>
+    <t>01a0d130-95bf-7752-9447-839261fb5d0b</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool definitions</t>
@@ -357,9 +357,9 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0be63b89bf4dc92a006ab36cbc7a7087d2a1d7d74fa055e1af", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2y9XDRLSkVTrLY5v91PlOqHPv504476Ch61y59qcC5WeZzNEU4hsksRNaapJYk7EZvEJldQ3O6ppVx3kZh0TS_aHmegwEvu7_maiQIvHUk_yL23q7FdTFAhi7mSxJdUFBoaa00u_D1AWIVjUJrZMkfjI7Xb0KzAhufCbkgcdywGkh7HK9WFn6fJeM6hb_iU_kySbeqEZEwh1ZIdhS2uLFy5I2TJ25C5Dw8CYTsG2WlDzIqp6-ZFAS84fb1utr_qrGy-xnwcF_Zo33gCUsRa7EUntxJSRryYo34k69LgqnnP0paIlzNwYQmtsRDCwvmiMaHel0_Y3hkdeSq2BUn81E6CHtYaBQdl9mgGmMdF289Ves4JzL8gpBvuAmjTQK8J6vvo3K3RdrUYf_9w7z50A-F0JxagnR04Fcq8EYFU5BIuHUgzvrfqDpb3QuGQCJeZG23sHr8GFjVNUWgfbQavZOpya-zLWHVyyiNOk-TIe_D0-m1bnzEgLsWKkK5UDDle7-0lfMYIoAWLoXnqKpThPowSTIslrByIJk7-Hc_nUOemXP8qWaCWA0rjHW1o_4m9wH-e7by9a4kYCRp9lRaOB_zOhYCx_lk68Eyjnf2ULn1N1GxvMDsyf6bBkrZkS05nHBGGmXbkmMqUuxSIGtY1-CI5WYpl5O3cDpU4c0YMAUztzZmtEI6p1zNVqiV0og_AQzzsbXHzu4pQlp00sWbc8DbbpIsQN6fXklLR0AKCC0jQUACyCdQ-yQcRw2Z77L5ZKyfI-U_6F65Gv1_KBh9-u2h7AfsBn52R2gM9X6AzAxSOMD4T80l-WYtAyc0T-vuelwkPSsHdWCwjXCKHWrq70dA5qR1Y2kgA0b03pus9_Y64UjSF0wyz4wZt0Eo1yeIAVWhlJGfePTB5vtVQU-dBP2-HrY7QdSbLUNysuh2d-271UozfvH9P4r7wtEEFIIl8J-v1Cke2YZxF3qWqwuO_UhBywqV0iASV-d1fEceKBbHzXuGGcbuHxa9K_gV4HqNhiqOc2W-bJ2Kx4bMgerhzOE4J4ZkKEUuh-W3SSmKxIdzzvTAVCO777QdoRQRa1kVz-XhQO3t_KYcBTEfYAWyAJWna0-7k_0IpDQNcNG_ulC6VK0rK2Zdap4mxeasP4DuyA_ZH-_0JJdsFBwWaUEvDg60qqNVIVnEfTdDTenRjMMFCnXV8V1MPODnKpODVB648terbMOXu5t3_OTJvaHEI7wxtO1dWXtBW0ksHEytfPFkUJVvSJOxMTg2MZMmZhEDYpW6Sg9djqACu5HAlt26UTzZqmdVC74wPLKgmiaezq5EkbB4="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/source.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_ymjhEvEzLR32bCmpdnAVgwsg", "id": "fc_0be63b89bf4dc92a006ab36cbda66487d2b5060e5c92d6d6d1", "index": 1}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_J0P3mDBwugsB5VQBS6x7sN9t", "id": "fc_0be63b89bf4dc92a006ab36cbda67c87d2a2812f7792d543b7", "index": 2}]
-{"name": "read_file", "args": {"file_path": "/source.txt", "offset": 0, "limit": 100}, "id": "call_ymjhEvEzLR32bCmpdnAVgwsg", "type": "tool_call"}
-{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_J0P3mDBwugsB5VQBS6x7sN9t", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0ef6622055025d64006ab487522cc887d2a068e714119e583e", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdSiu9Pe66-TN-54Ojc00tlKW7ldQjBxSarV0XW_uzKArv0gp4rXLcYQV2UXJfzh_5hOhzGQPxu6cDc06OEmelXvu8PRCsS8A16kDgvoAWYcaQTFN7iebe_hYVs5Fe5ONo5-bGZ1z-GQOJ8ssJ4TlSKtEysNZspmUvswqj6oq1O_rV5iWEbjLS2du4niINlQcdypd6lvwrtMfULfp-DCLU247p8FpOXPCCmY-bZTq8quLUmL88dRtsL5EE8wpdNYYWzpAMlR2pTylvUDs1S167ODe83xwGowuTlFygQlh0vcMEThYUfZRNeEsAjopd1bBo0Efepuig-JfW2EF2Rz34Tl5VnEuJ-yCMRGROAydcK8tgRnJ7YvkPPQeONLOY0_7F5k0AMVXc9l_cuWHiDCjc3_HqwXP-AQMfPT8y5G47DTRUFLCkVDrKlBmMxr3QmNAfBJ1_80IeJjPPifFn02PGxW8sOmGx0OrNLa97rL5qAV7OZ5FCqTjrpZO-KnFf55CQJ_k1mSus05fBgAD3SBjWrq178CUdM_qo2QNsCciZlF55D6M1TYLJNCEID1uJIwlAfLgrGex6ON-mtWj2h-hqINoCgDzQiyNy3N_sqguRqiRTQ8qXX6Mg8j3be8V69yRgzPDDMwsvqtc0JtI5ku511gRMTi8LmYh_w4sUa1Cnbk0_e1Ir1EW9YVIMFweknsmIpB8ghKY2MJBOkwP3vkhOyU3LdN0QgwB4B8EEvBY4sJL9MlLP57zZT7wMvKlm6ieY7VEH3DWZeTF_T67ARB6zDhE9QZpQm5ojP4wIAcE-m6b0O9bW-NtgDkWp9ZQiDmzeqHXoM1AwPHxos60camTQ2ByhTaKkJ0WshyhWs4dtmDmF3sfJhylKeeoMAMQXfv8jef7SVsQ0m5a6o7T82xoV6InlvithvuvR3MgntGbbE2mLjIqWLX7ltUTpJhkqOm-qM6nAQC_qSxOh81W1__M1ahOS9uXdVLB0C4mhT0SEJOQa1ooeP376lByjhtxt8AFII5UxJxy9peEhLi2Q9FhpJKlBdI0e1fTFGeDGtf7B7a_l8KQtdm4WC20NZALDTdzzDGGxHOxqaUd-O4cAcRwRGR0ExWMh6R4V4PnHWpQdSTOqI6VX34fPNnfIyOPDEwa9mBtVU8VhwwyoRGqfabBwvjRjXjU8_G084GNGegV8oZsnmp9CMBEoasiE0lXvj8TjghUbwqm3wuVhj93xbJkYbo0MIBLvJiL8c1tGWkyUW_Bz9e-OYCB6YYqTXuKiEmj2OJANSssMAHYWymqvuVR0tWv3K-xAH8otIe7TkS8RNDco="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/source.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_Ow3bq6MHlF2P40MSMtI2VE0e", "id": "fc_0ef6622055025d64006ab48752fe4c87d287984c43688f9535", "index": 1}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_dKniOaQCqSJIDX3yR3HUJuDR", "id": "fc_0ef6622055025d64006ab48752fe5c87d2b01a99bfd18ad1da", "index": 2}]
+{"name": "read_file", "args": {"file_path": "/source.txt", "offset": 0, "limit": 100}, "id": "call_Ow3bq6MHlF2P40MSMtI2VE0e", "type": "tool_call"}
+{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_dKniOaQCqSJIDX3yR3HUJuDR", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -371,7 +371,7 @@
     <t>Tool · read_file</t>
   </si>
   <si>
-    <t>01a0cce0-c65d-7f22-a15a-af95c767fec7</t>
+    <t>01a0d130-9cc0-7481-b17a-6d2dd428746a</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -388,145 +388,13 @@
 We prepare clear, practical reports.</t>
   </si>
   <si>
-    <t>01a0cce0-c65d-7f22-a15a-afa233874ea3</t>
+    <t>01a0d130-9cc1-75f2-9185-7d1216fd2f10</t>
   </si>
   <si>
     <t>{'file_path': '/target.txt', 'offset': 0, 'limit': 100}</t>
   </si>
   <si>
-    <t>@@ lines 1-11 of 11 @@
-Project summary
-We prepare clear, practical reports.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>01a0cce0-c663-7853-b277-58aa59dc1391</t>
-  </si>
-  <si>
-    <t>Conversation history · cache read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Tool result</t>
-  </si>
-  <si>
-    <t>@@ lines 1-2 of 2 @@
-Project summary
-We prepare clear, practical reports.
-@@ lines 1-11 of 11 @@
-Project summary
-We prepare clear, practical reports.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0be63b89bf4dc92a006ab36cbf2ce887d2a2d601fa43cd44fb", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2zEUa9kR18wRU5tKGaIOa8m_QT6fADG0bwGziTXXbMC33Hch_pup4QXlAnN29_eZ41zESludwXHUfdlVbVC615AF0GDtm2uXBZLSSd62NCqZSXia5r1GVZsJlw4PrxC0f6R800g10CNoyfVdp1pjf06gJLSNFej0wiVWe2vPWUpScGAJs4g8nb3-Uu5AqF_mTKyB2VLDvuaftJh_UNGTUQcHjZNCRXWB63cyb2lt6PBkcSgInjHDlrO5AdCOLlPghIou0qqaGpQ_zuQhY6TRwmctjGqAkXGQjM8BK09oeTBiCumNcmjKJ_i4WVI9BeFL4zwl-iBgJUMh49M_HIilL_PnQGRM0YgLXhbYAlkbTkRjIfrZC_XYy98k4CnYkC10v2jgpozAMS6lh2T46XDLyooe1CvsMSR2A7EPNzBIJFkM_dV4ay7X7CnvUmA04A2zJAAOzvLtpbN-ufwHbdcbjEj7IjkTq2jbhWLQh3Fba4KPpGV8s8GjXHgci-eTipVAsRcUzldQ3le6o6BSJbeqKfmMd7OEAEY_516FK8c1proyAcYqEvKvgRxcRsWu1CalUVCMpXdWjYEiZgFFmb1cVhlRm8qpUTUDTuRlj8kiULK5VPD5mPSF4SL-aWxfjp8PNOWBLAc4bvBZzyU15H9UjKHkQ0xGzJGOnf9uNMi37ukJY8Dm-lwloLIuRMhDkdn7z09NHCKj4lQe9Yz6DauWWDD0GWOBwU3VFP2N1qtELC5HqaI79aw4DShALT6aMUN58lVwkCdY5Yw42GJfRBcffyMsZWWwod-kJhspQoPdHpgZ1iMz_k3S4l9JLOkHyW1sRrfRJg084q5BEP3qlGjqel8izuSmzwZ-aYO29R2ELaoi-6zSbos4PRuK5zGUHMmLg_8IGJo7swHtMTuUH0cgN3OY9v2-fE5JeR0KTtRHys-qslQZKTzJGYXxxOnWmaFEzziO-yD0y7B1PCc2bf35r5wTIuhmm20Ca7IU0kiDvi2tKN7-2xlCijpdXkr4BXA0usJMy-Ch-Z9Lj7PMJXMk-rNLVJCQ8emD3qG16YgUpXs81xXidfvo2R5Skr5-U2438Bse9khOouEjJFZjpIPqaNzNUZPdMW_Ob0F-PKXx1Yp2HCbQPi4RnwwT0o68VtDuZytdWtO_rmZbx7du7Tz9LeAIrsGxJuTfZY7f0V1Y1D3gSjsbj8VHRKxcPjyDyo601yYlON-wTsIRwuNvPH-hY1S1qEMrvcXe8F_yTkIkVXcYZQvqs4U9HeYTQrdNp_a9LhsW3XZQv0bJfyznOuYp4tGachYlByHbFceVhlLuJZ51nbTeDO4E3agL5TuuQxaKGNwiLD0bflvkQ0BR-c9Dvky3EUobRAxs2cJU_vMbCCTi9eccO5uBDwhBH5pEhlW4mJ9_hOZlKu1Hq1Z1-FNpeRjb3jIR-r_cid5486b4gLDgDKdJF8JVppKivCZjRkt-qR_q3tBiDSJmzdImzglQmmWkIAooRs8_vV7dA_txiXAwvE7cU-ckkVu5G6ZoJq3shpWDtx50kmLf-Wnt3S3PZmYZk9_pTltJe_6wQ6f-FQA0zWJbNQQR_N8g0f41f2T5f81PSC5AVEn0SVpALqhNZvxaRtlXc0lFVZm7kpkvt95NhlQ2D6KsnBP2UUHP-_XgL1WXFImTdIToHILfEt2QL_MXu7K_p5OpGbWbHEHwxF99_JDmqWadUd0LyEisuRbMWwkJZ_JRl7l0HwVvKiknDTA6U-ZwgDQ7P6dOlQKcxZ6BLUQu8xF6KwBO4n5M2iOajnA1i6ajPTYw6_PAKYrZ5a7vTaw21LX7mlxgB_KInABuR0UXAFyhU5RsDWBaxrkbww8rixOSCzWEKKaExyNKxBmRBpW2jhX_oiA84E37B2dLQeJLqVGVewUP9JDTywp4Rk2DKb42_c1An78EcGoJK2FTYQ64cIXryTgTFE0bInni4S5_WKV279Z-rdK_H8IGWFX3BdQvfGyGQjwwv4AKD19XYLdJEgWSzdOefnRNYXmTkCU3rWpowM0ndLM8_bohuwOTtsJiAvqdAYaGI2Uei2IN4gUsdy2kqdaXn2XI9HRyf-wd-IRvF5c8Ktq9LwAdCXmHHurvjECAI3iUgz4XxZ_Il4xdpGS-ILF60i1cth_gS5h4tWS4rtKpF0c4pkC6vM0u-gUeRf7GNYMUXuZJf3MuuXEAHIfRJZ4LV1RqoFYc57dEm-KIo71yQ5Swl1LhKio5ALS1dsUbWAbr-lLjAkhvZPTw8kp1iZStLWOiLmmsltDZY-WjEKZVO-F40slNeM5mD6ukgoZ2azghvsWuKBdXTRc-JudB6Y5EhqpxnqrJkX0JXT2XVsSE1G_KI7HjSt8OPlrcOryizwwj7UTpVr5MkxZIDx_BOIH_hVpK9NH-iw65JcftMz1HUdogaWiei8XjwQFLw9eme9nk5e61NWYkH6xlU1v0Bej5TF9Su6X_Wll8c8qr2G9w8tws1hYQTwud6rxEPNM92EU3XFXQrAo4sT04DLppbicysJxuWMXltsbXJvU5OqmrE2MtouPllc9oq-atIzrh7VbeID2t1YbBjrrTRIfcuDMKH6zsirb1XYkUj4b8D5OOptQdoZd-AfvEnzVGGWD_Yym0xOjdBXE0MkFt6GTvaUwlfqbwTo2Aeh8SUhSEg-TcOVw_QvnntOw6oybvzVFuImVac7tvwkgPc-Qz5OZTYThKJ8ySjsSypM2xPnySaezD58DsLWY6eloY4aGbmAFjBcz8X98sJebmaY7NVvzqbs02g35O_iB0xPaCOZytXzlabES9510ltgjEZVye-RaaELc5-KbftVDz6zPmCEbO2u_BEEXV10uSY1oJX9sIU1QHbwZw31LYL8VF4K8A4VjQthkvA4YeFmMKimsQu_1wlZgtntxm1eKr7A="}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\",\"new_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"replace_all\":false}", "call_id": "call_vHsVsy2o9mAHYkwuQzWden0t", "id": "fc_0be63b89bf4dc92a006ab36cc477f887d2bc267f66d01c1675", "index": 1}]
-{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.", "new_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n", "replace_all": false}, "id": "call_vHsVsy2o9mAHYkwuQzWden0t", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>Tool · edit_file</t>
-  </si>
-  <si>
-    <t>01a0cce0-e58a-74d1-86cc-653d85029ab5</t>
-  </si>
-  <si>
-    <t>{'file_path': '/target.txt', 'old_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.', 'new_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n', 'replace_all': False}</t>
-  </si>
-  <si>
-    <t>Successfully replaced 1 instance(s) of the string in '/target.txt'</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>01a0cce0-e591-7600-87a9-e502f1a6ebc2</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0be63b89bf4dc92a006ab36cc6da6c87d286f8aad93fedeb65", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2zHKTg4fQx-VMPwtLLOp-eUM7GxOcfLqwxVg5QnA32DWcbP2C0QkLEZm73G--WX5pwdGN1a6Edn8Fb7DzGKlU4W4gfC2ASBJ8Ishmkr5j71KaaquofSr0R-VxHhGATy3rb13Gw9zoM01IyQB1fslFz0TQ7yI-aJfGVuDXvCixSpcZfrnopqu5FecI0MNU1Llrvh5NkYkTcxrWYJoHzxFDayjCH8FKIwYOUXjh583kkKhcGm09t_DpXhQbThotYnb7y2bweI8G8A_NJ4XxvSldJybYeXe1NHikP4onvyjNwiymcHoKUBcf_nkAS6nQ9J5SNl1wMwXPoxBnNpdfUq-xUxnPuoyWEtnfqtIYWj9gF3HtKXyTIp2si4wK0ZzhwyprYNXGnblyLp4TRt43LRL9CcwyQC2cNoTSPglzQvIHACFpi9W9mXLVMWhIeRhkbA9rmlaVHX57_DTueY2HkEj1nHG81uWQjaXfI4UeAbym9NvocYH90UM86zeXKqr7Szi9ppWTkTNFKp4zVYeSK_kd125K_FjChSegIYUD6Tq-_-1vCPf58Hem-7lJ76HHZIpoyNUXciThIKGOsKzTpeFIXMbk6KWibaNy1MBB7QhNwFi2gc-OV1I9iXwOd-Xl3jMY4JKBWulXTLZd38C0pyPf2zz51T8LzwI1IC_0BVVZeug1pmly4YVBJfbrIR6CjlUHVoDLqS5J4Xvz6xBlN3vCXEcK4aWbXz6meMdW7UvBVMq5DkSDigUu0i7z65IXuZ8pXv92njkQqys7QFZuuSe3BZ5HE3O5PcvWIbfSumaG1lOo7TofE8RoC_eFiBuqr4SUplNkdKtdNAPv7e4frCfU67qnIFGo80dkhoml8t5EcwoVXpAsJsknV435aqADHl5Zy2LXZgu65dA5mdf_Ozm-75elzoPiv9Xr4u0Cfj5sc0xSzaSNm3HJ49iVqF4qDITMtCa-I979ZHSg_3mWYDtOaPrWCWt8Ke6msa1o3c_g68uCGstMS4W5BwFzAkOb3AXRGceHyiqG-SQxTf_kj1N5SlVE7_5m4Hls5D6QOOcuDzkbqF9KjlcdX3mAe221ll7VxmK8u5fhV8oh9QSmclSOwzOom6qjL4TjLPAxAYvN3ii-h473A48gNr_5RSDjlpuLRjWqz1EQuW1b4B7hY75TkcmU4TqFLf9fP54lqM6OZuatZxpo6iWzITFDgV5ZxX1tHB3AtB3iFcyszeegx5Z7QYEGKanMrt3yYiEq2lnvmv-o6x9t6kphUqa6QGGy-1g1e589RTxzO9W-xAyT4oGGe33hrKtq5vRVTXuGBzWbhBkzA="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_Uh7wTF1aLj2DBW5qc2Gn9of2", "id": "fc_0be63b89bf4dc92a006ab36cc7781887d290a36597813ef5ed", "index": 1}]
-{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_Uh7wTF1aLj2DBW5qc2Gn9of2", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cce0-ecaa-7e70-8bbb-da40a697a8fe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@@ lines 1-14 of 14 @@
-Project summary
-We prepare clear, practical reports.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>01a0cce0-ecaf-7a30-a098-7ddc12630e0d</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0be63b89bf4dc92a006ab36cc8dcb887d2b2bf0dd6103ef5d0", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2zMUtdm2ObzIhhK3EZf8KUrdJC2w9KYfD_xQrJL0WbghAibhIVGPBM3GnZ19bXAPsquUt2507UQeWS022V0ExhbktCwJHdokmWchO5upBdsRp0eM9IKDM2XvDKY_6eNX8dNZjbINsNzrETAsBZxO_lC1U01rWHwv-vWMCCcoUaeY8wrCWNK8TDnfhAkYSSXvc816tYZ8PheQeJFpj4iTdcacrcSL9hbMEauWlIoHd3Vby9FO-ypTr5GpqUUsuvfUnJMzt3WLCz7mhkC4jrvnuUwr4cXvBh3cgTIpS4reRV9xd9kp7OaO0hPBAFAZU5juUKu7gtXogjDzfVA1Wor1y3dhAfyPrm4VE2H0HP4uliCAFpyw3B6ytx9lWTF38NsngaeNsSy3z9UaQjZv1BI9acoyz0QlIhGF9hcSdYAYFkHOJAIZv2DY7cJbC81YnHO4nEiPBiwtpQInhhWn6yy-G58lgex-x96Ul-9XX8Rf_anG4HgFAKCZnZ9sIlGi0vLKG_uEon8Xxy0-WvUgj9NAnnru8NeSZMMmm7fOB0yTKstP-iFIrpUuXd2vG5jookyfvCn6QLNcgx3zpb6SuUarsaTWlCG91IlmYhejZXqta7B5h94qIxvAu4aB_PRiWKuB43fmAGSmmBGUzPo7tKWkESRXNSwrAEAD2uOuqioC171ZW3l3N5h3Y8JZ4ia9RTsGSq0QDAkdKzPQSGf2wbmQ9TDzoZZl2WI2Unsip43YZnFD8DkhUx8EVzFoAU4P4pj6_w419G26kOJNtO1WvwIQ3P95y36D29CcizCz-zabbB4m-eHvHa9FlSUh5c6ck4JAvLjlcDq5ykA0RCAcA6-2nb2Ww111eMUGSETv-nD_9nUWGjE2ZMscfqhrEsBI-cx3DPctofCAXEH4vHB15SMRhWyQsghhCN9rsdlsWs7AtmS-rRv0dvIAIhITqWXS862aOMb9NW1JRKg4ltbRi6yjnTswUnzYIMzg7UA2inrbANHZOXOQ-X4zEUSf1RNM5RsKrwUUjBDPdbP-Zac8o7469wZT87PbgeN6xjKy0Mu5xD62DQOBvblK1f8wfFBFCA_wyvSNadi4mj17K69DP6zO-Ib-WJxmIjrse3iBDZ2WIxMBFqEJuoj653OK-Ows6_JXk2PdySO3vd1x7yz3p74Uf97mQjYD-CFAP6ZHVg_dXlp-gZwjtev96D3IaEH9REpnmeTSoFOeHVgjXronmUidzRr_fVX3ceZU67Y8j98BEsBw0UhdMeZUusBjmVHSLqsqsBwSnHgxfidpn0O4xx1r2ygVcOpqp2QSJNgE5MIc-4Bip-tgXCZEgkZq6T9YTG0uHOcny4_nQ8Aq_kz_kfGSZawfDupAiRyH8XS2mMtazTyOVrsjjEOB6O7nf9P2dBaDQphjO4PFD91M3t_yIvSaicwYGeR4udT_n7klYjiTWU5QmSljz-7TWynQuev1iTN0_UOXThrHtNYiSLNfxkqmobgLlzYH_K6l185yX-_gRauPE89snDmDBnXsSOeh02-2JLWn-NUBtxfNVyKGL5Qz6gNepy6tRNeGTRx3cw5zBA5Y6_Z8eNYuZDQ2D7lrGKiFjyxUooTsLITxHqsXbwHz1GB0ruw1kqUTZXLH5_Zpa5zsTGnhXCOjys-gGxE_OiX75sN9jjaxE9yPqkPwFP9RFM-wjuWeQ9uIDTq_FvbRre85nhNqfKqRbRwYlN2inqvGmzoi3Gu-MrW1aEJY2fqXSjZVIzBrtpKnUp1XlRgU9Jx_4CTcd-8ERQNLGaFU394W87k3k_cO8cmRtLpGxjsybnCCbRkq03WZRJkl0LLAV838woFd9QuOyhgREvFJQfDHJlBtxiXCb0u2Kh9tDKvgafCKy64tB1FtAdxwV-FIr95haY2WyP49fx9m11dwPXO02jRqC-amRJgCGftNcePyzYjoYTEr1no3kx7ZLOE3hALcqdaNh6OxmXaO8JwGtEBu7j4_k10XFWFlITFTGs7WgJBvxwD2GLzjvH635TiJYvgQvC_st5EAjj37d2RouFoBZTWrRgVGPvzstqeCAqvn42_t9Fj2I9uVExH89HJm0D1HKRjm36ov4HolODDpGvy7KbJ3WtwHIpQa_g0-78M8c0fZlrITo5a25n8c4KWWp0La4XYAJlSMVF5CCSVg_IssWGkG8U-DPfeRRxEWbV9xQxtNAkDBCjokHGpGVG4wtOd3BSSTx_OtCFS9nAhXuln_t26DX9f0B__iIsKDcqezb6jhZeB-y1KkFOSL6mDOy4vi-z1208nfe9D74Khr5_KyhYKswu_nLLtKre_qSksZg2YoXGdVmNl4xB6WEOEhZ9V6cSE9S2fVZLm4noOLXHnlk-1_GPEBmZ4np0s5VrphTnoxBGKQQD5c86wbWT6g7-X6_rFZ9AYhkIc0HKqLYRPdY9M"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Next step: request a quote.\\n\\nReviewed by the project team.\\n\",\"new_string\":\"Next step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"replace_all\":false}", "call_id": "call_xmGfNb5cXbcibuRLSEUUxD04", "id": "fc_0be63b89bf4dc92a006ab36cccc4e087d2821a22465e980e87", "index": 1}]
-{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Next step: request a quote.\n\nReviewed by the project team.\n", "new_string": "Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "replace_all": false}, "id": "call_xmGfNb5cXbcibuRLSEUUxD04", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>01a0cce1-0357-7193-a5f9-000e06bf8228</t>
-  </si>
-  <si>
-    <t>{'file_path': '/target.txt', 'old_string': 'Next step: request a quote.\n\nReviewed by the project team.\n', 'new_string': 'Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'replace_all': False}</t>
-  </si>
-  <si>
-    <t>Error: String 'Next step: request a quote.
-Reviewed by the project team.
-' appears 3 times in file. Use replace_all=True to replace all instances, or provide a more specific string with surrounding context.</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>01a0cce1-035b-7d43-8fa7-46141fd220ff</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0be63b89bf4dc92a006ab36ccea80087d2a3ed827cee0d2b27", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2zQTUuKw10VnA2dZ6EEBYCmAeQO01hfOeMSGetZt4szW5jOtJHkNhID2sHs_wrUgWiuAxmSEo745KfGJuH_3Z5Az-Sl_avtXJOEWsc6b-dtpXSr93-hwiW4LquyD7KRLHVj0kiJxXJtYTzWo2SxZIaQzcf-fFIXPi98vJWelKelFHRKlRuSoRZ0zLh-N2KTxlxWM04DxWyJ5NFUuJlnUO4rSYqOyeN33DlJ-jy-v8lDQlm_vvsXRcmv0bU24wMs6hgQ1ezKzMmlWwP5b0BgYc8Hbmct6GTFwXsk1nmFbEqObQjUJ25tl6NXQnGQh7d9tBB3_2KOYFggLWhmtCJmcIZZgatXEhEFL_YWfBjU4-l73nXTy8K2paTypIycqiykqJfrM62RLH8ceorx7ofpGibvic0iLhBI-Fc5z_a2L4kD97TRyeWb-rOtEswTeWu-ukkDf3ybe0vyz8iTufMDag8DkDUO5jbPd5JM2qhQXCQZ-vslfEZort5P1o4LHTjiRY3ogoCrhTwmro-VTaN-xjRbV3MV-GzwdVyQY2wdak5pXt5flg4zOQmMQVk6Eknt2IrckxiMPuhR4DYw97Mz86yIIi5aS-fR9YJEfHFbw77ebzGeN4JoV4KRZLMYX4OevnxvDQCAaKYBxRgQzy7_r4QpnTRJfM6Wp7yL6R3hcejxdtl7uy0zfnrC4RbDVMHWCoFm6q9qN35gLgdCAeY9LIZnDWCCbAaOosfMJ1LAjGTWuG0VuWkKGfTsNXZEyKyqmRolldjv-y51hnb2vRHJ0AKeYklA-uXk_yH4hn6uA7JTbs0hf1Eh4ZB8L3pEcZIBkov7GmDrmplm2NztUsQ9TdIbzhI6WEEH2EgpnKqAz2xtZbjlnV_gE1SzZAW_yq6YlIiSJwkaxKveZiOpxuKqqJV7rRjSBUloh0IcVMKVwOt54prT6NqAdMRBRtUh-5A0UwVpXY-VJxym_x97ATgtlQgqbpSU834Sou1epmFM6u7WbeC6pv8mOvX2uSMpFEaZAYfzrRE2nCxnJgdMf9mJsT0WlNF-9QXCImgZkPrujUQD3UXahEjoXd5B3XIb70_uQaIteS74Fn_uqxgq7NoGntSkiihDCbx9-Bj3gnWuca6E2GXy1rxAZOQsCuR5yDt845e3RdMSfB-e6sEtmT0xRTUQUwL72zYuP1XYMAVJLkVxa8WlPk3CYQ-yuois-m_WwFzp0lpUlfSbfpJDjP4HGVUlI2BCJe4HItCWVycVRK0DpR_P1hL6DqWKDIdjygZaUxd7WMW_UfV7T0D-X-PnQ54bcDG22XRn76nL-NnKWigeI8YWSxikFpARtLJ8xDuF_r1mmex73B5Tf6waeaIrjIkhBnPbjY7xWJloBqnUvWJ3qMm83K7ir_Kl-lvzWmLnSurGs_Oy249uOLVaaVNxlI_dqYMEW8vfj21TEMZLAYyqXtMOPnmUZGCIDbbb3fkVcCoR2a39PpQtJwRmMNrfpPuD2KbgHE9_T5emfPwM04_aJdpsHGc-mAFjlAVpmypK10_H38OXb68NF85OaCT71-c6wglqyo04afH1cm50wTFXZFCdiYp22GpN79yfwEDeDQEEN-DlxLiW5fbDZ3FzL8Uvv0N1TD9mM9u9xwLA_1pKriDsDHlzKS3C04e7NKNGZyIDvzDBT0nT0o2J8eOWtxogacCZE338HZx1ZWz45PWkuhOVChI6X7U7A9Ra-6MmSfIbRHksI-mIHUhlBJJgipe3DubpiE8aL2jiN9d3indqpCQLFLiivgUhZhQIeUMdGneGxNU0CAM3doTnnThAI5P6bX4Bar-xD6iSVNFY79fpjUbX8yDVZBtBo1M1jtlx85MB"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"new_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"replace_all\":false}", "call_id": "call_Y6Wa99qdOi8UzJbYBOnvPG3c", "id": "fc_0be63b89bf4dc92a006ab36cd07f8087d2b28e7018839137a9", "index": 1}]
-{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n", "new_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "replace_all": false}, "id": "call_Y6Wa99qdOi8UzJbYBOnvPG3c", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cce1-14c8-7592-bebd-2358da5aa44e</t>
-  </si>
-  <si>
-    <t>{'file_path': '/target.txt', 'old_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n', 'new_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'replace_all': False}</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>01a0cce1-14cd-7082-99be-5e5b03bda314</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0be63b89bf4dc92a006ab36cd3142087d28a43c44455603cad", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2zTPxmham_cuR4Gc1XV7ptAqvLLmmk3vSPepJfPd2SxnkfS7sBlVQ9EKaZFPaxEoUoEo3XGV3VTicCn6EFZzvIxl5f9kKKiN28FNfCh1AgkYA-38z4eqfxMQHlEqD-9Z9oCrdtD9wnnccpun9GT4vKcuSxZzuzpXWLV8jVuEc-2xQnwmnlDnJOKi1UUz7vJd6yzOXJxaZEdv3jPsTh_8tL_6Fs6iOdIHA3k6RCOpXnBuZa-oawlKKT28WSDMdJP44kUaWo8svfL0lmKWHBt5xEKVJOPZrzCp9BGKEh9uHA_8ATNKf0xnd3gZG_fyemu1knJyWPwU1yGdOY0z8l9WYKHYpaEv3UnRWGJ7qgMOfzy6reanBFfi2qwTt2fN3Igs6cZOA3lTTK8t8o1tQvcCkKtfRbFqq5LdhnVPeaYOyM90ZQ3sqMz2Lhnfr1zn5H9ro6D63FGnrP7aHSPNCveMtaN8h5yGB6OtrlTn8cwHykD2l-WkTJ_uRnWVGjJtz5OSWgBNR1eJzF7iGN1nzhKGRD3HzGrC_vy9Gs03y6bduiDUrtM1aap5WkfzKcJT-gg3bzq90aAVk1DcZQldKwZPd-_lUciz9tS_3LF4HUS7NZ-GIirUAazEK-QeNh-pVdtf4R5ryj7tIveDVIE9wgf9kZm2wSaUuhJvzs61XU-HMR7zSCSZJbnp9QK5Z7KvDNVp_E2-djKeZJP56PzsHMMkwu5fcI1DPONPRMmdk3c6HwZ2RvdO3O-zqekUvCdgdijeUYDI460WGX3minKDvf8sFPYTNBkxuKif6-pDanwLvUbwW_-XfJAaVTuD-ObhvMR9POIDKFp2PCN_k3UQSF6bAAz08eWS2azeGFqlTBKemeWkRvTa81rSA7Oyvywq1boz5dh95mtVEUgbm2h40A21ItQywAcHblBctgbn62XKbj2Yax6VZbSqnODhz2u3c5LeevT_9ECeJogIpVSDGjUq8XYnXEsROAlmaP8FCIOK9z-qtusGqvwBaQ3PoLRps7qSJx7AR-OZTWz_HOguSYdg2ri8IcRhw89UnubF6kmv72G5c8FjEF83er3yZdqdYjY_QnI-xlwqVVPj5eX0pU_EJYs1GdrDkTPu6fFPRGoIVedOhuCvXZhScoeE80AbKWjhtV6oIBBriYOj1qOkLy3FZewHpjKwJmheyXcAmurQHmjQuo="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_pXwFpExgHp1ByUyFdXXe1MBe", "id": "fc_0be63b89bf4dc92a006ab36cd3518087d2a6c907e70bbb2395", "index": 1}]
-{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_pXwFpExgHp1ByUyFdXXe1MBe", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cce1-1adc-71f1-98d8-be3a39d72496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@@ lines 1-16 of 16 @@
+    <t xml:space="preserve">@@ lines 1-20 of 20 @@
 Project summary
 We prepare clear, practical reports.
 Reviewed by the project team.
@@ -537,16 +405,213 @@
 Next step: request a quote.
 Reviewed by the project team.
 Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
 </t>
   </si>
   <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>01a0d130-9cc5-7de1-b35f-ae2cdd996869</t>
+  </si>
+  <si>
+    <t>Conversation history · cache read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Tool result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@@ lines 1-2 of 2 @@
+Project summary
+We prepare clear, practical reports.
+@@ lines 1-20 of 20 @@
+Project summary
+We prepare clear, practical reports.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0ef6622055025d64006ab48753d6e887d2a97f2ae2b5f0ffcd", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdYj2rPwgdZCcse2UsVVakgJEdaeNtbMXz3DBlBfIa8b5e1JUU_uHfwBl-ChTEtXHeuaoktyoI_yhgvj9uu283tqVz6D6KC_Bl40CRzKDr3k4COQP43e1HtTOuZYJHO7i6YBx3IFvyRPUiiuaz9Tajp8CrRSY3jz4yMVT_bemd9ZPVKhVyRZK731JJSXF1GYpzpmZEXBZTzIGpEXbEjHKaIeBS-Jc8Ccx6JIhRuPIf-KghWfbrCqeD0JeYx-9vk9pnfbujxEt1NM-OZXK_jGOAA-EZIlOQGYlaFdPpciXic1a_UObo3zvhg04O33WTrrL7MaaC_5e3c6y00WztdsPBcbxCbuh89KQP2d89Czhi0nvZIkh-SVORG7xb5XZBWkb7nrcR8G_x-EGipocLDJW_9nxpf5vrXG4JFIpf1JrvjWU4DW7V9QJ_r3r16H8zEz92SauXo7HyBJMq4nHOrRtnig3MC66l14w3MKayISbKkuI0qMVaxRI0kEajuUHu14NNuw0L1cPkjSEZ0Zf7hCf7xxspHtBNQ1fGrzAWjs00ulghp0ZgXAGnMDEPTWLz2dvOgmXE4VZ1NGjIYuoyiHDRc-J5_1pCLVaJsJMmWhZlswUaE71FEPfs5QSeT-m6ri7gY7UEFx2_lOx2Oc_2H0iE8cEPZTff6E44PTROV7yySIHCE8BIz3hYaqY3VGUXNSm5GdHaxz2qdXpqeDQw9mVL2T-cGTo3VElKR1vOpXfDaU1pL7Z50ulMxla87Bf9dpPG_ncIQEN3MH6pJpzCN4tvZz7sUEG2oRtSHMEUL49kAFoLTRZycevo3wOpz38KrRWeHw9ySaoWYAjozS1uh_KUFSS9AcOvkWoKmEeMABuvfM5T8v42IdcOytg5XDxRnfyiR8ULH99dfT5UxKLUAuxSe5gTkvttJ1IW2NyTbxXX6xbBFOV9tyyqEJw624_2qMuzx5rh8ZHhCF_HhR5eDkq48BSq-kTOj7puWWapOmAMeaZpfbtPzkYPolnBl-uLq7VIs44EKmmDp2ScLow5n-ckE7HYG5DtwNYkdaE5WPj-WBcTaudpgm0KxGADXuG-GqREXJSRohHsXVjKn6pOsjvyAlI7JAr7i5NIN3sIZEMbocfNB78Qac5QPKrF5wCVMldC_uiqtfP4CPvmJgKUN1WqXipek1uv9oYuxzxrjIkPNshEdbGTBhbEnr1cxv53Fvxx8tvEXyBC_1mVzSzcxW6H7s0BM9qqefJKEuqUza4Gmh01UgGdjlLiDfmi52cYvAJ25QYKLeXX8lS61WeTClHnAvB_BWe9AJVcjkQJyao0lqkNuK5W0N5Lpas8QwSoOMLj0FD3CucKDaf7JbLuX-IlDnEjKWzgmQ52fmxLaWs7oB_zALoiEk4YJHr-S-xmSB3vRe0F_NhOSTf4x3kls6NXgW6s0n1J7r3D3AMHyzunGD9wCwJWN4VMs5yKDZlKyI-SRBnwfcLLrD56TwrNqnVLg1clAEqHPywF_tvgEpp5FqxfRkrDaA7YOQGQG5iYt0zraym6mBt0S6aC8r21dYrRpFjUWyqf8665YTnUV7Hb0vLu58VBk2j8iNNo_61zkHjAqkpl0Grv1nuRkd1RAhsflW2Pk6oIKIOZKDdufc7VJJpFNQysdx76bzZGIUoag5qC88BeXtLcnwPWuN--gOu1P5SlK92_mnq3bqjD2trncjW0Di_QRsqBbJqc54RRewfkdu-Wcz0GkSncPhuUou26gFKwXI_1UeXHgyllnsa3zSXSBUirzBKHOlqryyPQcYDucIUKEJrmFCdavEcdUK9NMVd5rV172f5jsnzZaW8Fge8lS0oqp79TrSXYS4BhSMwaWbqi3o_6CmEAQEqEbcekd3KfqwxVGUKLuBgw-kN954U5RVNdnyuCnWkDo6s-KsBg5Dgd-A0GuhdZuRgx1exVmNGVo-brojO7Mh6HGqLMejyH4ptQOFDvl8Dwsyo3IE7tkCgXxcWlJdwKv9r_ZeugJCKYpoIkg_udPR7qZ68i8tkGDlTEGAZ-840XQQjNzfNiMBs4DH4mESGZetMpoKxfkses24SPo6ZrhU9kU2cuDGFUYFd9UZ-9Yukpl3uhjCQGDaiVKMPXtrCx3q9NgZ1EgAyaQfsWPf3JMV7oSEo2razQZGscYcqioY3pgYh499l2i5TZz3WnHht_6KqZUvs8vxtH0PN-0jPiRlQmgCMMzVCwWXX-diGTshoZs9QEjemDAkwftHIFbMarLxd0IF8xVnXkDRZCToG-bgtOshbfBWhzwqlfBbV2NEX_RxS9uwTEkB_itlvaAHXYWbCesKQltWPeUx_h6IoKm5jb5zpEGtyifMo_1Q17xZfgdLME-SzJBz8Tt19y1xvFNj_ZPVhxUL5nBf8XhmcPua9BbMLasHiIpe17E5h8SsUVWA8xtvQDp0boG6XbmlrIoEOlEC5b6CR-zHNR8EMhuzKlYSQWAPbL3APkbepCFEfFTCWrTcWOOAgyGFpEbergWQoQuzpUVGbcU-yAq3E8xKNQkd1Vc-DmbYN5eaUGgZfHJ4SIeFAP83_AIk_u04AAClrxEw2mMqad2VwyhrLkRxt2UPW_vAeSSHnfqVhDhtvEaUzeQlpk-WE_Jt67-1juyG6DL5Tv2J8dnaIFU5MgOqQqtOL_UWF52OVkeioFBKR4bjcSTU58lVEyW5N-jXcYiX3gsx80sqdduZDPPbBLLOyK7VIkcIprt5eJZ8Hg9UMxzQ81H-j28gGS45ZmDQXw-aHSyHZ1hOPWhlLx0DLscDo1TAmolLm9WHXzcMuSP5lBlB2Q2nx8ZMfYTgJa2Axncete0VP3RDEv-Ff66_4-f9eTZEz3SHV_4iOwKAvjWnaLoJquc8rNe6Mv2YazYmdbr7f7cHVqbLVSi9FbmeSdTh4TfNOcTfYD6tGpfL68IY-MSErBUhzJwLAhXhOjcjaGn9eg60Nau-HapJUCVz42ckcfJ9KPci6czsyPREBE5MCJqzGPslq61O20N7MytzNyOR6CIUKIGXrupgsf_9XgW6qFbKwjtokVzxwv4I0V40627E05zfEKcAlqQNGW9QJR7nv0xYhdJ0YJUo-qTtHk4SJXCFEaPtRs_qmC-Bjj2pLqOyldMacDfRzqPVu_73iCzYDz9C19y83yfY4RdN4_YNtdo4UYM8nuJnsFXddCoCA0Kw3YKqxt4Vv43du0oJHKenD3QPbTG94Ezx6ara7dR1l_6kQOEZ7vfkhC2P18w81_DYolFDwZdN2vfIk6hXdtbme3vWy0S2H25GHcAmJTlqLlmWv07zwv8MUV7KL-jIwo-tPef6aDMth4MYAfbYk2iVspSr1RwbTOANkMQ_tYa_EOW4rWXELelMr-QdAFWlK6hqqSCGxHaOTN3v4-x0bhVKRXUQvBVAYJ43eLVc5t-pO3Y_715o-dhZx2SQiL6GXyv1xbwJ8owOJmyIIMuSqYxobb3_thvxyMGw87BrGMTLv3qRkqxeE2rjKgJZx9VHnIkY_FvexZu"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"new_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"replace_all\":false}", "call_id": "call_Q0PnRv6pYD6wN73QtgSrkp1Q", "id": "fc_0ef6622055025d64006ab48758387c87d2bc621897a243318d", "index": 1}]
+{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Reviewed by the project team.\n\nNext step: request a quote.\n", "new_string": "Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n", "replace_all": false}, "id": "call_Q0PnRv6pYD6wN73QtgSrkp1Q", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>Tool · edit_file</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>01a0d130-b2ba-7b51-a5f3-f41a7e28c72c</t>
+  </si>
+  <si>
+    <t>{'file_path': '/target.txt', 'old_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n', 'new_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n', 'replace_all': False}</t>
+  </si>
+  <si>
+    <t>Error: String 'Reviewed by the project team.
+Next step: request a quote.
+' appears 2 times in file. Use replace_all=True to replace all instances, or provide a more specific string with surrounding context.</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>01a0d130-b2bd-7a82-883f-0c5e999c77e1</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0ef6622055025d64006ab48759c09487d298655cb503a07a08", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdcthrju7877DsObjwQyCCSdjIRUHSWNT5hAz5ybhTfFPGQ8Q3lKX-MoCQKa4rh157fYayAhD1pVM5cPsbv4iZy21zt-PTqbGjF0Yp8uzWpV3hsX-sVmoMNkZgXhmXygx4jP6liTcRdommUM4kqS_MbNKmVbrh1Gw6OtBlKf14e-Ni7g9PSYm5P1oxEgHAMOSAOwYlCXosuWjycLRPY238Bz5NKxETjcRnp7vo8HxviDbt1x9ujLJQYHDKhlsSCz-xRTNb_W00QdRW6f61SE7HS1G5eBeNkDHIFb5YLlSlDkvLUyO_LR9LqSL1o_fIytHnKV_L0anBIByeyE_AnXArVi8Puh_bF3zwwrYYM7IX4B6v9D2L2wXBKq_2OxmqlsFsj8rlfKsFY8R_EfLEVaMBiwEgp1tT8-Vupy_ZvWRKRNc0xeNR98S2Pe0kMCKjh1fOLC7DDcs6CK5lK5TCLyoCg6K3FhMmAJBTnwbIhJYblH-h3e2MWgvrctYfSPtW_LzccfBl8m01jsSTMVz0AlDQ7C0uNCRiHTPDw5G571fa61OzBkL_T0pWVm77T-vhhGP9AnVmK666VKdKC7Z3DeqEtdRkDuOOdG1Z5Geqsu0lc85old57pCVjkkYL6yhMCMUWOWi4_8kCiOrWOWBWVkk7YPyQjE3gYXUu16xbSBiswK3OF-yeWufx1rihDumHgKn7bb_zMC_QzmpvjOHZHc_cG6vw24SeoY8Kz-AKub-0nheFZMgxrFZU6rdsBwbNXX7pOsyOznFwTkZcZ3V7WSnrQwmnA846QscKa-u6ZTgyKsVNOuBmnaoZUUMRJufnZFoSpNjjFSCEoLRCt4j4jJKSnpGsvg_C_Isubyit2D1_nnA_uEdR6gHyYN0taFq05e6KGlDzBKj76tn9HD84Cd3BuHbK2aSff0fC5cRE-t9nFyN2DTWZyphFaqnBIFxpTlFb8KB0NE4j-_v7-0rNFy1YoJKc9lDkz1oKWyk4JOeh2AkLBzQI-qN-6b0q8sI9gboEIsRdMbs3zdI8eRWCY2eqrndkDXh8CWVdk9NK6jPsGde4WEJimPuE5bxbYzpPUuQls65LdEy5a0bGxfkKye0_nb1l3TShMuD0ZKrDP8Uves4HUcy_9n_hpDfX9fl7DACr7mtUelrw2mQKlQ86j6KuYGEzangou4ihcbjggD1qcCz-RhOAJcxSj3gz9KtMJsiyJ86IvIQ0Ea3ynJY6IlPLZj09wpiIM-o3mzj9NpEH0Ch7ZH1Xci72UfGu6ySv5COk_2HDIA6PsSJR7Rxg7Ql22H1Q281b6hSj_clE6_JM2k3dpAtT7Zg_XiCzLE2aMc8HFPMRLlWglh3IMF2zVhiaGW_WxVG5IBwt7yZHg0jV-8zWdLX4jOPog_-pDYce41S1IknRGLvsRKr6ztKLeLHFNYss_x4qfx2bry8XMuqK3LxUlGn21-xXPTRPXRGuSUPQuTv_ed4r0hbJIcfPzOcX1oQk8jc6rNfb-1JcCrTAxmd0L-dEPvEVmiCMoC0eN_iSG667Q5ez7_PkQpGVApll70oQQ5HVcvCmTGsn_FWNjiZNncqTK_Dqk03qh-QJyzbdn91JD9e9_z5jKuA5CsfWS1fWuUKy419eoa5V1nEzcKT2jGnp22NzemrKy71GScd1fPp8Sbc41EOMcJdHMz9gf2LJKQpzjwGedTkYMDh1wqdrly-MBLN6AKDNdhclWqg6HCZ21vDERH100exP5n-D386sBuHDO9fniQ-Hv0iE630F7uqnpUCq8FefOXRBJvYv4N8nB1AOrNCbe2-ndXY3ZcoIC2TJmWy_ezT3CUJoRTN-PErOURKWxnfln8NA4grFJu6vNt52TIt0F1OHWzvzmD7jWy9_d29eIVnqVUq0-pWcMe0UOFLClF1DQbAN7P5ayCfMPWF1ZIj0qxsjxw-xGD4pN6K_3jKTTSP1WXPjiWF46TJ_4A3_c3550-MqzSf13K2ixQpXzI9j_0iUWkVWxksAvqvCYQwMLMke0lvaGRxLlpS2gDbM9t_mHXLAYIugLM_UuyYYW-tH2xur-1Rw57fqN-J3-S9Px6Rf1rRneAgk-Vg5AMpoSBB46iDpfsM1aGyd1rwiD6qRYKlZXSXZjNPLC45tXUVypdw0VTYtDdW_vkzyj3JkWvAyOpLHj4am0vTEOmAHm8EdNCLKFCj2E8fiD_kLf3GE60IvhC9-yc1-sDte6e252DIPeLHbGImjqXkiWAbVfP9gSKOZSHRQihjclLiVkFDdDj6_ZmaErmN2J6aK64p7e3e-Q3Xc375D0qyLaK3mPeLf1TYrZ5kNwtQOVgzt75DoxQapcX_IwYl6Oyle0TcNVhLkG_gpamkduh2dIJ0lJQ7FR_h3dpAXLx9X3f9OBYLm40Dq6FwsW5LbUWfV1IEsFbcqXxHB4kunfMhady4uonSMtvopdjsBZqemYVQGbYSiZSmAxvhedxJcpm0zyNFve86qAaPjEAxhb"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"new_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"replace_all\":false}", "call_id": "call_Y2rxWvjT3QhCfswpZawwdILs", "id": "fc_0ef6622055025d64006ab4875c682487d2816703e11f52f9ab", "index": 1}]
+{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "new_string": "Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n", "replace_all": false}, "id": "call_Y2rxWvjT3QhCfswpZawwdILs", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d130-c984-7c71-8b2d-b849999f5622</t>
+  </si>
+  <si>
+    <t>{'file_path': '/target.txt', 'old_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'new_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n', 'replace_all': False}</t>
+  </si>
+  <si>
+    <t>Successfully replaced 1 instance(s) of the string in '/target.txt'</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>01a0d130-c98a-7450-9c4d-6b109245e6c7</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0ef6622055025d64006ab4875faa2887d29700576a7db43439", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdfBiRbciJx-bmph-twdFMewWo2Je1ERvpswm9acKGCOgbkHe8A82hEC6WFbAwXNgbms2VUOXNEpZG0B4exP-QFKYKLti14XiqStp9ibebBwIMkPdWXFT3D9dU26z4_H2v7Zow855q5hGXNzd0yt7XDuSD0CZaaTBAxNX1onIkwpoJuhSSOjVTbBcrLkouP4Po54YTFd46YNw1GoE7Acltx3EcD_69lMy1DPgz1-OgRj9DwXQxecn3612dzo35JY5NpCIkcAFMDNIXfvnpt181GloFxOSxrkn4P_OXUYRV4UJ_fuM5JdI0S9mJA03VNplz9C2zNHOp_DNQsV-5nfMkDSFtsN_gXGXOLZJomqjjq5ZYtCR-8wX_nXfzssGNh5D9XHcEKll0CUVejiwmWwNA7y5iyAyITYezS5i7YWVxAsev20L0w44gk0dSsnw5FkKzP652Q0prSwvLpuodbq14GlkxDJzVzJvA7YdawF-TnEvp3_IeE2teDTFDV58Jgvf9jI5wjz2Y5AnAmdex4v-aMnbNeiIjnl3LDVxNWAF31unB-83fItWUmdhYVTARX6RKM4uiwFQcJiSYuM3t_M9uNjM3k4QBjdDFAlox8AoDXtpSKlTEshJn3_RkZsit64eUByBxGF9FFAPkqiJAaCaQa6eNTbXypJMGKEqnrycZCm2R8zuZL8ng26-PJNCh931dgfWyN60NLLoAUl4RrhvLxfnYBI6G1I35_vh3NV45wa0xD2bFqzFrHTgYd826UMwKoh2KlwNAn50lkw3JTIJ56-QIbsnF6Th6HQZ9wACcAEyl2nunLJXE-rYaBZp_Ea6A5Kp9jTvUFbycegi0OcpXOnK4yIhmnb_guhw41g0jbbFow3737u-xls7ZH-nQtglT7xr94IbY7O6XdePEuYpkwZGTILrmhliJLiFSFzjp-YOQw23-ywt2Hb8j9QimtTZ1mPh61cj6Z7NeG7cYNXmOZxItEjeiRdSt4kNVR_eN3HM6JQSm9XJh2BUV8ASvHQGEfREUsHFBEc7KS1wa71wUhJCsEOddH9CBYC2m6EQUjoxt0FXULcG_3oOUhtWYQovldWddjAzRxLt36hh1AzzSlioPJu6EqyBUKhH5SeQBOyO1x84w9Y1pKaC0udwV964-6ZQIWo4Lh6kol-YsJ3BZQD7_APzeXkei1uihjl4UE3jo="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_TI1U6EUBXm0mObAVRCrVP3TR", "id": "fc_0ef6622055025d64006ab4875fd73087d285137c9b5ef0655f", "index": 1}]
+{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_TI1U6EUBXm0mObAVRCrVP3TR", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d130-cf46-7133-8f0b-a88c91d0d644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@@ lines 1-22 of 22 @@
+Project summary
+We prepare clear, practical reports.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>01a0d130-cf4b-7750-8db1-e7b28921cd5f</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0ef6622055025d64006ab48760f99887d2addf2d78363917ca", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdmCrtVUrf8dvapWHYcoBH1t59i9cMrkQiQBhh6B25AqQE2bH0VIPh0p8DrBnDnX6MEZ8d-tSGToMAAV_L_imFtRglasBTuMcr48FrYnolI5SvhG6iZU2rFhF5xnbvd8hX47386-x71uzd3wImL17uSyoLOltlM0uTnfuGCm_5_fj-5Fha090_XNOKf2ygZFtLP0-PbuXuTusBTsim0ks9aPLe814CY1issMXCseIz85dj2rbb7USWXTTuq76sRGhUUejeO555W4OzDwuXFVh7CkkjUoueDN7AZc4jgvpMRmbML-_afuczJ89IGg8mBfycplcyp-OQ9mQL_RA9M0ruT74na9RajNqJuzKlLhotg2gaFYGDp1zNYgaTaUmi9an75YHwoZWTZkhaqZeGDeqcMMPZonyUTOqmZYpLPfEDiXqlAEonhJgzzBU6eFqEUc5KkFOdBysGqOcFef1BQYHXnV-kRb-XsRRBnTUnIYg9OIhFNQJgY1fI7E9VJc3UsMhvJL6MyZ7SkthzQUltC9xSi8B9CnXUM07ZlFTnA0lE4Aj0iN_eCHEJX4oHWlqi8NYmtav-kq9nffZjxnrtn6-s6NwcW9W3j1Wd2z0XmtWMweVxdlpn8hVtquA5sP7fVRi2c5I2h610q-WRQ11UdAstzVNNF7H_IawU8qeoA0ifBxyL-yppccTIeNSVu3gHY7CR7XkYo2GKn3993H67C8wHk8TtdUtqT1EveAqtiHDfxtuD95KI0WNBEf9y2Apq0C1u71Gy4cFBI_MquBGZXDfYPziI4bKnOdIEQa-T0xqeTl3-2pZ83a5PFE7Z2-ujRVz0XsKYVpm8JnUW_vFnYLs-64zr7qkr84ukUs9j9BtuUwm9EeDQohypOfPInw-TcjbnaF1VHS0ZA6aiKKt0kc9vZfkckrhdUE9qs2OqcvnNGtOhskg9yiNuzaGrYB-UHNkmJ_o_UPm5_R-LVvwG6SW1mLQATcv9YsjUEhIJF0yt2yIddQgXBpAFOPgach6_lwOYAhP862V5VeKxykB7qwGJ2GRg_d48g58f1yTub4d0eykGu8FbJUaesyO21_LiskfAwC1-YnfL6LfcUeUg1tC1WEAu4aAEueoPzUfAqowLW5fBeBJsKaspa4jY9qB3tYTv6DC7BGuawXW5yyv2_b5mNca9RNV3ICHifmQdif0lYi_wzPSdSw_LPbf7EnUZeGP81hiFF4ZKIcShda7qFjOxvgFJDOtSljvFpHtgLYdFrtHBwr1v6qNCKyfrRzUFPcmns6LY_gh3U8OP9bLdidSskWiXpgWE5pXGlKQ0R6QCb7e3Dbe6XzFm_nj_7pgqwUD9LEAIAX-iWaBpecHhv7npCHE3xQo2cb2t6bbz5UYXhfGnzTHBC0URPgNUuJa8K56yAIBJtCLju9exINvs545JfoVLnHeixkAE9HcMBMnIvvEapnSOYt49TlyFPNNXGSR3J6DSCUch02J2CU4BdyBIwrp_f65ScuQSNwaQ-fzUlP3gv189QPY9VtNdef_LWkqArODw1rp092_ePeIqmBxVNS07H4kuqt0eRfnmFBSiDGTOmz_shWTK2JIJpnGwgu5toobqZcNmCc7onsi9l23pspxzXnNR6Q2vOp3k8yjMfgHtFzdNcT7eS9vfiIwB_GuZmML0En3hVKiz0302msiyg8-xxJ2E44cW0pLfG7qqSestGp3WLsVUe06riasU1kwwlKCGD3cANfMBfHrrqRIJpdQHKmDkeoYe-ug8I9IkksTAAvuI-8tZsQQoTAvNqa-AZL3pzlefmwhUSSmM4xa161tJHWUK7WfVr5LfTgxib39WdRjqhZHifz4hxbKOZX2PPBWwdV-gXNKkjoL2vR6viC3J4I4nYxRxZEtxath3SqLNEW1Hd6d_wCk_SkJw5ZRSD3tPckEQPw3Mg6cnHrWkglm_W8TOyUqlfQlRuB1xSSzGdMryk2dbGoh2E0Hv5VE55FgqPo1uzUcV3tXxccA95u2MXo0PpMGzvmo4P386miFoT6UH0Vo8izQDO7MvO3dNY0t1h2uQ8uZEbqSCNSzpMPeroO9ATZPcvsGLQwcv-Iwcti5Jk--wpw8iY_Q8VpuZ-DmcA0nKRckEH7iM-vCialH7HoYgW1x0SYuaMyAZyvyTqmo11MvOEs5akuO5c0ie3l5MmwKgcJpQwYM1hX4iY1kSZ1BNYkXkwP5E3j7SgZvw6uRDwMLNXjeo_eRuszcQX7l2bkQejDg3w6bcH5cg75ojbL5EDZF0hQr2k9AGp6wGI-IjVYoYgaasszkEz6v3Aa81Nf8K32yK3dl29zDDss6kRYmvPnU9mTlxr_e0clY9ToM5ai9fC1eEm30-5aviuS3cWpuyCGF526CmxxrYU9hnTbxn6pfP-Ta3RaCoBgSCYlpr-fhbqYCeJyTsJds8v_z4PeCUZpLLJvAF408o_HULntDqrAiATJkhDWQ2cauGTxR_hZ2Dsm12Pxhe0kLy3HBNw8C0U0oU6D8A_dHtIoTP5Cr4yz93SfjXex3XbV2smKtzK6qJGU_2d26oMdxGmpdDyJ2ThPenEiPjekCNiNZQdJpor5JYdZjmZRmDdtujSUg0mivoJR9QA5dIg45891Mf_bNPFoFMHKfwqtnoLsu-WrSGBFJrBLK8L3TmOlJbFDTafc-jIS3gmlZb1u_rwZ17bKBY3vbrLnNJAOWd6AYolEqfk4K0Z94IdNEf4KuQwdxCE0yBlWjyPa6QcdYUgG496pSS9VNKin52B4W-yvc3p3eJxr5qF8-siZ_NMFDZ3J_aFoq3PQXBo6htB6c_wn5Frs9psCCDiNWwsNGyRm4XHVRVwUjm81MhUTQfAas2XgcYCWzKze34IijbG7Qegb2b4CEMyafpHTfP9jUNOs7njl1UaMgfSYksnR6s5gBQT28VL0wCgNIvy6rxCtA28dv8jo-urEdKId_mBFDIaGFEsAsqoq8T-fwDdOlQ4cWqYHPIR_D75Gj0qpd2MhGWJWdspldwS9W0xOhk_1hDnahKGYMpr7VWBZ0OTpCivsuCvzfzMZFqVE4qesOt7CN6LcWIiB6ALa3dTuX2_dE3Wphkrl5ckI-8eLIfggtrtY5nx03VaL16y9jhHD3FbKou6pSzk2axPXCR-IRzifTtwIa4cODdFN3XV0G_uN_XzzEVtHrPwW4z62x6FeVGFrdEIBZGiXZo4AM0AVp3tfAivmb-Vo51K0NyqZnyfniZA2jG7dpU1ypIcASZZ_3jxkPMtwaGXD_mUIsmBacYFXYzKAKz2sa7HnS66RDE-eKngcMx6GUUoNpJum5KNAGqacADy1Fayz0AOEYZ2XxkXEYYsYGR01yeVQzizzjigPsJLI5ZZ2tXlwGW_6JS0FN8WKDbnqtLzZtLTsfpod4eHTx6KYOvo0pYjP--seefBEgRprsckJTle6Wsru8SwQjTcnqJ0-LCurWcsvzmsilFuvVd9cYSmfq9wRRJn6nko9BAVV6eUeWpeJnWwaclEd-tCFHhWZW7RTOmEu-i-9l0Yoxr2FsN-Cj6vCKK_JxIW6M8h8Ls3csJabBtwyDSVxLlFlYX3xHfPjGhq15IMu1HSw7Ze9h2xCgjF8_7ez1B8BaVwbhGXPLPF-cthRacdEVUrdGKJdBU8CSuCi1Kc24a-lxXSQfmYvKZzIsoFNftnU2a_CU_FX9aoSNGLQnTv2iGrzEG4"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Next step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"new_string\":\"Next step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"replace_all\":false}", "call_id": "call_Pw1xlCeoafd8hbXCttLkeeVP", "id": "fc_0ef6622055025d64006ab487667ec087d295acd3a047ea9e18", "index": 1}]
+{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n", "new_string": "Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "replace_all": false}, "id": "call_Pw1xlCeoafd8hbXCttLkeeVP", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d130-eb89-7003-b91c-df3bac35a355</t>
+  </si>
+  <si>
+    <t>{'file_path': '/target.txt', 'old_string': 'Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n', 'new_string': 'Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'replace_all': False}</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>01a0d130-eb8e-7e80-becc-c426dde82204</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0ef6622055025d64006ab4876870a487d2a03dad331d688a86", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdoJQaCEpUZdzT4Q9srZTjGAjeLoDcDohCar8kKAtbCqA5L78MX0eR1EQHwUFJjQ-nTZGGWyPJAGdYDiEJGUbDwZscMq93dF1iHzJPemsHvAH8Psuymcy4SRPeBuIb4eTLpa9jJBtyGDnxLUyHQVOywNi1WY3dbPtHFlItEiFoqdlqTjKWQOiF7tObEhTj3ZEGnKxf1dG4d2181PA_Ua-jNnQBLBwZFWFsIpIgP4RdaNBTyvgcr6T4u7aO6K9wVOYmEJpjBL2G-Eu5wurQ2d2Ee5WIF04QFRTmVCXYNYKtwh025cIDr9L23BC5hMBWggmsPnuAo3liYOK4QiZvVGCetYbw7oEulCfBbRCbD15nxruxeQGZQidkceGOJjmGsb_Q8FNyw9-pttrTPUoL6HRfPyMvbYqdYgm6wzpI1qfZLuSivcUuS3yhbysPxY9kiuV-4GOpPTmLAHY_JRH6suHdgR0OvtLFVHwzYb6DMI8KL_lHMUwakKqI9qVe2NBGQUuE6M4iBw2ZpW8oa59qfS7fcmoKidMTwrBxGaJH_bK6gqG4br8ISdZmSXm1wjh3gOuNFHp32WBQs0M8Pybka9m595IhhBdd04f_AckxWXnNlfIscf20jMiBIMzgzgkxaBEedMMPqMirdnTxNV6Tte0Xmr7HEJJ7u6Oi8iImIPaQEP91Jw2kjxWlCfAnoI8OjS3cwbZvjda-mkx-rfGG2D0zxIz6LZ9d3uoEyyalqDh9OObrQWX0bWVaexxpP7TxX79D6s6DFa4St9tPXDklPOiue7Q4nkenqE98PjcQVP2k-1bjYJAjWin5aP0l_aPQWP_u_vgq54lKDDtH8zexkvoANDKyMJLgCU9T-QVlIzh4c3mfaEDpG2aKGomb8y_uyWBTx1eSuBy0yNFqUN202zk6hp2mS-xbPsFlNMz8we3B0Htae7FilzmR93ux6YYNXS_rXIMcO6LY95Utv5qnVT-m7Qkx-CtZ6CSCIWHzNYfdtmBXh3-jjE7P1Ip5vw2yMAUz1g1Jkj37joCKQcmF5GMVUUQD2t6rx5tlekHzQlHePVJUxtVPLuFgTHqm8pQsgxKhEvcPoHhIIGLFjw6ZNoSzlP9s_jIAKZlLMcr9UJx09E11uyKF9IyLRS3Z4eqsmK-BNZNzPP1nB5OxIe4qecfCNBiJQq-JQBqavB2mWrp-nZao="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_HxFBvS8kQDTipCZuK23BxrvC", "id": "fc_0ef6622055025d64006ab48768a62487d2b6188e48132301d0", "index": 1}]
+{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_HxFBvS8kQDTipCZuK23BxrvC", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d130-f228-7e31-821b-b023dc110761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@@ lines 1-24 of 24 @@
+Project summary
+We prepare clear, practical reports.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Next step: request a quote.
+Reviewed by the project team.
+</t>
+  </si>
+  <si>
     <t>R7</t>
   </si>
   <si>
-    <t>01a0cce1-1ae1-7f00-9d83-5c140d10485c</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Appended both sentences to `/target.txt` as separate changes.", "phase": "final_answer", "index": 0, "id": "msg_0be63b89bf4dc92a006ab36cd461e887d2ae549e26ba5ed228"}]</t>
+    <t>01a0d130-f22c-7513-bc47-bee808061d2b</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0ef6622055025d64006ab48769c4b487d2b8672780da658a8a", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdxu9RAU9spk9uPhfkZyY7CDTRkFQWEuWgRAX4u5qqCUPcCZoVkP3srdtRGw6fqEgNWEx7Tx2dD_wpBeZD2zELGDbJpyRam9IiNHykFKXDyCC5JAV_Ctj8afpXkFv8OPlh7EWbjR9URn2QrzSeydMJjpjxa0TpXyv5SGicrvwMcAkxYXffCjQv21p11lJ_Dyhhbsbgd8319uPjkUxOeYTvkyB7w1CgATizJgnkfgkMd8UTAXm3J-bY3GNrYWbC5JrXr12LU1bwp3enyLLfxgFPZ_UdpxmyfJTL23CdVte5_NFT3mO3sRSDIQt7_EgJuETtH-6rz8hh6aWJE9ApCIlJvo8I6g0y2hZ9p7tcCb_suNByQuVU6CMtOOqs2sJwNKTAZR6gaxV2p1f1dDM8V6HDMtqxUqA0MCyh21d1Qald_YXTuOTmUnEWS9ewnGYj9jKZXD1TGPAUI0T3Ra0MjUdA8Gbh5SvlHLnFI2N10cmlBJkdxQnHtZ63IkcAxEuTlq3sKYfcK899p99XEBkoeiFvAHs8tNfNDudjkMhwCW1nUE2G01ubSuSbMIpgtttiQWpfXrpKBvfNn3uukb2hJdroc4j4bCmSX-EKCOg8yVmdGZi9OGGRRzFHbtGw0_2dp80UXrud1v5XSOA1TUAqgViDnR1JoacOGgQAsp93kizNgoAIcKaF3KoSY3-3iA-XsegngLPyZu17ePhjjg-QEo7SG5j6jf07WDbqDyr-Pl8I47kOLD6lXXLhgFHNwRhl610l2IkVDrMoCJg52tRwxMnuW4I1RnmFb0zjvybiGZqKmq4DZuo2JvZMm6RjTZbN2QmzzBlv335QvbAu23Eh024uBdbdaAiS6sXxucLCzXU4hSmB-9a_hQKQsk8mmrwl55fqNzI1vA8uKXShEp5ado1c3InVW0OxAJT7JFKX543ZPyQXMLbCHyZ0sootOItkuPobWeLOhK8bmWflU2w63x_u9vrPd0o1CTXEunQcv8W7dWMDeSAsebnKF5n4X0E70-td3Nzm7I0GM7w26AtMQU5dHbHoTtyBgA0wj6YBftMP2X9-JkPZUwfXK3PuXGNkdLZCbbcphxGic2TZgOqXxI3CE6VPG35gNMHM5lfac1mrYmZdIphIo3tbW32ETUJpUTY4MxiUGQUyOuNthIXr95O9LaAlOyw0oEuBsyWRuI6Z4zZITkSOVYQjTzBvBOfxGegOoO0RJ_XPTCC-qhZWWgVUddrHdtuHTenPAi3OXpDhYT23RstJC3b6XPb64-1oLZ8Y67qS28QEZBIJMQDKaKCWz8b7LmljTc6DPTlBI1BirVSOl2-nw2jgZe1pCHOo_uWEA_nw4zkPDr_eeIZIS2wOjlEhcXwx8rt79kH4XdTf5rR_PHmaIaV7a5oYFZkLzTyqzjz9LLf-7s0EqeHuZoP_sx-8hIMZOoSwzJY8yLjWCyrJA7RfFEmTmghi4lu0b5IrNiUMc2YoM9pODbUq-rYm9e2Wb6Ad5gwOaz3EEBb7rAjFeghqRx7HWQD1pvn2kHJzOPTVEJWt29rm7LUffN2xPapPxCXTnRh2doD5Vq9ZMvaPK9WpvtU9k-VKCtF2Cr8NMrGuAzBz3M1Tw9nIMD0bp2YJedxQUG_Ut1gZH1vpA-2VGTIeJRt9ilQpYDeTFn0NTZJeIQvqbNQVlWPmJvlcXDp6Z_Y6SOZYauegy-tA7oobRaXg7KcS9cT0JOmhW06Wab7LSKnZbrJgAsM7xG-5wct05L5--PNmW0vLAvGE8QnTkUvksUChi_UPu5iWDSzDlwN43_TLBLM4exWWmKudogRUkfvfoWMCUjiWT77ayw4zTKitBmaezDHtNzDvxGn8BZRT6YVoe30FQq1QEmjtZapk6QYl2miTRJ2dqnY72H_UOHceTCxSrivQIuCxX0qXqVuXOgeve-agib6cOCdQfhEl7vFe9ieNVgIQR3M9EYl324mEQdzCYdVmGTSspZwy6xBYglr1BQ3B3of6dMq5jCf7creB0U6JQ62rpRi5rma4R2dfxWdGNuEvlgCM94_rH-J72RTmdjacZzW-jRROloG5EaeOwpBVprXZyJdBNL_EqK3U6a0G7FespTb5XwXhQSOAlxUNXWEjWZXrvL-wbDuEXAbNHEufFW2gr7grwoutX5tD61sBx9Xewur3qSVPRaGoR3-UmkcF0scCKK2vYIw0063w4odqrlou0ceJ8R8SszMamOBbYQ9nRb3xOHzjp9KUDSACKy-a1czykR2Lq_FeUyibigM7vaKt4MSwOC6sisnZ_d13AJIzBPmatRTgh35JW8bsl_GuV1MdrHygRmjZ7a_NGXebI32VsSwuF--JB0MV5WUt-pDh6lmbMhG_Rle3rfckXn5yxUK4DJA0zIWrhjRlIPIPlO5NIvw_Dj1d31YrwkNxO0cIhrTK1pIdLmX0ceFlb5vMAhTkslkCGJE6AyPmIzWsnIa8qfYMsiAP7DDf-T5lijyr4uMyQZbFxqBHBARr6sxdekf1GPW9xrI87yiVHdo-L1F_NdJkdUlrzxuNncCvHWg1HHg4T9F4zVKwEMZXqRKwt6fz_YfR3Zqv3qKNJgBR4WhfoKp0XCDluheH9axciLXeBhvpXGrui1UWmV9POR86yPq_mpGVvCKulaToqwP7flL4D40s8WDbA0AYJUOMAu-fu_L7YLlLfKKhiDzhVOhDUX0P1i9bIF1hYksLKLUNciju6DXGD5HG6PjfSZBIZkCjQCtyjTVceVe1uFsY6WLio8Bp6PGS6VYPIXHldpD29IafJAPV9fypbQaC8xkwLzrc-KkKnqp33Xzh5KynugJHxB-c_FJBA_p5-wXlPAvgdkpwzyIepIHgGZ4OnGGfuXQhfVnsAlLQ2yKjV8B4T3oT2wPCWRhKoruTLEgidjz5iBZx5kryGzXWYiSi6_6eTA4GNGRFIC5m6yqN1EfH_sIfoRWtjY8vK8xpmomRcjHioL0JNywywSAQK-qmyzGWpONwdaflgX5zXdMkE_TCEUz4BzxTRSYSEwuts7FNld2QMP-nPXTn7ukPQLRl8hsVerDNxiuD6fUJInHsHHlu9D8fHF8RyTTgxBhT5F2SrqO2ST-df3T9jdJ48N3ULoXaVWmubro61nqU46WnN4Or_MfPjAIQwTr9YtHVuIV86myIF8-42cw7EaTtN_lavBTgLoaOngkyXhGqrH0E0rBqPMU9q4Ff6WqLtb8dE9UdDowfdqnli142hBWbVC90GwyAyps2cZpNkgm_9tv9305cRJ8-vgMdU5Pe4unUaHWyD0YoN5firK_TDMapAeccAg2OHpYfpfu6gaMIm0yh2dpkGxSqjIgA91A69UpOzyhSfHFQ7lIMC7jWuAgLRkGWKEnInbU0NV6PFGiFL7K6B9cDrYn5alduXmkZUjCMuR8JPh1KJbQdxhIBf-igdCs1nZnscyYmXAaImap4gQNWBIcZxDX7OBFiDedHvsmFI921sYQHxKGqFua4y1RCnVmPP5t_xOzcRvy2_Y961jvlvifaE9q6FA7JoyXc6-YmDduU3ODfcFHassu96tg6FZMBYTR76WIxGA9Z6cw2sn7fFiMbNAAGqDr7c-BXH4ttj1z1SBHC8ZbFP8DJRiaFipFdAGl9UrSKK2i5_84w2umeZVdQbPV6lQHaxtBd1HXqJmCNLKdwerQ6mDn3krHbKYchgZ12B4oCQqWM1qqoqgIkUv6UojcCaO5QHq9kMJzN_HRuvwYBECT2oFwEXZfAfDM7CisZDympjbQ4Bk46REf65OxsZq02E0kklXzo2dvnf6H552ZAyzKvsBN9MQXhxei5wn_rhqX261myW5y-bZa_H1WTQ5_GvZ4HS9H9vOgjoiahLASKfRZjpV8Feqe-IlKF-zO4efWCXgXlgw_Dxu-iIzZP6F0rz9yjZyp1UKIXlyi9d83CcgNiEuZ9nCGy3smYcHID431-9csgGdFFatIF8snoji9wf40yiL163jYNdBYCE2H-JGn1jr2otICrp6j51xn2mV5N52iR_Y9B9SdwVZqRnw05z5Yt2yZQwyvlw3j7ziyJdGB6laRPQ5Uh-7etoXU55s1vGAJYZ6BPD2rrxJaWGYM52qG4LTAjbbfJQAn0QvIRn2iTxckh4XVV_h0FM1vzjC7T7W3fIWjRnKw4Nh4OQv6curSZDH4aOetW8TAtJ1Admb6DkRVz9wK_rnQ_P4o2rJW77KQ-YQnuEQ1nH7qRVBqxVT9FKfexF-1knlcSGWSs0iqg5iIdTZgS9f3WM0KxKJ0Kxgb9xJViGXcX_DXmvXED7Xh6h2h1mTXCaO3LxvWMFy-FaF9KORnTeitXePqCFioX7ANe7zyv3mXWTUikBIEul4bUKtR1kuur8Xd79mYZVd7rwmTMhve3cGD6xLlaZ3TCiE-EXpbl-"}, {"id": "rs_0ef6622055025d64006ab48771030087d2bd5821ef6b858dd6", "summary": [], "type": "reasoning", "content": [], "index": 1, "encrypted_content": "gAAAAABqtId1nefwJ-xHd4wTEOXpkIqSf-ueYh1KO0mULGm4fgMGrIQjAqzvTm4pz_qztNGO2jMwhZp_KQM0hwd9f4n0GnQEFFrfyhxM4-cnUjIgCBs-ZqUXSMcqUuzP_UMY4njx56QbUG5YH4hL-GCdTbAuvnPcTjtfIqoLhHLQY91wqzaJts3Hpjq6Disno28eKz6yB4pn2Yc_WBlv1lax5_iBvJ2TRDn-Zs653_BSRd56dLfAX1FTn-iu-padsFztCd7c5xO2DyvnVbj-TVgOtG7NYOHIjXULyijyAyjx82RwmExqTWTCGIOtrsW1SzHDHmkYVG5J5vmiQnRUgn0lOyaZHEVMvs5hJBuG-CIoEBmjdBdbh_Kl1RVi5zz0qLj7Y42dSvzAD9Tj0MnH0CzFK-43PxKEuZ0P1CiAnCWP5zG8YG_GCyNT00z73l8eI0MwGRPruXPrLBeOYd5LXNyVskPse8RKXhlCV_JzOMGAuH4I0nTG66HuVmPcG_Ja6278ViuwljLTP7bC-XbyDQUZ-MeSN7swzyTIJGypeqfKRiz8sbcFMLayJYiEhw6MMXfISzNIel7q_3yjvdxfZLHWyxnz-6u7lYZXLU1k2wiyhpEPfP4rk_pfoqNTb9nVrjmv97ZVDNbSYA0GmThNGfmtpm1bHpkewEFQNQEZWWjtzgzfcRE7G0GyKOlECog3NbSWxYGKa0-bHp8WMiz_g4z6KvLoHSb3CP39BT_GpZzDMd1Bs7qF87ux-Ha9rF3NqezXZ6MmhKwT_GzKY_CPtc-80yZvWQ9SW_mFg71_OCzHPfEiyNtD1kZh96a2zLzmw6SxKwpndtPXnj3YrKKEKOKgvJ3x5LcU3P9V5uj4sqEtbPCSsOWHZtwZjVjJ2MKOY_ubsYW6YR5cJkMnVcZwM4kip4BwNMsNUI-GYQHVZzy5Ai361d6nDFQMotNhQ9XdMoIVDUkQ5HQR1OFlQW3T17HJTbbByvcmtxfuXu8HHlmbnBj16_v3NDpmvqnSrnYVnvh-G_vE8s_2pWzrZR5BecufvS8jOs48Bsf7Ed611KB_npQ06uTt5z2ICwxgF7Rq7tGBZrw9vEipAyJlzNymfFUc5eoEGBVr3j6bAkLiMJpq847yDojAg2OxrVT5GtBmoYeALHfBq-f28IzF6guiRhxnKu90bsqv5Jza3Nle-dnVs5mwWocB5aoNYtipAOJeriu4OYv_xWYd4PNpkQKTdvjFPPpz3KdQ3pEJ8nuXWtSq-QP0mQBnuNznf46WymI8Lp4arI9JlJWOG4QsBAKqAWixYIA3yxosh6o5pLLdmS8oqjTIl6KgUdX0ElqygtlVxmuEZBmVVrtj1Bc_KPZqDs8AcXIz9FXarJeHv4jO-vHefrpOnE2irRJOCAuEx5JsgPMMutVkJQkzCvTTCUgMtd_GTbZghuQZa46oQoYKSaPTDIQ8l0_jgWvOfE4D-bQWBsmsW_k0B51I3U14DnYcCwwpkLLbL2GIc3vplKBiS3yoq8xoklcrQ7pI-gxA54Jp_LTpq9yIsvFEP_O1kklXvX-__pFRQPi8nZwyUgC5jDRcrVg7Dx69k76sIg_rM20VM0vt2CMBVcDfLoTpU-Oq2uBmeojP0Ldz0Pl4XZaD2dWjOdmAfoAHEfdaA9xtc4UwCFd4YGjS9YzWHEd__rIAC8JCIVGFa8fAKfEQ7dA6x2PCevWHEIRDgGNjH3PhiR0d6jkmTqR0BpsH6WADkp8iKwBWhWHiAhC1x1iWiOo0tEhaGXjWEMfbnWkfe2hRDlpoTBAmIxyxwraxRePOonv64c7L1wXOvH-A2sITnzhgDEddzOoF0D6CgbwCCXhdqL6x57tcqODYZf4-Z8TJZDvy1TRoKotexrDRINmgeWrIsXusFCNEB2nu4pIoDW5R10hzE4FoR9A9RLPFxZhj3J7W0odgtlwz-kddvTaiWDXXRA4okp7S3crH9_B_Y8yw-pExSHIN7RBVnT0MSCAXB2czm3Osl5EGUSez5ULfvy9z4Kp6AvyE_ZC0OfrMHUI_O4ROVy-hWtlsfahbRGRiVlqXwXlVIVVf0Wd5ZEi-U1WQzquX-2_e1VdUhURZmWDGDMtoXwIlM-g2daZhs8Y-UzzdQF7bg4Q-vSSnlHJX0NNsP570HBiU-fFTBTsqAZVBD7aByI2d4dYRCSsXA65SnlCvGH8Bn4YrTypk6cUcqwDelbxhzHcQg9zGf7jBzU24wlah8a0C36X4ZEjt1Q3_Vir8gpZRGkG9ojPxXKj4pZFVTrvzdfoJhfgM7y3FZ9EQEsCu8SuVFybTEG5nOHCaDfPyqenHmrpdPT5pH2yRemeP-p7enYLClQvD73GR0JJvG7dU0Vwl0fXSixCndI80NeXdSrDcLPvza1rfCnuSFHgFHqNUa1GrgrpEjIRG3y-HAG3bIlJM8DlfdBrY4mX6yNImCrTcU50GUKC-Fc8ntH-moIvZ4iFtQ9zluB0mgMP_3Apj_Z5TmCiniE6TkpOJSUVVc2q28-Jhp6FpWWW3nHa0GTIJNsXkcNYEZLxMOj08Jw-IkJNKxaC-9woVmw39j5JeFboud27M2FRp7-12Li5PC76BINwSRePkrFNlpls5DKBECXr7antBxNPRNBZeAgZuhBFZjWy0Sy8Xz3e7FHryHcikuaqvOGmdn89WTtyfD_aRyUq3Jwv8Xru2qcllZ2Wjz2fiu8McH0emkzw8lD_TK-jN8PmUKNciW60E-AlF0rrjiolBj7H-jSghzVwDbphdfDJ2-mvq8bkqsW-iFUqM0R4vI7XDprXuwcQDvf2jyuWaZaD2LlmYFrRxMsrJgZf2CZsE7FWnsoqPv3zqzG1koZ7JPRsnFdUKeBhwYq8XWVJGrmaNELvOd5dYF51dZFOCrkGzYzt5WHHKHCicM7VrIONfdCTQs18zoy-NOuC396ON5qjq0Ro28qzidNRoCOAOTb_xlbil6dw4zSQxcn3_3dLodQtgScIhddxESh15Uw8S4POAsAba9BFBsk2-ZKppwHzWJStIMnAAJzHkDQv1bc8FuLMlfydk5K9vdScMtIzczPOsKmyC-5jKBVPUMP8GqKCJY4hHDdYSJXASxjPKdlUTFm4NpSwDcIeBaD7IWAXYbWvZCIXCgoOzeDf-rW4zrlqSYnn8yKKF8VGKD-2Zvx7vOooBKkvfgzmWjWS7_ByFlsjPANzCMyJoccGpGKqfe-52H2Yc5o1gK6Eq61W4UaqoPgGhCZ5qPBZFcrkdK2wg3BCWqs_JICKLrRwJVcubJ3WXHhf5wK3dBFhYBjDfJ5OiVzU77-aETdwMp1_m9Jp2MTa6xVWl99svxx1AqQUZvRyeBIatBZhQF9DuEEVcCrb7Bur_BPig7Y9TffcgNhdAaIepFbg9FOrsf0DG6PYrA6PF9P8JQYlZ9eGYZazNhMrlzMqVxML5uD3tSE1ZsAoYnCoGHN_7uIlyROubqzc5HQHf-p8sGcsuMg=="}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"new_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"replace_all\":false}", "call_id": "call_sY4qrJ1nQ4Iyoq1nkxOnT4xT", "id": "fc_0ef6622055025d64006ab48775a1f487d29e553e04239c0f11", "index": 2}]
+{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Reviewed by the project team.\n\nNext step: request a quote.\n\nNext step: request a quote.\n\nReviewed by the project team.\n", "new_string": "Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "replace_all": false}, "id": "call_sY4qrJ1nQ4Iyoq1nkxOnT4xT", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d131-2758-78f1-af21-3d5a0486d530</t>
+  </si>
+  <si>
+    <t>{'file_path': '/target.txt', 'old_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n\nNext step: request a quote.\n\nReviewed by the project team.\n', 'new_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'replace_all': False}</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>01a0d131-275d-7481-85a6-fe08706dcb62</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0ef6622055025d64006ab487777c8c87d2a3a072aab3de9bb0", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtId3r_UQ4wiw5isf_i2fcfJpp8fncDK4zqWkd_tBWVuM8ufE3HyLjK4xCNKJEp3NueNfKzXDyaVvxRz0ZD4ouzBnV35rOfwPDdRFiZ3iOyKOGlOgIaDqetLi3jnKvbZmUWWbGQjdcHMP_Q8NKZxFqO0CcmSleJKSYvBP0cP7o2lCcE9ewuFaJCCoeb0uryJKPyBThNOlLVeIgULBuhXoUCvWD76PkG5eaEVcHriHodBeZEzeT1N7lxFdcdd0FmGv1F5N_l3lXJKrXGHucb7kEfPmmA10bETm2WJ5AShcfDXlQ4Z9RXYxvgq6NoW8_BHcESBT4kl_7wCR6Tp7kR3oaBTlbcoBXDsiUVInGcPY8lzO5kgMD4yGg3AGUSfpuKBXS3GhAieANauUP4qu5ItgAfqEi0qBa3ctHHx_XRRmpOwkdZVzjBPs_Mx6wFg2JIEB_eiERoFkOGH898jEPPntuHS36aETm-X8gYST_IsqkNvFPNbufhj-JVDotJUAAzZZ6YUPH5nEDRZl6XbXKRksInYztHA74J82Qtkehl489Shq56hOgFlv04XetxFvw4svTg7zNDn71YutPWuW3e8sUrtxdZkbGStbS14THP0oLI5xL69As7juN8p44KiWDSqBccDwRE0DLV2XpXq1TnUdfvoQLMMh6Q967Ik5KR_9hu7bMV-h0O3CRM8jdw_IvSmIMJFfTx_neyXTn8s_9YBS5705qJ05XXiNQ67Ql471hg55jfIHm1aMABSlduxofOXZmeGmMqHxdryjPgNA1kG8JrT3n1nECkzBYYwe398rxnF-NPD5qnqcgeJaR6nPRzG2WCQ_DK2IR5fYNUhdDvXTzQtbffMe6GX5JuosjKvd9brjbb-NDLZ9XOc4KoronhqTj2l2m2r_ULPEHlFMAFfKWDR5lHRor1jrWow-8qCXxmDcV5AGiuqnzzG993JmzIkKa7cFgF3JRBMKmJUK_6nsQN8Y5_zDVFArH57VFBmfIhztizUUX8ZSeJYYAVPDdo1Vhv-hRGY75yvRFX0wfkCWjdCI0PL9e5mHDYdvNdIyNVILl36_DqjqlLKpIMYGpfWINeURlePxV5ftBOtgugnWo-Nad5k-Tp_md5FJE5XIqnhnM5J88qVJlJouL2Vycc5srXZMICDJ0_myZdrPc4VLGQg2tuAPlex6OEwUUxK9YbnKgw4="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_aQOE1HeYYYbzJwF5B5aHuF1Y", "id": "fc_0ef6622055025d64006ab48777ad1887d2b23753401401bb7c", "index": 1}]
+{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_aQOE1HeYYYbzJwF5B5aHuF1Y", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d131-2ef9-79a2-9853-1494bd8e5b40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@@ lines 1-24 of 24 @@
+Project summary
+We prepare clear, practical reports.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>01a0d131-2f00-7050-b7f5-6d654a935270</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "Appended both sentences as separate changes to `/target.txt`.", "phase": "final_answer", "index": 0, "id": "msg_0ef6622055025d64006ab48779978887d2a242165a2e73da5f"}]</t>
   </si>
   <si>
     <t>file_editor</t>
@@ -567,7 +632,7 @@
     <t>Execute the RestrictedToolApproval.before_model workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce0-bc32-7003-b125-44ac8cc900ae</t>
+    <t>01a0d130-9564-7e01-b769-98a522d85904</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -579,7 +644,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cce0-bc35-7bf0-b538-86ea9a24066b</t>
+    <t>01a0d130-9567-7a22-ab84-40685ab38e43</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -600,7 +665,7 @@
     <t>Execute the RestrictedToolApproval.after_model workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce0-c659-7871-908f-b1521d183f16</t>
+    <t>01a0d130-9cbd-7d02-8d77-aedbb23def4a</t>
   </si>
   <si>
     <t xml:space="preserve">    tools</t>
@@ -609,7 +674,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cce0-c65b-7c10-be9a-fed7be5c68fd</t>
+    <t>01a0d130-9cbf-7581-b096-1431805489da</t>
   </si>
   <si>
     <t xml:space="preserve">        read_file</t>
@@ -630,28 +695,28 @@
 - Always read a file before editing it.</t>
   </si>
   <si>
-    <t>01a0cce0-c65b-7c10-be9a-fee10c60ceb3</t>
-  </si>
-  <si>
-    <t>01a0cce0-c661-7ee1-b643-c7ac6b487d9e</t>
-  </si>
-  <si>
-    <t>01a0cce0-c662-7382-bf27-7180d5126953</t>
+    <t>01a0d130-9cbf-7581-b096-1446ff13da46</t>
+  </si>
+  <si>
+    <t>01a0d130-9cc4-7420-aa0c-6ecfc0ae7c6f</t>
+  </si>
+  <si>
+    <t>01a0d130-9cc4-7420-aa0c-6ed6ab3aa277</t>
   </si>
   <si>
     <t>interrupted</t>
   </si>
   <si>
-    <t>01a0cce0-e56c-7f50-ba17-fee13d85162c</t>
-  </si>
-  <si>
-    <t>01a0cce0-e585-7b82-b6b0-024d4e55b3b5</t>
-  </si>
-  <si>
-    <t>01a0cce0-e586-7a33-bf42-42a9b7d08b28</t>
-  </si>
-  <si>
-    <t>01a0cce0-e588-77a1-9782-a7b399473d65</t>
+    <t>01a0d130-b2a4-7f50-80a3-649e69e98208</t>
+  </si>
+  <si>
+    <t>01a0d130-b2b6-7680-ad9a-b6cf65725001</t>
+  </si>
+  <si>
+    <t>01a0d130-b2b7-7c93-993d-08e377f1dd38</t>
+  </si>
+  <si>
+    <t>01a0d130-b2b8-7091-b5a3-615686277856</t>
   </si>
   <si>
     <t xml:space="preserve">        edit_file</t>
@@ -665,73 +730,103 @@
 - Only use emojis if the user explicitly requests it.</t>
   </si>
   <si>
-    <t>01a0cce0-e58d-7513-9f48-f3743a84eeac</t>
-  </si>
-  <si>
-    <t>01a0cce0-e58f-7db2-9f40-40440aea8692</t>
-  </si>
-  <si>
-    <t>01a0cce0-eca7-72f3-a473-f53c33ec2c02</t>
-  </si>
-  <si>
-    <t>01a0cce0-eca8-7a50-8090-394c247047b4</t>
-  </si>
-  <si>
-    <t>01a0cce0-ecad-7533-9010-89499336d0a7</t>
-  </si>
-  <si>
-    <t>01a0cce0-ecae-75e0-9431-19509224642d</t>
-  </si>
-  <si>
-    <t>01a0cce1-033e-73c2-ae91-e2eba3d7d098</t>
-  </si>
-  <si>
-    <t>01a0cce1-0354-7b42-83a4-6040ba11231f</t>
-  </si>
-  <si>
-    <t>01a0cce1-0355-7433-a6aa-8217870285aa</t>
-  </si>
-  <si>
-    <t>01a0cce1-0356-7382-a298-74112364b53d</t>
-  </si>
-  <si>
-    <t>01a0cce1-035a-7c42-9e0d-feff1a0b125e</t>
-  </si>
-  <si>
-    <t>01a0cce1-035a-7c42-9e0d-ff01117ffb9e</t>
-  </si>
-  <si>
-    <t>01a0cce1-14b1-7e42-ad43-69840d5b7301</t>
-  </si>
-  <si>
-    <t>01a0cce1-14c4-7e92-b732-3a51284bf8f0</t>
-  </si>
-  <si>
-    <t>01a0cce1-14c5-77a3-8025-ecb3efc1d856</t>
-  </si>
-  <si>
-    <t>01a0cce1-14c6-7450-b467-0e072dadf26f</t>
-  </si>
-  <si>
-    <t>01a0cce1-14cb-78c1-a853-6e1b4c45ab41</t>
-  </si>
-  <si>
-    <t>01a0cce1-14cc-7d42-b663-8794ca39c99b</t>
-  </si>
-  <si>
-    <t>01a0cce1-1ad1-7440-a89d-62cbbf18f362</t>
-  </si>
-  <si>
-    <t>01a0cce1-1ad3-79a1-b434-3a4744ad4bd6</t>
-  </si>
-  <si>
-    <t>01a0cce1-1adf-7821-9e77-3d628f439c18</t>
-  </si>
-  <si>
-    <t>01a0cce1-1ae1-7f00-9d83-5c06f29af53d</t>
-  </si>
-  <si>
-    <t>01a0cce1-1eef-7630-9396-4c6640f589be</t>
+    <t>01a0d130-b2bc-7510-8d92-90a4bba24b47</t>
+  </si>
+  <si>
+    <t>01a0d130-b2bd-7a82-883f-0c4f68b3fa99</t>
+  </si>
+  <si>
+    <t>01a0d130-c95a-7581-a8a6-21b5e7a6472a</t>
+  </si>
+  <si>
+    <t>01a0d130-c97f-7990-89f2-177990bbe901</t>
+  </si>
+  <si>
+    <t>01a0d130-c981-75e3-ac7a-87a359cadb96</t>
+  </si>
+  <si>
+    <t>01a0d130-c982-7da3-b0ab-a255256c093c</t>
+  </si>
+  <si>
+    <t>01a0d130-c987-70d3-8376-0ef10a255674</t>
+  </si>
+  <si>
+    <t>01a0d130-c989-7543-93d7-60e725d95ff4</t>
+  </si>
+  <si>
+    <t>01a0d130-cf42-7e62-9f2d-2ee807578e64</t>
+  </si>
+  <si>
+    <t>01a0d130-cf44-7f60-99be-acca4edc1f82</t>
+  </si>
+  <si>
+    <t>01a0d130-cf49-7831-b139-36cccf0861c4</t>
+  </si>
+  <si>
+    <t>01a0d130-cf4a-7a52-84e2-6bd507da9111</t>
+  </si>
+  <si>
+    <t>01a0d130-eb60-7ea1-a62a-15341e91f96c</t>
+  </si>
+  <si>
+    <t>01a0d130-eb85-7a83-a666-b6228b22504a</t>
+  </si>
+  <si>
+    <t>01a0d130-eb86-7a01-bf11-2e7b7a73c5b9</t>
+  </si>
+  <si>
+    <t>01a0d130-eb88-74b3-9eb3-8c9109d897ac</t>
+  </si>
+  <si>
+    <t>01a0d130-eb8c-78f2-82e7-38caf88ef616</t>
+  </si>
+  <si>
+    <t>01a0d130-eb8d-7c40-9e64-1cf67511486b</t>
+  </si>
+  <si>
+    <t>01a0d130-f225-7501-8b72-d94592b63d18</t>
+  </si>
+  <si>
+    <t>01a0d130-f226-71d2-9c5c-07deb12213be</t>
+  </si>
+  <si>
+    <t>01a0d130-f22a-7f13-b522-94986ac6ad0b</t>
+  </si>
+  <si>
+    <t>01a0d130-f22b-7d20-bdc2-b9f017f5a267</t>
+  </si>
+  <si>
+    <t>01a0d131-272f-7a93-be58-02e6e0915dcb</t>
+  </si>
+  <si>
+    <t>01a0d131-2754-7d50-98c6-01611bca58dc</t>
+  </si>
+  <si>
+    <t>01a0d131-2756-74e2-b254-a9dac7e39aaa</t>
+  </si>
+  <si>
+    <t>01a0d131-2757-7e53-ba2a-82d71dff3114</t>
+  </si>
+  <si>
+    <t>01a0d131-275b-71a1-92d4-4feca6e34062</t>
+  </si>
+  <si>
+    <t>01a0d131-275c-73a1-8d35-1d449c2517be</t>
+  </si>
+  <si>
+    <t>01a0d131-2ef4-7920-ba64-16a9fb6a83fe</t>
+  </si>
+  <si>
+    <t>01a0d131-2ef6-7bd2-a499-8b7af8d30907</t>
+  </si>
+  <si>
+    <t>01a0d131-2efe-7453-9a5f-bc825c20b869</t>
+  </si>
+  <si>
+    <t>01a0d131-2eff-75a1-9048-4f6f80f29086</t>
+  </si>
+  <si>
+    <t>01a0d131-3439-7df3-bd95-3a723abb350b</t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1233,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M115"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1198,20 +1293,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E115)=7,SUM('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E115),"Unknown")</f>
-        <v>0.0020831410467</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E116,'Turns'!E132,'Turns'!E147)=9,SUM('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E116,'Turns'!E132,'Turns'!E147),"Unknown")</f>
+        <v>0.003957333695</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F115)=7,SUM('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F115),"Unknown")</f>
-        <v>0.00238791</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F116,'Turns'!F132,'Turns'!F147)=9,SUM('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F116,'Turns'!F132,'Turns'!F147),"Unknown")</f>
+        <v>0.0045157</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>208.0</v>
+        <v>396.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>239.0</v>
+        <v>452.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1222,20 +1317,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E115)=7,SUM('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E115),"Unknown")</f>
-        <v>0.0020831410467</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E116,'Turns'!E132,'Turns'!E147)=9,SUM('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E116,'Turns'!E132,'Turns'!E147),"Unknown")</f>
+        <v>0.003957333695</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F115)=7,SUM('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F115),"Unknown")</f>
-        <v>0.00238791</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F116,'Turns'!F132,'Turns'!F147)=9,SUM('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F116,'Turns'!F132,'Turns'!F147),"Unknown")</f>
+        <v>0.0045157</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>208.0</v>
+        <v>396.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>239.0</v>
+        <v>452.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1273,7 +1368,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000154932912</v>
+        <v>0.00015563976</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1281,7 +1376,7 @@
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1360,7 +1455,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1374,19 +1469,19 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>2.418726e-05</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>3.24e-05</v>
+        <v>2.76e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1408,7 +1503,7 @@
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.5372768e-05</v>
+        <v>7.571664e-05</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -1471,11 +1566,11 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.000258570468</v>
+        <v>0.00025554366</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.0002964</v>
+        <v>0.0002916</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1483,7 +1578,7 @@
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>111</v>
@@ -1550,7 +1645,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="164" customHeight="1">
+    <row r="23" spans="1:13" ht="268" customHeight="1">
       <c r="B23">
         <v>1</v>
       </c>
@@ -1572,7 +1667,7 @@
         <v>94</v>
       </c>
       <c r="D24" s="4">
-        <v>1088</v>
+        <v>1110</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>95</v>
@@ -1626,7 +1721,7 @@
       </c>
       <c r="E26" s="2">
         <f>IF(AND(ISNUMBER(F26),ISNUMBER('Reference data'!$B$3)),F26*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F26" s="2">
         <f>IF(D26=0,0,IF(ISNUMBER('Reference data'!B17),D26*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1641,7 +1736,7 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="203" customHeight="1">
+    <row r="27" spans="1:13" ht="307" customHeight="1">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -1666,15 +1761,15 @@
         <v>103</v>
       </c>
       <c r="D28" s="5">
-        <v>1085</v>
+        <v>1107</v>
       </c>
       <c r="E28" s="2">
         <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0002366303625</v>
+        <v>0.0002425298625</v>
       </c>
       <c r="F28" s="2">
         <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!D17),D28*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.00027125</v>
+        <v>0.00027675</v>
       </c>
       <c r="G28" s="5">
         <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1682,7 +1777,7 @@
       </c>
       <c r="H28" s="5">
         <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1">
@@ -1707,7 +1802,7 @@
         <v>105</v>
       </c>
       <c r="D30" s="4">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1">
@@ -1721,23 +1816,23 @@
         <v>106</v>
       </c>
       <c r="D31" s="5">
-        <v>267</v>
+        <v>365</v>
       </c>
       <c r="E31" s="2">
         <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000279507348</v>
+        <v>0.0003838413</v>
       </c>
       <c r="F31" s="2">
         <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!F17),D31*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.0003204</v>
+        <v>0.000438</v>
       </c>
       <c r="G31" s="5">
         <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>28.0</v>
+        <v>38.0</v>
       </c>
       <c r="H31" s="5">
         <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>32.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="24" customHeight="1">
@@ -1751,23 +1846,23 @@
         <v>107</v>
       </c>
       <c r="D32" s="5">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="E32" s="2">
         <f>IF(AND(ISNUMBER(F32),ISNUMBER('Reference data'!$B$3)),F32*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00016749504</v>
+        <v>7.992312e-05</v>
       </c>
       <c r="F32" s="2">
         <f>IF(D32=0,0,IF(ISNUMBER('Reference data'!E17),D32*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.000192</v>
+        <v>9.12e-05</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="H32" s="5">
         <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="409" customHeight="1">
@@ -1818,19 +1913,19 @@
       </c>
       <c r="E36" s="2">
         <f>IF(COUNT('Turns'!E25,'Turns'!E26,'Turns'!E28,'Turns'!E31,'Turns'!E32)=5,SUM('Turns'!E25,'Turns'!E26,'Turns'!E28,'Turns'!E31,'Turns'!E32),"Unknown")</f>
-        <v>0.0006841561725</v>
+        <v>0.0007068200925</v>
       </c>
       <c r="F36" s="2">
         <f>IF(COUNT('Turns'!F25,'Turns'!F26,'Turns'!F28,'Turns'!F31,'Turns'!F32)=5,SUM('Turns'!F25,'Turns'!F26,'Turns'!F28,'Turns'!F31,'Turns'!F32),"Unknown")</f>
-        <v>0.00078425</v>
+        <v>0.00080655</v>
       </c>
       <c r="G36" s="5">
         <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
       <c r="H36" s="5">
         <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>78.0</v>
+        <v>81.0</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>111</v>
@@ -1844,13 +1939,13 @@
         <v>127</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="99" customHeight="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="47" customHeight="1">
       <c r="B38">
         <v>1</v>
       </c>
@@ -1858,10 +1953,10 @@
         <v>114</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="24" customHeight="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="73" customHeight="1">
       <c r="B39">
         <v>1</v>
       </c>
@@ -1869,12 +1964,12 @@
         <v>116</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B40" s="4">
         <v>1</v>
@@ -1883,18 +1978,18 @@
         <v>94</v>
       </c>
       <c r="D40" s="4">
-        <v>1541</v>
+        <v>1606</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>95</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="24" customHeight="1">
       <c r="A41" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -1903,15 +1998,15 @@
         <v>123</v>
       </c>
       <c r="D41" s="5">
-        <v>1085</v>
+        <v>1107</v>
       </c>
       <c r="E41" s="2">
         <f>IF(AND(ISNUMBER(F41),ISNUMBER('Reference data'!$B$3)),F41*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.8930429e-05</v>
+        <v>1.9402389e-05</v>
       </c>
       <c r="F41" s="2">
         <f>IF(D41=0,0,IF(ISNUMBER('Reference data'!C17),D41*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>2.17e-05</v>
+        <v>2.214e-05</v>
       </c>
       <c r="G41" s="5">
         <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1924,7 +2019,7 @@
     </row>
     <row r="42" spans="1:13" ht="24" customHeight="1">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -1937,7 +2032,7 @@
       </c>
       <c r="E42" s="2">
         <f>IF(AND(ISNUMBER(F42),ISNUMBER('Reference data'!$B$3)),F42*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F42" s="2">
         <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!B17),D42*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1952,9 +2047,9 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="24" customHeight="1">
+    <row r="43" spans="1:13" ht="73" customHeight="1">
       <c r="A43" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -1963,12 +2058,12 @@
         <v>124</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="24" customHeight="1">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -1977,28 +2072,28 @@
         <v>103</v>
       </c>
       <c r="D44" s="5">
-        <v>453</v>
+        <v>496</v>
       </c>
       <c r="E44" s="2">
         <f>IF(AND(ISNUMBER(F44),ISNUMBER('Reference data'!$B$3)),F44*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.87959025e-05</v>
+        <v>0.0001086674</v>
       </c>
       <c r="F44" s="2">
         <f>IF(D44=0,0,IF(ISNUMBER('Reference data'!D17),D44*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.00011325</v>
+        <v>0.000124</v>
       </c>
       <c r="G44" s="5">
         <f>IF(ISNUMBER(E44),ROUND(E44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="H44" s="5">
         <f>IF(ISNUMBER(F44),ROUND(F44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="24" customHeight="1">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -2009,7 +2104,7 @@
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B46" s="4">
         <v>1</v>
@@ -2018,12 +2113,12 @@
         <v>105</v>
       </c>
       <c r="D46" s="4">
-        <v>59</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="24" customHeight="1">
       <c r="A47" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -2032,28 +2127,28 @@
         <v>106</v>
       </c>
       <c r="D47" s="5">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="E47" s="2">
         <f>IF(AND(ISNUMBER(F47),ISNUMBER('Reference data'!$B$3)),F47*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>0.0002208402</v>
       </c>
       <c r="F47" s="2">
         <f>IF(D47=0,0,IF(ISNUMBER('Reference data'!F17),D47*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>3.36e-05</v>
+        <v>0.000252</v>
       </c>
       <c r="G47" s="5">
         <f>IF(ISNUMBER(E47),ROUND(E47*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>22.0</v>
       </c>
       <c r="H47" s="5">
         <f>IF(ISNUMBER(F47),ROUND(F47*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="24" customHeight="1">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -2062,28 +2157,28 @@
         <v>107</v>
       </c>
       <c r="D48" s="5">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="E48" s="2">
         <f>IF(AND(ISNUMBER(F48),ISNUMBER('Reference data'!$B$3)),F48*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.2452164e-05</v>
+        <v>0.0001156782</v>
       </c>
       <c r="F48" s="2">
         <f>IF(D48=0,0,IF(ISNUMBER('Reference data'!E17),D48*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.72e-05</v>
+        <v>0.000132</v>
       </c>
       <c r="G48" s="5">
         <f>IF(ISNUMBER(E48),ROUND(E48*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="H48" s="5">
         <f>IF(ISNUMBER(F48),ROUND(F48*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="294" customHeight="1">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="409" customHeight="1">
       <c r="A49" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -2092,12 +2187,12 @@
         <v>108</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="24" customHeight="1">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -2108,7 +2203,7 @@
     </row>
     <row r="51" spans="1:13" ht="24" customHeight="1">
       <c r="A51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -2119,7 +2214,7 @@
     </row>
     <row r="52" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B52" s="4">
         <v>1</v>
@@ -2129,19 +2224,19 @@
       </c>
       <c r="E52" s="2">
         <f>IF(COUNT('Turns'!E41,'Turns'!E42,'Turns'!E44,'Turns'!E47,'Turns'!E48)=5,SUM('Turns'!E41,'Turns'!E42,'Turns'!E44,'Turns'!E47,'Turns'!E48),"Unknown")</f>
-        <v>0.0001800135495</v>
+        <v>0.000465113999</v>
       </c>
       <c r="F52" s="2">
         <f>IF(COUNT('Turns'!F41,'Turns'!F42,'Turns'!F44,'Turns'!F47,'Turns'!F48)=5,SUM('Turns'!F41,'Turns'!F42,'Turns'!F44,'Turns'!F47,'Turns'!F48),"Unknown")</f>
-        <v>0.00020635</v>
+        <v>0.00053074</v>
       </c>
       <c r="G52" s="5">
         <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>47.0</v>
       </c>
       <c r="H52" s="5">
         <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>53.0</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>111</v>
@@ -2152,16 +2247,16 @@
         <v>1</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>111</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="24" customHeight="1">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="73" customHeight="1">
       <c r="B54">
         <v>1</v>
       </c>
@@ -2169,10 +2264,10 @@
         <v>114</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="190" customHeight="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="24" customHeight="1">
       <c r="B55">
         <v>1</v>
       </c>
@@ -2180,12 +2275,12 @@
         <v>116</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B56" s="4">
         <v>1</v>
@@ -2194,18 +2289,18 @@
         <v>94</v>
       </c>
       <c r="D56" s="4">
-        <v>1677</v>
+        <v>1952</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>95</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="24" customHeight="1">
       <c r="A57" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -2214,15 +2309,15 @@
         <v>123</v>
       </c>
       <c r="D57" s="5">
-        <v>1538</v>
+        <v>1603</v>
       </c>
       <c r="E57" s="2">
         <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.68341012e-05</v>
+        <v>2.8095781e-05</v>
       </c>
       <c r="F57" s="2">
         <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!C17),D57*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.076e-05</v>
+        <v>3.206e-05</v>
       </c>
       <c r="G57" s="5">
         <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2235,7 +2330,7 @@
     </row>
     <row r="58" spans="1:13" ht="24" customHeight="1">
       <c r="A58" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -2248,7 +2343,7 @@
       </c>
       <c r="E58" s="2">
         <f>IF(AND(ISNUMBER(F58),ISNUMBER('Reference data'!$B$3)),F58*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F58" s="2">
         <f>IF(D58=0,0,IF(ISNUMBER('Reference data'!B17),D58*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -2263,9 +2358,9 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="190" customHeight="1">
+    <row r="59" spans="1:13" ht="24" customHeight="1">
       <c r="A59" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -2274,12 +2369,12 @@
         <v>124</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="24" customHeight="1">
       <c r="A60" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -2288,28 +2383,28 @@
         <v>103</v>
       </c>
       <c r="D60" s="5">
-        <v>136</v>
+        <v>346</v>
       </c>
       <c r="E60" s="2">
         <f>IF(AND(ISNUMBER(F60),ISNUMBER('Reference data'!$B$3)),F60*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.966058e-05</v>
+        <v>7.5804275e-05</v>
       </c>
       <c r="F60" s="2">
         <f>IF(D60=0,0,IF(ISNUMBER('Reference data'!D17),D60*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>3.4e-05</v>
+        <v>8.65e-05</v>
       </c>
       <c r="G60" s="5">
         <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="H60" s="5">
         <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="24" customHeight="1">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -2320,7 +2415,7 @@
     </row>
     <row r="62" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A62" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B62" s="4">
         <v>1</v>
@@ -2329,12 +2424,12 @@
         <v>105</v>
       </c>
       <c r="D62" s="4">
-        <v>268</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="24" customHeight="1">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -2343,28 +2438,28 @@
         <v>106</v>
       </c>
       <c r="D63" s="5">
-        <v>191</v>
+        <v>7</v>
       </c>
       <c r="E63" s="2">
         <f>IF(AND(ISNUMBER(F63),ISNUMBER('Reference data'!$B$3)),F63*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000199947204</v>
+        <v>7.36134e-06</v>
       </c>
       <c r="F63" s="2">
         <f>IF(D63=0,0,IF(ISNUMBER('Reference data'!F17),D63*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.0002292</v>
+        <v>8.4e-06</v>
       </c>
       <c r="G63" s="5">
         <f>IF(ISNUMBER(E63),ROUND(E63*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="H63" s="5">
         <f>IF(ISNUMBER(F63),ROUND(F63*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="24" customHeight="1">
       <c r="A64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -2373,28 +2468,28 @@
         <v>107</v>
       </c>
       <c r="D64" s="5">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="E64" s="2">
         <f>IF(AND(ISNUMBER(F64),ISNUMBER('Reference data'!$B$3)),F64*'Reference data'!$B$3,"Unknown")</f>
-        <v>8.0606988e-05</v>
+        <v>3.260022e-05</v>
       </c>
       <c r="F64" s="2">
         <f>IF(D64=0,0,IF(ISNUMBER('Reference data'!E17),D64*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>9.24e-05</v>
+        <v>3.72e-05</v>
       </c>
       <c r="G64" s="5">
         <f>IF(ISNUMBER(E64),ROUND(E64*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="H64" s="5">
         <f>IF(ISNUMBER(F64),ROUND(F64*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="409" customHeight="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="281" customHeight="1">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -2403,12 +2498,12 @@
         <v>108</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="24" customHeight="1">
       <c r="A66" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -2419,7 +2514,7 @@
     </row>
     <row r="67" spans="1:13" ht="24" customHeight="1">
       <c r="A67" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -2430,7 +2525,7 @@
     </row>
     <row r="68" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A68" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B68" s="4">
         <v>1</v>
@@ -2440,19 +2535,19 @@
       </c>
       <c r="E68" s="2">
         <f>IF(COUNT('Turns'!E57,'Turns'!E58,'Turns'!E60,'Turns'!E63,'Turns'!E64)=5,SUM('Turns'!E57,'Turns'!E58,'Turns'!E60,'Turns'!E63,'Turns'!E64),"Unknown")</f>
-        <v>0.0003375722952</v>
+        <v>0.000144387426</v>
       </c>
       <c r="F68" s="2">
         <f>IF(COUNT('Turns'!F57,'Turns'!F58,'Turns'!F60,'Turns'!F63,'Turns'!F64)=5,SUM('Turns'!F57,'Turns'!F58,'Turns'!F60,'Turns'!F63,'Turns'!F64),"Unknown")</f>
-        <v>0.00038696</v>
+        <v>0.00016476</v>
       </c>
       <c r="G68" s="5">
         <f>IF(ISNUMBER(E68),ROUND(E68*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>34.0</v>
+        <v>14.0</v>
       </c>
       <c r="H68" s="5">
         <f>IF(ISNUMBER(F68),ROUND(F68*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
+        <v>16.0</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>111</v>
@@ -2463,16 +2558,16 @@
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="47" customHeight="1">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="24" customHeight="1">
       <c r="B70">
         <v>1</v>
       </c>
@@ -2480,10 +2575,10 @@
         <v>114</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="73" customHeight="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="294" customHeight="1">
       <c r="B71">
         <v>1</v>
       </c>
@@ -2505,7 +2600,7 @@
         <v>94</v>
       </c>
       <c r="D72" s="4">
-        <v>2000</v>
+        <v>2093</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>95</v>
@@ -2525,15 +2620,15 @@
         <v>123</v>
       </c>
       <c r="D73" s="5">
-        <v>1674</v>
+        <v>1949</v>
       </c>
       <c r="E73" s="2">
         <f>IF(AND(ISNUMBER(F73),ISNUMBER('Reference data'!$B$3)),F73*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.92069476e-05</v>
+        <v>3.4160123e-05</v>
       </c>
       <c r="F73" s="2">
         <f>IF(D73=0,0,IF(ISNUMBER('Reference data'!C17),D73*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.348e-05</v>
+        <v>3.898e-05</v>
       </c>
       <c r="G73" s="5">
         <f>IF(ISNUMBER(E73),ROUND(E73*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2541,7 +2636,7 @@
       </c>
       <c r="H73" s="5">
         <f>IF(ISNUMBER(F73),ROUND(F73*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="24" customHeight="1">
@@ -2559,7 +2654,7 @@
       </c>
       <c r="E74" s="2">
         <f>IF(AND(ISNUMBER(F74),ISNUMBER('Reference data'!$B$3)),F74*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F74" s="2">
         <f>IF(D74=0,0,IF(ISNUMBER('Reference data'!B17),D74*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -2574,7 +2669,7 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="73" customHeight="1">
+    <row r="75" spans="1:13" ht="294" customHeight="1">
       <c r="A75" t="s">
         <v>143</v>
       </c>
@@ -2599,23 +2694,23 @@
         <v>103</v>
       </c>
       <c r="D76" s="5">
-        <v>323</v>
+        <v>141</v>
       </c>
       <c r="E76" s="2">
         <f>IF(AND(ISNUMBER(F76),ISNUMBER('Reference data'!$B$3)),F76*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.04438775e-05</v>
+        <v>3.08913375e-05</v>
       </c>
       <c r="F76" s="2">
         <f>IF(D76=0,0,IF(ISNUMBER('Reference data'!D17),D76*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>8.075e-05</v>
+        <v>3.525e-05</v>
       </c>
       <c r="G76" s="5">
         <f>IF(ISNUMBER(E76),ROUND(E76*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H76" s="5">
         <f>IF(ISNUMBER(F76),ROUND(F76*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="24" customHeight="1">
@@ -2640,7 +2735,7 @@
         <v>105</v>
       </c>
       <c r="D78" s="4">
-        <v>281</v>
+        <v>578</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="24" customHeight="1">
@@ -2654,23 +2749,23 @@
         <v>106</v>
       </c>
       <c r="D79" s="5">
-        <v>102</v>
+        <v>467</v>
       </c>
       <c r="E79" s="2">
         <f>IF(AND(ISNUMBER(F79),ISNUMBER('Reference data'!$B$3)),F79*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000106778088</v>
+        <v>0.00049110654</v>
       </c>
       <c r="F79" s="2">
         <f>IF(D79=0,0,IF(ISNUMBER('Reference data'!F17),D79*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.0001224</v>
+        <v>0.0005604</v>
       </c>
       <c r="G79" s="5">
         <f>IF(ISNUMBER(E79),ROUND(E79*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>49.0</v>
       </c>
       <c r="H79" s="5">
         <f>IF(ISNUMBER(F79),ROUND(F79*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="24" customHeight="1">
@@ -2684,23 +2779,23 @@
         <v>107</v>
       </c>
       <c r="D80" s="5">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="E80" s="2">
         <f>IF(AND(ISNUMBER(F80),ISNUMBER('Reference data'!$B$3)),F80*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000187385076</v>
+        <v>0.00011672982</v>
       </c>
       <c r="F80" s="2">
         <f>IF(D80=0,0,IF(ISNUMBER('Reference data'!E17),D80*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0002148</v>
+        <v>0.0001332</v>
       </c>
       <c r="G80" s="5">
         <f>IF(ISNUMBER(E80),ROUND(E80*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="H80" s="5">
         <f>IF(ISNUMBER(F80),ROUND(F80*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="409" customHeight="1">
@@ -2751,19 +2846,19 @@
       </c>
       <c r="E84" s="2">
         <f>IF(COUNT('Turns'!E73,'Turns'!E74,'Turns'!E76,'Turns'!E79,'Turns'!E80)=5,SUM('Turns'!E73,'Turns'!E74,'Turns'!E76,'Turns'!E79,'Turns'!E80),"Unknown")</f>
-        <v>0.0003943374111</v>
+        <v>0.0006734136305</v>
       </c>
       <c r="F84" s="2">
         <f>IF(COUNT('Turns'!F73,'Turns'!F74,'Turns'!F76,'Turns'!F79,'Turns'!F80)=5,SUM('Turns'!F73,'Turns'!F74,'Turns'!F76,'Turns'!F79,'Turns'!F80),"Unknown")</f>
-        <v>0.00045203</v>
+        <v>0.00076843</v>
       </c>
       <c r="G84" s="5">
         <f>IF(ISNUMBER(E84),ROUND(E84*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
+        <v>67.0</v>
       </c>
       <c r="H84" s="5">
         <f>IF(ISNUMBER(F84),ROUND(F84*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>45.0</v>
+        <v>77.0</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>111</v>
@@ -2783,7 +2878,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="112" customHeight="1">
+    <row r="86" spans="1:13" ht="73" customHeight="1">
       <c r="B86">
         <v>1</v>
       </c>
@@ -2802,7 +2897,7 @@
         <v>116</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -2816,7 +2911,7 @@
         <v>94</v>
       </c>
       <c r="D88" s="4">
-        <v>2307</v>
+        <v>2697</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>95</v>
@@ -2836,19 +2931,19 @@
         <v>123</v>
       </c>
       <c r="D89" s="5">
-        <v>1997</v>
+        <v>2090</v>
       </c>
       <c r="E89" s="2">
         <f>IF(AND(ISNUMBER(F89),ISNUMBER('Reference data'!$B$3)),F89*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.48424578e-05</v>
+        <v>3.663143e-05</v>
       </c>
       <c r="F89" s="2">
         <f>IF(D89=0,0,IF(ISNUMBER('Reference data'!C17),D89*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.994e-05</v>
+        <v>4.18e-05</v>
       </c>
       <c r="G89" s="5">
         <f>IF(ISNUMBER(E89),ROUND(E89*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H89" s="5">
         <f>IF(ISNUMBER(F89),ROUND(F89*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2870,7 +2965,7 @@
       </c>
       <c r="E90" s="2">
         <f>IF(AND(ISNUMBER(F90),ISNUMBER('Reference data'!$B$3)),F90*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F90" s="2">
         <f>IF(D90=0,0,IF(ISNUMBER('Reference data'!B17),D90*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -2896,7 +2991,7 @@
         <v>124</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="24" customHeight="1">
@@ -2910,23 +3005,23 @@
         <v>103</v>
       </c>
       <c r="D92" s="5">
-        <v>307</v>
+        <v>604</v>
       </c>
       <c r="E92" s="2">
         <f>IF(AND(ISNUMBER(F92),ISNUMBER('Reference data'!$B$3)),F92*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.69543975e-05</v>
+        <v>0.00013232885</v>
       </c>
       <c r="F92" s="2">
         <f>IF(D92=0,0,IF(ISNUMBER('Reference data'!D17),D92*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>7.675e-05</v>
+        <v>0.000151</v>
       </c>
       <c r="G92" s="5">
         <f>IF(ISNUMBER(E92),ROUND(E92*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="H92" s="5">
         <f>IF(ISNUMBER(F92),ROUND(F92*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="24" customHeight="1">
@@ -2951,7 +3046,7 @@
         <v>105</v>
       </c>
       <c r="D94" s="4">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="24" customHeight="1">
@@ -2965,15 +3060,15 @@
         <v>106</v>
       </c>
       <c r="D95" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E95" s="2">
         <f>IF(AND(ISNUMBER(F95),ISNUMBER('Reference data'!$B$3)),F95*'Reference data'!$B$3,"Unknown")</f>
-        <v>8.374752e-06</v>
+        <v>7.36134e-06</v>
       </c>
       <c r="F95" s="2">
         <f>IF(D95=0,0,IF(ISNUMBER('Reference data'!F17),D95*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>9.6e-06</v>
+        <v>8.4e-06</v>
       </c>
       <c r="G95" s="5">
         <f>IF(ISNUMBER(E95),ROUND(E95*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2999,7 +3094,7 @@
       </c>
       <c r="E96" s="2">
         <f>IF(AND(ISNUMBER(F96),ISNUMBER('Reference data'!$B$3)),F96*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.2452164e-05</v>
+        <v>3.260022e-05</v>
       </c>
       <c r="F96" s="2">
         <f>IF(D96=0,0,IF(ISNUMBER('Reference data'!E17),D96*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -3062,19 +3157,19 @@
       </c>
       <c r="E100" s="2">
         <f>IF(COUNT('Turns'!E89,'Turns'!E90,'Turns'!E92,'Turns'!E95,'Turns'!E96)=5,SUM('Turns'!E89,'Turns'!E90,'Turns'!E92,'Turns'!E95,'Turns'!E96),"Unknown")</f>
-        <v>0.0001431471933</v>
+        <v>0.00020944765</v>
       </c>
       <c r="F100" s="2">
         <f>IF(COUNT('Turns'!F89,'Turns'!F90,'Turns'!F92,'Turns'!F95,'Turns'!F96)=5,SUM('Turns'!F89,'Turns'!F90,'Turns'!F92,'Turns'!F95,'Turns'!F96),"Unknown")</f>
-        <v>0.00016409</v>
+        <v>0.000239</v>
       </c>
       <c r="G100" s="5">
         <f>IF(ISNUMBER(E100),ROUND(E100*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>21.0</v>
       </c>
       <c r="H100" s="5">
         <f>IF(ISNUMBER(F100),ROUND(F100*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="K100" s="4" t="s">
         <v>111</v>
@@ -3105,7 +3200,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="216" customHeight="1">
+    <row r="103" spans="1:13" ht="320" customHeight="1">
       <c r="B103">
         <v>1</v>
       </c>
@@ -3127,7 +3222,7 @@
         <v>94</v>
       </c>
       <c r="D104" s="4">
-        <v>2430</v>
+        <v>2845</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>95</v>
@@ -3147,19 +3242,19 @@
         <v>123</v>
       </c>
       <c r="D105" s="5">
-        <v>2304</v>
+        <v>2694</v>
       </c>
       <c r="E105" s="2">
         <f>IF(AND(ISNUMBER(F105),ISNUMBER('Reference data'!$B$3)),F105*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.01988096e-05</v>
+        <v>4.7217738e-05</v>
       </c>
       <c r="F105" s="2">
         <f>IF(D105=0,0,IF(ISNUMBER('Reference data'!C17),D105*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.608e-05</v>
+        <v>5.388e-05</v>
       </c>
       <c r="G105" s="5">
         <f>IF(ISNUMBER(E105),ROUND(E105*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H105" s="5">
         <f>IF(ISNUMBER(F105),ROUND(F105*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3181,7 +3276,7 @@
       </c>
       <c r="E106" s="2">
         <f>IF(AND(ISNUMBER(F106),ISNUMBER('Reference data'!$B$3)),F106*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F106" s="2">
         <f>IF(D106=0,0,IF(ISNUMBER('Reference data'!B17),D106*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -3196,7 +3291,7 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="216" customHeight="1">
+    <row r="107" spans="1:13" ht="320" customHeight="1">
       <c r="A107" t="s">
         <v>153</v>
       </c>
@@ -3221,15 +3316,15 @@
         <v>103</v>
       </c>
       <c r="D108" s="5">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="E108" s="2">
         <f>IF(AND(ISNUMBER(F108),ISNUMBER('Reference data'!$B$3)),F108*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.68253775e-05</v>
+        <v>3.242495e-05</v>
       </c>
       <c r="F108" s="2">
         <f>IF(D108=0,0,IF(ISNUMBER('Reference data'!D17),D108*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>3.075e-05</v>
+        <v>3.7e-05</v>
       </c>
       <c r="G108" s="5">
         <f>IF(ISNUMBER(E108),ROUND(E108*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3237,7 +3332,7 @@
       </c>
       <c r="H108" s="5">
         <f>IF(ISNUMBER(F108),ROUND(F108*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="24" customHeight="1">
@@ -3262,7 +3357,7 @@
         <v>105</v>
       </c>
       <c r="D110" s="4">
-        <v>17</v>
+        <v>952</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="24" customHeight="1">
@@ -3273,29 +3368,29 @@
         <v>1</v>
       </c>
       <c r="C111" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D111" s="5">
-        <v>17</v>
+        <v>850</v>
       </c>
       <c r="E111" s="2">
         <f>IF(AND(ISNUMBER(F111),ISNUMBER('Reference data'!$B$3)),F111*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.7796348e-05</v>
+        <v>0.000893877</v>
       </c>
       <c r="F111" s="2">
-        <f>IF(D111=0,0,IF(ISNUMBER('Reference data'!E17),D111*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.04e-05</v>
+        <f>IF(D111=0,0,IF(ISNUMBER('Reference data'!F17),D111*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>0.00102</v>
       </c>
       <c r="G111" s="5">
         <f>IF(ISNUMBER(E111),ROUND(E111*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>89.0</v>
       </c>
       <c r="H111" s="5">
         <f>IF(ISNUMBER(F111),ROUND(F111*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" ht="47" customHeight="1">
+        <v>102.0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="24" customHeight="1">
       <c r="A112" t="s">
         <v>153</v>
       </c>
@@ -3303,13 +3398,29 @@
         <v>1</v>
       </c>
       <c r="C112" t="s">
-        <v>108</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="24" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="D112" s="5">
+        <v>102</v>
+      </c>
+      <c r="E112" s="2">
+        <f>IF(AND(ISNUMBER(F112),ISNUMBER('Reference data'!$B$3)),F112*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.00010726524</v>
+      </c>
+      <c r="F112" s="2">
+        <f>IF(D112=0,0,IF(ISNUMBER('Reference data'!E17),D112*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.0001224</v>
+      </c>
+      <c r="G112" s="5">
+        <f>IF(ISNUMBER(E112),ROUND(E112*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+      <c r="H112" s="5">
+        <f>IF(ISNUMBER(F112),ROUND(F112*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="409" customHeight="1">
       <c r="A113" t="s">
         <v>153</v>
       </c>
@@ -3317,10 +3428,13 @@
         <v>1</v>
       </c>
       <c r="C113" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="24" customHeight="1">
+        <v>108</v>
+      </c>
+      <c r="I113" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="24" customHeight="1">
       <c r="A114" t="s">
         <v>153</v>
       </c>
@@ -3328,41 +3442,644 @@
         <v>1</v>
       </c>
       <c r="C114" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="24" customHeight="1">
+      <c r="A115" t="s">
+        <v>153</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="115" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A115" s="4" t="s">
+    <row r="116" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A116" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B115" s="4">
-        <v>1</v>
-      </c>
-      <c r="C115" s="4" t="s">
+      <c r="B116" s="4">
+        <v>1</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E115" s="2">
-        <f>IF(COUNT('Turns'!E105,'Turns'!E106,'Turns'!E108,'Turns'!E111)=4,SUM('Turns'!E105,'Turns'!E106,'Turns'!E108,'Turns'!E111),"Unknown")</f>
-        <v>8.53439571e-05</v>
-      </c>
-      <c r="F115" s="2">
-        <f>IF(COUNT('Turns'!F105,'Turns'!F106,'Turns'!F108,'Turns'!F111)=4,SUM('Turns'!F105,'Turns'!F106,'Turns'!F108,'Turns'!F111),"Unknown")</f>
-        <v>9.783e-05</v>
-      </c>
-      <c r="G115" s="5">
-        <f>IF(ISNUMBER(E115),ROUND(E115*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="H115" s="5">
-        <f>IF(ISNUMBER(F115),ROUND(F115*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-      <c r="K115" s="4" t="s">
+      <c r="E116" s="2">
+        <f>IF(COUNT('Turns'!E105,'Turns'!E106,'Turns'!E108,'Turns'!E111,'Turns'!E112)=5,SUM('Turns'!E105,'Turns'!E106,'Turns'!E108,'Turns'!E111,'Turns'!E112),"Unknown")</f>
+        <v>0.001081310738</v>
+      </c>
+      <c r="F116" s="2">
+        <f>IF(COUNT('Turns'!F105,'Turns'!F106,'Turns'!F108,'Turns'!F111,'Turns'!F112)=5,SUM('Turns'!F105,'Turns'!F106,'Turns'!F108,'Turns'!F111,'Turns'!F112),"Unknown")</f>
+        <v>0.00123388</v>
+      </c>
+      <c r="G116" s="5">
+        <f>IF(ISNUMBER(E116),ROUND(E116*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>108.0</v>
+      </c>
+      <c r="H116" s="5">
+        <f>IF(ISNUMBER(F116),ROUND(F116*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>123.0</v>
+      </c>
+      <c r="K116" s="4" t="s">
         <v>111</v>
       </c>
     </row>
+    <row r="117" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B117" s="4">
+        <v>1</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M117" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="60" customHeight="1">
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
+        <v>114</v>
+      </c>
+      <c r="I118" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="24" customHeight="1">
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119" t="s">
+        <v>116</v>
+      </c>
+      <c r="I119" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A120" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B120" s="4">
+        <v>1</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D120" s="4">
+        <v>3823</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M120" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" ht="24" customHeight="1">
+      <c r="A121" t="s">
+        <v>158</v>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121" t="s">
+        <v>123</v>
+      </c>
+      <c r="D121" s="5">
+        <v>2842</v>
+      </c>
+      <c r="E121" s="2">
+        <f>IF(AND(ISNUMBER(F121),ISNUMBER('Reference data'!$B$3)),F121*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.9811734e-05</v>
+      </c>
+      <c r="F121" s="2">
+        <f>IF(D121=0,0,IF(ISNUMBER('Reference data'!C17),D121*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>5.684e-05</v>
+      </c>
+      <c r="G121" s="5">
+        <f>IF(ISNUMBER(E121),ROUND(E121*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H121" s="5">
+        <f>IF(ISNUMBER(F121),ROUND(F121*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" ht="24" customHeight="1">
+      <c r="A122" t="s">
+        <v>158</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122" t="s">
+        <v>97</v>
+      </c>
+      <c r="D122" s="5">
+        <v>3</v>
+      </c>
+      <c r="E122" s="2">
+        <f>IF(AND(ISNUMBER(F122),ISNUMBER('Reference data'!$B$3)),F122*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F122" s="2">
+        <f>IF(D122=0,0,IF(ISNUMBER('Reference data'!B17),D122*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G122" s="5">
+        <f>IF(ISNUMBER(E122),ROUND(E122*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H122" s="5">
+        <f>IF(ISNUMBER(F122),ROUND(F122*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" ht="24" customHeight="1">
+      <c r="A123" t="s">
+        <v>158</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123" t="s">
+        <v>124</v>
+      </c>
+      <c r="I123" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" ht="24" customHeight="1">
+      <c r="A124" t="s">
+        <v>158</v>
+      </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124" t="s">
+        <v>103</v>
+      </c>
+      <c r="D124" s="5">
+        <v>978</v>
+      </c>
+      <c r="E124" s="2">
+        <f>IF(AND(ISNUMBER(F124),ISNUMBER('Reference data'!$B$3)),F124*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000214267575</v>
+      </c>
+      <c r="F124" s="2">
+        <f>IF(D124=0,0,IF(ISNUMBER('Reference data'!D17),D124*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>0.0002445</v>
+      </c>
+      <c r="G124" s="5">
+        <f>IF(ISNUMBER(E124),ROUND(E124*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>21.0</v>
+      </c>
+      <c r="H124" s="5">
+        <f>IF(ISNUMBER(F124),ROUND(F124*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" ht="24" customHeight="1">
+      <c r="A125" t="s">
+        <v>158</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A126" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B126" s="4">
+        <v>1</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D126" s="4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" ht="24" customHeight="1">
+      <c r="A127" t="s">
+        <v>158</v>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127" t="s">
+        <v>106</v>
+      </c>
+      <c r="D127" s="5">
+        <v>7</v>
+      </c>
+      <c r="E127" s="2">
+        <f>IF(AND(ISNUMBER(F127),ISNUMBER('Reference data'!$B$3)),F127*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.36134e-06</v>
+      </c>
+      <c r="F127" s="2">
+        <f>IF(D127=0,0,IF(ISNUMBER('Reference data'!F17),D127*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>8.4e-06</v>
+      </c>
+      <c r="G127" s="5">
+        <f>IF(ISNUMBER(E127),ROUND(E127*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H127" s="5">
+        <f>IF(ISNUMBER(F127),ROUND(F127*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" ht="24" customHeight="1">
+      <c r="A128" t="s">
+        <v>158</v>
+      </c>
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128" t="s">
+        <v>107</v>
+      </c>
+      <c r="D128" s="5">
+        <v>31</v>
+      </c>
+      <c r="E128" s="2">
+        <f>IF(AND(ISNUMBER(F128),ISNUMBER('Reference data'!$B$3)),F128*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.260022e-05</v>
+      </c>
+      <c r="F128" s="2">
+        <f>IF(D128=0,0,IF(ISNUMBER('Reference data'!E17),D128*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>3.72e-05</v>
+      </c>
+      <c r="G128" s="5">
+        <f>IF(ISNUMBER(E128),ROUND(E128*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H128" s="5">
+        <f>IF(ISNUMBER(F128),ROUND(F128*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="281" customHeight="1">
+      <c r="A129" t="s">
+        <v>158</v>
+      </c>
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129" t="s">
+        <v>108</v>
+      </c>
+      <c r="I129" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="24" customHeight="1">
+      <c r="A130" t="s">
+        <v>158</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="24" customHeight="1">
+      <c r="A131" t="s">
+        <v>158</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A132" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B132" s="4">
+        <v>1</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E132" s="2">
+        <f>IF(COUNT('Turns'!E121,'Turns'!E122,'Turns'!E124,'Turns'!E127,'Turns'!E128)=5,SUM('Turns'!E121,'Turns'!E122,'Turns'!E124,'Turns'!E127,'Turns'!E128),"Unknown")</f>
+        <v>0.000304566679</v>
+      </c>
+      <c r="F132" s="2">
+        <f>IF(COUNT('Turns'!F121,'Turns'!F122,'Turns'!F124,'Turns'!F127,'Turns'!F128)=5,SUM('Turns'!F121,'Turns'!F122,'Turns'!F124,'Turns'!F127,'Turns'!F128),"Unknown")</f>
+        <v>0.00034754</v>
+      </c>
+      <c r="G132" s="5">
+        <f>IF(ISNUMBER(E132),ROUND(E132*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>30.0</v>
+      </c>
+      <c r="H132" s="5">
+        <f>IF(ISNUMBER(F132),ROUND(F132*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>35.0</v>
+      </c>
+      <c r="K132" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B133" s="4">
+        <v>1</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K133" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M133" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" ht="24" customHeight="1">
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
+        <v>114</v>
+      </c>
+      <c r="I134" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" ht="320" customHeight="1">
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135" t="s">
+        <v>116</v>
+      </c>
+      <c r="I135" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A136" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B136" s="4">
+        <v>1</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D136" s="4">
+        <v>3971</v>
+      </c>
+      <c r="J136" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M136" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" ht="24" customHeight="1">
+      <c r="A137" t="s">
+        <v>163</v>
+      </c>
+      <c r="B137">
+        <v>1</v>
+      </c>
+      <c r="C137" t="s">
+        <v>123</v>
+      </c>
+      <c r="D137" s="5">
+        <v>3820</v>
+      </c>
+      <c r="E137" s="2">
+        <f>IF(AND(ISNUMBER(F137),ISNUMBER('Reference data'!$B$3)),F137*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.695314e-05</v>
+      </c>
+      <c r="F137" s="2">
+        <f>IF(D137=0,0,IF(ISNUMBER('Reference data'!C17),D137*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>7.64e-05</v>
+      </c>
+      <c r="G137" s="5">
+        <f>IF(ISNUMBER(E137),ROUND(E137*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="H137" s="5">
+        <f>IF(ISNUMBER(F137),ROUND(F137*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" ht="24" customHeight="1">
+      <c r="A138" t="s">
+        <v>163</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138" t="s">
+        <v>97</v>
+      </c>
+      <c r="D138" s="5">
+        <v>3</v>
+      </c>
+      <c r="E138" s="2">
+        <f>IF(AND(ISNUMBER(F138),ISNUMBER('Reference data'!$B$3)),F138*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F138" s="2">
+        <f>IF(D138=0,0,IF(ISNUMBER('Reference data'!B17),D138*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G138" s="5">
+        <f>IF(ISNUMBER(E138),ROUND(E138*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H138" s="5">
+        <f>IF(ISNUMBER(F138),ROUND(F138*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" ht="320" customHeight="1">
+      <c r="A139" t="s">
+        <v>163</v>
+      </c>
+      <c r="B139">
+        <v>1</v>
+      </c>
+      <c r="C139" t="s">
+        <v>124</v>
+      </c>
+      <c r="I139" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" ht="24" customHeight="1">
+      <c r="A140" t="s">
+        <v>163</v>
+      </c>
+      <c r="B140">
+        <v>1</v>
+      </c>
+      <c r="C140" t="s">
+        <v>103</v>
+      </c>
+      <c r="D140" s="5">
+        <v>148</v>
+      </c>
+      <c r="E140" s="2">
+        <f>IF(AND(ISNUMBER(F140),ISNUMBER('Reference data'!$B$3)),F140*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.242495e-05</v>
+      </c>
+      <c r="F140" s="2">
+        <f>IF(D140=0,0,IF(ISNUMBER('Reference data'!D17),D140*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>3.7e-05</v>
+      </c>
+      <c r="G140" s="5">
+        <f>IF(ISNUMBER(E140),ROUND(E140*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H140" s="5">
+        <f>IF(ISNUMBER(F140),ROUND(F140*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" ht="24" customHeight="1">
+      <c r="A141" t="s">
+        <v>163</v>
+      </c>
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="C141" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A142" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B142" s="4">
+        <v>1</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D142" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" ht="24" customHeight="1">
+      <c r="A143" t="s">
+        <v>163</v>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143" t="s">
+        <v>107</v>
+      </c>
+      <c r="D143" s="5">
+        <v>16</v>
+      </c>
+      <c r="E143" s="2">
+        <f>IF(AND(ISNUMBER(F143),ISNUMBER('Reference data'!$B$3)),F143*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.682592e-05</v>
+      </c>
+      <c r="F143" s="2">
+        <f>IF(D143=0,0,IF(ISNUMBER('Reference data'!E17),D143*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>1.92e-05</v>
+      </c>
+      <c r="G143" s="5">
+        <f>IF(ISNUMBER(E143),ROUND(E143*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H143" s="5">
+        <f>IF(ISNUMBER(F143),ROUND(F143*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="47" customHeight="1">
+      <c r="A144" t="s">
+        <v>163</v>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="C144" t="s">
+        <v>108</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="24" customHeight="1">
+      <c r="A145" t="s">
+        <v>163</v>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+      <c r="C145" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="24" customHeight="1">
+      <c r="A146" t="s">
+        <v>163</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A147" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B147" s="4">
+        <v>1</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E147" s="2">
+        <f>IF(COUNT('Turns'!E137,'Turns'!E138,'Turns'!E140,'Turns'!E143)=4,SUM('Turns'!E137,'Turns'!E138,'Turns'!E140,'Turns'!E143),"Unknown")</f>
+        <v>0.00011672982</v>
+      </c>
+      <c r="F147" s="2">
+        <f>IF(COUNT('Turns'!F137,'Turns'!F138,'Turns'!F140,'Turns'!F143)=4,SUM('Turns'!F137,'Turns'!F138,'Turns'!F140,'Turns'!F143),"Unknown")</f>
+        <v>0.0001332</v>
+      </c>
+      <c r="G147" s="5">
+        <f>IF(ISNUMBER(E147),ROUND(E147*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="H147" s="5">
+        <f>IF(ISNUMBER(F147),ROUND(F147*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+      <c r="K147" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE115">
+  <conditionalFormatting sqref="A2:AE147">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -3376,7 +4093,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE50"/>
+  <dimension ref="A1:AE64"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -3483,13 +4200,13 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
@@ -3498,7 +4215,7 @@
         <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
@@ -3509,7 +4226,7 @@
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E26)=2,SUM('Turns'!E5,'Turns'!E26),"Unknown")</f>
-        <v>0.000155456334</v>
+        <v>0.00015616557</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F26)=2,SUM('Turns'!F5,'Turns'!F26),"Unknown")</f>
@@ -3529,72 +4246,72 @@
       </c>
       <c r="P2" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>1085.0</v>
+        <v>1107.0</v>
       </c>
       <c r="Q2" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.0002366303625</v>
+        <v>0.0002425298625</v>
       </c>
       <c r="R2" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.00027125</v>
+        <v>0.00027675</v>
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D13,'Turns'!D32)=2,SUM('Turns'!D13,'Turns'!D32),"Unknown")</f>
-        <v>232.0</v>
+        <v>148.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E13,'Turns'!E32)=2,SUM('Turns'!E13,'Turns'!E32),"Unknown")</f>
-        <v>0.000242867808</v>
+        <v>0.00015563976</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F13,'Turns'!F32)=2,SUM('Turns'!F13,'Turns'!F32),"Unknown")</f>
-        <v>0.0002784</v>
+        <v>0.0001776</v>
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D12,'Turns'!D31)=2,SUM('Turns'!D12,'Turns'!D31),"Unknown")</f>
-        <v>294.0</v>
+        <v>388.0</v>
       </c>
       <c r="W2" s="2">
         <f>IF(COUNT('Turns'!E12,'Turns'!E31)=2,SUM('Turns'!E12,'Turns'!E31),"Unknown")</f>
-        <v>0.000307772136</v>
+        <v>0.00040802856</v>
       </c>
       <c r="X2" s="2">
         <f>IF(COUNT('Turns'!F12,'Turns'!F31)=2,SUM('Turns'!F12,'Turns'!F31),"Unknown")</f>
-        <v>0.0003528</v>
+        <v>0.0004656</v>
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E36)=2,SUM('Turns'!E17,'Turns'!E36),"Unknown")</f>
-        <v>0.0009427266405</v>
+        <v>0.0009623637525</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F36)=2,SUM('Turns'!F17,'Turns'!F36),"Unknown")</f>
-        <v>0.00108065</v>
+        <v>0.00109815</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>108.0</v>
+        <v>110.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>10557.352</v>
+        <v>7489.244</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
@@ -3603,30 +4320,30 @@
         <v>111</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>1.358</v>
+        <v>0.599</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
@@ -3635,10 +4352,10 @@
         <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H4" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
@@ -3649,7 +4366,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>0.000154932912</v>
+        <v>0.00015563976</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -3679,7 +4396,7 @@
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>7.5372768e-05</v>
+        <v>7.571664e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
@@ -3687,23 +4404,23 @@
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>27.0</v>
+        <v>23.0</v>
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>2.418726e-05</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>3.24e-05</v>
+        <v>2.76e-05</v>
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000258570468</v>
+        <v>0.00025554366</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0002964</v>
+        <v>0.0002916</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3711,24 +4428,24 @@
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>2595.144</v>
+        <v>1877.927</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>95</v>
@@ -3740,13 +4457,13 @@
         <v>888</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H5" t="s">
         <v>96</v>
       </c>
       <c r="I5" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="J5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -3754,7 +4471,7 @@
       </c>
       <c r="K5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>0.000154932912</v>
+        <v>0.00015563976</v>
       </c>
       <c r="L5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -3784,7 +4501,7 @@
       </c>
       <c r="T5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>7.5372768e-05</v>
+        <v>7.571664e-05</v>
       </c>
       <c r="U5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
@@ -3792,23 +4509,23 @@
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>27.0</v>
+        <v>23.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>2.418726e-05</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>3.24e-05</v>
+        <v>2.76e-05</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000258570468</v>
+        <v>0.00025554366</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0002964</v>
+        <v>0.0002916</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3816,27 +4533,27 @@
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>2590.657</v>
+        <v>1788.199</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
@@ -3845,30 +4562,30 @@
         <v>111</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H6" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>0.482</v>
+        <v>0.404</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
@@ -3877,30 +4594,30 @@
         <v>111</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H7" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
       </c>
       <c r="AD7" s="1">
-        <v>5.189</v>
+        <v>3.702</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>47</v>
@@ -3909,30 +4626,30 @@
         <v>111</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="H8" t="s">
         <v>113</v>
       </c>
       <c r="I8" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="AD8" s="1">
-        <v>2.67</v>
+        <v>1.184</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
@@ -3941,30 +4658,30 @@
         <v>111</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H9" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
       </c>
       <c r="AD9" s="1">
-        <v>3.745</v>
+        <v>3.477</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
@@ -3973,30 +4690,30 @@
         <v>111</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="H10" t="s">
         <v>118</v>
       </c>
       <c r="I10" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AD10" s="1">
-        <v>1.107</v>
+        <v>1.001</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
@@ -4005,30 +4722,30 @@
         <v>111</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H11" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.308</v>
+        <v>0.275</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
@@ -4037,10 +4754,10 @@
         <v>111</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -4051,7 +4768,7 @@
       </c>
       <c r="K12" s="2">
         <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L12" s="2">
         <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
@@ -4071,72 +4788,72 @@
       </c>
       <c r="P12" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>1085.0</v>
+        <v>1107.0</v>
       </c>
       <c r="Q12" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.0002366303625</v>
+        <v>0.0002425298625</v>
       </c>
       <c r="R12" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.00027125</v>
+        <v>0.00027675</v>
       </c>
       <c r="S12" s="2">
         <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>160.0</v>
+        <v>76.0</v>
       </c>
       <c r="T12" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.00016749504</v>
+        <v>7.992312e-05</v>
       </c>
       <c r="U12" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.000192</v>
+        <v>9.12e-05</v>
       </c>
       <c r="V12" s="2">
         <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>267.0</v>
+        <v>365.0</v>
       </c>
       <c r="W12" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.000279507348</v>
+        <v>0.0003838413</v>
       </c>
       <c r="X12" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0003204</v>
+        <v>0.000438</v>
       </c>
       <c r="Y12" s="2">
         <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.0006841561725</v>
+        <v>0.0007068200925</v>
       </c>
       <c r="Z12" s="2">
         <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.00078425</v>
+        <v>0.00080655</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>78.0</v>
+        <v>81.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>7938.058</v>
+        <v>5598.299</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>95</v>
@@ -4145,16 +4862,16 @@
         <v>111</v>
       </c>
       <c r="F13" s="1">
-        <v>1088</v>
+        <v>1110</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H13" t="s">
         <v>122</v>
       </c>
       <c r="I13" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="J13" s="2">
         <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
@@ -4162,7 +4879,7 @@
       </c>
       <c r="K13" s="2">
         <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L13" s="2">
         <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
@@ -4182,107 +4899,107 @@
       </c>
       <c r="P13" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>1085.0</v>
+        <v>1107.0</v>
       </c>
       <c r="Q13" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.0002366303625</v>
+        <v>0.0002425298625</v>
       </c>
       <c r="R13" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.00027125</v>
+        <v>0.00027675</v>
       </c>
       <c r="S13" s="2">
         <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>160.0</v>
+        <v>76.0</v>
       </c>
       <c r="T13" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.00016749504</v>
+        <v>7.992312e-05</v>
       </c>
       <c r="U13" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.000192</v>
+        <v>9.12e-05</v>
       </c>
       <c r="V13" s="2">
         <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>267.0</v>
+        <v>365.0</v>
       </c>
       <c r="W13" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.000279507348</v>
+        <v>0.0003838413</v>
       </c>
       <c r="X13" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.0003204</v>
+        <v>0.000438</v>
       </c>
       <c r="Y13" s="2">
         <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.0006841561725</v>
+        <v>0.0007068200925</v>
       </c>
       <c r="Z13" s="2">
         <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.00078425</v>
+        <v>0.00080655</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>78.0</v>
+        <v>81.0</v>
       </c>
       <c r="AC13" s="1" t="s">
         <v>121</v>
       </c>
       <c r="AD13" s="1">
-        <v>7932.653</v>
+        <v>5596.845</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H14" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
       </c>
       <c r="AD14" s="1">
-        <v>0.577</v>
+        <v>0.31</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
@@ -4291,103 +5008,103 @@
         <v>111</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H15" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="J15" s="2">
-        <f>IF(COUNT('Turns'!D42,'Turns'!D58)=2,SUM('Turns'!D42,'Turns'!D58),"Unknown")</f>
-        <v>6.0</v>
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>3.0</v>
       </c>
       <c r="K15" s="2">
-        <f>IF(COUNT('Turns'!E42,'Turns'!E58)=2,SUM('Turns'!E42,'Turns'!E58),"Unknown")</f>
-        <v>1.046844e-06</v>
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>5.2581e-07</v>
       </c>
       <c r="L15" s="2">
-        <f>IF(COUNT('Turns'!F42,'Turns'!F58)=2,SUM('Turns'!F42,'Turns'!F58),"Unknown")</f>
-        <v>1.2e-06</v>
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>6e-07</v>
       </c>
       <c r="M15" s="2">
-        <f>IF(COUNT('Turns'!D41,'Turns'!D57)=2,SUM('Turns'!D41,'Turns'!D57),"Unknown")</f>
-        <v>2623.0</v>
+        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
+        <v>1107.0</v>
       </c>
       <c r="N15" s="2">
-        <f>IF(COUNT('Turns'!E41,'Turns'!E57)=2,SUM('Turns'!E41,'Turns'!E57),"Unknown")</f>
-        <v>4.57645302e-05</v>
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
+        <v>1.9402389e-05</v>
       </c>
       <c r="O15" s="2">
-        <f>IF(COUNT('Turns'!F41,'Turns'!F57)=2,SUM('Turns'!F41,'Turns'!F57),"Unknown")</f>
-        <v>5.246e-05</v>
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <v>2.214e-05</v>
       </c>
       <c r="P15" s="2">
-        <f>IF(COUNT('Turns'!D44,'Turns'!D60)=2,SUM('Turns'!D44,'Turns'!D60),"Unknown")</f>
-        <v>589.0</v>
+        <f>IF(COUNT('Turns'!D44)=1,SUM('Turns'!D44),"Unknown")</f>
+        <v>496.0</v>
       </c>
       <c r="Q15" s="2">
-        <f>IF(COUNT('Turns'!E44,'Turns'!E60)=2,SUM('Turns'!E44,'Turns'!E60),"Unknown")</f>
-        <v>0.0001284564825</v>
+        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
+        <v>0.0001086674</v>
       </c>
       <c r="R15" s="2">
-        <f>IF(COUNT('Turns'!F44,'Turns'!F60)=2,SUM('Turns'!F44,'Turns'!F60),"Unknown")</f>
-        <v>0.00014725</v>
+        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
+        <v>0.000124</v>
       </c>
       <c r="S15" s="2">
-        <f>IF(COUNT('Turns'!D48,'Turns'!D64)=2,SUM('Turns'!D48,'Turns'!D64),"Unknown")</f>
-        <v>108.0</v>
+        <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
+        <v>110.0</v>
       </c>
       <c r="T15" s="2">
-        <f>IF(COUNT('Turns'!E48,'Turns'!E64)=2,SUM('Turns'!E48,'Turns'!E64),"Unknown")</f>
-        <v>0.000113059152</v>
+        <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
+        <v>0.0001156782</v>
       </c>
       <c r="U15" s="2">
-        <f>IF(COUNT('Turns'!F48,'Turns'!F64)=2,SUM('Turns'!F48,'Turns'!F64),"Unknown")</f>
-        <v>0.0001296</v>
+        <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
+        <v>0.000132</v>
       </c>
       <c r="V15" s="2">
-        <f>IF(COUNT('Turns'!D47,'Turns'!D63)=2,SUM('Turns'!D47,'Turns'!D63),"Unknown")</f>
-        <v>219.0</v>
+        <f>IF(COUNT('Turns'!D47)=1,SUM('Turns'!D47),"Unknown")</f>
+        <v>210.0</v>
       </c>
       <c r="W15" s="2">
-        <f>IF(COUNT('Turns'!E47,'Turns'!E63)=2,SUM('Turns'!E47,'Turns'!E63),"Unknown")</f>
-        <v>0.000229258836</v>
+        <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
+        <v>0.0002208402</v>
       </c>
       <c r="X15" s="2">
-        <f>IF(COUNT('Turns'!F47,'Turns'!F63)=2,SUM('Turns'!F47,'Turns'!F63),"Unknown")</f>
-        <v>0.0002628</v>
+        <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
+        <v>0.000252</v>
       </c>
       <c r="Y15" s="2">
-        <f>IF(COUNT('Turns'!E52,'Turns'!E68)=2,SUM('Turns'!E52,'Turns'!E68),"Unknown")</f>
-        <v>0.0005175858447</v>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>0.000465113999</v>
       </c>
       <c r="Z15" s="2">
-        <f>IF(COUNT('Turns'!F52,'Turns'!F68)=2,SUM('Turns'!F52,'Turns'!F68),"Unknown")</f>
-        <v>0.00059331</v>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <v>0.00053074</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>47.0</v>
       </c>
       <c r="AB15" s="5">
         <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>53.0</v>
       </c>
       <c r="AD15" s="1">
-        <v>7610.67</v>
+        <v>5797.066</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
@@ -4396,30 +5113,30 @@
         <v>111</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H16" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="I16" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="AD16" s="1">
-        <v>0.704</v>
+        <v>0.359</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>47</v>
@@ -4428,62 +5145,62 @@
         <v>111</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H17" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="I17" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="AD17" s="1">
-        <v>4.354</v>
+        <v>2.636</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="54" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="H18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I18" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="AD18" s="1">
-        <v>1.554</v>
+        <v>0.659</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="54" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>47</v>
@@ -4492,30 +5209,30 @@
         <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H19" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="I19" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.673</v>
+        <v>0.276</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="54" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>47</v>
@@ -4524,13 +5241,13 @@
         <v>111</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="I20" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="J20" s="2">
         <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
@@ -4538,7 +5255,7 @@
       </c>
       <c r="K20" s="2">
         <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L20" s="2">
         <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
@@ -4546,84 +5263,84 @@
       </c>
       <c r="M20" s="2">
         <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>1085.0</v>
+        <v>1107.0</v>
       </c>
       <c r="N20" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.8930429e-05</v>
+        <v>1.9402389e-05</v>
       </c>
       <c r="O20" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>2.17e-05</v>
+        <v>2.214e-05</v>
       </c>
       <c r="P20" s="2">
         <f>IF(COUNT('Turns'!D44)=1,SUM('Turns'!D44),"Unknown")</f>
-        <v>453.0</v>
+        <v>496.0</v>
       </c>
       <c r="Q20" s="2">
         <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>9.87959025e-05</v>
+        <v>0.0001086674</v>
       </c>
       <c r="R20" s="2">
         <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>0.00011325</v>
+        <v>0.000124</v>
       </c>
       <c r="S20" s="2">
         <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
-        <v>31.0</v>
+        <v>110.0</v>
       </c>
       <c r="T20" s="2">
         <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
-        <v>3.2452164e-05</v>
+        <v>0.0001156782</v>
       </c>
       <c r="U20" s="2">
         <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
-        <v>3.72e-05</v>
+        <v>0.000132</v>
       </c>
       <c r="V20" s="2">
         <f>IF(COUNT('Turns'!D47)=1,SUM('Turns'!D47),"Unknown")</f>
-        <v>28.0</v>
+        <v>210.0</v>
       </c>
       <c r="W20" s="2">
         <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>0.0002208402</v>
       </c>
       <c r="X20" s="2">
         <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>3.36e-05</v>
+        <v>0.000252</v>
       </c>
       <c r="Y20" s="2">
         <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>0.0001800135495</v>
+        <v>0.000465113999</v>
       </c>
       <c r="Z20" s="2">
         <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>0.00020635</v>
+        <v>0.00053074</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>47.0</v>
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>53.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>1814.838</v>
+        <v>5787.399</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="54" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>95</v>
@@ -4632,16 +5349,16 @@
         <v>111</v>
       </c>
       <c r="F21" s="1">
-        <v>1541</v>
+        <v>1606</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I21" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="J21" s="2">
         <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
@@ -4649,7 +5366,7 @@
       </c>
       <c r="K21" s="2">
         <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L21" s="2">
         <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
@@ -4657,119 +5374,119 @@
       </c>
       <c r="M21" s="2">
         <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>1085.0</v>
+        <v>1107.0</v>
       </c>
       <c r="N21" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.8930429e-05</v>
+        <v>1.9402389e-05</v>
       </c>
       <c r="O21" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>2.17e-05</v>
+        <v>2.214e-05</v>
       </c>
       <c r="P21" s="2">
         <f>IF(COUNT('Turns'!D44)=1,SUM('Turns'!D44),"Unknown")</f>
-        <v>453.0</v>
+        <v>496.0</v>
       </c>
       <c r="Q21" s="2">
         <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>9.87959025e-05</v>
+        <v>0.0001086674</v>
       </c>
       <c r="R21" s="2">
         <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>0.00011325</v>
+        <v>0.000124</v>
       </c>
       <c r="S21" s="2">
         <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
-        <v>31.0</v>
+        <v>110.0</v>
       </c>
       <c r="T21" s="2">
         <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
-        <v>3.2452164e-05</v>
+        <v>0.0001156782</v>
       </c>
       <c r="U21" s="2">
         <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
-        <v>3.72e-05</v>
+        <v>0.000132</v>
       </c>
       <c r="V21" s="2">
         <f>IF(COUNT('Turns'!D47)=1,SUM('Turns'!D47),"Unknown")</f>
-        <v>28.0</v>
+        <v>210.0</v>
       </c>
       <c r="W21" s="2">
         <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>0.0002208402</v>
       </c>
       <c r="X21" s="2">
         <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>3.36e-05</v>
+        <v>0.000252</v>
       </c>
       <c r="Y21" s="2">
         <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>0.0001800135495</v>
+        <v>0.000465113999</v>
       </c>
       <c r="Z21" s="2">
         <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>0.00020635</v>
+        <v>0.00053074</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>47.0</v>
       </c>
       <c r="AB21" s="5">
         <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>53.0</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AD21" s="1">
-        <v>1812.529</v>
+        <v>5784.355</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:31" ht="54" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H22" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="I22" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="AD22" s="1">
-        <v>0.36</v>
+        <v>0.657</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="54" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>47</v>
@@ -4778,30 +5495,103 @@
         <v>111</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="H23" t="s">
-        <v>193</v>
-      </c>
-      <c r="I23" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="J23" s="2">
+        <f>IF(COUNT('Turns'!D58,'Turns'!D74)=2,SUM('Turns'!D58,'Turns'!D74),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="K23" s="2">
+        <f>IF(COUNT('Turns'!E58,'Turns'!E74)=2,SUM('Turns'!E58,'Turns'!E74),"Unknown")</f>
+        <v>1.05162e-06</v>
+      </c>
+      <c r="L23" s="2">
+        <f>IF(COUNT('Turns'!F58,'Turns'!F74)=2,SUM('Turns'!F58,'Turns'!F74),"Unknown")</f>
+        <v>1.2e-06</v>
+      </c>
+      <c r="M23" s="2">
+        <f>IF(COUNT('Turns'!D57,'Turns'!D73)=2,SUM('Turns'!D57,'Turns'!D73),"Unknown")</f>
+        <v>3552.0</v>
+      </c>
+      <c r="N23" s="2">
+        <f>IF(COUNT('Turns'!E57,'Turns'!E73)=2,SUM('Turns'!E57,'Turns'!E73),"Unknown")</f>
+        <v>6.2255904e-05</v>
+      </c>
+      <c r="O23" s="2">
+        <f>IF(COUNT('Turns'!F57,'Turns'!F73)=2,SUM('Turns'!F57,'Turns'!F73),"Unknown")</f>
+        <v>7.104e-05</v>
+      </c>
+      <c r="P23" s="2">
+        <f>IF(COUNT('Turns'!D60,'Turns'!D76)=2,SUM('Turns'!D60,'Turns'!D76),"Unknown")</f>
+        <v>487.0</v>
+      </c>
+      <c r="Q23" s="2">
+        <f>IF(COUNT('Turns'!E60,'Turns'!E76)=2,SUM('Turns'!E60,'Turns'!E76),"Unknown")</f>
+        <v>0.0001066956125</v>
+      </c>
+      <c r="R23" s="2">
+        <f>IF(COUNT('Turns'!F60,'Turns'!F76)=2,SUM('Turns'!F60,'Turns'!F76),"Unknown")</f>
+        <v>0.00012175</v>
+      </c>
+      <c r="S23" s="2">
+        <f>IF(COUNT('Turns'!D64,'Turns'!D80)=2,SUM('Turns'!D64,'Turns'!D80),"Unknown")</f>
+        <v>142.0</v>
+      </c>
+      <c r="T23" s="2">
+        <f>IF(COUNT('Turns'!E64,'Turns'!E80)=2,SUM('Turns'!E64,'Turns'!E80),"Unknown")</f>
+        <v>0.00014933004</v>
+      </c>
+      <c r="U23" s="2">
+        <f>IF(COUNT('Turns'!F64,'Turns'!F80)=2,SUM('Turns'!F64,'Turns'!F80),"Unknown")</f>
+        <v>0.0001704</v>
+      </c>
+      <c r="V23" s="2">
+        <f>IF(COUNT('Turns'!D63,'Turns'!D79)=2,SUM('Turns'!D63,'Turns'!D79),"Unknown")</f>
+        <v>474.0</v>
+      </c>
+      <c r="W23" s="2">
+        <f>IF(COUNT('Turns'!E63,'Turns'!E79)=2,SUM('Turns'!E63,'Turns'!E79),"Unknown")</f>
+        <v>0.00049846788</v>
+      </c>
+      <c r="X23" s="2">
+        <f>IF(COUNT('Turns'!F63,'Turns'!F79)=2,SUM('Turns'!F63,'Turns'!F79),"Unknown")</f>
+        <v>0.0005688</v>
+      </c>
+      <c r="Y23" s="2">
+        <f>IF(COUNT('Turns'!E68,'Turns'!E84)=2,SUM('Turns'!E68,'Turns'!E84),"Unknown")</f>
+        <v>0.0008178010565</v>
+      </c>
+      <c r="Z23" s="2">
+        <f>IF(COUNT('Turns'!F68,'Turns'!F84)=2,SUM('Turns'!F68,'Turns'!F84),"Unknown")</f>
+        <v>0.00093319</v>
+      </c>
+      <c r="AA23" s="5">
+        <f>IF(ISNUMBER(Y23),ROUND(Y23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>82.0</v>
+      </c>
+      <c r="AB23" s="5">
+        <f>IF(ISNUMBER(Z23),ROUND(Z23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>93.0</v>
       </c>
       <c r="AD23" s="1">
-        <v>4.091</v>
+        <v>8673.907999999999</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="54" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>47</v>
@@ -4810,30 +5600,30 @@
         <v>111</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H24" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="I24" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="AD24" s="1">
-        <v>1.111</v>
+        <v>0.573</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="54" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>47</v>
@@ -4842,30 +5632,30 @@
         <v>111</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="H25" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="I25" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="AD25" s="1">
-        <v>0.32</v>
+        <v>4.014</v>
       </c>
       <c r="AE25" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="54" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="B26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>47</v>
@@ -4874,357 +5664,284 @@
         <v>111</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="H26" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="I26" t="s">
-        <v>185</v>
-      </c>
-      <c r="J26" s="2">
+        <v>205</v>
+      </c>
+      <c r="AD26" s="1">
+        <v>1.943</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" ht="54" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H27" t="s">
+        <v>206</v>
+      </c>
+      <c r="I27" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD27" s="1">
+        <v>0.407</v>
+      </c>
+      <c r="AE27" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" ht="54" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" t="s">
+        <v>207</v>
+      </c>
+      <c r="I28" t="s">
+        <v>203</v>
+      </c>
+      <c r="J28" s="2">
         <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
         <v>3.0</v>
       </c>
-      <c r="K26" s="2">
+      <c r="K28" s="2">
         <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L26" s="2">
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L28" s="2">
         <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
         <v>6e-07</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M28" s="2">
         <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>1538.0</v>
-      </c>
-      <c r="N26" s="2">
+        <v>1603.0</v>
+      </c>
+      <c r="N28" s="2">
         <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>2.68341012e-05</v>
-      </c>
-      <c r="O26" s="2">
+        <v>2.8095781e-05</v>
+      </c>
+      <c r="O28" s="2">
         <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>3.076e-05</v>
-      </c>
-      <c r="P26" s="2">
+        <v>3.206e-05</v>
+      </c>
+      <c r="P28" s="2">
         <f>IF(COUNT('Turns'!D60)=1,SUM('Turns'!D60),"Unknown")</f>
-        <v>136.0</v>
-      </c>
-      <c r="Q26" s="2">
+        <v>346.0</v>
+      </c>
+      <c r="Q28" s="2">
         <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>2.966058e-05</v>
-      </c>
-      <c r="R26" s="2">
+        <v>7.5804275e-05</v>
+      </c>
+      <c r="R28" s="2">
         <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>3.4e-05</v>
-      </c>
-      <c r="S26" s="2">
+        <v>8.65e-05</v>
+      </c>
+      <c r="S28" s="2">
         <f>IF(COUNT('Turns'!D64)=1,SUM('Turns'!D64),"Unknown")</f>
-        <v>77.0</v>
-      </c>
-      <c r="T26" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="T28" s="2">
         <f>IF(COUNT('Turns'!E64)=1,SUM('Turns'!E64),"Unknown")</f>
-        <v>8.0606988e-05</v>
-      </c>
-      <c r="U26" s="2">
+        <v>3.260022e-05</v>
+      </c>
+      <c r="U28" s="2">
         <f>IF(COUNT('Turns'!F64)=1,SUM('Turns'!F64),"Unknown")</f>
-        <v>9.24e-05</v>
-      </c>
-      <c r="V26" s="2">
+        <v>3.72e-05</v>
+      </c>
+      <c r="V28" s="2">
         <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
-        <v>191.0</v>
-      </c>
-      <c r="W26" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="W28" s="2">
         <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
-        <v>0.000199947204</v>
-      </c>
-      <c r="X26" s="2">
+        <v>7.36134e-06</v>
+      </c>
+      <c r="X28" s="2">
         <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
-        <v>0.0002292</v>
-      </c>
-      <c r="Y26" s="2">
+        <v>8.4e-06</v>
+      </c>
+      <c r="Y28" s="2">
         <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
-        <v>0.0003375722952</v>
-      </c>
-      <c r="Z26" s="2">
+        <v>0.000144387426</v>
+      </c>
+      <c r="Z28" s="2">
         <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
-        <v>0.00038696</v>
-      </c>
-      <c r="AA26" s="5">
-        <f>IF(ISNUMBER(Y26),ROUND(Y26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>34.0</v>
-      </c>
-      <c r="AB26" s="5">
-        <f>IF(ISNUMBER(Z26),ROUND(Z26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
-      </c>
-      <c r="AD26" s="1">
-        <v>5774.887</v>
-      </c>
-      <c r="AE26" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" ht="54" customHeight="1">
-      <c r="A27" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B27" s="1">
+        <v>0.00016476</v>
+      </c>
+      <c r="AA28" s="5">
+        <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>14.0</v>
+      </c>
+      <c r="AB28" s="5">
+        <f>IF(ISNUMBER(Z28),ROUND(Z28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+      <c r="AD28" s="1">
+        <v>1465.083</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" ht="54" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B29" s="1">
         <v>2</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="1">
-        <v>1677</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="H27" t="s">
-        <v>137</v>
-      </c>
-      <c r="I27" t="s">
-        <v>195</v>
-      </c>
-      <c r="J27" s="2">
+      <c r="F29" s="1">
+        <v>1952</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H29" t="s">
+        <v>139</v>
+      </c>
+      <c r="I29" t="s">
+        <v>207</v>
+      </c>
+      <c r="J29" s="2">
         <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
         <v>3.0</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K29" s="2">
         <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L27" s="2">
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L29" s="2">
         <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
         <v>6e-07</v>
       </c>
-      <c r="M27" s="2">
+      <c r="M29" s="2">
         <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>1538.0</v>
-      </c>
-      <c r="N27" s="2">
+        <v>1603.0</v>
+      </c>
+      <c r="N29" s="2">
         <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>2.68341012e-05</v>
-      </c>
-      <c r="O27" s="2">
+        <v>2.8095781e-05</v>
+      </c>
+      <c r="O29" s="2">
         <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>3.076e-05</v>
-      </c>
-      <c r="P27" s="2">
+        <v>3.206e-05</v>
+      </c>
+      <c r="P29" s="2">
         <f>IF(COUNT('Turns'!D60)=1,SUM('Turns'!D60),"Unknown")</f>
-        <v>136.0</v>
-      </c>
-      <c r="Q27" s="2">
+        <v>346.0</v>
+      </c>
+      <c r="Q29" s="2">
         <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>2.966058e-05</v>
-      </c>
-      <c r="R27" s="2">
+        <v>7.5804275e-05</v>
+      </c>
+      <c r="R29" s="2">
         <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>3.4e-05</v>
-      </c>
-      <c r="S27" s="2">
+        <v>8.65e-05</v>
+      </c>
+      <c r="S29" s="2">
         <f>IF(COUNT('Turns'!D64)=1,SUM('Turns'!D64),"Unknown")</f>
-        <v>77.0</v>
-      </c>
-      <c r="T27" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="T29" s="2">
         <f>IF(COUNT('Turns'!E64)=1,SUM('Turns'!E64),"Unknown")</f>
-        <v>8.0606988e-05</v>
-      </c>
-      <c r="U27" s="2">
+        <v>3.260022e-05</v>
+      </c>
+      <c r="U29" s="2">
         <f>IF(COUNT('Turns'!F64)=1,SUM('Turns'!F64),"Unknown")</f>
-        <v>9.24e-05</v>
-      </c>
-      <c r="V27" s="2">
+        <v>3.72e-05</v>
+      </c>
+      <c r="V29" s="2">
         <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
-        <v>191.0</v>
-      </c>
-      <c r="W27" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="W29" s="2">
         <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
-        <v>0.000199947204</v>
-      </c>
-      <c r="X27" s="2">
+        <v>7.36134e-06</v>
+      </c>
+      <c r="X29" s="2">
         <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
-        <v>0.0002292</v>
-      </c>
-      <c r="Y27" s="2">
+        <v>8.4e-06</v>
+      </c>
+      <c r="Y29" s="2">
         <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
-        <v>0.0003375722952</v>
-      </c>
-      <c r="Z27" s="2">
+        <v>0.000144387426</v>
+      </c>
+      <c r="Z29" s="2">
         <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
-        <v>0.00038696</v>
-      </c>
-      <c r="AA27" s="5">
-        <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>34.0</v>
-      </c>
-      <c r="AB27" s="5">
-        <f>IF(ISNUMBER(Z27),ROUND(Z27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
-      </c>
-      <c r="AC27" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AD27" s="1">
-        <v>5772.727</v>
-      </c>
-      <c r="AE27" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" ht="54" customHeight="1">
-      <c r="A28" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="H28" t="s">
-        <v>196</v>
-      </c>
-      <c r="I28" t="s">
-        <v>185</v>
-      </c>
-      <c r="AD28" s="1">
-        <v>0.599</v>
-      </c>
-      <c r="AE28" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" ht="54" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="H29" t="s">
-        <v>197</v>
-      </c>
-      <c r="J29" s="2">
-        <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K29" s="2">
-        <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L29" s="2">
-        <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M29" s="2">
-        <f>IF(COUNT('Turns'!D73)=1,SUM('Turns'!D73),"Unknown")</f>
-        <v>1674.0</v>
-      </c>
-      <c r="N29" s="2">
-        <f>IF(COUNT('Turns'!E73)=1,SUM('Turns'!E73),"Unknown")</f>
-        <v>2.92069476e-05</v>
-      </c>
-      <c r="O29" s="2">
-        <f>IF(COUNT('Turns'!F73)=1,SUM('Turns'!F73),"Unknown")</f>
-        <v>3.348e-05</v>
-      </c>
-      <c r="P29" s="2">
-        <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
-        <v>323.0</v>
-      </c>
-      <c r="Q29" s="2">
-        <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
-        <v>7.04438775e-05</v>
-      </c>
-      <c r="R29" s="2">
-        <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
-        <v>8.075e-05</v>
-      </c>
-      <c r="S29" s="2">
-        <f>IF(COUNT('Turns'!D80)=1,SUM('Turns'!D80),"Unknown")</f>
-        <v>179.0</v>
-      </c>
-      <c r="T29" s="2">
-        <f>IF(COUNT('Turns'!E80)=1,SUM('Turns'!E80),"Unknown")</f>
-        <v>0.000187385076</v>
-      </c>
-      <c r="U29" s="2">
-        <f>IF(COUNT('Turns'!F80)=1,SUM('Turns'!F80),"Unknown")</f>
-        <v>0.0002148</v>
-      </c>
-      <c r="V29" s="2">
-        <f>IF(COUNT('Turns'!D79)=1,SUM('Turns'!D79),"Unknown")</f>
-        <v>102.0</v>
-      </c>
-      <c r="W29" s="2">
-        <f>IF(COUNT('Turns'!E79)=1,SUM('Turns'!E79),"Unknown")</f>
-        <v>0.000106778088</v>
-      </c>
-      <c r="X29" s="2">
-        <f>IF(COUNT('Turns'!F79)=1,SUM('Turns'!F79),"Unknown")</f>
-        <v>0.0001224</v>
-      </c>
-      <c r="Y29" s="2">
-        <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>0.0003943374111</v>
-      </c>
-      <c r="Z29" s="2">
-        <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>0.00045203</v>
+        <v>0.00016476</v>
       </c>
       <c r="AA29" s="5">
         <f>IF(ISNUMBER(Y29),ROUND(Y29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
+        <v>14.0</v>
       </c>
       <c r="AB29" s="5">
         <f>IF(ISNUMBER(Z29),ROUND(Z29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>45.0</v>
+        <v>16.0</v>
+      </c>
+      <c r="AC29" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="AD29" s="1">
-        <v>4446.082</v>
+        <v>1463.083</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="54" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>47</v>
@@ -5233,30 +5950,30 @@
         <v>111</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H30" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="I30" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AD30" s="1">
-        <v>0.395</v>
+        <v>0.466</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="54" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B31" s="1">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>47</v>
@@ -5265,62 +5982,62 @@
         <v>111</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H31" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="I31" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AD31" s="1">
-        <v>3.047</v>
+        <v>3.977</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="54" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B32" s="1">
         <v>2</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>189</v>
       </c>
       <c r="H32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I32" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="AD32" s="1">
-        <v>0.93</v>
+        <v>0.897</v>
       </c>
       <c r="AE32" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="54" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B33" s="1">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>47</v>
@@ -5329,30 +6046,30 @@
         <v>111</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H33" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="I33" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AD33" s="1">
-        <v>0.297</v>
+        <v>0.584</v>
       </c>
       <c r="AE33" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="54" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B34" s="1">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>47</v>
@@ -5361,13 +6078,13 @@
         <v>111</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H34" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="I34" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J34" s="2">
         <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
@@ -5375,7 +6092,7 @@
       </c>
       <c r="K34" s="2">
         <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L34" s="2">
         <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
@@ -5383,84 +6100,84 @@
       </c>
       <c r="M34" s="2">
         <f>IF(COUNT('Turns'!D73)=1,SUM('Turns'!D73),"Unknown")</f>
-        <v>1674.0</v>
+        <v>1949.0</v>
       </c>
       <c r="N34" s="2">
         <f>IF(COUNT('Turns'!E73)=1,SUM('Turns'!E73),"Unknown")</f>
-        <v>2.92069476e-05</v>
+        <v>3.4160123e-05</v>
       </c>
       <c r="O34" s="2">
         <f>IF(COUNT('Turns'!F73)=1,SUM('Turns'!F73),"Unknown")</f>
-        <v>3.348e-05</v>
+        <v>3.898e-05</v>
       </c>
       <c r="P34" s="2">
         <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
-        <v>323.0</v>
+        <v>141.0</v>
       </c>
       <c r="Q34" s="2">
         <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
-        <v>7.04438775e-05</v>
+        <v>3.08913375e-05</v>
       </c>
       <c r="R34" s="2">
         <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
-        <v>8.075e-05</v>
+        <v>3.525e-05</v>
       </c>
       <c r="S34" s="2">
         <f>IF(COUNT('Turns'!D80)=1,SUM('Turns'!D80),"Unknown")</f>
-        <v>179.0</v>
+        <v>111.0</v>
       </c>
       <c r="T34" s="2">
         <f>IF(COUNT('Turns'!E80)=1,SUM('Turns'!E80),"Unknown")</f>
-        <v>0.000187385076</v>
+        <v>0.00011672982</v>
       </c>
       <c r="U34" s="2">
         <f>IF(COUNT('Turns'!F80)=1,SUM('Turns'!F80),"Unknown")</f>
-        <v>0.0002148</v>
+        <v>0.0001332</v>
       </c>
       <c r="V34" s="2">
         <f>IF(COUNT('Turns'!D79)=1,SUM('Turns'!D79),"Unknown")</f>
-        <v>102.0</v>
+        <v>467.0</v>
       </c>
       <c r="W34" s="2">
         <f>IF(COUNT('Turns'!E79)=1,SUM('Turns'!E79),"Unknown")</f>
-        <v>0.000106778088</v>
+        <v>0.00049110654</v>
       </c>
       <c r="X34" s="2">
         <f>IF(COUNT('Turns'!F79)=1,SUM('Turns'!F79),"Unknown")</f>
-        <v>0.0001224</v>
+        <v>0.0005604</v>
       </c>
       <c r="Y34" s="2">
         <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>0.0003943374111</v>
+        <v>0.0006734136305</v>
       </c>
       <c r="Z34" s="2">
         <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>0.00045203</v>
+        <v>0.00076843</v>
       </c>
       <c r="AA34" s="5">
         <f>IF(ISNUMBER(Y34),ROUND(Y34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
+        <v>67.0</v>
       </c>
       <c r="AB34" s="5">
         <f>IF(ISNUMBER(Z34),ROUND(Z34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>45.0</v>
+        <v>77.0</v>
       </c>
       <c r="AD34" s="1">
-        <v>4437.396</v>
+        <v>7186.948</v>
       </c>
       <c r="AE34" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="54" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B35" s="1">
         <v>2</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>95</v>
@@ -5469,16 +6186,16 @@
         <v>111</v>
       </c>
       <c r="F35" s="1">
-        <v>2000</v>
+        <v>2093</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H35" t="s">
         <v>144</v>
       </c>
       <c r="I35" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="J35" s="2">
         <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
@@ -5486,7 +6203,7 @@
       </c>
       <c r="K35" s="2">
         <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L35" s="2">
         <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
@@ -5494,119 +6211,119 @@
       </c>
       <c r="M35" s="2">
         <f>IF(COUNT('Turns'!D73)=1,SUM('Turns'!D73),"Unknown")</f>
-        <v>1674.0</v>
+        <v>1949.0</v>
       </c>
       <c r="N35" s="2">
         <f>IF(COUNT('Turns'!E73)=1,SUM('Turns'!E73),"Unknown")</f>
-        <v>2.92069476e-05</v>
+        <v>3.4160123e-05</v>
       </c>
       <c r="O35" s="2">
         <f>IF(COUNT('Turns'!F73)=1,SUM('Turns'!F73),"Unknown")</f>
-        <v>3.348e-05</v>
+        <v>3.898e-05</v>
       </c>
       <c r="P35" s="2">
         <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
-        <v>323.0</v>
+        <v>141.0</v>
       </c>
       <c r="Q35" s="2">
         <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
-        <v>7.04438775e-05</v>
+        <v>3.08913375e-05</v>
       </c>
       <c r="R35" s="2">
         <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
-        <v>8.075e-05</v>
+        <v>3.525e-05</v>
       </c>
       <c r="S35" s="2">
         <f>IF(COUNT('Turns'!D80)=1,SUM('Turns'!D80),"Unknown")</f>
-        <v>179.0</v>
+        <v>111.0</v>
       </c>
       <c r="T35" s="2">
         <f>IF(COUNT('Turns'!E80)=1,SUM('Turns'!E80),"Unknown")</f>
-        <v>0.000187385076</v>
+        <v>0.00011672982</v>
       </c>
       <c r="U35" s="2">
         <f>IF(COUNT('Turns'!F80)=1,SUM('Turns'!F80),"Unknown")</f>
-        <v>0.0002148</v>
+        <v>0.0001332</v>
       </c>
       <c r="V35" s="2">
         <f>IF(COUNT('Turns'!D79)=1,SUM('Turns'!D79),"Unknown")</f>
-        <v>102.0</v>
+        <v>467.0</v>
       </c>
       <c r="W35" s="2">
         <f>IF(COUNT('Turns'!E79)=1,SUM('Turns'!E79),"Unknown")</f>
-        <v>0.000106778088</v>
+        <v>0.00049110654</v>
       </c>
       <c r="X35" s="2">
         <f>IF(COUNT('Turns'!F79)=1,SUM('Turns'!F79),"Unknown")</f>
-        <v>0.0001224</v>
+        <v>0.0005604</v>
       </c>
       <c r="Y35" s="2">
         <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>0.0003943374111</v>
+        <v>0.0006734136305</v>
       </c>
       <c r="Z35" s="2">
         <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>0.00045203</v>
+        <v>0.00076843</v>
       </c>
       <c r="AA35" s="5">
         <f>IF(ISNUMBER(Y35),ROUND(Y35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
+        <v>67.0</v>
       </c>
       <c r="AB35" s="5">
         <f>IF(ISNUMBER(Z35),ROUND(Z35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>45.0</v>
+        <v>77.0</v>
       </c>
       <c r="AC35" s="1" t="s">
         <v>143</v>
       </c>
       <c r="AD35" s="1">
-        <v>4435.348</v>
+        <v>7183.92</v>
       </c>
       <c r="AE35" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="54" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H36" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="I36" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AD36" s="1">
-        <v>0.344</v>
+        <v>0.665</v>
       </c>
       <c r="AE36" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="54" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B37" s="1">
         <v>0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>47</v>
@@ -5615,10 +6332,10 @@
         <v>111</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H37" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="J37" s="2">
         <f>IF(COUNT('Turns'!D90,'Turns'!D106)=2,SUM('Turns'!D90,'Turns'!D106),"Unknown")</f>
@@ -5626,7 +6343,7 @@
       </c>
       <c r="K37" s="2">
         <f>IF(COUNT('Turns'!E90,'Turns'!E106)=2,SUM('Turns'!E90,'Turns'!E106),"Unknown")</f>
-        <v>1.046844e-06</v>
+        <v>1.05162e-06</v>
       </c>
       <c r="L37" s="2">
         <f>IF(COUNT('Turns'!F90,'Turns'!F106)=2,SUM('Turns'!F90,'Turns'!F106),"Unknown")</f>
@@ -5634,84 +6351,84 @@
       </c>
       <c r="M37" s="2">
         <f>IF(COUNT('Turns'!D89,'Turns'!D105)=2,SUM('Turns'!D89,'Turns'!D105),"Unknown")</f>
-        <v>4301.0</v>
+        <v>4784.0</v>
       </c>
       <c r="N37" s="2">
         <f>IF(COUNT('Turns'!E89,'Turns'!E105)=2,SUM('Turns'!E89,'Turns'!E105),"Unknown")</f>
-        <v>7.50412674e-05</v>
+        <v>8.3849168e-05</v>
       </c>
       <c r="O37" s="2">
         <f>IF(COUNT('Turns'!F89,'Turns'!F105)=2,SUM('Turns'!F89,'Turns'!F105),"Unknown")</f>
-        <v>8.602e-05</v>
+        <v>9.568e-05</v>
       </c>
       <c r="P37" s="2">
         <f>IF(COUNT('Turns'!D92,'Turns'!D108)=2,SUM('Turns'!D92,'Turns'!D108),"Unknown")</f>
-        <v>430.0</v>
+        <v>752.0</v>
       </c>
       <c r="Q37" s="2">
         <f>IF(COUNT('Turns'!E92,'Turns'!E108)=2,SUM('Turns'!E92,'Turns'!E108),"Unknown")</f>
-        <v>9.3779775e-05</v>
+        <v>0.0001647538</v>
       </c>
       <c r="R37" s="2">
         <f>IF(COUNT('Turns'!F92,'Turns'!F108)=2,SUM('Turns'!F92,'Turns'!F108),"Unknown")</f>
-        <v>0.0001075</v>
+        <v>0.000188</v>
       </c>
       <c r="S37" s="2">
-        <f>IF(COUNT('Turns'!D96,'Turns'!D111)=2,SUM('Turns'!D96,'Turns'!D111),"Unknown")</f>
-        <v>48.0</v>
+        <f>IF(COUNT('Turns'!D96,'Turns'!D112)=2,SUM('Turns'!D96,'Turns'!D112),"Unknown")</f>
+        <v>133.0</v>
       </c>
       <c r="T37" s="2">
-        <f>IF(COUNT('Turns'!E96,'Turns'!E111)=2,SUM('Turns'!E96,'Turns'!E111),"Unknown")</f>
-        <v>5.0248512e-05</v>
+        <f>IF(COUNT('Turns'!E96,'Turns'!E112)=2,SUM('Turns'!E96,'Turns'!E112),"Unknown")</f>
+        <v>0.00013986546</v>
       </c>
       <c r="U37" s="2">
-        <f>IF(COUNT('Turns'!F96,'Turns'!F111)=2,SUM('Turns'!F96,'Turns'!F111),"Unknown")</f>
-        <v>5.76e-05</v>
+        <f>IF(COUNT('Turns'!F96,'Turns'!F112)=2,SUM('Turns'!F96,'Turns'!F112),"Unknown")</f>
+        <v>0.0001596</v>
       </c>
       <c r="V37" s="2">
-        <f>IF(COUNT('Turns'!D95)=1,SUM('Turns'!D95),"Unknown")</f>
-        <v>8.0</v>
+        <f>IF(COUNT('Turns'!D95,'Turns'!D111)=2,SUM('Turns'!D95,'Turns'!D111),"Unknown")</f>
+        <v>857.0</v>
       </c>
       <c r="W37" s="2">
-        <f>IF(COUNT('Turns'!E95)=1,SUM('Turns'!E95),"Unknown")</f>
-        <v>8.374752e-06</v>
+        <f>IF(COUNT('Turns'!E95,'Turns'!E111)=2,SUM('Turns'!E95,'Turns'!E111),"Unknown")</f>
+        <v>0.00090123834</v>
       </c>
       <c r="X37" s="2">
-        <f>IF(COUNT('Turns'!F95)=1,SUM('Turns'!F95),"Unknown")</f>
-        <v>9.6e-06</v>
+        <f>IF(COUNT('Turns'!F95,'Turns'!F111)=2,SUM('Turns'!F95,'Turns'!F111),"Unknown")</f>
+        <v>0.0010284</v>
       </c>
       <c r="Y37" s="2">
-        <f>IF(COUNT('Turns'!E100,'Turns'!E115)=2,SUM('Turns'!E100,'Turns'!E115),"Unknown")</f>
-        <v>0.0002284911504</v>
+        <f>IF(COUNT('Turns'!E100,'Turns'!E116)=2,SUM('Turns'!E100,'Turns'!E116),"Unknown")</f>
+        <v>0.001290758388</v>
       </c>
       <c r="Z37" s="2">
-        <f>IF(COUNT('Turns'!F100,'Turns'!F115)=2,SUM('Turns'!F100,'Turns'!F115),"Unknown")</f>
-        <v>0.00026192</v>
+        <f>IF(COUNT('Turns'!F100,'Turns'!F116)=2,SUM('Turns'!F100,'Turns'!F116),"Unknown")</f>
+        <v>0.00147288</v>
       </c>
       <c r="AA37" s="5">
         <f>IF(ISNUMBER(Y37),ROUND(Y37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>129.0</v>
       </c>
       <c r="AB37" s="5">
         <f>IF(ISNUMBER(Z37),ROUND(Z37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>147.0</v>
       </c>
       <c r="AD37" s="1">
-        <v>2603.93</v>
+        <v>15275.325</v>
       </c>
       <c r="AE37" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="54" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>47</v>
@@ -5720,30 +6437,30 @@
         <v>111</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H38" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="I38" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="AD38" s="1">
-        <v>0.426</v>
+        <v>0.546</v>
       </c>
       <c r="AE38" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="54" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B39" s="1">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>47</v>
@@ -5752,30 +6469,30 @@
         <v>111</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H39" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="I39" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="AD39" s="1">
-        <v>3.827</v>
+        <v>3.347</v>
       </c>
       <c r="AE39" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:31" ht="54" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B40" s="1">
         <v>2</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>47</v>
@@ -5784,30 +6501,30 @@
         <v>111</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="H40" t="s">
         <v>146</v>
       </c>
       <c r="I40" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="AD40" s="1">
-        <v>1.289</v>
+        <v>1.144</v>
       </c>
       <c r="AE40" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:31" ht="54" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B41" s="1">
         <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>47</v>
@@ -5816,30 +6533,30 @@
         <v>111</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H41" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="I41" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="AD41" s="1">
-        <v>0.323</v>
+        <v>0.346</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:31" ht="54" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>47</v>
@@ -5848,13 +6565,13 @@
         <v>111</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H42" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="I42" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="J42" s="2">
         <f>IF(COUNT('Turns'!D90)=1,SUM('Turns'!D90),"Unknown")</f>
@@ -5862,7 +6579,7 @@
       </c>
       <c r="K42" s="2">
         <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L42" s="2">
         <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
@@ -5870,27 +6587,27 @@
       </c>
       <c r="M42" s="2">
         <f>IF(COUNT('Turns'!D89)=1,SUM('Turns'!D89),"Unknown")</f>
-        <v>1997.0</v>
+        <v>2090.0</v>
       </c>
       <c r="N42" s="2">
         <f>IF(COUNT('Turns'!E89)=1,SUM('Turns'!E89),"Unknown")</f>
-        <v>3.48424578e-05</v>
+        <v>3.663143e-05</v>
       </c>
       <c r="O42" s="2">
         <f>IF(COUNT('Turns'!F89)=1,SUM('Turns'!F89),"Unknown")</f>
-        <v>3.994e-05</v>
+        <v>4.18e-05</v>
       </c>
       <c r="P42" s="2">
         <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
-        <v>307.0</v>
+        <v>604.0</v>
       </c>
       <c r="Q42" s="2">
         <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
-        <v>6.69543975e-05</v>
+        <v>0.00013232885</v>
       </c>
       <c r="R42" s="2">
         <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
-        <v>7.675e-05</v>
+        <v>0.000151</v>
       </c>
       <c r="S42" s="2">
         <f>IF(COUNT('Turns'!D96)=1,SUM('Turns'!D96),"Unknown")</f>
@@ -5898,7 +6615,7 @@
       </c>
       <c r="T42" s="2">
         <f>IF(COUNT('Turns'!E96)=1,SUM('Turns'!E96),"Unknown")</f>
-        <v>3.2452164e-05</v>
+        <v>3.260022e-05</v>
       </c>
       <c r="U42" s="2">
         <f>IF(COUNT('Turns'!F96)=1,SUM('Turns'!F96),"Unknown")</f>
@@ -5906,48 +6623,48 @@
       </c>
       <c r="V42" s="2">
         <f>IF(COUNT('Turns'!D95)=1,SUM('Turns'!D95),"Unknown")</f>
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="W42" s="2">
         <f>IF(COUNT('Turns'!E95)=1,SUM('Turns'!E95),"Unknown")</f>
-        <v>8.374752e-06</v>
+        <v>7.36134e-06</v>
       </c>
       <c r="X42" s="2">
         <f>IF(COUNT('Turns'!F95)=1,SUM('Turns'!F95),"Unknown")</f>
-        <v>9.6e-06</v>
+        <v>8.4e-06</v>
       </c>
       <c r="Y42" s="2">
         <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
-        <v>0.0001431471933</v>
+        <v>0.00020944765</v>
       </c>
       <c r="Z42" s="2">
         <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
-        <v>0.00016409</v>
+        <v>0.000239</v>
       </c>
       <c r="AA42" s="5">
         <f>IF(ISNUMBER(Y42),ROUND(Y42*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>21.0</v>
       </c>
       <c r="AB42" s="5">
         <f>IF(ISNUMBER(Z42),ROUND(Z42*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="AD42" s="1">
-        <v>1539.551</v>
+        <v>1686.641</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:31" ht="54" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B43" s="1">
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>95</v>
@@ -5956,16 +6673,16 @@
         <v>111</v>
       </c>
       <c r="F43" s="1">
-        <v>2307</v>
+        <v>2697</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H43" t="s">
         <v>149</v>
       </c>
       <c r="I43" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="J43" s="2">
         <f>IF(COUNT('Turns'!D90)=1,SUM('Turns'!D90),"Unknown")</f>
@@ -5973,7 +6690,7 @@
       </c>
       <c r="K43" s="2">
         <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L43" s="2">
         <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
@@ -5981,27 +6698,27 @@
       </c>
       <c r="M43" s="2">
         <f>IF(COUNT('Turns'!D89)=1,SUM('Turns'!D89),"Unknown")</f>
-        <v>1997.0</v>
+        <v>2090.0</v>
       </c>
       <c r="N43" s="2">
         <f>IF(COUNT('Turns'!E89)=1,SUM('Turns'!E89),"Unknown")</f>
-        <v>3.48424578e-05</v>
+        <v>3.663143e-05</v>
       </c>
       <c r="O43" s="2">
         <f>IF(COUNT('Turns'!F89)=1,SUM('Turns'!F89),"Unknown")</f>
-        <v>3.994e-05</v>
+        <v>4.18e-05</v>
       </c>
       <c r="P43" s="2">
         <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
-        <v>307.0</v>
+        <v>604.0</v>
       </c>
       <c r="Q43" s="2">
         <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
-        <v>6.69543975e-05</v>
+        <v>0.00013232885</v>
       </c>
       <c r="R43" s="2">
         <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
-        <v>7.675e-05</v>
+        <v>0.000151</v>
       </c>
       <c r="S43" s="2">
         <f>IF(COUNT('Turns'!D96)=1,SUM('Turns'!D96),"Unknown")</f>
@@ -6009,7 +6726,7 @@
       </c>
       <c r="T43" s="2">
         <f>IF(COUNT('Turns'!E96)=1,SUM('Turns'!E96),"Unknown")</f>
-        <v>3.2452164e-05</v>
+        <v>3.260022e-05</v>
       </c>
       <c r="U43" s="2">
         <f>IF(COUNT('Turns'!F96)=1,SUM('Turns'!F96),"Unknown")</f>
@@ -6017,51 +6734,51 @@
       </c>
       <c r="V43" s="2">
         <f>IF(COUNT('Turns'!D95)=1,SUM('Turns'!D95),"Unknown")</f>
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="W43" s="2">
         <f>IF(COUNT('Turns'!E95)=1,SUM('Turns'!E95),"Unknown")</f>
-        <v>8.374752e-06</v>
+        <v>7.36134e-06</v>
       </c>
       <c r="X43" s="2">
         <f>IF(COUNT('Turns'!F95)=1,SUM('Turns'!F95),"Unknown")</f>
-        <v>9.6e-06</v>
+        <v>8.4e-06</v>
       </c>
       <c r="Y43" s="2">
         <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
-        <v>0.0001431471933</v>
+        <v>0.00020944765</v>
       </c>
       <c r="Z43" s="2">
         <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
-        <v>0.00016409</v>
+        <v>0.000239</v>
       </c>
       <c r="AA43" s="5">
         <f>IF(ISNUMBER(Y43),ROUND(Y43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>21.0</v>
       </c>
       <c r="AB43" s="5">
         <f>IF(ISNUMBER(Z43),ROUND(Z43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="AC43" s="1" t="s">
         <v>148</v>
       </c>
       <c r="AD43" s="1">
-        <v>1537.501</v>
+        <v>1685.019</v>
       </c>
       <c r="AE43" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:31" ht="54" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B44" s="1">
         <v>1</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>47</v>
@@ -6070,30 +6787,30 @@
         <v>111</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H44" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="I44" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="AD44" s="1">
-        <v>0.536</v>
+        <v>0.369</v>
       </c>
       <c r="AE44" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:31" ht="54" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B45" s="1">
         <v>1</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>47</v>
@@ -6102,30 +6819,30 @@
         <v>111</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H45" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="I45" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="AD45" s="1">
-        <v>11.007</v>
+        <v>3.645</v>
       </c>
       <c r="AE45" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:31" ht="54" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B46" s="1">
         <v>2</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>47</v>
@@ -6134,30 +6851,30 @@
         <v>111</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="H46" t="s">
         <v>151</v>
       </c>
       <c r="I46" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="AD46" s="1">
-        <v>1.052</v>
+        <v>0.671</v>
       </c>
       <c r="AE46" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:31" ht="54" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B47" s="1">
         <v>1</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>47</v>
@@ -6166,30 +6883,30 @@
         <v>111</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H47" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="I47" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="AD47" s="1">
-        <v>0.367</v>
+        <v>0.272</v>
       </c>
       <c r="AE47" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" spans="1:31" ht="54" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B48" s="1">
         <v>1</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>47</v>
@@ -6198,13 +6915,13 @@
         <v>111</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H48" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="I48" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="J48" s="2">
         <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
@@ -6212,7 +6929,7 @@
       </c>
       <c r="K48" s="2">
         <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L48" s="2">
         <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
@@ -6220,81 +6937,84 @@
       </c>
       <c r="M48" s="2">
         <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
-        <v>2304.0</v>
+        <v>2694.0</v>
       </c>
       <c r="N48" s="2">
         <f>IF(COUNT('Turns'!E105)=1,SUM('Turns'!E105),"Unknown")</f>
-        <v>4.01988096e-05</v>
+        <v>4.7217738e-05</v>
       </c>
       <c r="O48" s="2">
         <f>IF(COUNT('Turns'!F105)=1,SUM('Turns'!F105),"Unknown")</f>
-        <v>4.608e-05</v>
+        <v>5.388e-05</v>
       </c>
       <c r="P48" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>123.0</v>
+        <v>148.0</v>
       </c>
       <c r="Q48" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>2.68253775e-05</v>
+        <v>3.242495e-05</v>
       </c>
       <c r="R48" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>3.075e-05</v>
+        <v>3.7e-05</v>
       </c>
       <c r="S48" s="2">
+        <f>IF(COUNT('Turns'!D112)=1,SUM('Turns'!D112),"Unknown")</f>
+        <v>102.0</v>
+      </c>
+      <c r="T48" s="2">
+        <f>IF(COUNT('Turns'!E112)=1,SUM('Turns'!E112),"Unknown")</f>
+        <v>0.00010726524</v>
+      </c>
+      <c r="U48" s="2">
+        <f>IF(COUNT('Turns'!F112)=1,SUM('Turns'!F112),"Unknown")</f>
+        <v>0.0001224</v>
+      </c>
+      <c r="V48" s="2">
         <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
-        <v>17.0</v>
-      </c>
-      <c r="T48" s="2">
+        <v>850.0</v>
+      </c>
+      <c r="W48" s="2">
         <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
-        <v>1.7796348e-05</v>
-      </c>
-      <c r="U48" s="2">
+        <v>0.000893877</v>
+      </c>
+      <c r="X48" s="2">
         <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
-        <v>2.04e-05</v>
-      </c>
-      <c r="V48" s="2">
-        <v>0</v>
-      </c>
-      <c r="W48" s="2">
-        <v>0</v>
-      </c>
-      <c r="X48" s="2">
-        <v>0</v>
+        <v>0.00102</v>
       </c>
       <c r="Y48" s="2">
-        <f>IF(COUNT('Turns'!E115)=1,SUM('Turns'!E115),"Unknown")</f>
-        <v>8.53439571e-05</v>
+        <f>IF(COUNT('Turns'!E116)=1,SUM('Turns'!E116),"Unknown")</f>
+        <v>0.001081310738</v>
       </c>
       <c r="Z48" s="2">
-        <f>IF(COUNT('Turns'!F115)=1,SUM('Turns'!F115),"Unknown")</f>
-        <v>9.783e-05</v>
+        <f>IF(COUNT('Turns'!F116)=1,SUM('Turns'!F116),"Unknown")</f>
+        <v>0.00123388</v>
       </c>
       <c r="AA48" s="5">
         <f>IF(ISNUMBER(Y48),ROUND(Y48*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>108.0</v>
       </c>
       <c r="AB48" s="5">
         <f>IF(ISNUMBER(Z48),ROUND(Z48*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>123.0</v>
       </c>
       <c r="AD48" s="1">
-        <v>1038.006</v>
+        <v>13570.259</v>
       </c>
       <c r="AE48" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:31" ht="54" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B49" s="1">
         <v>2</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>95</v>
@@ -6303,16 +7023,16 @@
         <v>111</v>
       </c>
       <c r="F49" s="1">
-        <v>2430</v>
+        <v>2845</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H49" t="s">
         <v>154</v>
       </c>
       <c r="I49" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="J49" s="2">
         <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
@@ -6320,7 +7040,7 @@
       </c>
       <c r="K49" s="2">
         <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L49" s="2">
         <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
@@ -6328,109 +7048,943 @@
       </c>
       <c r="M49" s="2">
         <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
-        <v>2304.0</v>
+        <v>2694.0</v>
       </c>
       <c r="N49" s="2">
         <f>IF(COUNT('Turns'!E105)=1,SUM('Turns'!E105),"Unknown")</f>
-        <v>4.01988096e-05</v>
+        <v>4.7217738e-05</v>
       </c>
       <c r="O49" s="2">
         <f>IF(COUNT('Turns'!F105)=1,SUM('Turns'!F105),"Unknown")</f>
-        <v>4.608e-05</v>
+        <v>5.388e-05</v>
       </c>
       <c r="P49" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>123.0</v>
+        <v>148.0</v>
       </c>
       <c r="Q49" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>2.68253775e-05</v>
+        <v>3.242495e-05</v>
       </c>
       <c r="R49" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>3.075e-05</v>
+        <v>3.7e-05</v>
       </c>
       <c r="S49" s="2">
+        <f>IF(COUNT('Turns'!D112)=1,SUM('Turns'!D112),"Unknown")</f>
+        <v>102.0</v>
+      </c>
+      <c r="T49" s="2">
+        <f>IF(COUNT('Turns'!E112)=1,SUM('Turns'!E112),"Unknown")</f>
+        <v>0.00010726524</v>
+      </c>
+      <c r="U49" s="2">
+        <f>IF(COUNT('Turns'!F112)=1,SUM('Turns'!F112),"Unknown")</f>
+        <v>0.0001224</v>
+      </c>
+      <c r="V49" s="2">
         <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
-        <v>17.0</v>
-      </c>
-      <c r="T49" s="2">
+        <v>850.0</v>
+      </c>
+      <c r="W49" s="2">
         <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
-        <v>1.7796348e-05</v>
-      </c>
-      <c r="U49" s="2">
+        <v>0.000893877</v>
+      </c>
+      <c r="X49" s="2">
         <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
-        <v>2.04e-05</v>
-      </c>
-      <c r="V49" s="2">
-        <v>0</v>
-      </c>
-      <c r="W49" s="2">
-        <v>0</v>
-      </c>
-      <c r="X49" s="2">
-        <v>0</v>
+        <v>0.00102</v>
       </c>
       <c r="Y49" s="2">
-        <f>IF(COUNT('Turns'!E115)=1,SUM('Turns'!E115),"Unknown")</f>
-        <v>8.53439571e-05</v>
+        <f>IF(COUNT('Turns'!E116)=1,SUM('Turns'!E116),"Unknown")</f>
+        <v>0.001081310738</v>
       </c>
       <c r="Z49" s="2">
-        <f>IF(COUNT('Turns'!F115)=1,SUM('Turns'!F115),"Unknown")</f>
-        <v>9.783e-05</v>
+        <f>IF(COUNT('Turns'!F116)=1,SUM('Turns'!F116),"Unknown")</f>
+        <v>0.00123388</v>
       </c>
       <c r="AA49" s="5">
         <f>IF(ISNUMBER(Y49),ROUND(Y49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>108.0</v>
       </c>
       <c r="AB49" s="5">
         <f>IF(ISNUMBER(Z49),ROUND(Z49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>123.0</v>
       </c>
       <c r="AC49" s="1" t="s">
         <v>153</v>
       </c>
       <c r="AD49" s="1">
-        <v>1036.489</v>
+        <v>13566.758</v>
       </c>
       <c r="AE49" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:31" ht="54" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B50" s="1">
         <v>1</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H50" t="s">
+        <v>222</v>
+      </c>
+      <c r="I50" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD50" s="1">
+        <v>0.639</v>
+      </c>
+      <c r="AE50" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31" ht="54" customHeight="1">
+      <c r="A51" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" s="1">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="H50" t="s">
-        <v>212</v>
-      </c>
-      <c r="I50" t="s">
-        <v>203</v>
-      </c>
-      <c r="AD50" s="1">
-        <v>0.365</v>
-      </c>
-      <c r="AE50" s="1" t="s">
+      <c r="G51" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H51" t="s">
+        <v>223</v>
+      </c>
+      <c r="J51" s="2">
+        <f>IF(COUNT('Turns'!D122,'Turns'!D138)=2,SUM('Turns'!D122,'Turns'!D138),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="K51" s="2">
+        <f>IF(COUNT('Turns'!E122,'Turns'!E138)=2,SUM('Turns'!E122,'Turns'!E138),"Unknown")</f>
+        <v>1.05162e-06</v>
+      </c>
+      <c r="L51" s="2">
+        <f>IF(COUNT('Turns'!F122,'Turns'!F138)=2,SUM('Turns'!F122,'Turns'!F138),"Unknown")</f>
+        <v>1.2e-06</v>
+      </c>
+      <c r="M51" s="2">
+        <f>IF(COUNT('Turns'!D121,'Turns'!D137)=2,SUM('Turns'!D121,'Turns'!D137),"Unknown")</f>
+        <v>6662.0</v>
+      </c>
+      <c r="N51" s="2">
+        <f>IF(COUNT('Turns'!E121,'Turns'!E137)=2,SUM('Turns'!E121,'Turns'!E137),"Unknown")</f>
+        <v>0.000116764874</v>
+      </c>
+      <c r="O51" s="2">
+        <f>IF(COUNT('Turns'!F121,'Turns'!F137)=2,SUM('Turns'!F121,'Turns'!F137),"Unknown")</f>
+        <v>0.00013324</v>
+      </c>
+      <c r="P51" s="2">
+        <f>IF(COUNT('Turns'!D124,'Turns'!D140)=2,SUM('Turns'!D124,'Turns'!D140),"Unknown")</f>
+        <v>1126.0</v>
+      </c>
+      <c r="Q51" s="2">
+        <f>IF(COUNT('Turns'!E124,'Turns'!E140)=2,SUM('Turns'!E124,'Turns'!E140),"Unknown")</f>
+        <v>0.000246692525</v>
+      </c>
+      <c r="R51" s="2">
+        <f>IF(COUNT('Turns'!F124,'Turns'!F140)=2,SUM('Turns'!F124,'Turns'!F140),"Unknown")</f>
+        <v>0.0002815</v>
+      </c>
+      <c r="S51" s="2">
+        <f>IF(COUNT('Turns'!D128,'Turns'!D143)=2,SUM('Turns'!D128,'Turns'!D143),"Unknown")</f>
+        <v>47.0</v>
+      </c>
+      <c r="T51" s="2">
+        <f>IF(COUNT('Turns'!E128,'Turns'!E143)=2,SUM('Turns'!E128,'Turns'!E143),"Unknown")</f>
+        <v>4.942614e-05</v>
+      </c>
+      <c r="U51" s="2">
+        <f>IF(COUNT('Turns'!F128,'Turns'!F143)=2,SUM('Turns'!F128,'Turns'!F143),"Unknown")</f>
+        <v>5.64e-05</v>
+      </c>
+      <c r="V51" s="2">
+        <f>IF(COUNT('Turns'!D127)=1,SUM('Turns'!D127),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="W51" s="2">
+        <f>IF(COUNT('Turns'!E127)=1,SUM('Turns'!E127),"Unknown")</f>
+        <v>7.36134e-06</v>
+      </c>
+      <c r="X51" s="2">
+        <f>IF(COUNT('Turns'!F127)=1,SUM('Turns'!F127),"Unknown")</f>
+        <v>8.4e-06</v>
+      </c>
+      <c r="Y51" s="2">
+        <f>IF(COUNT('Turns'!E132,'Turns'!E147)=2,SUM('Turns'!E132,'Turns'!E147),"Unknown")</f>
+        <v>0.000421296499</v>
+      </c>
+      <c r="Z51" s="2">
+        <f>IF(COUNT('Turns'!F132,'Turns'!F147)=2,SUM('Turns'!F132,'Turns'!F147),"Unknown")</f>
+        <v>0.00048074</v>
+      </c>
+      <c r="AA51" s="5">
+        <f>IF(ISNUMBER(Y51),ROUND(Y51*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>42.0</v>
+      </c>
+      <c r="AB51" s="5">
+        <f>IF(ISNUMBER(Z51),ROUND(Z51*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>48.0</v>
+      </c>
+      <c r="AD51" s="1">
+        <v>3303.082</v>
+      </c>
+      <c r="AE51" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:31" ht="54" customHeight="1">
+      <c r="A52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H52" t="s">
+        <v>224</v>
+      </c>
+      <c r="I52" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD52" s="1">
+        <v>0.522</v>
+      </c>
+      <c r="AE52" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" ht="54" customHeight="1">
+      <c r="A53" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H53" t="s">
+        <v>225</v>
+      </c>
+      <c r="I53" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD53" s="1">
+        <v>3.172</v>
+      </c>
+      <c r="AE53" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31" ht="54" customHeight="1">
+      <c r="A54" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B54" s="1">
+        <v>2</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H54" t="s">
+        <v>156</v>
+      </c>
+      <c r="I54" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD54" s="1">
+        <v>1.274</v>
+      </c>
+      <c r="AE54" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31" ht="54" customHeight="1">
+      <c r="A55" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B55" s="1">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H55" t="s">
+        <v>226</v>
+      </c>
+      <c r="I55" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD55" s="1">
+        <v>0.353</v>
+      </c>
+      <c r="AE55" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" ht="54" customHeight="1">
+      <c r="A56" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H56" t="s">
+        <v>227</v>
+      </c>
+      <c r="I56" t="s">
+        <v>223</v>
+      </c>
+      <c r="J56" s="2">
+        <f>IF(COUNT('Turns'!D122)=1,SUM('Turns'!D122),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K56" s="2">
+        <f>IF(COUNT('Turns'!E122)=1,SUM('Turns'!E122),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L56" s="2">
+        <f>IF(COUNT('Turns'!F122)=1,SUM('Turns'!F122),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M56" s="2">
+        <f>IF(COUNT('Turns'!D121)=1,SUM('Turns'!D121),"Unknown")</f>
+        <v>2842.0</v>
+      </c>
+      <c r="N56" s="2">
+        <f>IF(COUNT('Turns'!E121)=1,SUM('Turns'!E121),"Unknown")</f>
+        <v>4.9811734e-05</v>
+      </c>
+      <c r="O56" s="2">
+        <f>IF(COUNT('Turns'!F121)=1,SUM('Turns'!F121),"Unknown")</f>
+        <v>5.684e-05</v>
+      </c>
+      <c r="P56" s="2">
+        <f>IF(COUNT('Turns'!D124)=1,SUM('Turns'!D124),"Unknown")</f>
+        <v>978.0</v>
+      </c>
+      <c r="Q56" s="2">
+        <f>IF(COUNT('Turns'!E124)=1,SUM('Turns'!E124),"Unknown")</f>
+        <v>0.000214267575</v>
+      </c>
+      <c r="R56" s="2">
+        <f>IF(COUNT('Turns'!F124)=1,SUM('Turns'!F124),"Unknown")</f>
+        <v>0.0002445</v>
+      </c>
+      <c r="S56" s="2">
+        <f>IF(COUNT('Turns'!D128)=1,SUM('Turns'!D128),"Unknown")</f>
+        <v>31.0</v>
+      </c>
+      <c r="T56" s="2">
+        <f>IF(COUNT('Turns'!E128)=1,SUM('Turns'!E128),"Unknown")</f>
+        <v>3.260022e-05</v>
+      </c>
+      <c r="U56" s="2">
+        <f>IF(COUNT('Turns'!F128)=1,SUM('Turns'!F128),"Unknown")</f>
+        <v>3.72e-05</v>
+      </c>
+      <c r="V56" s="2">
+        <f>IF(COUNT('Turns'!D127)=1,SUM('Turns'!D127),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="W56" s="2">
+        <f>IF(COUNT('Turns'!E127)=1,SUM('Turns'!E127),"Unknown")</f>
+        <v>7.36134e-06</v>
+      </c>
+      <c r="X56" s="2">
+        <f>IF(COUNT('Turns'!F127)=1,SUM('Turns'!F127),"Unknown")</f>
+        <v>8.4e-06</v>
+      </c>
+      <c r="Y56" s="2">
+        <f>IF(COUNT('Turns'!E132)=1,SUM('Turns'!E132),"Unknown")</f>
+        <v>0.000304566679</v>
+      </c>
+      <c r="Z56" s="2">
+        <f>IF(COUNT('Turns'!F132)=1,SUM('Turns'!F132),"Unknown")</f>
+        <v>0.00034754</v>
+      </c>
+      <c r="AA56" s="5">
+        <f>IF(ISNUMBER(Y56),ROUND(Y56*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>30.0</v>
+      </c>
+      <c r="AB56" s="5">
+        <f>IF(ISNUMBER(Z56),ROUND(Z56*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>35.0</v>
+      </c>
+      <c r="AD56" s="1">
+        <v>1942.237</v>
+      </c>
+      <c r="AE56" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:31" ht="54" customHeight="1">
+      <c r="A57" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B57" s="1">
+        <v>2</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F57" s="1">
+        <v>3823</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H57" t="s">
+        <v>159</v>
+      </c>
+      <c r="I57" t="s">
+        <v>227</v>
+      </c>
+      <c r="J57" s="2">
+        <f>IF(COUNT('Turns'!D122)=1,SUM('Turns'!D122),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K57" s="2">
+        <f>IF(COUNT('Turns'!E122)=1,SUM('Turns'!E122),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L57" s="2">
+        <f>IF(COUNT('Turns'!F122)=1,SUM('Turns'!F122),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M57" s="2">
+        <f>IF(COUNT('Turns'!D121)=1,SUM('Turns'!D121),"Unknown")</f>
+        <v>2842.0</v>
+      </c>
+      <c r="N57" s="2">
+        <f>IF(COUNT('Turns'!E121)=1,SUM('Turns'!E121),"Unknown")</f>
+        <v>4.9811734e-05</v>
+      </c>
+      <c r="O57" s="2">
+        <f>IF(COUNT('Turns'!F121)=1,SUM('Turns'!F121),"Unknown")</f>
+        <v>5.684e-05</v>
+      </c>
+      <c r="P57" s="2">
+        <f>IF(COUNT('Turns'!D124)=1,SUM('Turns'!D124),"Unknown")</f>
+        <v>978.0</v>
+      </c>
+      <c r="Q57" s="2">
+        <f>IF(COUNT('Turns'!E124)=1,SUM('Turns'!E124),"Unknown")</f>
+        <v>0.000214267575</v>
+      </c>
+      <c r="R57" s="2">
+        <f>IF(COUNT('Turns'!F124)=1,SUM('Turns'!F124),"Unknown")</f>
+        <v>0.0002445</v>
+      </c>
+      <c r="S57" s="2">
+        <f>IF(COUNT('Turns'!D128)=1,SUM('Turns'!D128),"Unknown")</f>
+        <v>31.0</v>
+      </c>
+      <c r="T57" s="2">
+        <f>IF(COUNT('Turns'!E128)=1,SUM('Turns'!E128),"Unknown")</f>
+        <v>3.260022e-05</v>
+      </c>
+      <c r="U57" s="2">
+        <f>IF(COUNT('Turns'!F128)=1,SUM('Turns'!F128),"Unknown")</f>
+        <v>3.72e-05</v>
+      </c>
+      <c r="V57" s="2">
+        <f>IF(COUNT('Turns'!D127)=1,SUM('Turns'!D127),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="W57" s="2">
+        <f>IF(COUNT('Turns'!E127)=1,SUM('Turns'!E127),"Unknown")</f>
+        <v>7.36134e-06</v>
+      </c>
+      <c r="X57" s="2">
+        <f>IF(COUNT('Turns'!F127)=1,SUM('Turns'!F127),"Unknown")</f>
+        <v>8.4e-06</v>
+      </c>
+      <c r="Y57" s="2">
+        <f>IF(COUNT('Turns'!E132)=1,SUM('Turns'!E132),"Unknown")</f>
+        <v>0.000304566679</v>
+      </c>
+      <c r="Z57" s="2">
+        <f>IF(COUNT('Turns'!F132)=1,SUM('Turns'!F132),"Unknown")</f>
+        <v>0.00034754</v>
+      </c>
+      <c r="AA57" s="5">
+        <f>IF(ISNUMBER(Y57),ROUND(Y57*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>30.0</v>
+      </c>
+      <c r="AB57" s="5">
+        <f>IF(ISNUMBER(Z57),ROUND(Z57*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>35.0</v>
+      </c>
+      <c r="AC57" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD57" s="1">
+        <v>1939.813</v>
+      </c>
+      <c r="AE57" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31" ht="54" customHeight="1">
+      <c r="A58" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B58" s="1">
+        <v>1</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H58" t="s">
+        <v>228</v>
+      </c>
+      <c r="I58" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD58" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="AE58" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" ht="54" customHeight="1">
+      <c r="A59" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B59" s="1">
+        <v>1</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H59" t="s">
+        <v>229</v>
+      </c>
+      <c r="I59" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD59" s="1">
+        <v>5.563</v>
+      </c>
+      <c r="AE59" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31" ht="54" customHeight="1">
+      <c r="A60" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B60" s="1">
+        <v>2</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H60" t="s">
+        <v>161</v>
+      </c>
+      <c r="I60" t="s">
+        <v>229</v>
+      </c>
+      <c r="AD60" s="1">
+        <v>1.433</v>
+      </c>
+      <c r="AE60" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:31" ht="54" customHeight="1">
+      <c r="A61" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B61" s="1">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H61" t="s">
+        <v>230</v>
+      </c>
+      <c r="I61" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD61" s="1">
+        <v>0.579</v>
+      </c>
+      <c r="AE61" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="62" spans="1:31" ht="54" customHeight="1">
+      <c r="A62" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B62" s="1">
+        <v>1</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H62" t="s">
+        <v>231</v>
+      </c>
+      <c r="I62" t="s">
+        <v>223</v>
+      </c>
+      <c r="J62" s="2">
+        <f>IF(COUNT('Turns'!D138)=1,SUM('Turns'!D138),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K62" s="2">
+        <f>IF(COUNT('Turns'!E138)=1,SUM('Turns'!E138),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L62" s="2">
+        <f>IF(COUNT('Turns'!F138)=1,SUM('Turns'!F138),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M62" s="2">
+        <f>IF(COUNT('Turns'!D137)=1,SUM('Turns'!D137),"Unknown")</f>
+        <v>3820.0</v>
+      </c>
+      <c r="N62" s="2">
+        <f>IF(COUNT('Turns'!E137)=1,SUM('Turns'!E137),"Unknown")</f>
+        <v>6.695314e-05</v>
+      </c>
+      <c r="O62" s="2">
+        <f>IF(COUNT('Turns'!F137)=1,SUM('Turns'!F137),"Unknown")</f>
+        <v>7.64e-05</v>
+      </c>
+      <c r="P62" s="2">
+        <f>IF(COUNT('Turns'!D140)=1,SUM('Turns'!D140),"Unknown")</f>
+        <v>148.0</v>
+      </c>
+      <c r="Q62" s="2">
+        <f>IF(COUNT('Turns'!E140)=1,SUM('Turns'!E140),"Unknown")</f>
+        <v>3.242495e-05</v>
+      </c>
+      <c r="R62" s="2">
+        <f>IF(COUNT('Turns'!F140)=1,SUM('Turns'!F140),"Unknown")</f>
+        <v>3.7e-05</v>
+      </c>
+      <c r="S62" s="2">
+        <f>IF(COUNT('Turns'!D143)=1,SUM('Turns'!D143),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+      <c r="T62" s="2">
+        <f>IF(COUNT('Turns'!E143)=1,SUM('Turns'!E143),"Unknown")</f>
+        <v>1.682592e-05</v>
+      </c>
+      <c r="U62" s="2">
+        <f>IF(COUNT('Turns'!F143)=1,SUM('Turns'!F143),"Unknown")</f>
+        <v>1.92e-05</v>
+      </c>
+      <c r="V62" s="2">
+        <v>0</v>
+      </c>
+      <c r="W62" s="2">
+        <v>0</v>
+      </c>
+      <c r="X62" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="2">
+        <f>IF(COUNT('Turns'!E147)=1,SUM('Turns'!E147),"Unknown")</f>
+        <v>0.00011672982</v>
+      </c>
+      <c r="Z62" s="2">
+        <f>IF(COUNT('Turns'!F147)=1,SUM('Turns'!F147),"Unknown")</f>
+        <v>0.0001332</v>
+      </c>
+      <c r="AA62" s="5">
+        <f>IF(ISNUMBER(Y62),ROUND(Y62*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="AB62" s="5">
+        <f>IF(ISNUMBER(Z62),ROUND(Z62*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+      <c r="AD62" s="1">
+        <v>1336.344</v>
+      </c>
+      <c r="AE62" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:31" ht="54" customHeight="1">
+      <c r="A63" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B63" s="1">
+        <v>2</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F63" s="1">
+        <v>3971</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H63" t="s">
+        <v>164</v>
+      </c>
+      <c r="I63" t="s">
+        <v>231</v>
+      </c>
+      <c r="J63" s="2">
+        <f>IF(COUNT('Turns'!D138)=1,SUM('Turns'!D138),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K63" s="2">
+        <f>IF(COUNT('Turns'!E138)=1,SUM('Turns'!E138),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L63" s="2">
+        <f>IF(COUNT('Turns'!F138)=1,SUM('Turns'!F138),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M63" s="2">
+        <f>IF(COUNT('Turns'!D137)=1,SUM('Turns'!D137),"Unknown")</f>
+        <v>3820.0</v>
+      </c>
+      <c r="N63" s="2">
+        <f>IF(COUNT('Turns'!E137)=1,SUM('Turns'!E137),"Unknown")</f>
+        <v>6.695314e-05</v>
+      </c>
+      <c r="O63" s="2">
+        <f>IF(COUNT('Turns'!F137)=1,SUM('Turns'!F137),"Unknown")</f>
+        <v>7.64e-05</v>
+      </c>
+      <c r="P63" s="2">
+        <f>IF(COUNT('Turns'!D140)=1,SUM('Turns'!D140),"Unknown")</f>
+        <v>148.0</v>
+      </c>
+      <c r="Q63" s="2">
+        <f>IF(COUNT('Turns'!E140)=1,SUM('Turns'!E140),"Unknown")</f>
+        <v>3.242495e-05</v>
+      </c>
+      <c r="R63" s="2">
+        <f>IF(COUNT('Turns'!F140)=1,SUM('Turns'!F140),"Unknown")</f>
+        <v>3.7e-05</v>
+      </c>
+      <c r="S63" s="2">
+        <f>IF(COUNT('Turns'!D143)=1,SUM('Turns'!D143),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+      <c r="T63" s="2">
+        <f>IF(COUNT('Turns'!E143)=1,SUM('Turns'!E143),"Unknown")</f>
+        <v>1.682592e-05</v>
+      </c>
+      <c r="U63" s="2">
+        <f>IF(COUNT('Turns'!F143)=1,SUM('Turns'!F143),"Unknown")</f>
+        <v>1.92e-05</v>
+      </c>
+      <c r="V63" s="2">
+        <v>0</v>
+      </c>
+      <c r="W63" s="2">
+        <v>0</v>
+      </c>
+      <c r="X63" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="2">
+        <f>IF(COUNT('Turns'!E147)=1,SUM('Turns'!E147),"Unknown")</f>
+        <v>0.00011672982</v>
+      </c>
+      <c r="Z63" s="2">
+        <f>IF(COUNT('Turns'!F147)=1,SUM('Turns'!F147),"Unknown")</f>
+        <v>0.0001332</v>
+      </c>
+      <c r="AA63" s="5">
+        <f>IF(ISNUMBER(Y63),ROUND(Y63*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="AB63" s="5">
+        <f>IF(ISNUMBER(Z63),ROUND(Z63*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+      <c r="AC63" s="1" t="s">
         <v>163</v>
       </c>
+      <c r="AD63" s="1">
+        <v>1333.261</v>
+      </c>
+      <c r="AE63" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:31" ht="54" customHeight="1">
+      <c r="A64" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B64" s="1">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H64" t="s">
+        <v>232</v>
+      </c>
+      <c r="I64" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD64" s="1">
+        <v>0.781</v>
+      </c>
+      <c r="AE64" s="1" t="s">
+        <v>173</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE50">
+  <conditionalFormatting sqref="A2:AE64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>
@@ -6481,7 +8035,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87237</v>
+        <v>0.87635</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/file_approval/report.xlsx
+++ b/reports/file_approval/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="200">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d130-9561-7081-adf9-e8f52d82f0d8</t>
+    <t>01a0d584-97f5-7b91-9174-923e6ed969d2</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-23</t>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-24T02:09:35.117183Z</t>
+    <t>2026-09-24T22:21:31.719587Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0d130-95bf-7752-9447-839261fb5d0b</t>
+    <t>01a0d584-97ff-7a70-b756-172cd54c9249</t>
   </si>
   <si>
     <t>Input at standard rate</t>
@@ -357,9 +357,9 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0ef6622055025d64006ab487522cc887d2a068e714119e583e", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdSiu9Pe66-TN-54Ojc00tlKW7ldQjBxSarV0XW_uzKArv0gp4rXLcYQV2UXJfzh_5hOhzGQPxu6cDc06OEmelXvu8PRCsS8A16kDgvoAWYcaQTFN7iebe_hYVs5Fe5ONo5-bGZ1z-GQOJ8ssJ4TlSKtEysNZspmUvswqj6oq1O_rV5iWEbjLS2du4niINlQcdypd6lvwrtMfULfp-DCLU247p8FpOXPCCmY-bZTq8quLUmL88dRtsL5EE8wpdNYYWzpAMlR2pTylvUDs1S167ODe83xwGowuTlFygQlh0vcMEThYUfZRNeEsAjopd1bBo0Efepuig-JfW2EF2Rz34Tl5VnEuJ-yCMRGROAydcK8tgRnJ7YvkPPQeONLOY0_7F5k0AMVXc9l_cuWHiDCjc3_HqwXP-AQMfPT8y5G47DTRUFLCkVDrKlBmMxr3QmNAfBJ1_80IeJjPPifFn02PGxW8sOmGx0OrNLa97rL5qAV7OZ5FCqTjrpZO-KnFf55CQJ_k1mSus05fBgAD3SBjWrq178CUdM_qo2QNsCciZlF55D6M1TYLJNCEID1uJIwlAfLgrGex6ON-mtWj2h-hqINoCgDzQiyNy3N_sqguRqiRTQ8qXX6Mg8j3be8V69yRgzPDDMwsvqtc0JtI5ku511gRMTi8LmYh_w4sUa1Cnbk0_e1Ir1EW9YVIMFweknsmIpB8ghKY2MJBOkwP3vkhOyU3LdN0QgwB4B8EEvBY4sJL9MlLP57zZT7wMvKlm6ieY7VEH3DWZeTF_T67ARB6zDhE9QZpQm5ojP4wIAcE-m6b0O9bW-NtgDkWp9ZQiDmzeqHXoM1AwPHxos60camTQ2ByhTaKkJ0WshyhWs4dtmDmF3sfJhylKeeoMAMQXfv8jef7SVsQ0m5a6o7T82xoV6InlvithvuvR3MgntGbbE2mLjIqWLX7ltUTpJhkqOm-qM6nAQC_qSxOh81W1__M1ahOS9uXdVLB0C4mhT0SEJOQa1ooeP376lByjhtxt8AFII5UxJxy9peEhLi2Q9FhpJKlBdI0e1fTFGeDGtf7B7a_l8KQtdm4WC20NZALDTdzzDGGxHOxqaUd-O4cAcRwRGR0ExWMh6R4V4PnHWpQdSTOqI6VX34fPNnfIyOPDEwa9mBtVU8VhwwyoRGqfabBwvjRjXjU8_G084GNGegV8oZsnmp9CMBEoasiE0lXvj8TjghUbwqm3wuVhj93xbJkYbo0MIBLvJiL8c1tGWkyUW_Bz9e-OYCB6YYqTXuKiEmj2OJANSssMAHYWymqvuVR0tWv3K-xAH8otIe7TkS8RNDco="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/source.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_Ow3bq6MHlF2P40MSMtI2VE0e", "id": "fc_0ef6622055025d64006ab48752fe4c87d287984c43688f9535", "index": 1}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_dKniOaQCqSJIDX3yR3HUJuDR", "id": "fc_0ef6622055025d64006ab48752fe5c87d2b01a99bfd18ad1da", "index": 2}]
-{"name": "read_file", "args": {"file_path": "/source.txt", "offset": 0, "limit": 100}, "id": "call_Ow3bq6MHlF2P40MSMtI2VE0e", "type": "tool_call"}
-{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_dKniOaQCqSJIDX3yR3HUJuDR", "type": "tool_call"}</t>
+    <t>[{"id": "rs_079598387a6ba76d006ab5a2f8ad2c87d28b93d7429f3814ec", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaL53HTntsSZ2ylpSNakhMFCT0-I-yqu2goDSqmAbCMX57xcIW1wZgAYfkkhy62S-Nj0QSy6IUfSdXPPD7EL1pCeno4Nu1Te_c2-24rNhrZyaI7kckE2Zm-HVttcd2CleBo-8EvYpkTAiPtxG6ORkLl-S0aj7CIqKuYseS26KbtzDWNrnRXYxZ082vecmmkqc1uUw1Cl4_HLH0JlfnaCGmoIn87Rcp02wGVAPTNSACoArd6cpywM61ZQgmhO78IaJWVjzmhNbVFMEE4okwLfYCMB0_KM9ckpljqpf7r9f5eNaBbXss0HrJFLbvCDU-5WVNoHwW0z5i3QAtTsSmqzwZqrpFiqid4wuQYcAvQuKBZ-MD2WPY0QQ-U0fE2SAFBv0bLnzX8sNGug6ZFvKT5LxEELvAgzPnp3fW3kCVyDHTBmaD-ntbT0C-aZXLQMWOB2xYV0u3M23Px8gGISu5dsuuW4G1o2xaqGGbdYk6UVLUbd5nvHk_Y1WylMUqCcN4qiDZ_mX09hZ0hsPnDTzrNiNe0Z4ioDNEP89L6gBMgXsImSxSMzt0GpDnFHme-aKezjFg5uNrFyyTjfj4tfZE5U_aJnO8MPZGnnC7gPHqcVVL8aGWNy-SEdOjxbnyu2LVpHef8j_g39WGAtT28g9rVUuVdpOWQsGHTOlauop9QD1eBZVSinZm2U-A3jDWS36cq3KKQSnArhjmlxRfwroPLhKrJwKa8hqaONss49t3BqWWq0LyVLZwz2bGTX_N-PjlDr6SvrSmhekNFXSl-q8Qv6IJZ0oWhf3F0QGkteUzhsQtXLEt_xmu1AZ4vbf1W4uDT6Fudk7nAZ4rSQxElGilJA2t3E6YVVTNI4e1uUE1nki7YqX6VCD_N60GV-_yNVlMOiFie7Omc_g0jkS_W-GuEs2w6K-28qfnL2pVKvjkgXXlZGa45kNH4WNWjnVa86olsm3i83DqCFmyvoit2EO3zqxEZhr6W7vfQj_hsCnxMysPiLKvdP-YXrsKfND_RUJlcWNt4FsgABXHmnep5pII-TdESL8T7HQecOjG7TUwHtEZMPaXp497eWYBRtobwveQ5XEIXkjaK76vI9RP69JsPpOEjwRsNJo7LW05PlO-I_ueiiwxuvkPRBKyVu2zN5jX5NSIbM--P_VciXS4SpKCTcR5OOGAeZpJS0peR3d6Iw_8BCwt_KUeEI_pi_frslnP3cm1kJd0aHoJHBYveF69owRNQMO3UauqrMgVo9qpHZdeU_qcI="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/source.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_IMRPXvy70jiSfAhlOkCdrc39", "id": "fc_079598387a6ba76d006ab5a2f930dc87d2819970aada0067f1", "index": 1}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_ykIvJkeuTFl02bF5g42oMqCL", "id": "fc_079598387a6ba76d006ab5a2f930f087d2be3bc63011ec3163", "index": 2}]
+{"name": "read_file", "args": {"file_path": "/source.txt", "offset": 0, "limit": 100}, "id": "call_IMRPXvy70jiSfAhlOkCdrc39", "type": "tool_call"}
+{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_ykIvJkeuTFl02bF5g42oMqCL", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -371,7 +371,7 @@
     <t>Tool · read_file</t>
   </si>
   <si>
-    <t>01a0d130-9cc0-7481-b17a-6d2dd428746a</t>
+    <t>01a0d584-9e5d-7331-bfbb-839f45a62020</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -388,203 +388,10 @@
 We prepare clear, practical reports.</t>
   </si>
   <si>
-    <t>01a0d130-9cc1-75f2-9185-7d1216fd2f10</t>
+    <t>01a0d584-9e5e-7ca2-92cb-408344d24951</t>
   </si>
   <si>
     <t>{'file_path': '/target.txt', 'offset': 0, 'limit': 100}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@@ lines 1-20 of 20 @@
-Project summary
-We prepare clear, practical reports.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>01a0d130-9cc5-7de1-b35f-ae2cdd996869</t>
-  </si>
-  <si>
-    <t>Conversation history · cache read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Tool result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@@ lines 1-2 of 2 @@
-Project summary
-We prepare clear, practical reports.
-@@ lines 1-20 of 20 @@
-Project summary
-We prepare clear, practical reports.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0ef6622055025d64006ab48753d6e887d2a97f2ae2b5f0ffcd", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdYj2rPwgdZCcse2UsVVakgJEdaeNtbMXz3DBlBfIa8b5e1JUU_uHfwBl-ChTEtXHeuaoktyoI_yhgvj9uu283tqVz6D6KC_Bl40CRzKDr3k4COQP43e1HtTOuZYJHO7i6YBx3IFvyRPUiiuaz9Tajp8CrRSY3jz4yMVT_bemd9ZPVKhVyRZK731JJSXF1GYpzpmZEXBZTzIGpEXbEjHKaIeBS-Jc8Ccx6JIhRuPIf-KghWfbrCqeD0JeYx-9vk9pnfbujxEt1NM-OZXK_jGOAA-EZIlOQGYlaFdPpciXic1a_UObo3zvhg04O33WTrrL7MaaC_5e3c6y00WztdsPBcbxCbuh89KQP2d89Czhi0nvZIkh-SVORG7xb5XZBWkb7nrcR8G_x-EGipocLDJW_9nxpf5vrXG4JFIpf1JrvjWU4DW7V9QJ_r3r16H8zEz92SauXo7HyBJMq4nHOrRtnig3MC66l14w3MKayISbKkuI0qMVaxRI0kEajuUHu14NNuw0L1cPkjSEZ0Zf7hCf7xxspHtBNQ1fGrzAWjs00ulghp0ZgXAGnMDEPTWLz2dvOgmXE4VZ1NGjIYuoyiHDRc-J5_1pCLVaJsJMmWhZlswUaE71FEPfs5QSeT-m6ri7gY7UEFx2_lOx2Oc_2H0iE8cEPZTff6E44PTROV7yySIHCE8BIz3hYaqY3VGUXNSm5GdHaxz2qdXpqeDQw9mVL2T-cGTo3VElKR1vOpXfDaU1pL7Z50ulMxla87Bf9dpPG_ncIQEN3MH6pJpzCN4tvZz7sUEG2oRtSHMEUL49kAFoLTRZycevo3wOpz38KrRWeHw9ySaoWYAjozS1uh_KUFSS9AcOvkWoKmEeMABuvfM5T8v42IdcOytg5XDxRnfyiR8ULH99dfT5UxKLUAuxSe5gTkvttJ1IW2NyTbxXX6xbBFOV9tyyqEJw624_2qMuzx5rh8ZHhCF_HhR5eDkq48BSq-kTOj7puWWapOmAMeaZpfbtPzkYPolnBl-uLq7VIs44EKmmDp2ScLow5n-ckE7HYG5DtwNYkdaE5WPj-WBcTaudpgm0KxGADXuG-GqREXJSRohHsXVjKn6pOsjvyAlI7JAr7i5NIN3sIZEMbocfNB78Qac5QPKrF5wCVMldC_uiqtfP4CPvmJgKUN1WqXipek1uv9oYuxzxrjIkPNshEdbGTBhbEnr1cxv53Fvxx8tvEXyBC_1mVzSzcxW6H7s0BM9qqefJKEuqUza4Gmh01UgGdjlLiDfmi52cYvAJ25QYKLeXX8lS61WeTClHnAvB_BWe9AJVcjkQJyao0lqkNuK5W0N5Lpas8QwSoOMLj0FD3CucKDaf7JbLuX-IlDnEjKWzgmQ52fmxLaWs7oB_zALoiEk4YJHr-S-xmSB3vRe0F_NhOSTf4x3kls6NXgW6s0n1J7r3D3AMHyzunGD9wCwJWN4VMs5yKDZlKyI-SRBnwfcLLrD56TwrNqnVLg1clAEqHPywF_tvgEpp5FqxfRkrDaA7YOQGQG5iYt0zraym6mBt0S6aC8r21dYrRpFjUWyqf8665YTnUV7Hb0vLu58VBk2j8iNNo_61zkHjAqkpl0Grv1nuRkd1RAhsflW2Pk6oIKIOZKDdufc7VJJpFNQysdx76bzZGIUoag5qC88BeXtLcnwPWuN--gOu1P5SlK92_mnq3bqjD2trncjW0Di_QRsqBbJqc54RRewfkdu-Wcz0GkSncPhuUou26gFKwXI_1UeXHgyllnsa3zSXSBUirzBKHOlqryyPQcYDucIUKEJrmFCdavEcdUK9NMVd5rV172f5jsnzZaW8Fge8lS0oqp79TrSXYS4BhSMwaWbqi3o_6CmEAQEqEbcekd3KfqwxVGUKLuBgw-kN954U5RVNdnyuCnWkDo6s-KsBg5Dgd-A0GuhdZuRgx1exVmNGVo-brojO7Mh6HGqLMejyH4ptQOFDvl8Dwsyo3IE7tkCgXxcWlJdwKv9r_ZeugJCKYpoIkg_udPR7qZ68i8tkGDlTEGAZ-840XQQjNzfNiMBs4DH4mESGZetMpoKxfkses24SPo6ZrhU9kU2cuDGFUYFd9UZ-9Yukpl3uhjCQGDaiVKMPXtrCx3q9NgZ1EgAyaQfsWPf3JMV7oSEo2razQZGscYcqioY3pgYh499l2i5TZz3WnHht_6KqZUvs8vxtH0PN-0jPiRlQmgCMMzVCwWXX-diGTshoZs9QEjemDAkwftHIFbMarLxd0IF8xVnXkDRZCToG-bgtOshbfBWhzwqlfBbV2NEX_RxS9uwTEkB_itlvaAHXYWbCesKQltWPeUx_h6IoKm5jb5zpEGtyifMo_1Q17xZfgdLME-SzJBz8Tt19y1xvFNj_ZPVhxUL5nBf8XhmcPua9BbMLasHiIpe17E5h8SsUVWA8xtvQDp0boG6XbmlrIoEOlEC5b6CR-zHNR8EMhuzKlYSQWAPbL3APkbepCFEfFTCWrTcWOOAgyGFpEbergWQoQuzpUVGbcU-yAq3E8xKNQkd1Vc-DmbYN5eaUGgZfHJ4SIeFAP83_AIk_u04AAClrxEw2mMqad2VwyhrLkRxt2UPW_vAeSSHnfqVhDhtvEaUzeQlpk-WE_Jt67-1juyG6DL5Tv2J8dnaIFU5MgOqQqtOL_UWF52OVkeioFBKR4bjcSTU58lVEyW5N-jXcYiX3gsx80sqdduZDPPbBLLOyK7VIkcIprt5eJZ8Hg9UMxzQ81H-j28gGS45ZmDQXw-aHSyHZ1hOPWhlLx0DLscDo1TAmolLm9WHXzcMuSP5lBlB2Q2nx8ZMfYTgJa2Axncete0VP3RDEv-Ff66_4-f9eTZEz3SHV_4iOwKAvjWnaLoJquc8rNe6Mv2YazYmdbr7f7cHVqbLVSi9FbmeSdTh4TfNOcTfYD6tGpfL68IY-MSErBUhzJwLAhXhOjcjaGn9eg60Nau-HapJUCVz42ckcfJ9KPci6czsyPREBE5MCJqzGPslq61O20N7MytzNyOR6CIUKIGXrupgsf_9XgW6qFbKwjtokVzxwv4I0V40627E05zfEKcAlqQNGW9QJR7nv0xYhdJ0YJUo-qTtHk4SJXCFEaPtRs_qmC-Bjj2pLqOyldMacDfRzqPVu_73iCzYDz9C19y83yfY4RdN4_YNtdo4UYM8nuJnsFXddCoCA0Kw3YKqxt4Vv43du0oJHKenD3QPbTG94Ezx6ara7dR1l_6kQOEZ7vfkhC2P18w81_DYolFDwZdN2vfIk6hXdtbme3vWy0S2H25GHcAmJTlqLlmWv07zwv8MUV7KL-jIwo-tPef6aDMth4MYAfbYk2iVspSr1RwbTOANkMQ_tYa_EOW4rWXELelMr-QdAFWlK6hqqSCGxHaOTN3v4-x0bhVKRXUQvBVAYJ43eLVc5t-pO3Y_715o-dhZx2SQiL6GXyv1xbwJ8owOJmyIIMuSqYxobb3_thvxyMGw87BrGMTLv3qRkqxeE2rjKgJZx9VHnIkY_FvexZu"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"new_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"replace_all\":false}", "call_id": "call_Q0PnRv6pYD6wN73QtgSrkp1Q", "id": "fc_0ef6622055025d64006ab48758387c87d2bc621897a243318d", "index": 1}]
-{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Reviewed by the project team.\n\nNext step: request a quote.\n", "new_string": "Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n", "replace_all": false}, "id": "call_Q0PnRv6pYD6wN73QtgSrkp1Q", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>Tool · edit_file</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>01a0d130-b2ba-7b51-a5f3-f41a7e28c72c</t>
-  </si>
-  <si>
-    <t>{'file_path': '/target.txt', 'old_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n', 'new_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n', 'replace_all': False}</t>
-  </si>
-  <si>
-    <t>Error: String 'Reviewed by the project team.
-Next step: request a quote.
-' appears 2 times in file. Use replace_all=True to replace all instances, or provide a more specific string with surrounding context.</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>01a0d130-b2bd-7a82-883f-0c5e999c77e1</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0ef6622055025d64006ab48759c09487d298655cb503a07a08", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdcthrju7877DsObjwQyCCSdjIRUHSWNT5hAz5ybhTfFPGQ8Q3lKX-MoCQKa4rh157fYayAhD1pVM5cPsbv4iZy21zt-PTqbGjF0Yp8uzWpV3hsX-sVmoMNkZgXhmXygx4jP6liTcRdommUM4kqS_MbNKmVbrh1Gw6OtBlKf14e-Ni7g9PSYm5P1oxEgHAMOSAOwYlCXosuWjycLRPY238Bz5NKxETjcRnp7vo8HxviDbt1x9ujLJQYHDKhlsSCz-xRTNb_W00QdRW6f61SE7HS1G5eBeNkDHIFb5YLlSlDkvLUyO_LR9LqSL1o_fIytHnKV_L0anBIByeyE_AnXArVi8Puh_bF3zwwrYYM7IX4B6v9D2L2wXBKq_2OxmqlsFsj8rlfKsFY8R_EfLEVaMBiwEgp1tT8-Vupy_ZvWRKRNc0xeNR98S2Pe0kMCKjh1fOLC7DDcs6CK5lK5TCLyoCg6K3FhMmAJBTnwbIhJYblH-h3e2MWgvrctYfSPtW_LzccfBl8m01jsSTMVz0AlDQ7C0uNCRiHTPDw5G571fa61OzBkL_T0pWVm77T-vhhGP9AnVmK666VKdKC7Z3DeqEtdRkDuOOdG1Z5Geqsu0lc85old57pCVjkkYL6yhMCMUWOWi4_8kCiOrWOWBWVkk7YPyQjE3gYXUu16xbSBiswK3OF-yeWufx1rihDumHgKn7bb_zMC_QzmpvjOHZHc_cG6vw24SeoY8Kz-AKub-0nheFZMgxrFZU6rdsBwbNXX7pOsyOznFwTkZcZ3V7WSnrQwmnA846QscKa-u6ZTgyKsVNOuBmnaoZUUMRJufnZFoSpNjjFSCEoLRCt4j4jJKSnpGsvg_C_Isubyit2D1_nnA_uEdR6gHyYN0taFq05e6KGlDzBKj76tn9HD84Cd3BuHbK2aSff0fC5cRE-t9nFyN2DTWZyphFaqnBIFxpTlFb8KB0NE4j-_v7-0rNFy1YoJKc9lDkz1oKWyk4JOeh2AkLBzQI-qN-6b0q8sI9gboEIsRdMbs3zdI8eRWCY2eqrndkDXh8CWVdk9NK6jPsGde4WEJimPuE5bxbYzpPUuQls65LdEy5a0bGxfkKye0_nb1l3TShMuD0ZKrDP8Uves4HUcy_9n_hpDfX9fl7DACr7mtUelrw2mQKlQ86j6KuYGEzangou4ihcbjggD1qcCz-RhOAJcxSj3gz9KtMJsiyJ86IvIQ0Ea3ynJY6IlPLZj09wpiIM-o3mzj9NpEH0Ch7ZH1Xci72UfGu6ySv5COk_2HDIA6PsSJR7Rxg7Ql22H1Q281b6hSj_clE6_JM2k3dpAtT7Zg_XiCzLE2aMc8HFPMRLlWglh3IMF2zVhiaGW_WxVG5IBwt7yZHg0jV-8zWdLX4jOPog_-pDYce41S1IknRGLvsRKr6ztKLeLHFNYss_x4qfx2bry8XMuqK3LxUlGn21-xXPTRPXRGuSUPQuTv_ed4r0hbJIcfPzOcX1oQk8jc6rNfb-1JcCrTAxmd0L-dEPvEVmiCMoC0eN_iSG667Q5ez7_PkQpGVApll70oQQ5HVcvCmTGsn_FWNjiZNncqTK_Dqk03qh-QJyzbdn91JD9e9_z5jKuA5CsfWS1fWuUKy419eoa5V1nEzcKT2jGnp22NzemrKy71GScd1fPp8Sbc41EOMcJdHMz9gf2LJKQpzjwGedTkYMDh1wqdrly-MBLN6AKDNdhclWqg6HCZ21vDERH100exP5n-D386sBuHDO9fniQ-Hv0iE630F7uqnpUCq8FefOXRBJvYv4N8nB1AOrNCbe2-ndXY3ZcoIC2TJmWy_ezT3CUJoRTN-PErOURKWxnfln8NA4grFJu6vNt52TIt0F1OHWzvzmD7jWy9_d29eIVnqVUq0-pWcMe0UOFLClF1DQbAN7P5ayCfMPWF1ZIj0qxsjxw-xGD4pN6K_3jKTTSP1WXPjiWF46TJ_4A3_c3550-MqzSf13K2ixQpXzI9j_0iUWkVWxksAvqvCYQwMLMke0lvaGRxLlpS2gDbM9t_mHXLAYIugLM_UuyYYW-tH2xur-1Rw57fqN-J3-S9Px6Rf1rRneAgk-Vg5AMpoSBB46iDpfsM1aGyd1rwiD6qRYKlZXSXZjNPLC45tXUVypdw0VTYtDdW_vkzyj3JkWvAyOpLHj4am0vTEOmAHm8EdNCLKFCj2E8fiD_kLf3GE60IvhC9-yc1-sDte6e252DIPeLHbGImjqXkiWAbVfP9gSKOZSHRQihjclLiVkFDdDj6_ZmaErmN2J6aK64p7e3e-Q3Xc375D0qyLaK3mPeLf1TYrZ5kNwtQOVgzt75DoxQapcX_IwYl6Oyle0TcNVhLkG_gpamkduh2dIJ0lJQ7FR_h3dpAXLx9X3f9OBYLm40Dq6FwsW5LbUWfV1IEsFbcqXxHB4kunfMhady4uonSMtvopdjsBZqemYVQGbYSiZSmAxvhedxJcpm0zyNFve86qAaPjEAxhb"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"new_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"replace_all\":false}", "call_id": "call_Y2rxWvjT3QhCfswpZawwdILs", "id": "fc_0ef6622055025d64006ab4875c682487d2816703e11f52f9ab", "index": 1}]
-{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "new_string": "Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n", "replace_all": false}, "id": "call_Y2rxWvjT3QhCfswpZawwdILs", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0d130-c984-7c71-8b2d-b849999f5622</t>
-  </si>
-  <si>
-    <t>{'file_path': '/target.txt', 'old_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'new_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n', 'replace_all': False}</t>
-  </si>
-  <si>
-    <t>Successfully replaced 1 instance(s) of the string in '/target.txt'</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>01a0d130-c98a-7450-9c4d-6b109245e6c7</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0ef6622055025d64006ab4875faa2887d29700576a7db43439", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdfBiRbciJx-bmph-twdFMewWo2Je1ERvpswm9acKGCOgbkHe8A82hEC6WFbAwXNgbms2VUOXNEpZG0B4exP-QFKYKLti14XiqStp9ibebBwIMkPdWXFT3D9dU26z4_H2v7Zow855q5hGXNzd0yt7XDuSD0CZaaTBAxNX1onIkwpoJuhSSOjVTbBcrLkouP4Po54YTFd46YNw1GoE7Acltx3EcD_69lMy1DPgz1-OgRj9DwXQxecn3612dzo35JY5NpCIkcAFMDNIXfvnpt181GloFxOSxrkn4P_OXUYRV4UJ_fuM5JdI0S9mJA03VNplz9C2zNHOp_DNQsV-5nfMkDSFtsN_gXGXOLZJomqjjq5ZYtCR-8wX_nXfzssGNh5D9XHcEKll0CUVejiwmWwNA7y5iyAyITYezS5i7YWVxAsev20L0w44gk0dSsnw5FkKzP652Q0prSwvLpuodbq14GlkxDJzVzJvA7YdawF-TnEvp3_IeE2teDTFDV58Jgvf9jI5wjz2Y5AnAmdex4v-aMnbNeiIjnl3LDVxNWAF31unB-83fItWUmdhYVTARX6RKM4uiwFQcJiSYuM3t_M9uNjM3k4QBjdDFAlox8AoDXtpSKlTEshJn3_RkZsit64eUByBxGF9FFAPkqiJAaCaQa6eNTbXypJMGKEqnrycZCm2R8zuZL8ng26-PJNCh931dgfWyN60NLLoAUl4RrhvLxfnYBI6G1I35_vh3NV45wa0xD2bFqzFrHTgYd826UMwKoh2KlwNAn50lkw3JTIJ56-QIbsnF6Th6HQZ9wACcAEyl2nunLJXE-rYaBZp_Ea6A5Kp9jTvUFbycegi0OcpXOnK4yIhmnb_guhw41g0jbbFow3737u-xls7ZH-nQtglT7xr94IbY7O6XdePEuYpkwZGTILrmhliJLiFSFzjp-YOQw23-ywt2Hb8j9QimtTZ1mPh61cj6Z7NeG7cYNXmOZxItEjeiRdSt4kNVR_eN3HM6JQSm9XJh2BUV8ASvHQGEfREUsHFBEc7KS1wa71wUhJCsEOddH9CBYC2m6EQUjoxt0FXULcG_3oOUhtWYQovldWddjAzRxLt36hh1AzzSlioPJu6EqyBUKhH5SeQBOyO1x84w9Y1pKaC0udwV964-6ZQIWo4Lh6kol-YsJ3BZQD7_APzeXkei1uihjl4UE3jo="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_TI1U6EUBXm0mObAVRCrVP3TR", "id": "fc_0ef6622055025d64006ab4875fd73087d285137c9b5ef0655f", "index": 1}]
-{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_TI1U6EUBXm0mObAVRCrVP3TR", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0d130-cf46-7133-8f0b-a88c91d0d644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@@ lines 1-22 of 22 @@
-Project summary
-We prepare clear, practical reports.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>01a0d130-cf4b-7750-8db1-e7b28921cd5f</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0ef6622055025d64006ab48760f99887d2addf2d78363917ca", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdmCrtVUrf8dvapWHYcoBH1t59i9cMrkQiQBhh6B25AqQE2bH0VIPh0p8DrBnDnX6MEZ8d-tSGToMAAV_L_imFtRglasBTuMcr48FrYnolI5SvhG6iZU2rFhF5xnbvd8hX47386-x71uzd3wImL17uSyoLOltlM0uTnfuGCm_5_fj-5Fha090_XNOKf2ygZFtLP0-PbuXuTusBTsim0ks9aPLe814CY1issMXCseIz85dj2rbb7USWXTTuq76sRGhUUejeO555W4OzDwuXFVh7CkkjUoueDN7AZc4jgvpMRmbML-_afuczJ89IGg8mBfycplcyp-OQ9mQL_RA9M0ruT74na9RajNqJuzKlLhotg2gaFYGDp1zNYgaTaUmi9an75YHwoZWTZkhaqZeGDeqcMMPZonyUTOqmZYpLPfEDiXqlAEonhJgzzBU6eFqEUc5KkFOdBysGqOcFef1BQYHXnV-kRb-XsRRBnTUnIYg9OIhFNQJgY1fI7E9VJc3UsMhvJL6MyZ7SkthzQUltC9xSi8B9CnXUM07ZlFTnA0lE4Aj0iN_eCHEJX4oHWlqi8NYmtav-kq9nffZjxnrtn6-s6NwcW9W3j1Wd2z0XmtWMweVxdlpn8hVtquA5sP7fVRi2c5I2h610q-WRQ11UdAstzVNNF7H_IawU8qeoA0ifBxyL-yppccTIeNSVu3gHY7CR7XkYo2GKn3993H67C8wHk8TtdUtqT1EveAqtiHDfxtuD95KI0WNBEf9y2Apq0C1u71Gy4cFBI_MquBGZXDfYPziI4bKnOdIEQa-T0xqeTl3-2pZ83a5PFE7Z2-ujRVz0XsKYVpm8JnUW_vFnYLs-64zr7qkr84ukUs9j9BtuUwm9EeDQohypOfPInw-TcjbnaF1VHS0ZA6aiKKt0kc9vZfkckrhdUE9qs2OqcvnNGtOhskg9yiNuzaGrYB-UHNkmJ_o_UPm5_R-LVvwG6SW1mLQATcv9YsjUEhIJF0yt2yIddQgXBpAFOPgach6_lwOYAhP862V5VeKxykB7qwGJ2GRg_d48g58f1yTub4d0eykGu8FbJUaesyO21_LiskfAwC1-YnfL6LfcUeUg1tC1WEAu4aAEueoPzUfAqowLW5fBeBJsKaspa4jY9qB3tYTv6DC7BGuawXW5yyv2_b5mNca9RNV3ICHifmQdif0lYi_wzPSdSw_LPbf7EnUZeGP81hiFF4ZKIcShda7qFjOxvgFJDOtSljvFpHtgLYdFrtHBwr1v6qNCKyfrRzUFPcmns6LY_gh3U8OP9bLdidSskWiXpgWE5pXGlKQ0R6QCb7e3Dbe6XzFm_nj_7pgqwUD9LEAIAX-iWaBpecHhv7npCHE3xQo2cb2t6bbz5UYXhfGnzTHBC0URPgNUuJa8K56yAIBJtCLju9exINvs545JfoVLnHeixkAE9HcMBMnIvvEapnSOYt49TlyFPNNXGSR3J6DSCUch02J2CU4BdyBIwrp_f65ScuQSNwaQ-fzUlP3gv189QPY9VtNdef_LWkqArODw1rp092_ePeIqmBxVNS07H4kuqt0eRfnmFBSiDGTOmz_shWTK2JIJpnGwgu5toobqZcNmCc7onsi9l23pspxzXnNR6Q2vOp3k8yjMfgHtFzdNcT7eS9vfiIwB_GuZmML0En3hVKiz0302msiyg8-xxJ2E44cW0pLfG7qqSestGp3WLsVUe06riasU1kwwlKCGD3cANfMBfHrrqRIJpdQHKmDkeoYe-ug8I9IkksTAAvuI-8tZsQQoTAvNqa-AZL3pzlefmwhUSSmM4xa161tJHWUK7WfVr5LfTgxib39WdRjqhZHifz4hxbKOZX2PPBWwdV-gXNKkjoL2vR6viC3J4I4nYxRxZEtxath3SqLNEW1Hd6d_wCk_SkJw5ZRSD3tPckEQPw3Mg6cnHrWkglm_W8TOyUqlfQlRuB1xSSzGdMryk2dbGoh2E0Hv5VE55FgqPo1uzUcV3tXxccA95u2MXo0PpMGzvmo4P386miFoT6UH0Vo8izQDO7MvO3dNY0t1h2uQ8uZEbqSCNSzpMPeroO9ATZPcvsGLQwcv-Iwcti5Jk--wpw8iY_Q8VpuZ-DmcA0nKRckEH7iM-vCialH7HoYgW1x0SYuaMyAZyvyTqmo11MvOEs5akuO5c0ie3l5MmwKgcJpQwYM1hX4iY1kSZ1BNYkXkwP5E3j7SgZvw6uRDwMLNXjeo_eRuszcQX7l2bkQejDg3w6bcH5cg75ojbL5EDZF0hQr2k9AGp6wGI-IjVYoYgaasszkEz6v3Aa81Nf8K32yK3dl29zDDss6kRYmvPnU9mTlxr_e0clY9ToM5ai9fC1eEm30-5aviuS3cWpuyCGF526CmxxrYU9hnTbxn6pfP-Ta3RaCoBgSCYlpr-fhbqYCeJyTsJds8v_z4PeCUZpLLJvAF408o_HULntDqrAiATJkhDWQ2cauGTxR_hZ2Dsm12Pxhe0kLy3HBNw8C0U0oU6D8A_dHtIoTP5Cr4yz93SfjXex3XbV2smKtzK6qJGU_2d26oMdxGmpdDyJ2ThPenEiPjekCNiNZQdJpor5JYdZjmZRmDdtujSUg0mivoJR9QA5dIg45891Mf_bNPFoFMHKfwqtnoLsu-WrSGBFJrBLK8L3TmOlJbFDTafc-jIS3gmlZb1u_rwZ17bKBY3vbrLnNJAOWd6AYolEqfk4K0Z94IdNEf4KuQwdxCE0yBlWjyPa6QcdYUgG496pSS9VNKin52B4W-yvc3p3eJxr5qF8-siZ_NMFDZ3J_aFoq3PQXBo6htB6c_wn5Frs9psCCDiNWwsNGyRm4XHVRVwUjm81MhUTQfAas2XgcYCWzKze34IijbG7Qegb2b4CEMyafpHTfP9jUNOs7njl1UaMgfSYksnR6s5gBQT28VL0wCgNIvy6rxCtA28dv8jo-urEdKId_mBFDIaGFEsAsqoq8T-fwDdOlQ4cWqYHPIR_D75Gj0qpd2MhGWJWdspldwS9W0xOhk_1hDnahKGYMpr7VWBZ0OTpCivsuCvzfzMZFqVE4qesOt7CN6LcWIiB6ALa3dTuX2_dE3Wphkrl5ckI-8eLIfggtrtY5nx03VaL16y9jhHD3FbKou6pSzk2axPXCR-IRzifTtwIa4cODdFN3XV0G_uN_XzzEVtHrPwW4z62x6FeVGFrdEIBZGiXZo4AM0AVp3tfAivmb-Vo51K0NyqZnyfniZA2jG7dpU1ypIcASZZ_3jxkPMtwaGXD_mUIsmBacYFXYzKAKz2sa7HnS66RDE-eKngcMx6GUUoNpJum5KNAGqacADy1Fayz0AOEYZ2XxkXEYYsYGR01yeVQzizzjigPsJLI5ZZ2tXlwGW_6JS0FN8WKDbnqtLzZtLTsfpod4eHTx6KYOvo0pYjP--seefBEgRprsckJTle6Wsru8SwQjTcnqJ0-LCurWcsvzmsilFuvVd9cYSmfq9wRRJn6nko9BAVV6eUeWpeJnWwaclEd-tCFHhWZW7RTOmEu-i-9l0Yoxr2FsN-Cj6vCKK_JxIW6M8h8Ls3csJabBtwyDSVxLlFlYX3xHfPjGhq15IMu1HSw7Ze9h2xCgjF8_7ez1B8BaVwbhGXPLPF-cthRacdEVUrdGKJdBU8CSuCi1Kc24a-lxXSQfmYvKZzIsoFNftnU2a_CU_FX9aoSNGLQnTv2iGrzEG4"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Next step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"new_string\":\"Next step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"replace_all\":false}", "call_id": "call_Pw1xlCeoafd8hbXCttLkeeVP", "id": "fc_0ef6622055025d64006ab487667ec087d295acd3a047ea9e18", "index": 1}]
-{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n", "new_string": "Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "replace_all": false}, "id": "call_Pw1xlCeoafd8hbXCttLkeeVP", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0d130-eb89-7003-b91c-df3bac35a355</t>
-  </si>
-  <si>
-    <t>{'file_path': '/target.txt', 'old_string': 'Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n', 'new_string': 'Next step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'replace_all': False}</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>01a0d130-eb8e-7e80-becc-c426dde82204</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0ef6622055025d64006ab4876870a487d2a03dad331d688a86", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdoJQaCEpUZdzT4Q9srZTjGAjeLoDcDohCar8kKAtbCqA5L78MX0eR1EQHwUFJjQ-nTZGGWyPJAGdYDiEJGUbDwZscMq93dF1iHzJPemsHvAH8Psuymcy4SRPeBuIb4eTLpa9jJBtyGDnxLUyHQVOywNi1WY3dbPtHFlItEiFoqdlqTjKWQOiF7tObEhTj3ZEGnKxf1dG4d2181PA_Ua-jNnQBLBwZFWFsIpIgP4RdaNBTyvgcr6T4u7aO6K9wVOYmEJpjBL2G-Eu5wurQ2d2Ee5WIF04QFRTmVCXYNYKtwh025cIDr9L23BC5hMBWggmsPnuAo3liYOK4QiZvVGCetYbw7oEulCfBbRCbD15nxruxeQGZQidkceGOJjmGsb_Q8FNyw9-pttrTPUoL6HRfPyMvbYqdYgm6wzpI1qfZLuSivcUuS3yhbysPxY9kiuV-4GOpPTmLAHY_JRH6suHdgR0OvtLFVHwzYb6DMI8KL_lHMUwakKqI9qVe2NBGQUuE6M4iBw2ZpW8oa59qfS7fcmoKidMTwrBxGaJH_bK6gqG4br8ISdZmSXm1wjh3gOuNFHp32WBQs0M8Pybka9m595IhhBdd04f_AckxWXnNlfIscf20jMiBIMzgzgkxaBEedMMPqMirdnTxNV6Tte0Xmr7HEJJ7u6Oi8iImIPaQEP91Jw2kjxWlCfAnoI8OjS3cwbZvjda-mkx-rfGG2D0zxIz6LZ9d3uoEyyalqDh9OObrQWX0bWVaexxpP7TxX79D6s6DFa4St9tPXDklPOiue7Q4nkenqE98PjcQVP2k-1bjYJAjWin5aP0l_aPQWP_u_vgq54lKDDtH8zexkvoANDKyMJLgCU9T-QVlIzh4c3mfaEDpG2aKGomb8y_uyWBTx1eSuBy0yNFqUN202zk6hp2mS-xbPsFlNMz8we3B0Htae7FilzmR93ux6YYNXS_rXIMcO6LY95Utv5qnVT-m7Qkx-CtZ6CSCIWHzNYfdtmBXh3-jjE7P1Ip5vw2yMAUz1g1Jkj37joCKQcmF5GMVUUQD2t6rx5tlekHzQlHePVJUxtVPLuFgTHqm8pQsgxKhEvcPoHhIIGLFjw6ZNoSzlP9s_jIAKZlLMcr9UJx09E11uyKF9IyLRS3Z4eqsmK-BNZNzPP1nB5OxIe4qecfCNBiJQq-JQBqavB2mWrp-nZao="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_HxFBvS8kQDTipCZuK23BxrvC", "id": "fc_0ef6622055025d64006ab48768a62487d2b6188e48132301d0", "index": 1}]
-{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_HxFBvS8kQDTipCZuK23BxrvC", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0d130-f228-7e31-821b-b023dc110761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@@ lines 1-24 of 24 @@
-Project summary
-We prepare clear, practical reports.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Reviewed by the project team.
-Next step: request a quote.
-Next step: request a quote.
-Reviewed by the project team.
-</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>01a0d130-f22c-7513-bc47-bee808061d2b</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0ef6622055025d64006ab48769c4b487d2b8672780da658a8a", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIdxu9RAU9spk9uPhfkZyY7CDTRkFQWEuWgRAX4u5qqCUPcCZoVkP3srdtRGw6fqEgNWEx7Tx2dD_wpBeZD2zELGDbJpyRam9IiNHykFKXDyCC5JAV_Ctj8afpXkFv8OPlh7EWbjR9URn2QrzSeydMJjpjxa0TpXyv5SGicrvwMcAkxYXffCjQv21p11lJ_Dyhhbsbgd8319uPjkUxOeYTvkyB7w1CgATizJgnkfgkMd8UTAXm3J-bY3GNrYWbC5JrXr12LU1bwp3enyLLfxgFPZ_UdpxmyfJTL23CdVte5_NFT3mO3sRSDIQt7_EgJuETtH-6rz8hh6aWJE9ApCIlJvo8I6g0y2hZ9p7tcCb_suNByQuVU6CMtOOqs2sJwNKTAZR6gaxV2p1f1dDM8V6HDMtqxUqA0MCyh21d1Qald_YXTuOTmUnEWS9ewnGYj9jKZXD1TGPAUI0T3Ra0MjUdA8Gbh5SvlHLnFI2N10cmlBJkdxQnHtZ63IkcAxEuTlq3sKYfcK899p99XEBkoeiFvAHs8tNfNDudjkMhwCW1nUE2G01ubSuSbMIpgtttiQWpfXrpKBvfNn3uukb2hJdroc4j4bCmSX-EKCOg8yVmdGZi9OGGRRzFHbtGw0_2dp80UXrud1v5XSOA1TUAqgViDnR1JoacOGgQAsp93kizNgoAIcKaF3KoSY3-3iA-XsegngLPyZu17ePhjjg-QEo7SG5j6jf07WDbqDyr-Pl8I47kOLD6lXXLhgFHNwRhl610l2IkVDrMoCJg52tRwxMnuW4I1RnmFb0zjvybiGZqKmq4DZuo2JvZMm6RjTZbN2QmzzBlv335QvbAu23Eh024uBdbdaAiS6sXxucLCzXU4hSmB-9a_hQKQsk8mmrwl55fqNzI1vA8uKXShEp5ado1c3InVW0OxAJT7JFKX543ZPyQXMLbCHyZ0sootOItkuPobWeLOhK8bmWflU2w63x_u9vrPd0o1CTXEunQcv8W7dWMDeSAsebnKF5n4X0E70-td3Nzm7I0GM7w26AtMQU5dHbHoTtyBgA0wj6YBftMP2X9-JkPZUwfXK3PuXGNkdLZCbbcphxGic2TZgOqXxI3CE6VPG35gNMHM5lfac1mrYmZdIphIo3tbW32ETUJpUTY4MxiUGQUyOuNthIXr95O9LaAlOyw0oEuBsyWRuI6Z4zZITkSOVYQjTzBvBOfxGegOoO0RJ_XPTCC-qhZWWgVUddrHdtuHTenPAi3OXpDhYT23RstJC3b6XPb64-1oLZ8Y67qS28QEZBIJMQDKaKCWz8b7LmljTc6DPTlBI1BirVSOl2-nw2jgZe1pCHOo_uWEA_nw4zkPDr_eeIZIS2wOjlEhcXwx8rt79kH4XdTf5rR_PHmaIaV7a5oYFZkLzTyqzjz9LLf-7s0EqeHuZoP_sx-8hIMZOoSwzJY8yLjWCyrJA7RfFEmTmghi4lu0b5IrNiUMc2YoM9pODbUq-rYm9e2Wb6Ad5gwOaz3EEBb7rAjFeghqRx7HWQD1pvn2kHJzOPTVEJWt29rm7LUffN2xPapPxCXTnRh2doD5Vq9ZMvaPK9WpvtU9k-VKCtF2Cr8NMrGuAzBz3M1Tw9nIMD0bp2YJedxQUG_Ut1gZH1vpA-2VGTIeJRt9ilQpYDeTFn0NTZJeIQvqbNQVlWPmJvlcXDp6Z_Y6SOZYauegy-tA7oobRaXg7KcS9cT0JOmhW06Wab7LSKnZbrJgAsM7xG-5wct05L5--PNmW0vLAvGE8QnTkUvksUChi_UPu5iWDSzDlwN43_TLBLM4exWWmKudogRUkfvfoWMCUjiWT77ayw4zTKitBmaezDHtNzDvxGn8BZRT6YVoe30FQq1QEmjtZapk6QYl2miTRJ2dqnY72H_UOHceTCxSrivQIuCxX0qXqVuXOgeve-agib6cOCdQfhEl7vFe9ieNVgIQR3M9EYl324mEQdzCYdVmGTSspZwy6xBYglr1BQ3B3of6dMq5jCf7creB0U6JQ62rpRi5rma4R2dfxWdGNuEvlgCM94_rH-J72RTmdjacZzW-jRROloG5EaeOwpBVprXZyJdBNL_EqK3U6a0G7FespTb5XwXhQSOAlxUNXWEjWZXrvL-wbDuEXAbNHEufFW2gr7grwoutX5tD61sBx9Xewur3qSVPRaGoR3-UmkcF0scCKK2vYIw0063w4odqrlou0ceJ8R8SszMamOBbYQ9nRb3xOHzjp9KUDSACKy-a1czykR2Lq_FeUyibigM7vaKt4MSwOC6sisnZ_d13AJIzBPmatRTgh35JW8bsl_GuV1MdrHygRmjZ7a_NGXebI32VsSwuF--JB0MV5WUt-pDh6lmbMhG_Rle3rfckXn5yxUK4DJA0zIWrhjRlIPIPlO5NIvw_Dj1d31YrwkNxO0cIhrTK1pIdLmX0ceFlb5vMAhTkslkCGJE6AyPmIzWsnIa8qfYMsiAP7DDf-T5lijyr4uMyQZbFxqBHBARr6sxdekf1GPW9xrI87yiVHdo-L1F_NdJkdUlrzxuNncCvHWg1HHg4T9F4zVKwEMZXqRKwt6fz_YfR3Zqv3qKNJgBR4WhfoKp0XCDluheH9axciLXeBhvpXGrui1UWmV9POR86yPq_mpGVvCKulaToqwP7flL4D40s8WDbA0AYJUOMAu-fu_L7YLlLfKKhiDzhVOhDUX0P1i9bIF1hYksLKLUNciju6DXGD5HG6PjfSZBIZkCjQCtyjTVceVe1uFsY6WLio8Bp6PGS6VYPIXHldpD29IafJAPV9fypbQaC8xkwLzrc-KkKnqp33Xzh5KynugJHxB-c_FJBA_p5-wXlPAvgdkpwzyIepIHgGZ4OnGGfuXQhfVnsAlLQ2yKjV8B4T3oT2wPCWRhKoruTLEgidjz5iBZx5kryGzXWYiSi6_6eTA4GNGRFIC5m6yqN1EfH_sIfoRWtjY8vK8xpmomRcjHioL0JNywywSAQK-qmyzGWpONwdaflgX5zXdMkE_TCEUz4BzxTRSYSEwuts7FNld2QMP-nPXTn7ukPQLRl8hsVerDNxiuD6fUJInHsHHlu9D8fHF8RyTTgxBhT5F2SrqO2ST-df3T9jdJ48N3ULoXaVWmubro61nqU46WnN4Or_MfPjAIQwTr9YtHVuIV86myIF8-42cw7EaTtN_lavBTgLoaOngkyXhGqrH0E0rBqPMU9q4Ff6WqLtb8dE9UdDowfdqnli142hBWbVC90GwyAyps2cZpNkgm_9tv9305cRJ8-vgMdU5Pe4unUaHWyD0YoN5firK_TDMapAeccAg2OHpYfpfu6gaMIm0yh2dpkGxSqjIgA91A69UpOzyhSfHFQ7lIMC7jWuAgLRkGWKEnInbU0NV6PFGiFL7K6B9cDrYn5alduXmkZUjCMuR8JPh1KJbQdxhIBf-igdCs1nZnscyYmXAaImap4gQNWBIcZxDX7OBFiDedHvsmFI921sYQHxKGqFua4y1RCnVmPP5t_xOzcRvy2_Y961jvlvifaE9q6FA7JoyXc6-YmDduU3ODfcFHassu96tg6FZMBYTR76WIxGA9Z6cw2sn7fFiMbNAAGqDr7c-BXH4ttj1z1SBHC8ZbFP8DJRiaFipFdAGl9UrSKK2i5_84w2umeZVdQbPV6lQHaxtBd1HXqJmCNLKdwerQ6mDn3krHbKYchgZ12B4oCQqWM1qqoqgIkUv6UojcCaO5QHq9kMJzN_HRuvwYBECT2oFwEXZfAfDM7CisZDympjbQ4Bk46REf65OxsZq02E0kklXzo2dvnf6H552ZAyzKvsBN9MQXhxei5wn_rhqX261myW5y-bZa_H1WTQ5_GvZ4HS9H9vOgjoiahLASKfRZjpV8Feqe-IlKF-zO4efWCXgXlgw_Dxu-iIzZP6F0rz9yjZyp1UKIXlyi9d83CcgNiEuZ9nCGy3smYcHID431-9csgGdFFatIF8snoji9wf40yiL163jYNdBYCE2H-JGn1jr2otICrp6j51xn2mV5N52iR_Y9B9SdwVZqRnw05z5Yt2yZQwyvlw3j7ziyJdGB6laRPQ5Uh-7etoXU55s1vGAJYZ6BPD2rrxJaWGYM52qG4LTAjbbfJQAn0QvIRn2iTxckh4XVV_h0FM1vzjC7T7W3fIWjRnKw4Nh4OQv6curSZDH4aOetW8TAtJ1Admb6DkRVz9wK_rnQ_P4o2rJW77KQ-YQnuEQ1nH7qRVBqxVT9FKfexF-1knlcSGWSs0iqg5iIdTZgS9f3WM0KxKJ0Kxgb9xJViGXcX_DXmvXED7Xh6h2h1mTXCaO3LxvWMFy-FaF9KORnTeitXePqCFioX7ANe7zyv3mXWTUikBIEul4bUKtR1kuur8Xd79mYZVd7rwmTMhve3cGD6xLlaZ3TCiE-EXpbl-"}, {"id": "rs_0ef6622055025d64006ab48771030087d2bd5821ef6b858dd6", "summary": [], "type": "reasoning", "content": [], "index": 1, "encrypted_content": "gAAAAABqtId1nefwJ-xHd4wTEOXpkIqSf-ueYh1KO0mULGm4fgMGrIQjAqzvTm4pz_qztNGO2jMwhZp_KQM0hwd9f4n0GnQEFFrfyhxM4-cnUjIgCBs-ZqUXSMcqUuzP_UMY4njx56QbUG5YH4hL-GCdTbAuvnPcTjtfIqoLhHLQY91wqzaJts3Hpjq6Disno28eKz6yB4pn2Yc_WBlv1lax5_iBvJ2TRDn-Zs653_BSRd56dLfAX1FTn-iu-padsFztCd7c5xO2DyvnVbj-TVgOtG7NYOHIjXULyijyAyjx82RwmExqTWTCGIOtrsW1SzHDHmkYVG5J5vmiQnRUgn0lOyaZHEVMvs5hJBuG-CIoEBmjdBdbh_Kl1RVi5zz0qLj7Y42dSvzAD9Tj0MnH0CzFK-43PxKEuZ0P1CiAnCWP5zG8YG_GCyNT00z73l8eI0MwGRPruXPrLBeOYd5LXNyVskPse8RKXhlCV_JzOMGAuH4I0nTG66HuVmPcG_Ja6278ViuwljLTP7bC-XbyDQUZ-MeSN7swzyTIJGypeqfKRiz8sbcFMLayJYiEhw6MMXfISzNIel7q_3yjvdxfZLHWyxnz-6u7lYZXLU1k2wiyhpEPfP4rk_pfoqNTb9nVrjmv97ZVDNbSYA0GmThNGfmtpm1bHpkewEFQNQEZWWjtzgzfcRE7G0GyKOlECog3NbSWxYGKa0-bHp8WMiz_g4z6KvLoHSb3CP39BT_GpZzDMd1Bs7qF87ux-Ha9rF3NqezXZ6MmhKwT_GzKY_CPtc-80yZvWQ9SW_mFg71_OCzHPfEiyNtD1kZh96a2zLzmw6SxKwpndtPXnj3YrKKEKOKgvJ3x5LcU3P9V5uj4sqEtbPCSsOWHZtwZjVjJ2MKOY_ubsYW6YR5cJkMnVcZwM4kip4BwNMsNUI-GYQHVZzy5Ai361d6nDFQMotNhQ9XdMoIVDUkQ5HQR1OFlQW3T17HJTbbByvcmtxfuXu8HHlmbnBj16_v3NDpmvqnSrnYVnvh-G_vE8s_2pWzrZR5BecufvS8jOs48Bsf7Ed611KB_npQ06uTt5z2ICwxgF7Rq7tGBZrw9vEipAyJlzNymfFUc5eoEGBVr3j6bAkLiMJpq847yDojAg2OxrVT5GtBmoYeALHfBq-f28IzF6guiRhxnKu90bsqv5Jza3Nle-dnVs5mwWocB5aoNYtipAOJeriu4OYv_xWYd4PNpkQKTdvjFPPpz3KdQ3pEJ8nuXWtSq-QP0mQBnuNznf46WymI8Lp4arI9JlJWOG4QsBAKqAWixYIA3yxosh6o5pLLdmS8oqjTIl6KgUdX0ElqygtlVxmuEZBmVVrtj1Bc_KPZqDs8AcXIz9FXarJeHv4jO-vHefrpOnE2irRJOCAuEx5JsgPMMutVkJQkzCvTTCUgMtd_GTbZghuQZa46oQoYKSaPTDIQ8l0_jgWvOfE4D-bQWBsmsW_k0B51I3U14DnYcCwwpkLLbL2GIc3vplKBiS3yoq8xoklcrQ7pI-gxA54Jp_LTpq9yIsvFEP_O1kklXvX-__pFRQPi8nZwyUgC5jDRcrVg7Dx69k76sIg_rM20VM0vt2CMBVcDfLoTpU-Oq2uBmeojP0Ldz0Pl4XZaD2dWjOdmAfoAHEfdaA9xtc4UwCFd4YGjS9YzWHEd__rIAC8JCIVGFa8fAKfEQ7dA6x2PCevWHEIRDgGNjH3PhiR0d6jkmTqR0BpsH6WADkp8iKwBWhWHiAhC1x1iWiOo0tEhaGXjWEMfbnWkfe2hRDlpoTBAmIxyxwraxRePOonv64c7L1wXOvH-A2sITnzhgDEddzOoF0D6CgbwCCXhdqL6x57tcqODYZf4-Z8TJZDvy1TRoKotexrDRINmgeWrIsXusFCNEB2nu4pIoDW5R10hzE4FoR9A9RLPFxZhj3J7W0odgtlwz-kddvTaiWDXXRA4okp7S3crH9_B_Y8yw-pExSHIN7RBVnT0MSCAXB2czm3Osl5EGUSez5ULfvy9z4Kp6AvyE_ZC0OfrMHUI_O4ROVy-hWtlsfahbRGRiVlqXwXlVIVVf0Wd5ZEi-U1WQzquX-2_e1VdUhURZmWDGDMtoXwIlM-g2daZhs8Y-UzzdQF7bg4Q-vSSnlHJX0NNsP570HBiU-fFTBTsqAZVBD7aByI2d4dYRCSsXA65SnlCvGH8Bn4YrTypk6cUcqwDelbxhzHcQg9zGf7jBzU24wlah8a0C36X4ZEjt1Q3_Vir8gpZRGkG9ojPxXKj4pZFVTrvzdfoJhfgM7y3FZ9EQEsCu8SuVFybTEG5nOHCaDfPyqenHmrpdPT5pH2yRemeP-p7enYLClQvD73GR0JJvG7dU0Vwl0fXSixCndI80NeXdSrDcLPvza1rfCnuSFHgFHqNUa1GrgrpEjIRG3y-HAG3bIlJM8DlfdBrY4mX6yNImCrTcU50GUKC-Fc8ntH-moIvZ4iFtQ9zluB0mgMP_3Apj_Z5TmCiniE6TkpOJSUVVc2q28-Jhp6FpWWW3nHa0GTIJNsXkcNYEZLxMOj08Jw-IkJNKxaC-9woVmw39j5JeFboud27M2FRp7-12Li5PC76BINwSRePkrFNlpls5DKBECXr7antBxNPRNBZeAgZuhBFZjWy0Sy8Xz3e7FHryHcikuaqvOGmdn89WTtyfD_aRyUq3Jwv8Xru2qcllZ2Wjz2fiu8McH0emkzw8lD_TK-jN8PmUKNciW60E-AlF0rrjiolBj7H-jSghzVwDbphdfDJ2-mvq8bkqsW-iFUqM0R4vI7XDprXuwcQDvf2jyuWaZaD2LlmYFrRxMsrJgZf2CZsE7FWnsoqPv3zqzG1koZ7JPRsnFdUKeBhwYq8XWVJGrmaNELvOd5dYF51dZFOCrkGzYzt5WHHKHCicM7VrIONfdCTQs18zoy-NOuC396ON5qjq0Ro28qzidNRoCOAOTb_xlbil6dw4zSQxcn3_3dLodQtgScIhddxESh15Uw8S4POAsAba9BFBsk2-ZKppwHzWJStIMnAAJzHkDQv1bc8FuLMlfydk5K9vdScMtIzczPOsKmyC-5jKBVPUMP8GqKCJY4hHDdYSJXASxjPKdlUTFm4NpSwDcIeBaD7IWAXYbWvZCIXCgoOzeDf-rW4zrlqSYnn8yKKF8VGKD-2Zvx7vOooBKkvfgzmWjWS7_ByFlsjPANzCMyJoccGpGKqfe-52H2Yc5o1gK6Eq61W4UaqoPgGhCZ5qPBZFcrkdK2wg3BCWqs_JICKLrRwJVcubJ3WXHhf5wK3dBFhYBjDfJ5OiVzU77-aETdwMp1_m9Jp2MTa6xVWl99svxx1AqQUZvRyeBIatBZhQF9DuEEVcCrb7Bur_BPig7Y9TffcgNhdAaIepFbg9FOrsf0DG6PYrA6PF9P8JQYlZ9eGYZazNhMrlzMqVxML5uD3tSE1ZsAoYnCoGHN_7uIlyROubqzc5HQHf-p8sGcsuMg=="}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"new_string\":\"Reviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"replace_all\":false}", "call_id": "call_sY4qrJ1nQ4Iyoq1nkxOnT4xT", "id": "fc_0ef6622055025d64006ab48775a1f487d29e553e04239c0f11", "index": 2}]
-{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Reviewed by the project team.\n\nNext step: request a quote.\n\nNext step: request a quote.\n\nReviewed by the project team.\n", "new_string": "Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "replace_all": false}, "id": "call_sY4qrJ1nQ4Iyoq1nkxOnT4xT", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0d131-2758-78f1-af21-3d5a0486d530</t>
-  </si>
-  <si>
-    <t>{'file_path': '/target.txt', 'old_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n\nNext step: request a quote.\n\nReviewed by the project team.\n', 'new_string': 'Reviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'replace_all': False}</t>
-  </si>
-  <si>
-    <t>R8</t>
-  </si>
-  <si>
-    <t>01a0d131-275d-7481-85a6-fe08706dcb62</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0ef6622055025d64006ab487777c8c87d2a3a072aab3de9bb0", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtId3r_UQ4wiw5isf_i2fcfJpp8fncDK4zqWkd_tBWVuM8ufE3HyLjK4xCNKJEp3NueNfKzXDyaVvxRz0ZD4ouzBnV35rOfwPDdRFiZ3iOyKOGlOgIaDqetLi3jnKvbZmUWWbGQjdcHMP_Q8NKZxFqO0CcmSleJKSYvBP0cP7o2lCcE9ewuFaJCCoeb0uryJKPyBThNOlLVeIgULBuhXoUCvWD76PkG5eaEVcHriHodBeZEzeT1N7lxFdcdd0FmGv1F5N_l3lXJKrXGHucb7kEfPmmA10bETm2WJ5AShcfDXlQ4Z9RXYxvgq6NoW8_BHcESBT4kl_7wCR6Tp7kR3oaBTlbcoBXDsiUVInGcPY8lzO5kgMD4yGg3AGUSfpuKBXS3GhAieANauUP4qu5ItgAfqEi0qBa3ctHHx_XRRmpOwkdZVzjBPs_Mx6wFg2JIEB_eiERoFkOGH898jEPPntuHS36aETm-X8gYST_IsqkNvFPNbufhj-JVDotJUAAzZZ6YUPH5nEDRZl6XbXKRksInYztHA74J82Qtkehl489Shq56hOgFlv04XetxFvw4svTg7zNDn71YutPWuW3e8sUrtxdZkbGStbS14THP0oLI5xL69As7juN8p44KiWDSqBccDwRE0DLV2XpXq1TnUdfvoQLMMh6Q967Ik5KR_9hu7bMV-h0O3CRM8jdw_IvSmIMJFfTx_neyXTn8s_9YBS5705qJ05XXiNQ67Ql471hg55jfIHm1aMABSlduxofOXZmeGmMqHxdryjPgNA1kG8JrT3n1nECkzBYYwe398rxnF-NPD5qnqcgeJaR6nPRzG2WCQ_DK2IR5fYNUhdDvXTzQtbffMe6GX5JuosjKvd9brjbb-NDLZ9XOc4KoronhqTj2l2m2r_ULPEHlFMAFfKWDR5lHRor1jrWow-8qCXxmDcV5AGiuqnzzG993JmzIkKa7cFgF3JRBMKmJUK_6nsQN8Y5_zDVFArH57VFBmfIhztizUUX8ZSeJYYAVPDdo1Vhv-hRGY75yvRFX0wfkCWjdCI0PL9e5mHDYdvNdIyNVILl36_DqjqlLKpIMYGpfWINeURlePxV5ftBOtgugnWo-Nad5k-Tp_md5FJE5XIqnhnM5J88qVJlJouL2Vycc5srXZMICDJ0_myZdrPc4VLGQg2tuAPlex6OEwUUxK9YbnKgw4="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_aQOE1HeYYYbzJwF5B5aHuF1Y", "id": "fc_0ef6622055025d64006ab48777ad1887d2b23753401401bb7c", "index": 1}]
-{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_aQOE1HeYYYbzJwF5B5aHuF1Y", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0d131-2ef9-79a2-9853-1494bd8e5b40</t>
   </si>
   <si>
     <t xml:space="preserve">@@ lines 1-24 of 24 @@
@@ -605,13 +412,143 @@
 </t>
   </si>
   <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>01a0d131-2f00-7050-b7f5-6d654a935270</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Appended both sentences as separate changes to `/target.txt`.", "phase": "final_answer", "index": 0, "id": "msg_0ef6622055025d64006ab48779978887d2a242165a2e73da5f"}]</t>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>01a0d584-9e68-7362-99cf-6878e7868b98</t>
+  </si>
+  <si>
+    <t>Conversation history · cache read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Tool result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@@ lines 1-2 of 2 @@
+Project summary
+We prepare clear, practical reports.
+@@ lines 1-24 of 24 @@
+Project summary
+We prepare clear, practical reports.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_079598387a6ba76d006ab5a2fa12d487d286ae57253d66c1b7", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaL82RIYzW41MZgrA0Py6R0enZqk1erbb-xhcOvZNMF3Ag36T6La-CZVf4TTwvTY2MMc_LcQVZfEykH-UY0uh6jdm94DveAQAQf_TN08V3ut-PoGdbTB4T9kleHczdE0SngsCYw5qd_i34djhKQ95IUL6WMfaYdZNIUhI77leSfFN_bOcAUgCYgFAOhfz552dsBMkLMYPdFjY98N42I_haIg7ZWwoyzZWJZ6kFEDGtyIiAsk8N7PAjuDB7PXQNHsIEfteekSzCVyo1C1m9bDrSELflWZa_LwIs2turByPCnARcDAeob4EI2P-Dxm0fHKKgEBqvtERyVzWAaPJxk_YgmGlFFp9KSBs-xv5RhGui1VxSVxunvY84BZEAQ0_WtL1HWd2fagx5vX0gjQyxQ1WubZ3no0eysNsANsepLqSSF4rsZ12RY4gTVZGmKQaXAIVkU_APobC9ssdmdW43oX_XPztW0pwFJR7XPQsTgQFxGDTZqvST7Z3DOUq4lJOMCezNWzN1sfT2LJUo-NZa4n5q0FGsTq5jL7O47lMYjOG0Gx-q5Jp8kP8hOLJijUQp7x09_kiMOPy5MH6MsXrIYeGEkQwethvUSE6t8n3xYGAb2wBHIGVJMGzsplybbz0lAVxGsCrAdEQ5TPMfjm9yRbAcsromnL9lLbsCV25Qj25XIIJR0rOErZi4k3y8JqS-dZXmz3Mq6ItLna4w4yERjnQ_XNgQhV_-ED2-L5yi5g9FRwlyfyuoKgTMQ8p2GIrCcQCo1roOJTagea8Crb9bwtUTRGIJZfsQZaslMkWS_J1GRnx63alukpzYaD1IgPMDPMN7PoIniFIyd6rtOgonAE45A7B3jpwAZgbJznhJLUTBWQJtOz70YEKy-umGoTlDR3mx4unz3ElkZaAPAlCF_Xc7HvmufUukg2xcf-m8L0t33MhXvYsVClVJo6JDP8mAtTcumOll5xkqzLRn6ohI9uRk7TqqjwjdCY7rC_TvuQ-ihPJ5WFKNZO-SgPePGzNFnp0ov9k1GRxfoCTlVsIw9NeUGAQGAgspABvvFlq3lHl8F2VDD7Alj8hbT9wcQ5RoU97GN-67CPlhHibwcAGoHYsmYE6l-v8yW9R6Ar0yBwgs5yu7GCNjEzUU1av43Z5G7sAK9bcxNkMIKmxkUhn95m8jAhh2MHhoHc7iZSyyZ6si8qJP4IoMTh92bgW6CCWfkqWGD0z50NknrVmaZAWuWRqU1piTQAhdNeb-_RZ1rwqSff-9gm2TdzAW0cQy10rFSSQrWCtGgfgWFD-L0kN49z3rpvaPYg5b0dJZ4h3HrALWsLWZ9u2xXHtKXDuu0KMO6wEW8kNNAa8dAYJ5pu00391e4pHv8ISy81RaMnsGVWYVVMWMeoJtbMEYOZtLtXt3l0nMMdLWA4qJ1If4T5ixT33zdVpz-_NTttk2wSjGNjnFRjHx2v8Snc8mwGrf1TBD_qPE4SXFqHFoOtUg7fbiaEfQnfcOr_kRXycTI_BCCu3c5y_tj5lTWkRsK1XNZOMou1ide4ejqSXnzg-na3dm8dZ6pXuCCdQIxTPK3C9A17L4T8guJG8TKFc7L9mA1uLynFFukveetmOfPjt9CGwGIB9T9VNJkQa8IrtQ6SaeOjvRkN1qxgedGYoOXQ0Cbu1EWlZEvUe4q9yeKc84OgEcZQ9w-ZuaIMXrGkiNJUs_AbU-nShy-bm1IqjmsmJ0pzMpGnLGiBh_dyTmFihiR1K3Qhi8DHAqxpiKHi_WcgZPr-83zWOtZqwsZ_cVKAYhJB0yWyqO73ay9jeTEYnSffCC8AcBp86-c_W22IHF_Rcr3lY5UQVnGggjBs9z32AMmltmPgDaatPP94pcMJksWs82h2HdxEse3rjDh3myZWeAKrE4KydnBnhnYARtewp4h3Z7uENGM4DrxjF0aiV1BEYVeJs0g4Lv3jAYIF1aYJGbX8k1VA6_nr9HJuWhUa1x0E_lRA1H5-XP5JtYtLEBngQbVfHF9ySwBG4G2GR_veo-YlT6vqZc_siMsAmn7xgphdUDGoxeIKRZ1EEIdZe9bgEaiTxij-v8dReBkvWbxT9zYJuJ1pNf3VrygFLZx5bKuhEgBnmmvCXBR_y2u2_kMbbdcLPk2mczy6HvkJoo6WmcJFSxKPI3P_k0EQn0kULXwxBxOI85QGg6tLhBqcAS3QMXin6xrdfEOlw2lvLLPPayUicQEpeKm3PNyDKEvvTwOfOfvoHK157lWbpjv4D6_-QhHdw93zQcrSER5548eC9ZhXToHnZuTXUANSkFptzZeldPnlu4520BdZHWPXnD0GLY-obTVJZIak3APliIxm_smZ9SQiMKL1hsTaS_I9cmX2q8PRUCGN-7K-5r4miZzz8R88CKXR3XO44i8u0HbPCLk_437QMm3MlxFXZLXilY5eJHfZHDoZMBN_Yvao0Kf2RAJgvHlHWmXZcJUNmsIKuwS-UIEPu-dcaWdOojxAHUQ_YLXnkWtsAc5w2lTuSo_uInJEZh0NFDfTk5oEtw6ro7pYl-QuuzDnrfLDR7rWFCVozmLI60C_pO4x6UaPf3YwBxlfeqcYxYVAsxtQSFDZ3o-XK1oLNvcYzVy4TI1xxsX3qeLFttgG9OvX1tlBLELQzEaNvgCOpYHv6kDFFeWCbtCo0cDDlVVDS5YLWzE_5a2DfxRd5osJEEK2-XKCFEXx7uss_DXOT-w-FsOyOCkIo8vCbGm-HS7VypGlMnqhwDapvF9etC40pLfwLaqoBryELFMwWoZJHKmfd38UB7cIZ1XD9c_e0w4="}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"new_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"replace_all\":false}", "call_id": "call_VYYS6J2FMTFhW0KejPCjRgGd", "id": "fc_079598387a6ba76d006ab5a2fc853087d28c58bd83be62dc11", "index": 1}]
+{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "new_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n", "replace_all": false}, "id": "call_VYYS6J2FMTFhW0KejPCjRgGd", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>Tool · edit_file</t>
+  </si>
+  <si>
+    <t>01a0d584-b099-7c43-8b18-4f9252cd4ad1</t>
+  </si>
+  <si>
+    <t>{'file_path': '/target.txt', 'old_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'new_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n', 'replace_all': False}</t>
+  </si>
+  <si>
+    <t>Successfully replaced 1 instance(s) of the string in '/target.txt'</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>01a0d584-b0a0-7d71-8189-c6a238d510e6</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_079598387a6ba76d006ab5a2fea61087d282af123ed014b137", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaL-yB-ts6k24JbpUYRju2EVzC3VFewiy1NiKPDfaPdR5fw4cWctTWDzvL67MYry6jJsyOkKiG_4gEYnHrMqYocqo_IyZPzmCCNbJ3MK9WXf25JGTFlM60SGwP-k483j-h3J5xL7LWqJXSKoz0S069W67tH-vuhvTyAGtxvJRRp9F3tBZ88ggoYyt4y_BUbnXeyJnyiBrLPQeayQgLEO5yfwYp1WY2u2Vxu22-Q_19Hw-RPjLzmn5nVFqhEssNBB8IGcnOAD6FogFWfqVkzypE1QWHagZ7Oj0HVX3SAAZ4mImucDgg4pBrQq5QSKJLLih8eVZgTyU2gRl-0gEFPmtc7LPO16qTQ3YjqvTVryY8K2pxQmYFHPNK5_ku1xGweRCc6RqBORIeG0Uzd63IOw3Hj6h7LYB3HK2MYzJk_MjKFVtCCurEzClZrh2VeuiJ11za7hlMTbbd3NimdZU1dAPugM_8rnCPnhNHCCIjrcDveXtW-4Jh-EyA27wV_o88ZfmDEmsyvXmvcLCL-17oOf1iB7ydczxS9rKzSUBRTHFhWr_WFDZFSThJPMRK1rpoq7tS6uA9u--d9wZTIsn1l42GYJNa9DeDlpgbF-SJoGdyOYHZMqtR3euA-3cm4hSv1Blwdk7chje9uC0s_DfaGIpKrQYoMfULsoCHSYDes4pvSkupHatN2ze9ulOqZMLwNvfee_IjWsBPncBIouR-41kqdxcM0TSgWVPLd9TmcjjJqb-UZY28fc0MvBzzRWHXTqDuuteZyNwfsizxHH7y-vt7VwoFGLdADf0l5s1usS06bYvhMtZ2PIXJc835YHGYywvK3dP6_xL7cd93ZIcWeGEFcvOmLG0YPUNKnh0qNKNqzOM4H-mlY6bHS-8czdAocmmUI0qSFpITyKYO4gNvEvilgefCHrhGg8ae-feuwTNzTTa88HVRUjzBB-lauYewBu2EX7wfauXo5D00TGtPgVTSxzrS7j9pSVb6ScesAIyPXLTHvH_OHhnifz-r9NwSvPV-LHlGKLuu5BXqmoahosarrBW4rbMoCssyl5RNd2pXwOChU7IAFLgCAO2ZMSMNyW-CmhqVOfafsa297n9fUPxr_0ck2d23TUzmurxKtGMnAbu0qV4jaWBkf1iS2jPIBlHbl0WEGofzjd5CXa99ycCoY9RRal8qvUM2hXyYTPtc-GbQ-c0YVT1dNzmd5mTTVq6SJF"}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_MqDh5MoklYs4fkQzTsBNOj9Y", "id": "fc_079598387a6ba76d006ab5a2fed2d887d2a72761027c12e5a6", "index": 1}]
+{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_MqDh5MoklYs4fkQzTsBNOj9Y", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d584-b43f-7a41-aeb2-c280c2f3f32d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@@ lines 1-26 of 26 @@
+Project summary
+We prepare clear, practical reports.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>01a0d584-b446-70d3-9c38-ca717edc16bc</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_079598387a6ba76d006ab5a2ffb24487d2a12d0ebd38c0a8bc", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaMAKPlwtys--nsHS0SX_SxQ-vlJp_2beKtw4ia6YTc2UxbPx5XvAn3rUfE5JozgIfVGQD64Zj3f3uk6yrWaB5dvHZYfsXnDyk7060p5RKN5Uw7uWRjFKvPx8yHPNEJycoX5BQOIKlW6MzRXfq0WrG5jYoZNsuRTt3DxYYm4KBux70jqMHnZpVpbzHemgmuuBDbCcIST9X-pPB_f0TgEzoUhvlr-BZxOzIJZJcYfViK1CvU9xUB0-0K-yc8ylwgJdukWCEKvy4lPR2MGuuHp7ME9rXVA3Ydk8HH9b_H_8TF9AgkcZPzzEmbvpr7SE54GeMf8u_DyNTwX-wRcbWNma8loQBC7q7TcqkWIyh_FTAd5eTXdm1hIbA9o_ZHW376SrCVbz3ck98UeXPUvEsXbRpMF_gQbpKXXkqLc--4OOCrHWNlTup7YFbQGb4zGeXvk_1l6kVmvk8Na1xvPshiyVUCkR_V-lZ088VlUSGuCNNvfmEEbSvwPfCrfDRs5UI5kbSgpH_eb6oiLPzk-WI8HQn9Q92Y135HIdvljtrF83TVbUgPkwNfv7PFkAVz8pPgb-AUDd_aSUZNpYXeI2ljAd7bKjSprDDaG_R5otCm8Ffp7X7UPkxy8yDf6CUINdLkTU1MbKaCohJw_bnKl3oTgsFkAOoEXn-axEiIaaUhhbXbkU9-S_i6wVoBL-WJjTb5M1HrpmEbWYfQSOro2qcfc-jk7Fc6OLnxT8TcjA3V0iG8CI3NfL5HuxcKFZ6UJP3WBk1iOAb4lbyAj11SNwN0BUhqcn1J1ALqOMMM-hOtu_h5DvC36nyDxyXsT_ui4ORPY5dJ3kuqhYtcDsE5uaS7klktDyAMVRTQ9EoSv_j7pzeweKur6RNNENNCBk7Qbi5IGZJo42BzJfZUColFcSXdGzTH9nDQ9YrhlY6Ycv8ubVPMWxyeJ5vki7N-AKTMv4tqMFF9VYFuoEOvPS_A4W79Pysft457kNwz_f0hQU3fQE_ls54abZneJ20Uubkl2_9Ev9X2Rlvv6VRAgFvcerIncQcuJX_k5DaXFewEtEDciH6HIV4g2LvAqF4UZ7dWO3muZsKLszVMgRyHbBKCwxF-G7Lyu1UmIz4VV9LSdGO4fPGfZS46qFLCfWjxWLrEj1bWcRl81qOmptVVzDKoQIprj_w193rJDwQK6l4a97OY4Rlsr6UNFUBHv0kZvqlUZjtVAq9ispHI9EheopY5yyCoje9L_Zu2fECM_TQZphogowPWDs54GpcZZpwtBhNPyywqaFeJi6OZ4PJjlQnVHwHbAWaPs1YeK8F3wejjzcBIBq_uUiMBPaBdQYNwYXSvetNoEkr01"}, {"type": "function_call", "name": "edit_file", "arguments": "{\"file_path\":\"/target.txt\",\"old_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\",\"new_string\":\"Project summary\\nWe prepare clear, practical reports.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\\nReviewed by the project team.\\n\\nNext step: request a quote.\\n\",\"replace_all\":false}", "call_id": "call_HqwNjwnlvQowtNsm9V7wugg4", "id": "fc_079598387a6ba76d006ab5a3000a8c87d2afd06e7a8fdd4391", "index": 1}]
+{"name": "edit_file", "args": {"file_path": "/target.txt", "old_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n", "new_string": "Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n", "replace_all": false}, "id": "call_HqwNjwnlvQowtNsm9V7wugg4", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d584-bd8e-70c1-85db-6bc07c7b6a1b</t>
+  </si>
+  <si>
+    <t>{'file_path': '/target.txt', 'old_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n', 'new_string': 'Project summary\nWe prepare clear, practical reports.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n\nReviewed by the project team.\n\nNext step: request a quote.\n', 'replace_all': False}</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>01a0d584-bd94-7ae0-9dcc-5d526209ea8a</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_079598387a6ba76d006ab5a30207a487d29a2ca2d1d1c46dc3", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaMCXuGc77GXwZjpvfh_GAhYnA7snfN9IhQ827i1g0ZVVwmKuxktw7clcBHxkEQVblH73tuGNYNSJTZVYnPq9tlCSqQTKooAVBI0afojDBNTBV1_0aDC2-eVh9uxMWzH_T6F8Uiy--R69lNtDm3SQorNLs7dlig5aukYV4BaHUFqNOxmnbGq-P42pGNW1PZj9ahwxOucxcXLhUzGpTb7yoTATxaqWrJLnhvUmKYCk00U16jRZJZd3TCQvKaDgaFZ067ct-v2HjwpY4NLxOy2VQGnQ4HqDlNYJjtMM_s37VIugVTFZqYZTg2R864LJZz79oVYAC1MdQ7eheATaMC-8za6U45ArP7htnSIGOxABKfklbzJsD-n_ZfvvyQSzY_reymXubUK7WzZLFd2aK6WJ_V2ABORpVGt97Vvzj7w6yiN892r54BrtAF78wLjkU4B5XmYHTazdMh0f3EbR81Qov1crzlHs3pv92MZ6zH5Gnftoef6l0blXU1pDnuxHVmlIue0R1xdsx0YjSYZ-yMqPohDgDxmfb4hQmnmg343MmaDQules6UWVVT7sgClTPGh0SYJ5crHfnTJ7E8O3heKRH3WwlWuEXnoX0QeEd3yW8ZW9bJKMsnEQ_nyewqaqihiIwTd103FO2wNATyD7xPPD1jMyCAmrIWlWICuQW7m1BwHU42JZIPQbTxvzqhKuVN70aaRmJ_rq-Rlumqh1YtuW_gSMqU1bdd4ns7mY2D3cdNePJFscqdPCzXF6xzWCVxS3JjL-bz-iTuvQByoygt4NT0pf5XkbdJiuCwXC8OD_DAMAJUrPCEK6dUGl3k98nL4VmWM8vxg27vEAK9En80eq6sg1E7BimRKnMBnrlPFcswm6LTE0Kg3_pA3j7eaJFjOMrBJt1HYBQZAgsUAnjfwkSdasslTM3naAApjTp-_HYa_xNB5W-gbxsJ4VXb9PcxDi22_R-iUSH91e124zYs3zS4beB6nrTJeY2B3NfCCPW-Z5hzXM3b6Zq5VdOTvg_10DC-AXFTv1qEvve3zcSRpwpG7PFXzh-IRsvFXgYfp-wrYkwpir-J2FVJVp8rBlBZU4mX2ClIvdM0w4--A1uT9EYcdOcKu7g_EBZ3grOwsQ4L0Gz0HKlpy05GgQuFMNzrEFr72B6yS1TRuDIid-BbuEzSU7Jysd1H6UUXgYvc79EU8AtKeT4uPasNjgU4LnUynzwoaS2PFWG_DZM0XxEkEKx6MIqJrIvDWmXvtseysZhs9ciiDGXw-bLV6I0n4xyHWbT0s3iJaualA1zIA-UFUVTUu7A=="}, {"type": "function_call", "name": "read_file", "arguments": "{\"file_path\":\"/target.txt\",\"offset\":0,\"limit\":100}", "call_id": "call_ue7UpFal0FFQmyTYltskPAIV", "id": "fc_079598387a6ba76d006ab5a3024a6887d298593133e5ef8019", "index": 1}]
+{"name": "read_file", "args": {"file_path": "/target.txt", "offset": 0, "limit": 100}, "id": "call_ue7UpFal0FFQmyTYltskPAIV", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d584-c1d7-7f40-ab26-4998532b81df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@@ lines 1-28 of 28 @@
+Project summary
+We prepare clear, practical reports.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+Reviewed by the project team.
+Next step: request a quote.
+</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>01a0d584-c1df-7731-959a-5bdf56550d1c</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "Appended separately to `/target.txt`:\n\n1. `Reviewed by the project team.`\n2. `Next step: request a quote.`", "phase": "final_answer", "index": 0, "id": "msg_079598387a6ba76d006ab5a3033fc487d2932f8db3d1e16945"}]</t>
   </si>
   <si>
     <t>file_editor</t>
@@ -632,7 +569,7 @@
     <t>Execute the RestrictedToolApproval.before_model workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d130-9564-7e01-b769-98a522d85904</t>
+    <t>01a0d584-97f8-7cb2-bc9a-343f233811e7</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -644,7 +581,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0d130-9567-7a22-ab84-40685ab38e43</t>
+    <t>01a0d584-97fb-7cb0-be73-462e45ce8d69</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -665,7 +602,7 @@
     <t>Execute the RestrictedToolApproval.after_model workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d130-9cbd-7d02-8d77-aedbb23def4a</t>
+    <t>01a0d584-9e58-7c23-ae0d-64fa75215735</t>
   </si>
   <si>
     <t xml:space="preserve">    tools</t>
@@ -674,7 +611,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0d130-9cbf-7581-b096-1431805489da</t>
+    <t>01a0d584-9e5b-7341-8f44-1bc642f325dd</t>
   </si>
   <si>
     <t xml:space="preserve">        read_file</t>
@@ -695,28 +632,28 @@
 - Always read a file before editing it.</t>
   </si>
   <si>
-    <t>01a0d130-9cbf-7581-b096-1446ff13da46</t>
-  </si>
-  <si>
-    <t>01a0d130-9cc4-7420-aa0c-6ecfc0ae7c6f</t>
-  </si>
-  <si>
-    <t>01a0d130-9cc4-7420-aa0c-6ed6ab3aa277</t>
+    <t>01a0d584-9e5b-7341-8f44-1bdcfd616b98</t>
+  </si>
+  <si>
+    <t>01a0d584-9e65-7621-9638-fc77a5e73d03</t>
+  </si>
+  <si>
+    <t>01a0d584-9e67-73a3-9e06-8268bc73b9a8</t>
   </si>
   <si>
     <t>interrupted</t>
   </si>
   <si>
-    <t>01a0d130-b2a4-7f50-80a3-649e69e98208</t>
-  </si>
-  <si>
-    <t>01a0d130-b2b6-7680-ad9a-b6cf65725001</t>
-  </si>
-  <si>
-    <t>01a0d130-b2b7-7c93-993d-08e377f1dd38</t>
-  </si>
-  <si>
-    <t>01a0d130-b2b8-7091-b5a3-615686277856</t>
+    <t>01a0d584-b068-7c91-a7f8-03c81c7c5ad2</t>
+  </si>
+  <si>
+    <t>01a0d584-b093-7943-b1d1-cb0b430754ef</t>
+  </si>
+  <si>
+    <t>01a0d584-b094-7853-9254-abdf50cf696e</t>
+  </si>
+  <si>
+    <t>01a0d584-b097-7a80-9d4d-6d4501f77a3c</t>
   </si>
   <si>
     <t xml:space="preserve">        edit_file</t>
@@ -730,103 +667,55 @@
 - Only use emojis if the user explicitly requests it.</t>
   </si>
   <si>
-    <t>01a0d130-b2bc-7510-8d92-90a4bba24b47</t>
-  </si>
-  <si>
-    <t>01a0d130-b2bd-7a82-883f-0c4f68b3fa99</t>
-  </si>
-  <si>
-    <t>01a0d130-c95a-7581-a8a6-21b5e7a6472a</t>
-  </si>
-  <si>
-    <t>01a0d130-c97f-7990-89f2-177990bbe901</t>
-  </si>
-  <si>
-    <t>01a0d130-c981-75e3-ac7a-87a359cadb96</t>
-  </si>
-  <si>
-    <t>01a0d130-c982-7da3-b0ab-a255256c093c</t>
-  </si>
-  <si>
-    <t>01a0d130-c987-70d3-8376-0ef10a255674</t>
-  </si>
-  <si>
-    <t>01a0d130-c989-7543-93d7-60e725d95ff4</t>
-  </si>
-  <si>
-    <t>01a0d130-cf42-7e62-9f2d-2ee807578e64</t>
-  </si>
-  <si>
-    <t>01a0d130-cf44-7f60-99be-acca4edc1f82</t>
-  </si>
-  <si>
-    <t>01a0d130-cf49-7831-b139-36cccf0861c4</t>
-  </si>
-  <si>
-    <t>01a0d130-cf4a-7a52-84e2-6bd507da9111</t>
-  </si>
-  <si>
-    <t>01a0d130-eb60-7ea1-a62a-15341e91f96c</t>
-  </si>
-  <si>
-    <t>01a0d130-eb85-7a83-a666-b6228b22504a</t>
-  </si>
-  <si>
-    <t>01a0d130-eb86-7a01-bf11-2e7b7a73c5b9</t>
-  </si>
-  <si>
-    <t>01a0d130-eb88-74b3-9eb3-8c9109d897ac</t>
-  </si>
-  <si>
-    <t>01a0d130-eb8c-78f2-82e7-38caf88ef616</t>
-  </si>
-  <si>
-    <t>01a0d130-eb8d-7c40-9e64-1cf67511486b</t>
-  </si>
-  <si>
-    <t>01a0d130-f225-7501-8b72-d94592b63d18</t>
-  </si>
-  <si>
-    <t>01a0d130-f226-71d2-9c5c-07deb12213be</t>
-  </si>
-  <si>
-    <t>01a0d130-f22a-7f13-b522-94986ac6ad0b</t>
-  </si>
-  <si>
-    <t>01a0d130-f22b-7d20-bdc2-b9f017f5a267</t>
-  </si>
-  <si>
-    <t>01a0d131-272f-7a93-be58-02e6e0915dcb</t>
-  </si>
-  <si>
-    <t>01a0d131-2754-7d50-98c6-01611bca58dc</t>
-  </si>
-  <si>
-    <t>01a0d131-2756-74e2-b254-a9dac7e39aaa</t>
-  </si>
-  <si>
-    <t>01a0d131-2757-7e53-ba2a-82d71dff3114</t>
-  </si>
-  <si>
-    <t>01a0d131-275b-71a1-92d4-4feca6e34062</t>
-  </si>
-  <si>
-    <t>01a0d131-275c-73a1-8d35-1d449c2517be</t>
-  </si>
-  <si>
-    <t>01a0d131-2ef4-7920-ba64-16a9fb6a83fe</t>
-  </si>
-  <si>
-    <t>01a0d131-2ef6-7bd2-a499-8b7af8d30907</t>
-  </si>
-  <si>
-    <t>01a0d131-2efe-7453-9a5f-bc825c20b869</t>
-  </si>
-  <si>
-    <t>01a0d131-2eff-75a1-9048-4f6f80f29086</t>
-  </si>
-  <si>
-    <t>01a0d131-3439-7df3-bd95-3a723abb350b</t>
+    <t>01a0d584-b09d-7b10-8c3b-c44c8efe30dc</t>
+  </si>
+  <si>
+    <t>01a0d584-b09f-7620-bb92-a38747c20eba</t>
+  </si>
+  <si>
+    <t>01a0d584-b43b-74e0-904e-bee13038c100</t>
+  </si>
+  <si>
+    <t>01a0d584-b43d-7802-89ab-6ecd788151a4</t>
+  </si>
+  <si>
+    <t>01a0d584-b443-70d0-951b-05f4fe3efbd6</t>
+  </si>
+  <si>
+    <t>01a0d584-b445-7c32-a4cd-2f464fb8b3eb</t>
+  </si>
+  <si>
+    <t>01a0d584-bd72-7230-b838-3f31c394086e</t>
+  </si>
+  <si>
+    <t>01a0d584-bd89-77b1-ad50-a619d414860c</t>
+  </si>
+  <si>
+    <t>01a0d584-bd8a-74e0-8f47-081c5b21262a</t>
+  </si>
+  <si>
+    <t>01a0d584-bd8c-74c3-90fd-69435071b077</t>
+  </si>
+  <si>
+    <t>01a0d584-bd91-7d12-a39a-0fea1fefdf38</t>
+  </si>
+  <si>
+    <t>01a0d584-bd93-7b22-a479-8c839e363bc9</t>
+  </si>
+  <si>
+    <t>01a0d584-c1d2-7612-a2ab-9623e97ab516</t>
+  </si>
+  <si>
+    <t>01a0d584-c1d5-7dc2-bd3d-89271b55eac8</t>
+  </si>
+  <si>
+    <t>01a0d584-c1da-7862-a6d0-5e1f469b97cb</t>
+  </si>
+  <si>
+    <t>01a0d584-c1dd-7890-a17a-b2ecea917653</t>
+  </si>
+  <si>
+    <t>01a0d584-c5d8-78d0-938d-6dd9d48a3fae</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1122,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1293,20 +1182,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E116,'Turns'!E132,'Turns'!E147)=9,SUM('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E116,'Turns'!E132,'Turns'!E147),"Unknown")</f>
-        <v>0.003957333695</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E99)=6,SUM('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E99),"Unknown")</f>
+        <v>0.0018622248346</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F116,'Turns'!F132,'Turns'!F147)=9,SUM('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F116,'Turns'!F132,'Turns'!F147),"Unknown")</f>
-        <v>0.0045157</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F99)=6,SUM('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F99),"Unknown")</f>
+        <v>0.00211679</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>396.0</v>
+        <v>186.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>452.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1317,20 +1206,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E116,'Turns'!E132,'Turns'!E147)=9,SUM('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E100,'Turns'!E116,'Turns'!E132,'Turns'!E147),"Unknown")</f>
-        <v>0.003957333695</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E99)=6,SUM('Turns'!E17,'Turns'!E36,'Turns'!E52,'Turns'!E68,'Turns'!E84,'Turns'!E99),"Unknown")</f>
+        <v>0.0018622248346</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F116,'Turns'!F132,'Turns'!F147)=9,SUM('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F100,'Turns'!F116,'Turns'!F132,'Turns'!F147),"Unknown")</f>
-        <v>0.0045157</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F99)=6,SUM('Turns'!F17,'Turns'!F36,'Turns'!F52,'Turns'!F68,'Turns'!F84,'Turns'!F99),"Unknown")</f>
+        <v>0.00211679</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>396.0</v>
+        <v>186.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>452.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1368,7 +1257,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00015563976</v>
+        <v>0.000156241824</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1455,7 +1344,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1469,15 +1358,15 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.418726e-05</v>
+        <v>1.583532e-05</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>2.76e-05</v>
+        <v>1.8e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1485,7 +1374,7 @@
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1503,7 +1392,7 @@
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.571664e-05</v>
+        <v>7.6009536e-05</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -1518,7 +1407,7 @@
         <v>9.0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="359" customHeight="1">
+    <row r="14" spans="1:13" ht="346" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1566,19 +1455,19 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.00025554366</v>
+        <v>0.00024808668</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.0002916</v>
+        <v>0.000282</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>111</v>
@@ -1645,7 +1534,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="268" customHeight="1">
+    <row r="23" spans="1:13" ht="320" customHeight="1">
       <c r="B23">
         <v>1</v>
       </c>
@@ -1667,7 +1556,7 @@
         <v>94</v>
       </c>
       <c r="D24" s="4">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>95</v>
@@ -1721,7 +1610,7 @@
       </c>
       <c r="E26" s="2">
         <f>IF(AND(ISNUMBER(F26),ISNUMBER('Reference data'!$B$3)),F26*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F26" s="2">
         <f>IF(D26=0,0,IF(ISNUMBER('Reference data'!B17),D26*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1736,7 +1625,7 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="307" customHeight="1">
+    <row r="27" spans="1:13" ht="359" customHeight="1">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -1761,15 +1650,15 @@
         <v>103</v>
       </c>
       <c r="D28" s="5">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="E28" s="2">
         <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0002425298625</v>
+        <v>0.00024456772</v>
       </c>
       <c r="F28" s="2">
         <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!D17),D28*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.00027675</v>
+        <v>0.000278</v>
       </c>
       <c r="G28" s="5">
         <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1802,7 +1691,7 @@
         <v>105</v>
       </c>
       <c r="D30" s="4">
-        <v>441</v>
+        <v>501</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1">
@@ -1816,23 +1705,23 @@
         <v>106</v>
       </c>
       <c r="D31" s="5">
-        <v>365</v>
+        <v>237</v>
       </c>
       <c r="E31" s="2">
         <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0003838413</v>
+        <v>0.000250198056</v>
       </c>
       <c r="F31" s="2">
         <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!F17),D31*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.000438</v>
+        <v>0.0002844</v>
       </c>
       <c r="G31" s="5">
         <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>38.0</v>
+        <v>25.0</v>
       </c>
       <c r="H31" s="5">
         <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="24" customHeight="1">
@@ -1846,23 +1735,23 @@
         <v>107</v>
       </c>
       <c r="D32" s="5">
-        <v>76</v>
+        <v>264</v>
       </c>
       <c r="E32" s="2">
         <f>IF(AND(ISNUMBER(F32),ISNUMBER('Reference data'!$B$3)),F32*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.992312e-05</v>
+        <v>0.000278701632</v>
       </c>
       <c r="F32" s="2">
         <f>IF(D32=0,0,IF(ISNUMBER('Reference data'!E17),D32*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>9.12e-05</v>
+        <v>0.0003168</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>28.0</v>
       </c>
       <c r="H32" s="5">
         <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="409" customHeight="1">
@@ -1913,19 +1802,19 @@
       </c>
       <c r="E36" s="2">
         <f>IF(COUNT('Turns'!E25,'Turns'!E26,'Turns'!E28,'Turns'!E31,'Turns'!E32)=5,SUM('Turns'!E25,'Turns'!E26,'Turns'!E28,'Turns'!E31,'Turns'!E32),"Unknown")</f>
-        <v>0.0007068200925</v>
+        <v>0.000773995252</v>
       </c>
       <c r="F36" s="2">
         <f>IF(COUNT('Turns'!F25,'Turns'!F26,'Turns'!F28,'Turns'!F31,'Turns'!F32)=5,SUM('Turns'!F25,'Turns'!F26,'Turns'!F28,'Turns'!F31,'Turns'!F32),"Unknown")</f>
-        <v>0.00080655</v>
+        <v>0.0008798</v>
       </c>
       <c r="G36" s="5">
         <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>71.0</v>
+        <v>77.0</v>
       </c>
       <c r="H36" s="5">
         <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>81.0</v>
+        <v>88.0</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>111</v>
@@ -1939,13 +1828,13 @@
         <v>127</v>
       </c>
       <c r="K37" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M37" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="M37" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="47" customHeight="1">
+    </row>
+    <row r="38" spans="1:13" ht="164" customHeight="1">
       <c r="B38">
         <v>1</v>
       </c>
@@ -1953,10 +1842,10 @@
         <v>114</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="73" customHeight="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="24" customHeight="1">
       <c r="B39">
         <v>1</v>
       </c>
@@ -1964,12 +1853,12 @@
         <v>116</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B40" s="4">
         <v>1</v>
@@ -1978,18 +1867,18 @@
         <v>94</v>
       </c>
       <c r="D40" s="4">
-        <v>1606</v>
+        <v>1642</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>95</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="24" customHeight="1">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -1998,15 +1887,15 @@
         <v>123</v>
       </c>
       <c r="D41" s="5">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="E41" s="2">
         <f>IF(AND(ISNUMBER(F41),ISNUMBER('Reference data'!$B$3)),F41*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.9402389e-05</v>
+        <v>1.95654176e-05</v>
       </c>
       <c r="F41" s="2">
         <f>IF(D41=0,0,IF(ISNUMBER('Reference data'!C17),D41*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>2.214e-05</v>
+        <v>2.224e-05</v>
       </c>
       <c r="G41" s="5">
         <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2019,7 +1908,7 @@
     </row>
     <row r="42" spans="1:13" ht="24" customHeight="1">
       <c r="A42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -2032,7 +1921,7 @@
       </c>
       <c r="E42" s="2">
         <f>IF(AND(ISNUMBER(F42),ISNUMBER('Reference data'!$B$3)),F42*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F42" s="2">
         <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!B17),D42*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -2047,9 +1936,9 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="73" customHeight="1">
+    <row r="43" spans="1:13" ht="24" customHeight="1">
       <c r="A43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -2058,12 +1947,12 @@
         <v>124</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="24" customHeight="1">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -2072,28 +1961,28 @@
         <v>103</v>
       </c>
       <c r="D44" s="5">
-        <v>496</v>
+        <v>527</v>
       </c>
       <c r="E44" s="2">
         <f>IF(AND(ISNUMBER(F44),ISNUMBER('Reference data'!$B$3)),F44*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0001086674</v>
+        <v>0.000115905745</v>
       </c>
       <c r="F44" s="2">
         <f>IF(D44=0,0,IF(ISNUMBER('Reference data'!D17),D44*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.000124</v>
+        <v>0.00013175</v>
       </c>
       <c r="G44" s="5">
         <f>IF(ISNUMBER(E44),ROUND(E44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="H44" s="5">
         <f>IF(ISNUMBER(F44),ROUND(F44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="24" customHeight="1">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -2104,7 +1993,7 @@
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B46" s="4">
         <v>1</v>
@@ -2113,12 +2002,12 @@
         <v>105</v>
       </c>
       <c r="D46" s="4">
-        <v>320</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="24" customHeight="1">
       <c r="A47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -2127,28 +2016,28 @@
         <v>106</v>
       </c>
       <c r="D47" s="5">
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="E47" s="2">
         <f>IF(AND(ISNUMBER(F47),ISNUMBER('Reference data'!$B$3)),F47*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0002208402</v>
+        <v>1.055688e-05</v>
       </c>
       <c r="F47" s="2">
         <f>IF(D47=0,0,IF(ISNUMBER('Reference data'!F17),D47*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.000252</v>
+        <v>1.2e-05</v>
       </c>
       <c r="G47" s="5">
         <f>IF(ISNUMBER(E47),ROUND(E47*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>1.0</v>
       </c>
       <c r="H47" s="5">
         <f>IF(ISNUMBER(F47),ROUND(F47*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="24" customHeight="1">
       <c r="A48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -2157,28 +2046,28 @@
         <v>107</v>
       </c>
       <c r="D48" s="5">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="E48" s="2">
         <f>IF(AND(ISNUMBER(F48),ISNUMBER('Reference data'!$B$3)),F48*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0001156782</v>
+        <v>3.2726328e-05</v>
       </c>
       <c r="F48" s="2">
         <f>IF(D48=0,0,IF(ISNUMBER('Reference data'!E17),D48*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.000132</v>
+        <v>3.72e-05</v>
       </c>
       <c r="G48" s="5">
         <f>IF(ISNUMBER(E48),ROUND(E48*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="H48" s="5">
         <f>IF(ISNUMBER(F48),ROUND(F48*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="409" customHeight="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="281" customHeight="1">
       <c r="A49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -2187,12 +2076,12 @@
         <v>108</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="24" customHeight="1">
       <c r="A50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -2203,7 +2092,7 @@
     </row>
     <row r="51" spans="1:13" ht="24" customHeight="1">
       <c r="A51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -2214,7 +2103,7 @@
     </row>
     <row r="52" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B52" s="4">
         <v>1</v>
@@ -2224,19 +2113,19 @@
       </c>
       <c r="E52" s="2">
         <f>IF(COUNT('Turns'!E41,'Turns'!E42,'Turns'!E44,'Turns'!E47,'Turns'!E48)=5,SUM('Turns'!E41,'Turns'!E42,'Turns'!E44,'Turns'!E47,'Turns'!E48),"Unknown")</f>
-        <v>0.000465113999</v>
+        <v>0.0001792822146</v>
       </c>
       <c r="F52" s="2">
         <f>IF(COUNT('Turns'!F41,'Turns'!F42,'Turns'!F44,'Turns'!F47,'Turns'!F48)=5,SUM('Turns'!F41,'Turns'!F42,'Turns'!F44,'Turns'!F47,'Turns'!F48),"Unknown")</f>
-        <v>0.00053074</v>
+        <v>0.00020379</v>
       </c>
       <c r="G52" s="5">
         <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>18.0</v>
       </c>
       <c r="H52" s="5">
         <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>20.0</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>111</v>
@@ -2247,16 +2136,16 @@
         <v>1</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>111</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="73" customHeight="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="24" customHeight="1">
       <c r="B54">
         <v>1</v>
       </c>
@@ -2264,10 +2153,10 @@
         <v>114</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="24" customHeight="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="346" customHeight="1">
       <c r="B55">
         <v>1</v>
       </c>
@@ -2275,12 +2164,12 @@
         <v>116</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B56" s="4">
         <v>1</v>
@@ -2289,18 +2178,18 @@
         <v>94</v>
       </c>
       <c r="D56" s="4">
-        <v>1952</v>
+        <v>1799</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>95</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="24" customHeight="1">
       <c r="A57" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -2309,15 +2198,15 @@
         <v>123</v>
       </c>
       <c r="D57" s="5">
-        <v>1603</v>
+        <v>1639</v>
       </c>
       <c r="E57" s="2">
         <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.8095781e-05</v>
+        <v>2.88378772e-05</v>
       </c>
       <c r="F57" s="2">
         <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!C17),D57*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.206e-05</v>
+        <v>3.278e-05</v>
       </c>
       <c r="G57" s="5">
         <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2330,7 +2219,7 @@
     </row>
     <row r="58" spans="1:13" ht="24" customHeight="1">
       <c r="A58" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -2343,7 +2232,7 @@
       </c>
       <c r="E58" s="2">
         <f>IF(AND(ISNUMBER(F58),ISNUMBER('Reference data'!$B$3)),F58*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F58" s="2">
         <f>IF(D58=0,0,IF(ISNUMBER('Reference data'!B17),D58*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -2358,9 +2247,9 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="24" customHeight="1">
+    <row r="59" spans="1:13" ht="346" customHeight="1">
       <c r="A59" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -2369,12 +2258,12 @@
         <v>124</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="24" customHeight="1">
       <c r="A60" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -2383,28 +2272,28 @@
         <v>103</v>
       </c>
       <c r="D60" s="5">
-        <v>346</v>
+        <v>157</v>
       </c>
       <c r="E60" s="2">
         <f>IF(AND(ISNUMBER(F60),ISNUMBER('Reference data'!$B$3)),F60*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.5804275e-05</v>
+        <v>3.4529795e-05</v>
       </c>
       <c r="F60" s="2">
         <f>IF(D60=0,0,IF(ISNUMBER('Reference data'!D17),D60*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>8.65e-05</v>
+        <v>3.925e-05</v>
       </c>
       <c r="G60" s="5">
         <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="H60" s="5">
         <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="24" customHeight="1">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -2415,7 +2304,7 @@
     </row>
     <row r="62" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A62" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B62" s="4">
         <v>1</v>
@@ -2424,12 +2313,12 @@
         <v>105</v>
       </c>
       <c r="D62" s="4">
-        <v>38</v>
+        <v>308</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="24" customHeight="1">
       <c r="A63" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -2438,28 +2327,28 @@
         <v>106</v>
       </c>
       <c r="D63" s="5">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E63" s="2">
         <f>IF(AND(ISNUMBER(F63),ISNUMBER('Reference data'!$B$3)),F63*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.36134e-06</v>
+        <v>2.8503576e-05</v>
       </c>
       <c r="F63" s="2">
         <f>IF(D63=0,0,IF(ISNUMBER('Reference data'!F17),D63*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>8.4e-06</v>
+        <v>3.24e-05</v>
       </c>
       <c r="G63" s="5">
         <f>IF(ISNUMBER(E63),ROUND(E63*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H63" s="5">
         <f>IF(ISNUMBER(F63),ROUND(F63*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="24" customHeight="1">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -2468,28 +2357,28 @@
         <v>107</v>
       </c>
       <c r="D64" s="5">
-        <v>31</v>
+        <v>281</v>
       </c>
       <c r="E64" s="2">
         <f>IF(AND(ISNUMBER(F64),ISNUMBER('Reference data'!$B$3)),F64*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.260022e-05</v>
+        <v>0.000296648328</v>
       </c>
       <c r="F64" s="2">
         <f>IF(D64=0,0,IF(ISNUMBER('Reference data'!E17),D64*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.72e-05</v>
+        <v>0.0003372</v>
       </c>
       <c r="G64" s="5">
         <f>IF(ISNUMBER(E64),ROUND(E64*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>30.0</v>
       </c>
       <c r="H64" s="5">
         <f>IF(ISNUMBER(F64),ROUND(F64*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="281" customHeight="1">
+        <v>34.0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="409" customHeight="1">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -2498,12 +2387,12 @@
         <v>108</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="24" customHeight="1">
       <c r="A66" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -2514,7 +2403,7 @@
     </row>
     <row r="67" spans="1:13" ht="24" customHeight="1">
       <c r="A67" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -2525,7 +2414,7 @@
     </row>
     <row r="68" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A68" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B68" s="4">
         <v>1</v>
@@ -2535,19 +2424,19 @@
       </c>
       <c r="E68" s="2">
         <f>IF(COUNT('Turns'!E57,'Turns'!E58,'Turns'!E60,'Turns'!E63,'Turns'!E64)=5,SUM('Turns'!E57,'Turns'!E58,'Turns'!E60,'Turns'!E63,'Turns'!E64),"Unknown")</f>
-        <v>0.000144387426</v>
+        <v>0.0003890474202</v>
       </c>
       <c r="F68" s="2">
         <f>IF(COUNT('Turns'!F57,'Turns'!F58,'Turns'!F60,'Turns'!F63,'Turns'!F64)=5,SUM('Turns'!F57,'Turns'!F58,'Turns'!F60,'Turns'!F63,'Turns'!F64),"Unknown")</f>
-        <v>0.00016476</v>
+        <v>0.00044223</v>
       </c>
       <c r="G68" s="5">
         <f>IF(ISNUMBER(E68),ROUND(E68*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>39.0</v>
       </c>
       <c r="H68" s="5">
         <f>IF(ISNUMBER(F68),ROUND(F68*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>44.0</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>111</v>
@@ -2558,16 +2447,16 @@
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>111</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="24" customHeight="1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="164" customHeight="1">
       <c r="B70">
         <v>1</v>
       </c>
@@ -2575,10 +2464,10 @@
         <v>114</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="294" customHeight="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="24" customHeight="1">
       <c r="B71">
         <v>1</v>
       </c>
@@ -2586,12 +2475,12 @@
         <v>116</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="72" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A72" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B72" s="4">
         <v>1</v>
@@ -2600,18 +2489,18 @@
         <v>94</v>
       </c>
       <c r="D72" s="4">
-        <v>2093</v>
+        <v>2133</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>95</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="24" customHeight="1">
       <c r="A73" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -2620,15 +2509,15 @@
         <v>123</v>
       </c>
       <c r="D73" s="5">
-        <v>1949</v>
+        <v>1796</v>
       </c>
       <c r="E73" s="2">
         <f>IF(AND(ISNUMBER(F73),ISNUMBER('Reference data'!$B$3)),F73*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.4160123e-05</v>
+        <v>3.16002608e-05</v>
       </c>
       <c r="F73" s="2">
         <f>IF(D73=0,0,IF(ISNUMBER('Reference data'!C17),D73*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.898e-05</v>
+        <v>3.592e-05</v>
       </c>
       <c r="G73" s="5">
         <f>IF(ISNUMBER(E73),ROUND(E73*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2641,7 +2530,7 @@
     </row>
     <row r="74" spans="1:13" ht="24" customHeight="1">
       <c r="A74" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -2654,7 +2543,7 @@
       </c>
       <c r="E74" s="2">
         <f>IF(AND(ISNUMBER(F74),ISNUMBER('Reference data'!$B$3)),F74*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F74" s="2">
         <f>IF(D74=0,0,IF(ISNUMBER('Reference data'!B17),D74*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -2669,9 +2558,9 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="294" customHeight="1">
+    <row r="75" spans="1:13" ht="24" customHeight="1">
       <c r="A75" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -2680,12 +2569,12 @@
         <v>124</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="24" customHeight="1">
       <c r="A76" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -2694,28 +2583,28 @@
         <v>103</v>
       </c>
       <c r="D76" s="5">
-        <v>141</v>
+        <v>334</v>
       </c>
       <c r="E76" s="2">
         <f>IF(AND(ISNUMBER(F76),ISNUMBER('Reference data'!$B$3)),F76*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.08913375e-05</v>
+        <v>7.345829e-05</v>
       </c>
       <c r="F76" s="2">
         <f>IF(D76=0,0,IF(ISNUMBER('Reference data'!D17),D76*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>3.525e-05</v>
+        <v>8.35e-05</v>
       </c>
       <c r="G76" s="5">
         <f>IF(ISNUMBER(E76),ROUND(E76*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H76" s="5">
         <f>IF(ISNUMBER(F76),ROUND(F76*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="24" customHeight="1">
       <c r="A77" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -2726,7 +2615,7 @@
     </row>
     <row r="78" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A78" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B78" s="4">
         <v>1</v>
@@ -2735,12 +2624,12 @@
         <v>105</v>
       </c>
       <c r="D78" s="4">
-        <v>578</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="24" customHeight="1">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -2749,28 +2638,28 @@
         <v>106</v>
       </c>
       <c r="D79" s="5">
-        <v>467</v>
+        <v>21</v>
       </c>
       <c r="E79" s="2">
         <f>IF(AND(ISNUMBER(F79),ISNUMBER('Reference data'!$B$3)),F79*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00049110654</v>
+        <v>2.2169448e-05</v>
       </c>
       <c r="F79" s="2">
         <f>IF(D79=0,0,IF(ISNUMBER('Reference data'!F17),D79*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.0005604</v>
+        <v>2.52e-05</v>
       </c>
       <c r="G79" s="5">
         <f>IF(ISNUMBER(E79),ROUND(E79*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>49.0</v>
+        <v>2.0</v>
       </c>
       <c r="H79" s="5">
         <f>IF(ISNUMBER(F79),ROUND(F79*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>56.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="24" customHeight="1">
       <c r="A80" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -2779,28 +2668,28 @@
         <v>107</v>
       </c>
       <c r="D80" s="5">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="E80" s="2">
         <f>IF(AND(ISNUMBER(F80),ISNUMBER('Reference data'!$B$3)),F80*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00011672982</v>
+        <v>3.2726328e-05</v>
       </c>
       <c r="F80" s="2">
         <f>IF(D80=0,0,IF(ISNUMBER('Reference data'!E17),D80*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001332</v>
+        <v>3.72e-05</v>
       </c>
       <c r="G80" s="5">
         <f>IF(ISNUMBER(E80),ROUND(E80*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="H80" s="5">
         <f>IF(ISNUMBER(F80),ROUND(F80*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="409" customHeight="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="294" customHeight="1">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -2809,12 +2698,12 @@
         <v>108</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="24" customHeight="1">
       <c r="A82" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -2825,7 +2714,7 @@
     </row>
     <row r="83" spans="1:13" ht="24" customHeight="1">
       <c r="A83" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -2836,7 +2725,7 @@
     </row>
     <row r="84" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A84" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B84" s="4">
         <v>1</v>
@@ -2846,19 +2735,19 @@
       </c>
       <c r="E84" s="2">
         <f>IF(COUNT('Turns'!E73,'Turns'!E74,'Turns'!E76,'Turns'!E79,'Turns'!E80)=5,SUM('Turns'!E73,'Turns'!E74,'Turns'!E76,'Turns'!E79,'Turns'!E80),"Unknown")</f>
-        <v>0.0006734136305</v>
+        <v>0.0001604821708</v>
       </c>
       <c r="F84" s="2">
         <f>IF(COUNT('Turns'!F73,'Turns'!F74,'Turns'!F76,'Turns'!F79,'Turns'!F80)=5,SUM('Turns'!F73,'Turns'!F74,'Turns'!F76,'Turns'!F79,'Turns'!F80),"Unknown")</f>
-        <v>0.00076843</v>
+        <v>0.00018242</v>
       </c>
       <c r="G84" s="5">
         <f>IF(ISNUMBER(E84),ROUND(E84*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>67.0</v>
+        <v>16.0</v>
       </c>
       <c r="H84" s="5">
         <f>IF(ISNUMBER(F84),ROUND(F84*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>77.0</v>
+        <v>18.0</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>111</v>
@@ -2869,16 +2758,16 @@
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>111</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="73" customHeight="1">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="24" customHeight="1">
       <c r="B86">
         <v>1</v>
       </c>
@@ -2886,10 +2775,10 @@
         <v>114</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="24" customHeight="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="372" customHeight="1">
       <c r="B87">
         <v>1</v>
       </c>
@@ -2897,12 +2786,12 @@
         <v>116</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A88" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B88" s="4">
         <v>1</v>
@@ -2911,18 +2800,18 @@
         <v>94</v>
       </c>
       <c r="D88" s="4">
-        <v>2697</v>
+        <v>2308</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>95</v>
       </c>
       <c r="M88" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="24" customHeight="1">
       <c r="A89" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -2931,15 +2820,15 @@
         <v>123</v>
       </c>
       <c r="D89" s="5">
-        <v>2090</v>
+        <v>2130</v>
       </c>
       <c r="E89" s="2">
         <f>IF(AND(ISNUMBER(F89),ISNUMBER('Reference data'!$B$3)),F89*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.663143e-05</v>
+        <v>3.7476924e-05</v>
       </c>
       <c r="F89" s="2">
         <f>IF(D89=0,0,IF(ISNUMBER('Reference data'!C17),D89*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.18e-05</v>
+        <v>4.26e-05</v>
       </c>
       <c r="G89" s="5">
         <f>IF(ISNUMBER(E89),ROUND(E89*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2952,7 +2841,7 @@
     </row>
     <row r="90" spans="1:13" ht="24" customHeight="1">
       <c r="A90" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -2965,7 +2854,7 @@
       </c>
       <c r="E90" s="2">
         <f>IF(AND(ISNUMBER(F90),ISNUMBER('Reference data'!$B$3)),F90*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F90" s="2">
         <f>IF(D90=0,0,IF(ISNUMBER('Reference data'!B17),D90*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -2980,9 +2869,9 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="24" customHeight="1">
+    <row r="91" spans="1:13" ht="372" customHeight="1">
       <c r="A91" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -2991,12 +2880,12 @@
         <v>124</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="24" customHeight="1">
       <c r="A92" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -3005,28 +2894,28 @@
         <v>103</v>
       </c>
       <c r="D92" s="5">
-        <v>604</v>
+        <v>175</v>
       </c>
       <c r="E92" s="2">
         <f>IF(AND(ISNUMBER(F92),ISNUMBER('Reference data'!$B$3)),F92*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00013232885</v>
+        <v>3.8488625e-05</v>
       </c>
       <c r="F92" s="2">
         <f>IF(D92=0,0,IF(ISNUMBER('Reference data'!D17),D92*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.000151</v>
+        <v>4.375e-05</v>
       </c>
       <c r="G92" s="5">
         <f>IF(ISNUMBER(E92),ROUND(E92*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="H92" s="5">
         <f>IF(ISNUMBER(F92),ROUND(F92*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="24" customHeight="1">
       <c r="A93" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -3037,7 +2926,7 @@
     </row>
     <row r="94" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A94" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B94" s="4">
         <v>1</v>
@@ -3046,1040 +2935,107 @@
         <v>105</v>
       </c>
       <c r="D94" s="4">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="24" customHeight="1">
       <c r="A95" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D95" s="5">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E95" s="2">
         <f>IF(AND(ISNUMBER(F95),ISNUMBER('Reference data'!$B$3)),F95*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.36134e-06</v>
+        <v>3.4837704e-05</v>
       </c>
       <c r="F95" s="2">
-        <f>IF(D95=0,0,IF(ISNUMBER('Reference data'!F17),D95*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>8.4e-06</v>
+        <f>IF(D95=0,0,IF(ISNUMBER('Reference data'!E17),D95*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>3.96e-05</v>
       </c>
       <c r="G95" s="5">
         <f>IF(ISNUMBER(E95),ROUND(E95*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H95" s="5">
         <f>IF(ISNUMBER(F95),ROUND(F95*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="24" customHeight="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="47" customHeight="1">
       <c r="A96" t="s">
+        <v>146</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" t="s">
+        <v>108</v>
+      </c>
+      <c r="I96" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="C96" t="s">
-        <v>107</v>
-      </c>
-      <c r="D96" s="5">
-        <v>31</v>
-      </c>
-      <c r="E96" s="2">
-        <f>IF(AND(ISNUMBER(F96),ISNUMBER('Reference data'!$B$3)),F96*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.260022e-05</v>
-      </c>
-      <c r="F96" s="2">
-        <f>IF(D96=0,0,IF(ISNUMBER('Reference data'!E17),D96*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.72e-05</v>
-      </c>
-      <c r="G96" s="5">
-        <f>IF(ISNUMBER(E96),ROUND(E96*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H96" s="5">
-        <f>IF(ISNUMBER(F96),ROUND(F96*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="281" customHeight="1">
+    </row>
+    <row r="97" spans="1:11" ht="24" customHeight="1">
       <c r="A97" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>108</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="24" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="24" customHeight="1">
       <c r="A98" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" ht="24" customHeight="1">
-      <c r="A99" t="s">
-        <v>148</v>
-      </c>
-      <c r="B99">
-        <v>1</v>
-      </c>
-      <c r="C99" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="100" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A100" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B100" s="4">
-        <v>1</v>
-      </c>
-      <c r="C100" s="4" t="s">
+    <row r="99" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A99" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B99" s="4">
+        <v>1</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E100" s="2">
-        <f>IF(COUNT('Turns'!E89,'Turns'!E90,'Turns'!E92,'Turns'!E95,'Turns'!E96)=5,SUM('Turns'!E89,'Turns'!E90,'Turns'!E92,'Turns'!E95,'Turns'!E96),"Unknown")</f>
-        <v>0.00020944765</v>
-      </c>
-      <c r="F100" s="2">
-        <f>IF(COUNT('Turns'!F89,'Turns'!F90,'Turns'!F92,'Turns'!F95,'Turns'!F96)=5,SUM('Turns'!F89,'Turns'!F90,'Turns'!F92,'Turns'!F95,'Turns'!F96),"Unknown")</f>
-        <v>0.000239</v>
-      </c>
-      <c r="G100" s="5">
-        <f>IF(ISNUMBER(E100),ROUND(E100*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="H100" s="5">
-        <f>IF(ISNUMBER(F100),ROUND(F100*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
-      </c>
-      <c r="K100" s="4" t="s">
+      <c r="E99" s="2">
+        <f>IF(COUNT('Turns'!E89,'Turns'!E90,'Turns'!E92,'Turns'!E95)=4,SUM('Turns'!E89,'Turns'!E90,'Turns'!E92,'Turns'!E95),"Unknown")</f>
+        <v>0.000111331097</v>
+      </c>
+      <c r="F99" s="2">
+        <f>IF(COUNT('Turns'!F89,'Turns'!F90,'Turns'!F92,'Turns'!F95)=4,SUM('Turns'!F89,'Turns'!F90,'Turns'!F92,'Turns'!F95),"Unknown")</f>
+        <v>0.00012655</v>
+      </c>
+      <c r="G99" s="5">
+        <f>IF(ISNUMBER(E99),ROUND(E99*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+      <c r="H99" s="5">
+        <f>IF(ISNUMBER(F99),ROUND(F99*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+      <c r="K99" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="101" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B101" s="4">
-        <v>1</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K101" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M101" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="24" customHeight="1">
-      <c r="B102">
-        <v>1</v>
-      </c>
-      <c r="C102" t="s">
-        <v>114</v>
-      </c>
-      <c r="I102" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" ht="320" customHeight="1">
-      <c r="B103">
-        <v>1</v>
-      </c>
-      <c r="C103" t="s">
-        <v>116</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A104" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B104" s="4">
-        <v>1</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D104" s="4">
-        <v>2845</v>
-      </c>
-      <c r="J104" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M104" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="24" customHeight="1">
-      <c r="A105" t="s">
-        <v>153</v>
-      </c>
-      <c r="B105">
-        <v>1</v>
-      </c>
-      <c r="C105" t="s">
-        <v>123</v>
-      </c>
-      <c r="D105" s="5">
-        <v>2694</v>
-      </c>
-      <c r="E105" s="2">
-        <f>IF(AND(ISNUMBER(F105),ISNUMBER('Reference data'!$B$3)),F105*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.7217738e-05</v>
-      </c>
-      <c r="F105" s="2">
-        <f>IF(D105=0,0,IF(ISNUMBER('Reference data'!C17),D105*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>5.388e-05</v>
-      </c>
-      <c r="G105" s="5">
-        <f>IF(ISNUMBER(E105),ROUND(E105*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H105" s="5">
-        <f>IF(ISNUMBER(F105),ROUND(F105*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" ht="24" customHeight="1">
-      <c r="A106" t="s">
-        <v>153</v>
-      </c>
-      <c r="B106">
-        <v>1</v>
-      </c>
-      <c r="C106" t="s">
-        <v>97</v>
-      </c>
-      <c r="D106" s="5">
-        <v>3</v>
-      </c>
-      <c r="E106" s="2">
-        <f>IF(AND(ISNUMBER(F106),ISNUMBER('Reference data'!$B$3)),F106*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F106" s="2">
-        <f>IF(D106=0,0,IF(ISNUMBER('Reference data'!B17),D106*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G106" s="5">
-        <f>IF(ISNUMBER(E106),ROUND(E106*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H106" s="5">
-        <f>IF(ISNUMBER(F106),ROUND(F106*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" ht="320" customHeight="1">
-      <c r="A107" t="s">
-        <v>153</v>
-      </c>
-      <c r="B107">
-        <v>1</v>
-      </c>
-      <c r="C107" t="s">
-        <v>124</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" ht="24" customHeight="1">
-      <c r="A108" t="s">
-        <v>153</v>
-      </c>
-      <c r="B108">
-        <v>1</v>
-      </c>
-      <c r="C108" t="s">
-        <v>103</v>
-      </c>
-      <c r="D108" s="5">
-        <v>148</v>
-      </c>
-      <c r="E108" s="2">
-        <f>IF(AND(ISNUMBER(F108),ISNUMBER('Reference data'!$B$3)),F108*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.242495e-05</v>
-      </c>
-      <c r="F108" s="2">
-        <f>IF(D108=0,0,IF(ISNUMBER('Reference data'!D17),D108*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>3.7e-05</v>
-      </c>
-      <c r="G108" s="5">
-        <f>IF(ISNUMBER(E108),ROUND(E108*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H108" s="5">
-        <f>IF(ISNUMBER(F108),ROUND(F108*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" ht="24" customHeight="1">
-      <c r="A109" t="s">
-        <v>153</v>
-      </c>
-      <c r="B109">
-        <v>1</v>
-      </c>
-      <c r="C109" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A110" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B110" s="4">
-        <v>1</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D110" s="4">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" ht="24" customHeight="1">
-      <c r="A111" t="s">
-        <v>153</v>
-      </c>
-      <c r="B111">
-        <v>1</v>
-      </c>
-      <c r="C111" t="s">
-        <v>106</v>
-      </c>
-      <c r="D111" s="5">
-        <v>850</v>
-      </c>
-      <c r="E111" s="2">
-        <f>IF(AND(ISNUMBER(F111),ISNUMBER('Reference data'!$B$3)),F111*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000893877</v>
-      </c>
-      <c r="F111" s="2">
-        <f>IF(D111=0,0,IF(ISNUMBER('Reference data'!F17),D111*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>0.00102</v>
-      </c>
-      <c r="G111" s="5">
-        <f>IF(ISNUMBER(E111),ROUND(E111*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>89.0</v>
-      </c>
-      <c r="H111" s="5">
-        <f>IF(ISNUMBER(F111),ROUND(F111*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>102.0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" ht="24" customHeight="1">
-      <c r="A112" t="s">
-        <v>153</v>
-      </c>
-      <c r="B112">
-        <v>1</v>
-      </c>
-      <c r="C112" t="s">
-        <v>107</v>
-      </c>
-      <c r="D112" s="5">
-        <v>102</v>
-      </c>
-      <c r="E112" s="2">
-        <f>IF(AND(ISNUMBER(F112),ISNUMBER('Reference data'!$B$3)),F112*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00010726524</v>
-      </c>
-      <c r="F112" s="2">
-        <f>IF(D112=0,0,IF(ISNUMBER('Reference data'!E17),D112*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001224</v>
-      </c>
-      <c r="G112" s="5">
-        <f>IF(ISNUMBER(E112),ROUND(E112*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="H112" s="5">
-        <f>IF(ISNUMBER(F112),ROUND(F112*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" ht="409" customHeight="1">
-      <c r="A113" t="s">
-        <v>153</v>
-      </c>
-      <c r="B113">
-        <v>1</v>
-      </c>
-      <c r="C113" t="s">
-        <v>108</v>
-      </c>
-      <c r="I113" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" ht="24" customHeight="1">
-      <c r="A114" t="s">
-        <v>153</v>
-      </c>
-      <c r="B114">
-        <v>1</v>
-      </c>
-      <c r="C114" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" ht="24" customHeight="1">
-      <c r="A115" t="s">
-        <v>153</v>
-      </c>
-      <c r="B115">
-        <v>1</v>
-      </c>
-      <c r="C115" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A116" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B116" s="4">
-        <v>1</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E116" s="2">
-        <f>IF(COUNT('Turns'!E105,'Turns'!E106,'Turns'!E108,'Turns'!E111,'Turns'!E112)=5,SUM('Turns'!E105,'Turns'!E106,'Turns'!E108,'Turns'!E111,'Turns'!E112),"Unknown")</f>
-        <v>0.001081310738</v>
-      </c>
-      <c r="F116" s="2">
-        <f>IF(COUNT('Turns'!F105,'Turns'!F106,'Turns'!F108,'Turns'!F111,'Turns'!F112)=5,SUM('Turns'!F105,'Turns'!F106,'Turns'!F108,'Turns'!F111,'Turns'!F112),"Unknown")</f>
-        <v>0.00123388</v>
-      </c>
-      <c r="G116" s="5">
-        <f>IF(ISNUMBER(E116),ROUND(E116*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>108.0</v>
-      </c>
-      <c r="H116" s="5">
-        <f>IF(ISNUMBER(F116),ROUND(F116*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>123.0</v>
-      </c>
-      <c r="K116" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B117" s="4">
-        <v>1</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="K117" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M117" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" ht="60" customHeight="1">
-      <c r="B118">
-        <v>1</v>
-      </c>
-      <c r="C118" t="s">
-        <v>114</v>
-      </c>
-      <c r="I118" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" ht="24" customHeight="1">
-      <c r="B119">
-        <v>1</v>
-      </c>
-      <c r="C119" t="s">
-        <v>116</v>
-      </c>
-      <c r="I119" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A120" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B120" s="4">
-        <v>1</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D120" s="4">
-        <v>3823</v>
-      </c>
-      <c r="J120" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M120" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" ht="24" customHeight="1">
-      <c r="A121" t="s">
-        <v>158</v>
-      </c>
-      <c r="B121">
-        <v>1</v>
-      </c>
-      <c r="C121" t="s">
-        <v>123</v>
-      </c>
-      <c r="D121" s="5">
-        <v>2842</v>
-      </c>
-      <c r="E121" s="2">
-        <f>IF(AND(ISNUMBER(F121),ISNUMBER('Reference data'!$B$3)),F121*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.9811734e-05</v>
-      </c>
-      <c r="F121" s="2">
-        <f>IF(D121=0,0,IF(ISNUMBER('Reference data'!C17),D121*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>5.684e-05</v>
-      </c>
-      <c r="G121" s="5">
-        <f>IF(ISNUMBER(E121),ROUND(E121*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H121" s="5">
-        <f>IF(ISNUMBER(F121),ROUND(F121*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" ht="24" customHeight="1">
-      <c r="A122" t="s">
-        <v>158</v>
-      </c>
-      <c r="B122">
-        <v>1</v>
-      </c>
-      <c r="C122" t="s">
-        <v>97</v>
-      </c>
-      <c r="D122" s="5">
-        <v>3</v>
-      </c>
-      <c r="E122" s="2">
-        <f>IF(AND(ISNUMBER(F122),ISNUMBER('Reference data'!$B$3)),F122*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F122" s="2">
-        <f>IF(D122=0,0,IF(ISNUMBER('Reference data'!B17),D122*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G122" s="5">
-        <f>IF(ISNUMBER(E122),ROUND(E122*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H122" s="5">
-        <f>IF(ISNUMBER(F122),ROUND(F122*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" ht="24" customHeight="1">
-      <c r="A123" t="s">
-        <v>158</v>
-      </c>
-      <c r="B123">
-        <v>1</v>
-      </c>
-      <c r="C123" t="s">
-        <v>124</v>
-      </c>
-      <c r="I123" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" ht="24" customHeight="1">
-      <c r="A124" t="s">
-        <v>158</v>
-      </c>
-      <c r="B124">
-        <v>1</v>
-      </c>
-      <c r="C124" t="s">
-        <v>103</v>
-      </c>
-      <c r="D124" s="5">
-        <v>978</v>
-      </c>
-      <c r="E124" s="2">
-        <f>IF(AND(ISNUMBER(F124),ISNUMBER('Reference data'!$B$3)),F124*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000214267575</v>
-      </c>
-      <c r="F124" s="2">
-        <f>IF(D124=0,0,IF(ISNUMBER('Reference data'!D17),D124*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.0002445</v>
-      </c>
-      <c r="G124" s="5">
-        <f>IF(ISNUMBER(E124),ROUND(E124*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="H124" s="5">
-        <f>IF(ISNUMBER(F124),ROUND(F124*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" ht="24" customHeight="1">
-      <c r="A125" t="s">
-        <v>158</v>
-      </c>
-      <c r="B125">
-        <v>1</v>
-      </c>
-      <c r="C125" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A126" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B126" s="4">
-        <v>1</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D126" s="4">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" ht="24" customHeight="1">
-      <c r="A127" t="s">
-        <v>158</v>
-      </c>
-      <c r="B127">
-        <v>1</v>
-      </c>
-      <c r="C127" t="s">
-        <v>106</v>
-      </c>
-      <c r="D127" s="5">
-        <v>7</v>
-      </c>
-      <c r="E127" s="2">
-        <f>IF(AND(ISNUMBER(F127),ISNUMBER('Reference data'!$B$3)),F127*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.36134e-06</v>
-      </c>
-      <c r="F127" s="2">
-        <f>IF(D127=0,0,IF(ISNUMBER('Reference data'!F17),D127*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>8.4e-06</v>
-      </c>
-      <c r="G127" s="5">
-        <f>IF(ISNUMBER(E127),ROUND(E127*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H127" s="5">
-        <f>IF(ISNUMBER(F127),ROUND(F127*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" ht="24" customHeight="1">
-      <c r="A128" t="s">
-        <v>158</v>
-      </c>
-      <c r="B128">
-        <v>1</v>
-      </c>
-      <c r="C128" t="s">
-        <v>107</v>
-      </c>
-      <c r="D128" s="5">
-        <v>31</v>
-      </c>
-      <c r="E128" s="2">
-        <f>IF(AND(ISNUMBER(F128),ISNUMBER('Reference data'!$B$3)),F128*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.260022e-05</v>
-      </c>
-      <c r="F128" s="2">
-        <f>IF(D128=0,0,IF(ISNUMBER('Reference data'!E17),D128*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.72e-05</v>
-      </c>
-      <c r="G128" s="5">
-        <f>IF(ISNUMBER(E128),ROUND(E128*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H128" s="5">
-        <f>IF(ISNUMBER(F128),ROUND(F128*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" ht="281" customHeight="1">
-      <c r="A129" t="s">
-        <v>158</v>
-      </c>
-      <c r="B129">
-        <v>1</v>
-      </c>
-      <c r="C129" t="s">
-        <v>108</v>
-      </c>
-      <c r="I129" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" ht="24" customHeight="1">
-      <c r="A130" t="s">
-        <v>158</v>
-      </c>
-      <c r="B130">
-        <v>1</v>
-      </c>
-      <c r="C130" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" ht="24" customHeight="1">
-      <c r="A131" t="s">
-        <v>158</v>
-      </c>
-      <c r="B131">
-        <v>1</v>
-      </c>
-      <c r="C131" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A132" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B132" s="4">
-        <v>1</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E132" s="2">
-        <f>IF(COUNT('Turns'!E121,'Turns'!E122,'Turns'!E124,'Turns'!E127,'Turns'!E128)=5,SUM('Turns'!E121,'Turns'!E122,'Turns'!E124,'Turns'!E127,'Turns'!E128),"Unknown")</f>
-        <v>0.000304566679</v>
-      </c>
-      <c r="F132" s="2">
-        <f>IF(COUNT('Turns'!F121,'Turns'!F122,'Turns'!F124,'Turns'!F127,'Turns'!F128)=5,SUM('Turns'!F121,'Turns'!F122,'Turns'!F124,'Turns'!F127,'Turns'!F128),"Unknown")</f>
-        <v>0.00034754</v>
-      </c>
-      <c r="G132" s="5">
-        <f>IF(ISNUMBER(E132),ROUND(E132*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>30.0</v>
-      </c>
-      <c r="H132" s="5">
-        <f>IF(ISNUMBER(F132),ROUND(F132*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
-      </c>
-      <c r="K132" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B133" s="4">
-        <v>1</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K133" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M133" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="134" spans="1:13" ht="24" customHeight="1">
-      <c r="B134">
-        <v>1</v>
-      </c>
-      <c r="C134" t="s">
-        <v>114</v>
-      </c>
-      <c r="I134" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" ht="320" customHeight="1">
-      <c r="B135">
-        <v>1</v>
-      </c>
-      <c r="C135" t="s">
-        <v>116</v>
-      </c>
-      <c r="I135" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A136" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B136" s="4">
-        <v>1</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D136" s="4">
-        <v>3971</v>
-      </c>
-      <c r="J136" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M136" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" ht="24" customHeight="1">
-      <c r="A137" t="s">
-        <v>163</v>
-      </c>
-      <c r="B137">
-        <v>1</v>
-      </c>
-      <c r="C137" t="s">
-        <v>123</v>
-      </c>
-      <c r="D137" s="5">
-        <v>3820</v>
-      </c>
-      <c r="E137" s="2">
-        <f>IF(AND(ISNUMBER(F137),ISNUMBER('Reference data'!$B$3)),F137*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.695314e-05</v>
-      </c>
-      <c r="F137" s="2">
-        <f>IF(D137=0,0,IF(ISNUMBER('Reference data'!C17),D137*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>7.64e-05</v>
-      </c>
-      <c r="G137" s="5">
-        <f>IF(ISNUMBER(E137),ROUND(E137*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="H137" s="5">
-        <f>IF(ISNUMBER(F137),ROUND(F137*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" ht="24" customHeight="1">
-      <c r="A138" t="s">
-        <v>163</v>
-      </c>
-      <c r="B138">
-        <v>1</v>
-      </c>
-      <c r="C138" t="s">
-        <v>97</v>
-      </c>
-      <c r="D138" s="5">
-        <v>3</v>
-      </c>
-      <c r="E138" s="2">
-        <f>IF(AND(ISNUMBER(F138),ISNUMBER('Reference data'!$B$3)),F138*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F138" s="2">
-        <f>IF(D138=0,0,IF(ISNUMBER('Reference data'!B17),D138*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G138" s="5">
-        <f>IF(ISNUMBER(E138),ROUND(E138*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H138" s="5">
-        <f>IF(ISNUMBER(F138),ROUND(F138*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" ht="320" customHeight="1">
-      <c r="A139" t="s">
-        <v>163</v>
-      </c>
-      <c r="B139">
-        <v>1</v>
-      </c>
-      <c r="C139" t="s">
-        <v>124</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" ht="24" customHeight="1">
-      <c r="A140" t="s">
-        <v>163</v>
-      </c>
-      <c r="B140">
-        <v>1</v>
-      </c>
-      <c r="C140" t="s">
-        <v>103</v>
-      </c>
-      <c r="D140" s="5">
-        <v>148</v>
-      </c>
-      <c r="E140" s="2">
-        <f>IF(AND(ISNUMBER(F140),ISNUMBER('Reference data'!$B$3)),F140*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.242495e-05</v>
-      </c>
-      <c r="F140" s="2">
-        <f>IF(D140=0,0,IF(ISNUMBER('Reference data'!D17),D140*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>3.7e-05</v>
-      </c>
-      <c r="G140" s="5">
-        <f>IF(ISNUMBER(E140),ROUND(E140*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H140" s="5">
-        <f>IF(ISNUMBER(F140),ROUND(F140*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" ht="24" customHeight="1">
-      <c r="A141" t="s">
-        <v>163</v>
-      </c>
-      <c r="B141">
-        <v>1</v>
-      </c>
-      <c r="C141" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A142" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B142" s="4">
-        <v>1</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D142" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" ht="24" customHeight="1">
-      <c r="A143" t="s">
-        <v>163</v>
-      </c>
-      <c r="B143">
-        <v>1</v>
-      </c>
-      <c r="C143" t="s">
-        <v>107</v>
-      </c>
-      <c r="D143" s="5">
-        <v>16</v>
-      </c>
-      <c r="E143" s="2">
-        <f>IF(AND(ISNUMBER(F143),ISNUMBER('Reference data'!$B$3)),F143*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.682592e-05</v>
-      </c>
-      <c r="F143" s="2">
-        <f>IF(D143=0,0,IF(ISNUMBER('Reference data'!E17),D143*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>1.92e-05</v>
-      </c>
-      <c r="G143" s="5">
-        <f>IF(ISNUMBER(E143),ROUND(E143*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H143" s="5">
-        <f>IF(ISNUMBER(F143),ROUND(F143*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" ht="47" customHeight="1">
-      <c r="A144" t="s">
-        <v>163</v>
-      </c>
-      <c r="B144">
-        <v>1</v>
-      </c>
-      <c r="C144" t="s">
-        <v>108</v>
-      </c>
-      <c r="I144" s="6" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" ht="24" customHeight="1">
-      <c r="A145" t="s">
-        <v>163</v>
-      </c>
-      <c r="B145">
-        <v>1</v>
-      </c>
-      <c r="C145" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" ht="24" customHeight="1">
-      <c r="A146" t="s">
-        <v>163</v>
-      </c>
-      <c r="B146">
-        <v>1</v>
-      </c>
-      <c r="C146" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A147" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B147" s="4">
-        <v>1</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E147" s="2">
-        <f>IF(COUNT('Turns'!E137,'Turns'!E138,'Turns'!E140,'Turns'!E143)=4,SUM('Turns'!E137,'Turns'!E138,'Turns'!E140,'Turns'!E143),"Unknown")</f>
-        <v>0.00011672982</v>
-      </c>
-      <c r="F147" s="2">
-        <f>IF(COUNT('Turns'!F137,'Turns'!F138,'Turns'!F140,'Turns'!F143)=4,SUM('Turns'!F137,'Turns'!F138,'Turns'!F140,'Turns'!F143),"Unknown")</f>
-        <v>0.0001332</v>
-      </c>
-      <c r="G147" s="5">
-        <f>IF(ISNUMBER(E147),ROUND(E147*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-      <c r="H147" s="5">
-        <f>IF(ISNUMBER(F147),ROUND(F147*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="K147" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE147">
+  <conditionalFormatting sqref="A2:AE99">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -4093,7 +3049,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE64"/>
+  <dimension ref="A1:AE42"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -4200,13 +3156,13 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
@@ -4215,7 +3171,7 @@
         <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
@@ -4226,7 +3182,7 @@
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E26)=2,SUM('Turns'!E5,'Turns'!E26),"Unknown")</f>
-        <v>0.00015616557</v>
+        <v>0.000156769668</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F26)=2,SUM('Turns'!F5,'Turns'!F26),"Unknown")</f>
@@ -4246,72 +3202,72 @@
       </c>
       <c r="P2" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>1107.0</v>
+        <v>1112.0</v>
       </c>
       <c r="Q2" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.0002425298625</v>
+        <v>0.00024456772</v>
       </c>
       <c r="R2" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.00027675</v>
+        <v>0.000278</v>
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D13,'Turns'!D32)=2,SUM('Turns'!D13,'Turns'!D32),"Unknown")</f>
-        <v>148.0</v>
+        <v>336.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E13,'Turns'!E32)=2,SUM('Turns'!E13,'Turns'!E32),"Unknown")</f>
-        <v>0.00015563976</v>
+        <v>0.000354711168</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F13,'Turns'!F32)=2,SUM('Turns'!F13,'Turns'!F32),"Unknown")</f>
-        <v>0.0001776</v>
+        <v>0.0004032</v>
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D12,'Turns'!D31)=2,SUM('Turns'!D12,'Turns'!D31),"Unknown")</f>
-        <v>388.0</v>
+        <v>252.0</v>
       </c>
       <c r="W2" s="2">
         <f>IF(COUNT('Turns'!E12,'Turns'!E31)=2,SUM('Turns'!E12,'Turns'!E31),"Unknown")</f>
-        <v>0.00040802856</v>
+        <v>0.000266033376</v>
       </c>
       <c r="X2" s="2">
         <f>IF(COUNT('Turns'!F12,'Turns'!F31)=2,SUM('Turns'!F12,'Turns'!F31),"Unknown")</f>
-        <v>0.0004656</v>
+        <v>0.0003024</v>
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E36)=2,SUM('Turns'!E17,'Turns'!E36),"Unknown")</f>
-        <v>0.0009623637525</v>
+        <v>0.001022081932</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F36)=2,SUM('Turns'!F17,'Turns'!F36),"Unknown")</f>
-        <v>0.00109815</v>
+        <v>0.0011618</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>96.0</v>
+        <v>102.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>110.0</v>
+        <v>116.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>7489.244</v>
+        <v>6259.472</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
@@ -4320,30 +3276,30 @@
         <v>111</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="H3" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.599</v>
+        <v>2.297</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
@@ -4352,10 +3308,10 @@
         <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="H4" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
@@ -4366,7 +3322,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>0.00015563976</v>
+        <v>0.000156241824</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -4396,7 +3352,7 @@
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>7.571664e-05</v>
+        <v>7.6009536e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
@@ -4404,48 +3360,48 @@
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>23.0</v>
+        <v>15.0</v>
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>2.418726e-05</v>
+        <v>1.583532e-05</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>2.76e-05</v>
+        <v>1.8e-05</v>
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.00025554366</v>
+        <v>0.00024808668</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0002916</v>
+        <v>0.000282</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>1877.927</v>
+        <v>1626.442</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>95</v>
@@ -4457,13 +3413,13 @@
         <v>888</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="H5" t="s">
         <v>96</v>
       </c>
       <c r="I5" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="J5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
@@ -4471,7 +3427,7 @@
       </c>
       <c r="K5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>0.00015563976</v>
+        <v>0.000156241824</v>
       </c>
       <c r="L5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -4501,7 +3457,7 @@
       </c>
       <c r="T5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>7.571664e-05</v>
+        <v>7.6009536e-05</v>
       </c>
       <c r="U5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
@@ -4509,51 +3465,51 @@
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>23.0</v>
+        <v>15.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>2.418726e-05</v>
+        <v>1.583532e-05</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>2.76e-05</v>
+        <v>1.8e-05</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.00025554366</v>
+        <v>0.00024808668</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0002916</v>
+        <v>0.000282</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>1788.199</v>
+        <v>1620.867</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
@@ -4562,30 +3518,30 @@
         <v>111</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H6" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>0.404</v>
+        <v>1.149</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
@@ -4594,30 +3550,30 @@
         <v>111</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="H7" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
       </c>
       <c r="AD7" s="1">
-        <v>3.702</v>
+        <v>8.435</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>47</v>
@@ -4626,30 +3582,30 @@
         <v>111</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="H8" t="s">
         <v>113</v>
       </c>
       <c r="I8" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="AD8" s="1">
-        <v>1.184</v>
+        <v>3.39</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
@@ -4658,30 +3614,30 @@
         <v>111</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="H9" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
       </c>
       <c r="AD9" s="1">
-        <v>3.477</v>
+        <v>6.234</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
@@ -4690,30 +3646,30 @@
         <v>111</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="H10" t="s">
         <v>118</v>
       </c>
       <c r="I10" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="AD10" s="1">
-        <v>1.001</v>
+        <v>2.085</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
@@ -4722,30 +3678,30 @@
         <v>111</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="H11" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.275</v>
+        <v>0.963</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
@@ -4754,10 +3710,10 @@
         <v>111</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H12" t="s">
         <v>175</v>
-      </c>
-      <c r="H12" t="s">
-        <v>192</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -4768,7 +3724,7 @@
       </c>
       <c r="K12" s="2">
         <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L12" s="2">
         <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
@@ -4788,72 +3744,72 @@
       </c>
       <c r="P12" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>1107.0</v>
+        <v>1112.0</v>
       </c>
       <c r="Q12" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.0002425298625</v>
+        <v>0.00024456772</v>
       </c>
       <c r="R12" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.00027675</v>
+        <v>0.000278</v>
       </c>
       <c r="S12" s="2">
         <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>76.0</v>
+        <v>264.0</v>
       </c>
       <c r="T12" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.992312e-05</v>
+        <v>0.000278701632</v>
       </c>
       <c r="U12" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>9.12e-05</v>
+        <v>0.0003168</v>
       </c>
       <c r="V12" s="2">
         <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>365.0</v>
+        <v>237.0</v>
       </c>
       <c r="W12" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0003838413</v>
+        <v>0.000250198056</v>
       </c>
       <c r="X12" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.000438</v>
+        <v>0.0002844</v>
       </c>
       <c r="Y12" s="2">
         <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.0007068200925</v>
+        <v>0.000773995252</v>
       </c>
       <c r="Z12" s="2">
         <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.00080655</v>
+        <v>0.0008798</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>71.0</v>
+        <v>77.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>81.0</v>
+        <v>88.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>5598.299</v>
+        <v>4606.116</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>95</v>
@@ -4862,16 +3818,16 @@
         <v>111</v>
       </c>
       <c r="F13" s="1">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="H13" t="s">
         <v>122</v>
       </c>
       <c r="I13" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="J13" s="2">
         <f>IF(COUNT('Turns'!D26)=1,SUM('Turns'!D26),"Unknown")</f>
@@ -4879,7 +3835,7 @@
       </c>
       <c r="K13" s="2">
         <f>IF(COUNT('Turns'!E26)=1,SUM('Turns'!E26),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L13" s="2">
         <f>IF(COUNT('Turns'!F26)=1,SUM('Turns'!F26),"Unknown")</f>
@@ -4899,107 +3855,107 @@
       </c>
       <c r="P13" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>1107.0</v>
+        <v>1112.0</v>
       </c>
       <c r="Q13" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.0002425298625</v>
+        <v>0.00024456772</v>
       </c>
       <c r="R13" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.00027675</v>
+        <v>0.000278</v>
       </c>
       <c r="S13" s="2">
         <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>76.0</v>
+        <v>264.0</v>
       </c>
       <c r="T13" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.992312e-05</v>
+        <v>0.000278701632</v>
       </c>
       <c r="U13" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>9.12e-05</v>
+        <v>0.0003168</v>
       </c>
       <c r="V13" s="2">
         <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>365.0</v>
+        <v>237.0</v>
       </c>
       <c r="W13" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>0.0003838413</v>
+        <v>0.000250198056</v>
       </c>
       <c r="X13" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>0.000438</v>
+        <v>0.0002844</v>
       </c>
       <c r="Y13" s="2">
         <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>0.0007068200925</v>
+        <v>0.000773995252</v>
       </c>
       <c r="Z13" s="2">
         <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>0.00080655</v>
+        <v>0.0008798</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>71.0</v>
+        <v>77.0</v>
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>81.0</v>
+        <v>88.0</v>
       </c>
       <c r="AC13" s="1" t="s">
         <v>121</v>
       </c>
       <c r="AD13" s="1">
-        <v>5596.845</v>
+        <v>4601.821</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H14" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
       </c>
       <c r="AD14" s="1">
-        <v>0.31</v>
+        <v>0.677</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
@@ -5008,103 +3964,103 @@
         <v>111</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="H15" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="J15" s="2">
-        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D42,'Turns'!D58)=2,SUM('Turns'!D42,'Turns'!D58),"Unknown")</f>
+        <v>6.0</v>
       </c>
       <c r="K15" s="2">
-        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E42,'Turns'!E58)=2,SUM('Turns'!E42,'Turns'!E58),"Unknown")</f>
+        <v>1.055688e-06</v>
       </c>
       <c r="L15" s="2">
-        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F42,'Turns'!F58)=2,SUM('Turns'!F42,'Turns'!F58),"Unknown")</f>
+        <v>1.2e-06</v>
       </c>
       <c r="M15" s="2">
-        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>1107.0</v>
+        <f>IF(COUNT('Turns'!D41,'Turns'!D57)=2,SUM('Turns'!D41,'Turns'!D57),"Unknown")</f>
+        <v>2751.0</v>
       </c>
       <c r="N15" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.9402389e-05</v>
+        <f>IF(COUNT('Turns'!E41,'Turns'!E57)=2,SUM('Turns'!E41,'Turns'!E57),"Unknown")</f>
+        <v>4.84032948e-05</v>
       </c>
       <c r="O15" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>2.214e-05</v>
+        <f>IF(COUNT('Turns'!F41,'Turns'!F57)=2,SUM('Turns'!F41,'Turns'!F57),"Unknown")</f>
+        <v>5.502e-05</v>
       </c>
       <c r="P15" s="2">
-        <f>IF(COUNT('Turns'!D44)=1,SUM('Turns'!D44),"Unknown")</f>
-        <v>496.0</v>
+        <f>IF(COUNT('Turns'!D44,'Turns'!D60)=2,SUM('Turns'!D44,'Turns'!D60),"Unknown")</f>
+        <v>684.0</v>
       </c>
       <c r="Q15" s="2">
-        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>0.0001086674</v>
+        <f>IF(COUNT('Turns'!E44,'Turns'!E60)=2,SUM('Turns'!E44,'Turns'!E60),"Unknown")</f>
+        <v>0.00015043554</v>
       </c>
       <c r="R15" s="2">
-        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>0.000124</v>
+        <f>IF(COUNT('Turns'!F44,'Turns'!F60)=2,SUM('Turns'!F44,'Turns'!F60),"Unknown")</f>
+        <v>0.000171</v>
       </c>
       <c r="S15" s="2">
-        <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
-        <v>110.0</v>
+        <f>IF(COUNT('Turns'!D48,'Turns'!D64)=2,SUM('Turns'!D48,'Turns'!D64),"Unknown")</f>
+        <v>312.0</v>
       </c>
       <c r="T15" s="2">
-        <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
-        <v>0.0001156782</v>
+        <f>IF(COUNT('Turns'!E48,'Turns'!E64)=2,SUM('Turns'!E48,'Turns'!E64),"Unknown")</f>
+        <v>0.000329374656</v>
       </c>
       <c r="U15" s="2">
-        <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
-        <v>0.000132</v>
+        <f>IF(COUNT('Turns'!F48,'Turns'!F64)=2,SUM('Turns'!F48,'Turns'!F64),"Unknown")</f>
+        <v>0.0003744</v>
       </c>
       <c r="V15" s="2">
-        <f>IF(COUNT('Turns'!D47)=1,SUM('Turns'!D47),"Unknown")</f>
-        <v>210.0</v>
+        <f>IF(COUNT('Turns'!D47,'Turns'!D63)=2,SUM('Turns'!D47,'Turns'!D63),"Unknown")</f>
+        <v>37.0</v>
       </c>
       <c r="W15" s="2">
-        <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>0.0002208402</v>
+        <f>IF(COUNT('Turns'!E47,'Turns'!E63)=2,SUM('Turns'!E47,'Turns'!E63),"Unknown")</f>
+        <v>3.9060456e-05</v>
       </c>
       <c r="X15" s="2">
-        <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>0.000252</v>
+        <f>IF(COUNT('Turns'!F47,'Turns'!F63)=2,SUM('Turns'!F47,'Turns'!F63),"Unknown")</f>
+        <v>4.44e-05</v>
       </c>
       <c r="Y15" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>0.000465113999</v>
+        <f>IF(COUNT('Turns'!E52,'Turns'!E68)=2,SUM('Turns'!E52,'Turns'!E68),"Unknown")</f>
+        <v>0.0005683296348</v>
       </c>
       <c r="Z15" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>0.00053074</v>
+        <f>IF(COUNT('Turns'!F52,'Turns'!F68)=2,SUM('Turns'!F52,'Turns'!F68),"Unknown")</f>
+        <v>0.00064602</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>57.0</v>
       </c>
       <c r="AB15" s="5">
         <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>65.0</v>
       </c>
       <c r="AD15" s="1">
-        <v>5797.066</v>
+        <v>3296.949</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
@@ -5113,30 +4069,30 @@
         <v>111</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H16" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="I16" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="AD16" s="1">
-        <v>0.359</v>
+        <v>1.492</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>47</v>
@@ -5145,62 +4101,62 @@
         <v>111</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="H17" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="I17" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="AD17" s="1">
-        <v>2.636</v>
+        <v>5.953</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="54" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H18" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="H18" t="s">
-        <v>129</v>
-      </c>
       <c r="I18" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="AD18" s="1">
-        <v>0.659</v>
+        <v>2.326</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="54" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>47</v>
@@ -5209,30 +4165,30 @@
         <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="H19" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="I19" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.276</v>
+        <v>0.355</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="54" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>47</v>
@@ -5241,13 +4197,13 @@
         <v>111</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="H20" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="I20" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="J20" s="2">
         <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
@@ -5255,7 +4211,7 @@
       </c>
       <c r="K20" s="2">
         <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L20" s="2">
         <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
@@ -5263,84 +4219,84 @@
       </c>
       <c r="M20" s="2">
         <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>1107.0</v>
+        <v>1112.0</v>
       </c>
       <c r="N20" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.9402389e-05</v>
+        <v>1.95654176e-05</v>
       </c>
       <c r="O20" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>2.214e-05</v>
+        <v>2.224e-05</v>
       </c>
       <c r="P20" s="2">
         <f>IF(COUNT('Turns'!D44)=1,SUM('Turns'!D44),"Unknown")</f>
-        <v>496.0</v>
+        <v>527.0</v>
       </c>
       <c r="Q20" s="2">
         <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>0.0001086674</v>
+        <v>0.000115905745</v>
       </c>
       <c r="R20" s="2">
         <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>0.000124</v>
+        <v>0.00013175</v>
       </c>
       <c r="S20" s="2">
         <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
-        <v>110.0</v>
+        <v>31.0</v>
       </c>
       <c r="T20" s="2">
         <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
-        <v>0.0001156782</v>
+        <v>3.2726328e-05</v>
       </c>
       <c r="U20" s="2">
         <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
-        <v>0.000132</v>
+        <v>3.72e-05</v>
       </c>
       <c r="V20" s="2">
         <f>IF(COUNT('Turns'!D47)=1,SUM('Turns'!D47),"Unknown")</f>
-        <v>210.0</v>
+        <v>10.0</v>
       </c>
       <c r="W20" s="2">
         <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>0.0002208402</v>
+        <v>1.055688e-05</v>
       </c>
       <c r="X20" s="2">
         <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>0.000252</v>
+        <v>1.2e-05</v>
       </c>
       <c r="Y20" s="2">
         <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>0.000465113999</v>
+        <v>0.0001792822146</v>
       </c>
       <c r="Z20" s="2">
         <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>0.00053074</v>
+        <v>0.00020379</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>5787.399</v>
+        <v>923.681</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="54" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>95</v>
@@ -5349,16 +4305,16 @@
         <v>111</v>
       </c>
       <c r="F21" s="1">
-        <v>1606</v>
+        <v>1642</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="H21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I21" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="J21" s="2">
         <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
@@ -5366,7 +4322,7 @@
       </c>
       <c r="K21" s="2">
         <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L21" s="2">
         <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
@@ -5374,119 +4330,119 @@
       </c>
       <c r="M21" s="2">
         <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>1107.0</v>
+        <v>1112.0</v>
       </c>
       <c r="N21" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.9402389e-05</v>
+        <v>1.95654176e-05</v>
       </c>
       <c r="O21" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>2.214e-05</v>
+        <v>2.224e-05</v>
       </c>
       <c r="P21" s="2">
         <f>IF(COUNT('Turns'!D44)=1,SUM('Turns'!D44),"Unknown")</f>
-        <v>496.0</v>
+        <v>527.0</v>
       </c>
       <c r="Q21" s="2">
         <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>0.0001086674</v>
+        <v>0.000115905745</v>
       </c>
       <c r="R21" s="2">
         <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>0.000124</v>
+        <v>0.00013175</v>
       </c>
       <c r="S21" s="2">
         <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
-        <v>110.0</v>
+        <v>31.0</v>
       </c>
       <c r="T21" s="2">
         <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
-        <v>0.0001156782</v>
+        <v>3.2726328e-05</v>
       </c>
       <c r="U21" s="2">
         <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
-        <v>0.000132</v>
+        <v>3.72e-05</v>
       </c>
       <c r="V21" s="2">
         <f>IF(COUNT('Turns'!D47)=1,SUM('Turns'!D47),"Unknown")</f>
-        <v>210.0</v>
+        <v>10.0</v>
       </c>
       <c r="W21" s="2">
         <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>0.0002208402</v>
+        <v>1.055688e-05</v>
       </c>
       <c r="X21" s="2">
         <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>0.000252</v>
+        <v>1.2e-05</v>
       </c>
       <c r="Y21" s="2">
         <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>0.000465113999</v>
+        <v>0.0001792822146</v>
       </c>
       <c r="Z21" s="2">
         <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>0.00053074</v>
+        <v>0.00020379</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB21" s="5">
         <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>20.0</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AD21" s="1">
-        <v>5784.355</v>
+        <v>921.101</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:31" ht="54" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H22" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="I22" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="AD22" s="1">
-        <v>0.657</v>
+        <v>0.473</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="54" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>47</v>
@@ -5498,100 +4454,27 @@
         <v>168</v>
       </c>
       <c r="H23" t="s">
-        <v>203</v>
-      </c>
-      <c r="J23" s="2">
-        <f>IF(COUNT('Turns'!D58,'Turns'!D74)=2,SUM('Turns'!D58,'Turns'!D74),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="K23" s="2">
-        <f>IF(COUNT('Turns'!E58,'Turns'!E74)=2,SUM('Turns'!E58,'Turns'!E74),"Unknown")</f>
-        <v>1.05162e-06</v>
-      </c>
-      <c r="L23" s="2">
-        <f>IF(COUNT('Turns'!F58,'Turns'!F74)=2,SUM('Turns'!F58,'Turns'!F74),"Unknown")</f>
-        <v>1.2e-06</v>
-      </c>
-      <c r="M23" s="2">
-        <f>IF(COUNT('Turns'!D57,'Turns'!D73)=2,SUM('Turns'!D57,'Turns'!D73),"Unknown")</f>
-        <v>3552.0</v>
-      </c>
-      <c r="N23" s="2">
-        <f>IF(COUNT('Turns'!E57,'Turns'!E73)=2,SUM('Turns'!E57,'Turns'!E73),"Unknown")</f>
-        <v>6.2255904e-05</v>
-      </c>
-      <c r="O23" s="2">
-        <f>IF(COUNT('Turns'!F57,'Turns'!F73)=2,SUM('Turns'!F57,'Turns'!F73),"Unknown")</f>
-        <v>7.104e-05</v>
-      </c>
-      <c r="P23" s="2">
-        <f>IF(COUNT('Turns'!D60,'Turns'!D76)=2,SUM('Turns'!D60,'Turns'!D76),"Unknown")</f>
-        <v>487.0</v>
-      </c>
-      <c r="Q23" s="2">
-        <f>IF(COUNT('Turns'!E60,'Turns'!E76)=2,SUM('Turns'!E60,'Turns'!E76),"Unknown")</f>
-        <v>0.0001066956125</v>
-      </c>
-      <c r="R23" s="2">
-        <f>IF(COUNT('Turns'!F60,'Turns'!F76)=2,SUM('Turns'!F60,'Turns'!F76),"Unknown")</f>
-        <v>0.00012175</v>
-      </c>
-      <c r="S23" s="2">
-        <f>IF(COUNT('Turns'!D64,'Turns'!D80)=2,SUM('Turns'!D64,'Turns'!D80),"Unknown")</f>
-        <v>142.0</v>
-      </c>
-      <c r="T23" s="2">
-        <f>IF(COUNT('Turns'!E64,'Turns'!E80)=2,SUM('Turns'!E64,'Turns'!E80),"Unknown")</f>
-        <v>0.00014933004</v>
-      </c>
-      <c r="U23" s="2">
-        <f>IF(COUNT('Turns'!F64,'Turns'!F80)=2,SUM('Turns'!F64,'Turns'!F80),"Unknown")</f>
-        <v>0.0001704</v>
-      </c>
-      <c r="V23" s="2">
-        <f>IF(COUNT('Turns'!D63,'Turns'!D79)=2,SUM('Turns'!D63,'Turns'!D79),"Unknown")</f>
-        <v>474.0</v>
-      </c>
-      <c r="W23" s="2">
-        <f>IF(COUNT('Turns'!E63,'Turns'!E79)=2,SUM('Turns'!E63,'Turns'!E79),"Unknown")</f>
-        <v>0.00049846788</v>
-      </c>
-      <c r="X23" s="2">
-        <f>IF(COUNT('Turns'!F63,'Turns'!F79)=2,SUM('Turns'!F63,'Turns'!F79),"Unknown")</f>
-        <v>0.0005688</v>
-      </c>
-      <c r="Y23" s="2">
-        <f>IF(COUNT('Turns'!E68,'Turns'!E84)=2,SUM('Turns'!E68,'Turns'!E84),"Unknown")</f>
-        <v>0.0008178010565</v>
-      </c>
-      <c r="Z23" s="2">
-        <f>IF(COUNT('Turns'!F68,'Turns'!F84)=2,SUM('Turns'!F68,'Turns'!F84),"Unknown")</f>
-        <v>0.00093319</v>
-      </c>
-      <c r="AA23" s="5">
-        <f>IF(ISNUMBER(Y23),ROUND(Y23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>82.0</v>
-      </c>
-      <c r="AB23" s="5">
-        <f>IF(ISNUMBER(Z23),ROUND(Z23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>93.0</v>
+        <v>186</v>
+      </c>
+      <c r="I23" t="s">
+        <v>178</v>
       </c>
       <c r="AD23" s="1">
-        <v>8673.907999999999</v>
+        <v>5.703</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="54" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>47</v>
@@ -5600,30 +4483,30 @@
         <v>111</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="H24" t="s">
-        <v>204</v>
+        <v>134</v>
       </c>
       <c r="I24" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="AD24" s="1">
-        <v>0.573</v>
+        <v>1.72</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="54" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>47</v>
@@ -5632,30 +4515,30 @@
         <v>111</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="H25" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="I25" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="AD25" s="1">
-        <v>4.014</v>
+        <v>0.384</v>
       </c>
       <c r="AE25" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="54" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="B26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>47</v>
@@ -5664,284 +4547,357 @@
         <v>111</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="H26" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="I26" t="s">
-        <v>205</v>
+        <v>178</v>
+      </c>
+      <c r="J26" s="2">
+        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K26" s="2">
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>5.27844e-07</v>
+      </c>
+      <c r="L26" s="2">
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M26" s="2">
+        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
+        <v>1639.0</v>
+      </c>
+      <c r="N26" s="2">
+        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
+        <v>2.88378772e-05</v>
+      </c>
+      <c r="O26" s="2">
+        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
+        <v>3.278e-05</v>
+      </c>
+      <c r="P26" s="2">
+        <f>IF(COUNT('Turns'!D60)=1,SUM('Turns'!D60),"Unknown")</f>
+        <v>157.0</v>
+      </c>
+      <c r="Q26" s="2">
+        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
+        <v>3.4529795e-05</v>
+      </c>
+      <c r="R26" s="2">
+        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
+        <v>3.925e-05</v>
+      </c>
+      <c r="S26" s="2">
+        <f>IF(COUNT('Turns'!D64)=1,SUM('Turns'!D64),"Unknown")</f>
+        <v>281.0</v>
+      </c>
+      <c r="T26" s="2">
+        <f>IF(COUNT('Turns'!E64)=1,SUM('Turns'!E64),"Unknown")</f>
+        <v>0.000296648328</v>
+      </c>
+      <c r="U26" s="2">
+        <f>IF(COUNT('Turns'!F64)=1,SUM('Turns'!F64),"Unknown")</f>
+        <v>0.0003372</v>
+      </c>
+      <c r="V26" s="2">
+        <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
+        <v>27.0</v>
+      </c>
+      <c r="W26" s="2">
+        <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
+        <v>2.8503576e-05</v>
+      </c>
+      <c r="X26" s="2">
+        <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
+        <v>3.24e-05</v>
+      </c>
+      <c r="Y26" s="2">
+        <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
+        <v>0.0003890474202</v>
+      </c>
+      <c r="Z26" s="2">
+        <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
+        <v>0.00044223</v>
+      </c>
+      <c r="AA26" s="5">
+        <f>IF(ISNUMBER(Y26),ROUND(Y26*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>39.0</v>
+      </c>
+      <c r="AB26" s="5">
+        <f>IF(ISNUMBER(Z26),ROUND(Z26*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>44.0</v>
       </c>
       <c r="AD26" s="1">
-        <v>1.943</v>
+        <v>2348.284</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="54" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>111</v>
       </c>
+      <c r="F27" s="1">
+        <v>1799</v>
+      </c>
       <c r="G27" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H27" t="s">
-        <v>206</v>
+        <v>137</v>
       </c>
       <c r="I27" t="s">
-        <v>203</v>
+        <v>188</v>
+      </c>
+      <c r="J27" s="2">
+        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K27" s="2">
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>5.27844e-07</v>
+      </c>
+      <c r="L27" s="2">
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M27" s="2">
+        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
+        <v>1639.0</v>
+      </c>
+      <c r="N27" s="2">
+        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
+        <v>2.88378772e-05</v>
+      </c>
+      <c r="O27" s="2">
+        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
+        <v>3.278e-05</v>
+      </c>
+      <c r="P27" s="2">
+        <f>IF(COUNT('Turns'!D60)=1,SUM('Turns'!D60),"Unknown")</f>
+        <v>157.0</v>
+      </c>
+      <c r="Q27" s="2">
+        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
+        <v>3.4529795e-05</v>
+      </c>
+      <c r="R27" s="2">
+        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
+        <v>3.925e-05</v>
+      </c>
+      <c r="S27" s="2">
+        <f>IF(COUNT('Turns'!D64)=1,SUM('Turns'!D64),"Unknown")</f>
+        <v>281.0</v>
+      </c>
+      <c r="T27" s="2">
+        <f>IF(COUNT('Turns'!E64)=1,SUM('Turns'!E64),"Unknown")</f>
+        <v>0.000296648328</v>
+      </c>
+      <c r="U27" s="2">
+        <f>IF(COUNT('Turns'!F64)=1,SUM('Turns'!F64),"Unknown")</f>
+        <v>0.0003372</v>
+      </c>
+      <c r="V27" s="2">
+        <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
+        <v>27.0</v>
+      </c>
+      <c r="W27" s="2">
+        <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
+        <v>2.8503576e-05</v>
+      </c>
+      <c r="X27" s="2">
+        <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
+        <v>3.24e-05</v>
+      </c>
+      <c r="Y27" s="2">
+        <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
+        <v>0.0003890474202</v>
+      </c>
+      <c r="Z27" s="2">
+        <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
+        <v>0.00044223</v>
+      </c>
+      <c r="AA27" s="5">
+        <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>39.0</v>
+      </c>
+      <c r="AB27" s="5">
+        <f>IF(ISNUMBER(Z27),ROUND(Z27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>44.0</v>
+      </c>
+      <c r="AC27" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="AD27" s="1">
-        <v>0.407</v>
+        <v>2346.122</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="54" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B28" s="1">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H28" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I28" t="s">
-        <v>203</v>
-      </c>
-      <c r="J28" s="2">
-        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K28" s="2">
-        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L28" s="2">
-        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M28" s="2">
-        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>1603.0</v>
-      </c>
-      <c r="N28" s="2">
-        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>2.8095781e-05</v>
-      </c>
-      <c r="O28" s="2">
-        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>3.206e-05</v>
-      </c>
-      <c r="P28" s="2">
-        <f>IF(COUNT('Turns'!D60)=1,SUM('Turns'!D60),"Unknown")</f>
-        <v>346.0</v>
-      </c>
-      <c r="Q28" s="2">
-        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>7.5804275e-05</v>
-      </c>
-      <c r="R28" s="2">
-        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>8.65e-05</v>
-      </c>
-      <c r="S28" s="2">
-        <f>IF(COUNT('Turns'!D64)=1,SUM('Turns'!D64),"Unknown")</f>
-        <v>31.0</v>
-      </c>
-      <c r="T28" s="2">
-        <f>IF(COUNT('Turns'!E64)=1,SUM('Turns'!E64),"Unknown")</f>
-        <v>3.260022e-05</v>
-      </c>
-      <c r="U28" s="2">
-        <f>IF(COUNT('Turns'!F64)=1,SUM('Turns'!F64),"Unknown")</f>
-        <v>3.72e-05</v>
-      </c>
-      <c r="V28" s="2">
-        <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="W28" s="2">
-        <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
-        <v>7.36134e-06</v>
-      </c>
-      <c r="X28" s="2">
-        <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
-        <v>8.4e-06</v>
-      </c>
-      <c r="Y28" s="2">
-        <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
-        <v>0.000144387426</v>
-      </c>
-      <c r="Z28" s="2">
-        <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
-        <v>0.00016476</v>
-      </c>
-      <c r="AA28" s="5">
-        <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
-      </c>
-      <c r="AB28" s="5">
-        <f>IF(ISNUMBER(Z28),ROUND(Z28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>178</v>
       </c>
       <c r="AD28" s="1">
-        <v>1465.083</v>
+        <v>0.771</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="54" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="B29" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="1">
-        <v>1952</v>
-      </c>
       <c r="G29" s="6" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="H29" t="s">
-        <v>139</v>
-      </c>
-      <c r="I29" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="J29" s="2">
-        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D74,'Turns'!D90)=2,SUM('Turns'!D74,'Turns'!D90),"Unknown")</f>
+        <v>6.0</v>
       </c>
       <c r="K29" s="2">
-        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E74,'Turns'!E90)=2,SUM('Turns'!E74,'Turns'!E90),"Unknown")</f>
+        <v>1.055688e-06</v>
       </c>
       <c r="L29" s="2">
-        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F74,'Turns'!F90)=2,SUM('Turns'!F74,'Turns'!F90),"Unknown")</f>
+        <v>1.2e-06</v>
       </c>
       <c r="M29" s="2">
-        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>1603.0</v>
+        <f>IF(COUNT('Turns'!D73,'Turns'!D89)=2,SUM('Turns'!D73,'Turns'!D89),"Unknown")</f>
+        <v>3926.0</v>
       </c>
       <c r="N29" s="2">
-        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>2.8095781e-05</v>
+        <f>IF(COUNT('Turns'!E73,'Turns'!E89)=2,SUM('Turns'!E73,'Turns'!E89),"Unknown")</f>
+        <v>6.90771848e-05</v>
       </c>
       <c r="O29" s="2">
-        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>3.206e-05</v>
+        <f>IF(COUNT('Turns'!F73,'Turns'!F89)=2,SUM('Turns'!F73,'Turns'!F89),"Unknown")</f>
+        <v>7.852e-05</v>
       </c>
       <c r="P29" s="2">
-        <f>IF(COUNT('Turns'!D60)=1,SUM('Turns'!D60),"Unknown")</f>
-        <v>346.0</v>
+        <f>IF(COUNT('Turns'!D76,'Turns'!D92)=2,SUM('Turns'!D76,'Turns'!D92),"Unknown")</f>
+        <v>509.0</v>
       </c>
       <c r="Q29" s="2">
-        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>7.5804275e-05</v>
+        <f>IF(COUNT('Turns'!E76,'Turns'!E92)=2,SUM('Turns'!E76,'Turns'!E92),"Unknown")</f>
+        <v>0.000111946915</v>
       </c>
       <c r="R29" s="2">
-        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>8.65e-05</v>
+        <f>IF(COUNT('Turns'!F76,'Turns'!F92)=2,SUM('Turns'!F76,'Turns'!F92),"Unknown")</f>
+        <v>0.00012725</v>
       </c>
       <c r="S29" s="2">
-        <f>IF(COUNT('Turns'!D64)=1,SUM('Turns'!D64),"Unknown")</f>
-        <v>31.0</v>
+        <f>IF(COUNT('Turns'!D80,'Turns'!D95)=2,SUM('Turns'!D80,'Turns'!D95),"Unknown")</f>
+        <v>64.0</v>
       </c>
       <c r="T29" s="2">
-        <f>IF(COUNT('Turns'!E64)=1,SUM('Turns'!E64),"Unknown")</f>
-        <v>3.260022e-05</v>
+        <f>IF(COUNT('Turns'!E80,'Turns'!E95)=2,SUM('Turns'!E80,'Turns'!E95),"Unknown")</f>
+        <v>6.7564032e-05</v>
       </c>
       <c r="U29" s="2">
-        <f>IF(COUNT('Turns'!F64)=1,SUM('Turns'!F64),"Unknown")</f>
-        <v>3.72e-05</v>
+        <f>IF(COUNT('Turns'!F80,'Turns'!F95)=2,SUM('Turns'!F80,'Turns'!F95),"Unknown")</f>
+        <v>7.68e-05</v>
       </c>
       <c r="V29" s="2">
-        <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
-        <v>7.0</v>
+        <f>IF(COUNT('Turns'!D79)=1,SUM('Turns'!D79),"Unknown")</f>
+        <v>21.0</v>
       </c>
       <c r="W29" s="2">
-        <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
-        <v>7.36134e-06</v>
+        <f>IF(COUNT('Turns'!E79)=1,SUM('Turns'!E79),"Unknown")</f>
+        <v>2.2169448e-05</v>
       </c>
       <c r="X29" s="2">
-        <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
-        <v>8.4e-06</v>
+        <f>IF(COUNT('Turns'!F79)=1,SUM('Turns'!F79),"Unknown")</f>
+        <v>2.52e-05</v>
       </c>
       <c r="Y29" s="2">
-        <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
-        <v>0.000144387426</v>
+        <f>IF(COUNT('Turns'!E84,'Turns'!E99)=2,SUM('Turns'!E84,'Turns'!E99),"Unknown")</f>
+        <v>0.0002718132678</v>
       </c>
       <c r="Z29" s="2">
-        <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
-        <v>0.00016476</v>
+        <f>IF(COUNT('Turns'!F84,'Turns'!F99)=2,SUM('Turns'!F84,'Turns'!F99),"Unknown")</f>
+        <v>0.00030897</v>
       </c>
       <c r="AA29" s="5">
         <f>IF(ISNUMBER(Y29),ROUND(Y29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>27.0</v>
       </c>
       <c r="AB29" s="5">
         <f>IF(ISNUMBER(Z29),ROUND(Z29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
-      </c>
-      <c r="AC29" s="1" t="s">
-        <v>138</v>
+        <v>31.0</v>
       </c>
       <c r="AD29" s="1">
-        <v>1463.083</v>
+        <v>2128.032</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="54" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>47</v>
@@ -5950,30 +4906,30 @@
         <v>111</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H30" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="I30" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="AD30" s="1">
-        <v>0.466</v>
+        <v>0.622</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="54" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="B31" s="1">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>47</v>
@@ -5982,30 +4938,30 @@
         <v>111</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="H31" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="I31" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="AD31" s="1">
-        <v>3.977</v>
+        <v>4.072</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="54" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B32" s="1">
         <v>2</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>47</v>
@@ -6014,30 +4970,30 @@
         <v>111</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H32" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I32" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="AD32" s="1">
-        <v>0.897</v>
+        <v>1.336</v>
       </c>
       <c r="AE32" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="54" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="B33" s="1">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>47</v>
@@ -6046,30 +5002,30 @@
         <v>111</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="H33" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="I33" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="AD33" s="1">
-        <v>0.584</v>
+        <v>0.368</v>
       </c>
       <c r="AE33" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="54" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B34" s="1">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>47</v>
@@ -6078,13 +5034,13 @@
         <v>111</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="H34" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I34" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="J34" s="2">
         <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
@@ -6092,7 +5048,7 @@
       </c>
       <c r="K34" s="2">
         <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L34" s="2">
         <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
@@ -6100,84 +5056,84 @@
       </c>
       <c r="M34" s="2">
         <f>IF(COUNT('Turns'!D73)=1,SUM('Turns'!D73),"Unknown")</f>
-        <v>1949.0</v>
+        <v>1796.0</v>
       </c>
       <c r="N34" s="2">
         <f>IF(COUNT('Turns'!E73)=1,SUM('Turns'!E73),"Unknown")</f>
-        <v>3.4160123e-05</v>
+        <v>3.16002608e-05</v>
       </c>
       <c r="O34" s="2">
         <f>IF(COUNT('Turns'!F73)=1,SUM('Turns'!F73),"Unknown")</f>
-        <v>3.898e-05</v>
+        <v>3.592e-05</v>
       </c>
       <c r="P34" s="2">
         <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
-        <v>141.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q34" s="2">
         <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
-        <v>3.08913375e-05</v>
+        <v>7.345829e-05</v>
       </c>
       <c r="R34" s="2">
         <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
-        <v>3.525e-05</v>
+        <v>8.35e-05</v>
       </c>
       <c r="S34" s="2">
         <f>IF(COUNT('Turns'!D80)=1,SUM('Turns'!D80),"Unknown")</f>
-        <v>111.0</v>
+        <v>31.0</v>
       </c>
       <c r="T34" s="2">
         <f>IF(COUNT('Turns'!E80)=1,SUM('Turns'!E80),"Unknown")</f>
-        <v>0.00011672982</v>
+        <v>3.2726328e-05</v>
       </c>
       <c r="U34" s="2">
         <f>IF(COUNT('Turns'!F80)=1,SUM('Turns'!F80),"Unknown")</f>
-        <v>0.0001332</v>
+        <v>3.72e-05</v>
       </c>
       <c r="V34" s="2">
         <f>IF(COUNT('Turns'!D79)=1,SUM('Turns'!D79),"Unknown")</f>
-        <v>467.0</v>
+        <v>21.0</v>
       </c>
       <c r="W34" s="2">
         <f>IF(COUNT('Turns'!E79)=1,SUM('Turns'!E79),"Unknown")</f>
-        <v>0.00049110654</v>
+        <v>2.2169448e-05</v>
       </c>
       <c r="X34" s="2">
         <f>IF(COUNT('Turns'!F79)=1,SUM('Turns'!F79),"Unknown")</f>
-        <v>0.0005604</v>
+        <v>2.52e-05</v>
       </c>
       <c r="Y34" s="2">
         <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>0.0006734136305</v>
+        <v>0.0001604821708</v>
       </c>
       <c r="Z34" s="2">
         <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>0.00076843</v>
+        <v>0.00018242</v>
       </c>
       <c r="AA34" s="5">
         <f>IF(ISNUMBER(Y34),ROUND(Y34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>67.0</v>
+        <v>16.0</v>
       </c>
       <c r="AB34" s="5">
         <f>IF(ISNUMBER(Z34),ROUND(Z34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>77.0</v>
+        <v>18.0</v>
       </c>
       <c r="AD34" s="1">
-        <v>7186.948</v>
+        <v>1085.905</v>
       </c>
       <c r="AE34" s="1" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="54" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B35" s="1">
         <v>2</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>95</v>
@@ -6186,16 +5142,16 @@
         <v>111</v>
       </c>
       <c r="F35" s="1">
-        <v>2093</v>
+        <v>2133</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="H35" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I35" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="J35" s="2">
         <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
@@ -6203,7 +5159,7 @@
       </c>
       <c r="K35" s="2">
         <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L35" s="2">
         <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
@@ -6211,119 +5167,119 @@
       </c>
       <c r="M35" s="2">
         <f>IF(COUNT('Turns'!D73)=1,SUM('Turns'!D73),"Unknown")</f>
-        <v>1949.0</v>
+        <v>1796.0</v>
       </c>
       <c r="N35" s="2">
         <f>IF(COUNT('Turns'!E73)=1,SUM('Turns'!E73),"Unknown")</f>
-        <v>3.4160123e-05</v>
+        <v>3.16002608e-05</v>
       </c>
       <c r="O35" s="2">
         <f>IF(COUNT('Turns'!F73)=1,SUM('Turns'!F73),"Unknown")</f>
-        <v>3.898e-05</v>
+        <v>3.592e-05</v>
       </c>
       <c r="P35" s="2">
         <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
-        <v>141.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q35" s="2">
         <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
-        <v>3.08913375e-05</v>
+        <v>7.345829e-05</v>
       </c>
       <c r="R35" s="2">
         <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
-        <v>3.525e-05</v>
+        <v>8.35e-05</v>
       </c>
       <c r="S35" s="2">
         <f>IF(COUNT('Turns'!D80)=1,SUM('Turns'!D80),"Unknown")</f>
-        <v>111.0</v>
+        <v>31.0</v>
       </c>
       <c r="T35" s="2">
         <f>IF(COUNT('Turns'!E80)=1,SUM('Turns'!E80),"Unknown")</f>
-        <v>0.00011672982</v>
+        <v>3.2726328e-05</v>
       </c>
       <c r="U35" s="2">
         <f>IF(COUNT('Turns'!F80)=1,SUM('Turns'!F80),"Unknown")</f>
-        <v>0.0001332</v>
+        <v>3.72e-05</v>
       </c>
       <c r="V35" s="2">
         <f>IF(COUNT('Turns'!D79)=1,SUM('Turns'!D79),"Unknown")</f>
-        <v>467.0</v>
+        <v>21.0</v>
       </c>
       <c r="W35" s="2">
         <f>IF(COUNT('Turns'!E79)=1,SUM('Turns'!E79),"Unknown")</f>
-        <v>0.00049110654</v>
+        <v>2.2169448e-05</v>
       </c>
       <c r="X35" s="2">
         <f>IF(COUNT('Turns'!F79)=1,SUM('Turns'!F79),"Unknown")</f>
-        <v>0.0005604</v>
+        <v>2.52e-05</v>
       </c>
       <c r="Y35" s="2">
         <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>0.0006734136305</v>
+        <v>0.0001604821708</v>
       </c>
       <c r="Z35" s="2">
         <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>0.00076843</v>
+        <v>0.00018242</v>
       </c>
       <c r="AA35" s="5">
         <f>IF(ISNUMBER(Y35),ROUND(Y35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>67.0</v>
+        <v>16.0</v>
       </c>
       <c r="AB35" s="5">
         <f>IF(ISNUMBER(Z35),ROUND(Z35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>77.0</v>
+        <v>18.0</v>
       </c>
       <c r="AC35" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AD35" s="1">
-        <v>7183.92</v>
+        <v>1082.65</v>
       </c>
       <c r="AE35" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="54" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H36" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="I36" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="AD36" s="1">
-        <v>0.665</v>
+        <v>1.147</v>
       </c>
       <c r="AE36" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="54" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>47</v>
@@ -6335,100 +5291,27 @@
         <v>168</v>
       </c>
       <c r="H37" t="s">
-        <v>213</v>
-      </c>
-      <c r="J37" s="2">
-        <f>IF(COUNT('Turns'!D90,'Turns'!D106)=2,SUM('Turns'!D90,'Turns'!D106),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="K37" s="2">
-        <f>IF(COUNT('Turns'!E90,'Turns'!E106)=2,SUM('Turns'!E90,'Turns'!E106),"Unknown")</f>
-        <v>1.05162e-06</v>
-      </c>
-      <c r="L37" s="2">
-        <f>IF(COUNT('Turns'!F90,'Turns'!F106)=2,SUM('Turns'!F90,'Turns'!F106),"Unknown")</f>
-        <v>1.2e-06</v>
-      </c>
-      <c r="M37" s="2">
-        <f>IF(COUNT('Turns'!D89,'Turns'!D105)=2,SUM('Turns'!D89,'Turns'!D105),"Unknown")</f>
-        <v>4784.0</v>
-      </c>
-      <c r="N37" s="2">
-        <f>IF(COUNT('Turns'!E89,'Turns'!E105)=2,SUM('Turns'!E89,'Turns'!E105),"Unknown")</f>
-        <v>8.3849168e-05</v>
-      </c>
-      <c r="O37" s="2">
-        <f>IF(COUNT('Turns'!F89,'Turns'!F105)=2,SUM('Turns'!F89,'Turns'!F105),"Unknown")</f>
-        <v>9.568e-05</v>
-      </c>
-      <c r="P37" s="2">
-        <f>IF(COUNT('Turns'!D92,'Turns'!D108)=2,SUM('Turns'!D92,'Turns'!D108),"Unknown")</f>
-        <v>752.0</v>
-      </c>
-      <c r="Q37" s="2">
-        <f>IF(COUNT('Turns'!E92,'Turns'!E108)=2,SUM('Turns'!E92,'Turns'!E108),"Unknown")</f>
-        <v>0.0001647538</v>
-      </c>
-      <c r="R37" s="2">
-        <f>IF(COUNT('Turns'!F92,'Turns'!F108)=2,SUM('Turns'!F92,'Turns'!F108),"Unknown")</f>
-        <v>0.000188</v>
-      </c>
-      <c r="S37" s="2">
-        <f>IF(COUNT('Turns'!D96,'Turns'!D112)=2,SUM('Turns'!D96,'Turns'!D112),"Unknown")</f>
-        <v>133.0</v>
-      </c>
-      <c r="T37" s="2">
-        <f>IF(COUNT('Turns'!E96,'Turns'!E112)=2,SUM('Turns'!E96,'Turns'!E112),"Unknown")</f>
-        <v>0.00013986546</v>
-      </c>
-      <c r="U37" s="2">
-        <f>IF(COUNT('Turns'!F96,'Turns'!F112)=2,SUM('Turns'!F96,'Turns'!F112),"Unknown")</f>
-        <v>0.0001596</v>
-      </c>
-      <c r="V37" s="2">
-        <f>IF(COUNT('Turns'!D95,'Turns'!D111)=2,SUM('Turns'!D95,'Turns'!D111),"Unknown")</f>
-        <v>857.0</v>
-      </c>
-      <c r="W37" s="2">
-        <f>IF(COUNT('Turns'!E95,'Turns'!E111)=2,SUM('Turns'!E95,'Turns'!E111),"Unknown")</f>
-        <v>0.00090123834</v>
-      </c>
-      <c r="X37" s="2">
-        <f>IF(COUNT('Turns'!F95,'Turns'!F111)=2,SUM('Turns'!F95,'Turns'!F111),"Unknown")</f>
-        <v>0.0010284</v>
-      </c>
-      <c r="Y37" s="2">
-        <f>IF(COUNT('Turns'!E100,'Turns'!E116)=2,SUM('Turns'!E100,'Turns'!E116),"Unknown")</f>
-        <v>0.001290758388</v>
-      </c>
-      <c r="Z37" s="2">
-        <f>IF(COUNT('Turns'!F100,'Turns'!F116)=2,SUM('Turns'!F100,'Turns'!F116),"Unknown")</f>
-        <v>0.00147288</v>
-      </c>
-      <c r="AA37" s="5">
-        <f>IF(ISNUMBER(Y37),ROUND(Y37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>129.0</v>
-      </c>
-      <c r="AB37" s="5">
-        <f>IF(ISNUMBER(Z37),ROUND(Z37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>147.0</v>
+        <v>196</v>
+      </c>
+      <c r="I37" t="s">
+        <v>190</v>
       </c>
       <c r="AD37" s="1">
-        <v>15275.325</v>
+        <v>4.047</v>
       </c>
       <c r="AE37" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="54" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B38" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>47</v>
@@ -6437,30 +5320,30 @@
         <v>111</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="H38" t="s">
-        <v>214</v>
+        <v>144</v>
       </c>
       <c r="I38" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="AD38" s="1">
-        <v>0.546</v>
+        <v>0.999</v>
       </c>
       <c r="AE38" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="54" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="B39" s="1">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>47</v>
@@ -6469,30 +5352,30 @@
         <v>111</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="H39" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="I39" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="AD39" s="1">
-        <v>3.347</v>
+        <v>1.008</v>
       </c>
       <c r="AE39" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:31" ht="54" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="B40" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>47</v>
@@ -6501,62 +5384,214 @@
         <v>111</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="H40" t="s">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="I40" t="s">
-        <v>215</v>
+        <v>190</v>
+      </c>
+      <c r="J40" s="2">
+        <f>IF(COUNT('Turns'!D90)=1,SUM('Turns'!D90),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K40" s="2">
+        <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
+        <v>5.27844e-07</v>
+      </c>
+      <c r="L40" s="2">
+        <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M40" s="2">
+        <f>IF(COUNT('Turns'!D89)=1,SUM('Turns'!D89),"Unknown")</f>
+        <v>2130.0</v>
+      </c>
+      <c r="N40" s="2">
+        <f>IF(COUNT('Turns'!E89)=1,SUM('Turns'!E89),"Unknown")</f>
+        <v>3.7476924e-05</v>
+      </c>
+      <c r="O40" s="2">
+        <f>IF(COUNT('Turns'!F89)=1,SUM('Turns'!F89),"Unknown")</f>
+        <v>4.26e-05</v>
+      </c>
+      <c r="P40" s="2">
+        <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
+        <v>175.0</v>
+      </c>
+      <c r="Q40" s="2">
+        <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
+        <v>3.8488625e-05</v>
+      </c>
+      <c r="R40" s="2">
+        <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
+        <v>4.375e-05</v>
+      </c>
+      <c r="S40" s="2">
+        <f>IF(COUNT('Turns'!D95)=1,SUM('Turns'!D95),"Unknown")</f>
+        <v>33.0</v>
+      </c>
+      <c r="T40" s="2">
+        <f>IF(COUNT('Turns'!E95)=1,SUM('Turns'!E95),"Unknown")</f>
+        <v>3.4837704e-05</v>
+      </c>
+      <c r="U40" s="2">
+        <f>IF(COUNT('Turns'!F95)=1,SUM('Turns'!F95),"Unknown")</f>
+        <v>3.96e-05</v>
+      </c>
+      <c r="V40" s="2">
+        <v>0</v>
+      </c>
+      <c r="W40" s="2">
+        <v>0</v>
+      </c>
+      <c r="X40" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="2">
+        <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
+        <v>0.000111331097</v>
+      </c>
+      <c r="Z40" s="2">
+        <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
+        <v>0.00012655</v>
+      </c>
+      <c r="AA40" s="5">
+        <f>IF(ISNUMBER(Y40),ROUND(Y40*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+      <c r="AB40" s="5">
+        <f>IF(ISNUMBER(Z40),ROUND(Z40*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
       </c>
       <c r="AD40" s="1">
-        <v>1.144</v>
+        <v>1018.443</v>
       </c>
       <c r="AE40" s="1" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:31" ht="54" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B41" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>111</v>
       </c>
+      <c r="F41" s="1">
+        <v>2308</v>
+      </c>
       <c r="G41" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H41" t="s">
-        <v>216</v>
+        <v>147</v>
       </c>
       <c r="I41" t="s">
-        <v>213</v>
+        <v>198</v>
+      </c>
+      <c r="J41" s="2">
+        <f>IF(COUNT('Turns'!D90)=1,SUM('Turns'!D90),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K41" s="2">
+        <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
+        <v>5.27844e-07</v>
+      </c>
+      <c r="L41" s="2">
+        <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M41" s="2">
+        <f>IF(COUNT('Turns'!D89)=1,SUM('Turns'!D89),"Unknown")</f>
+        <v>2130.0</v>
+      </c>
+      <c r="N41" s="2">
+        <f>IF(COUNT('Turns'!E89)=1,SUM('Turns'!E89),"Unknown")</f>
+        <v>3.7476924e-05</v>
+      </c>
+      <c r="O41" s="2">
+        <f>IF(COUNT('Turns'!F89)=1,SUM('Turns'!F89),"Unknown")</f>
+        <v>4.26e-05</v>
+      </c>
+      <c r="P41" s="2">
+        <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
+        <v>175.0</v>
+      </c>
+      <c r="Q41" s="2">
+        <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
+        <v>3.8488625e-05</v>
+      </c>
+      <c r="R41" s="2">
+        <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
+        <v>4.375e-05</v>
+      </c>
+      <c r="S41" s="2">
+        <f>IF(COUNT('Turns'!D95)=1,SUM('Turns'!D95),"Unknown")</f>
+        <v>33.0</v>
+      </c>
+      <c r="T41" s="2">
+        <f>IF(COUNT('Turns'!E95)=1,SUM('Turns'!E95),"Unknown")</f>
+        <v>3.4837704e-05</v>
+      </c>
+      <c r="U41" s="2">
+        <f>IF(COUNT('Turns'!F95)=1,SUM('Turns'!F95),"Unknown")</f>
+        <v>3.96e-05</v>
+      </c>
+      <c r="V41" s="2">
+        <v>0</v>
+      </c>
+      <c r="W41" s="2">
+        <v>0</v>
+      </c>
+      <c r="X41" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="2">
+        <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
+        <v>0.000111331097</v>
+      </c>
+      <c r="Z41" s="2">
+        <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
+        <v>0.00012655</v>
+      </c>
+      <c r="AA41" s="5">
+        <f>IF(ISNUMBER(Y41),ROUND(Y41*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+      <c r="AB41" s="5">
+        <f>IF(ISNUMBER(Z41),ROUND(Z41*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+      <c r="AC41" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="AD41" s="1">
-        <v>0.346</v>
+        <v>1015.827</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:31" ht="54" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>47</v>
@@ -6565,1426 +5600,23 @@
         <v>111</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H42" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="I42" t="s">
-        <v>213</v>
-      </c>
-      <c r="J42" s="2">
-        <f>IF(COUNT('Turns'!D90)=1,SUM('Turns'!D90),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K42" s="2">
-        <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L42" s="2">
-        <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M42" s="2">
-        <f>IF(COUNT('Turns'!D89)=1,SUM('Turns'!D89),"Unknown")</f>
-        <v>2090.0</v>
-      </c>
-      <c r="N42" s="2">
-        <f>IF(COUNT('Turns'!E89)=1,SUM('Turns'!E89),"Unknown")</f>
-        <v>3.663143e-05</v>
-      </c>
-      <c r="O42" s="2">
-        <f>IF(COUNT('Turns'!F89)=1,SUM('Turns'!F89),"Unknown")</f>
-        <v>4.18e-05</v>
-      </c>
-      <c r="P42" s="2">
-        <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
-        <v>604.0</v>
-      </c>
-      <c r="Q42" s="2">
-        <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
-        <v>0.00013232885</v>
-      </c>
-      <c r="R42" s="2">
-        <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
-        <v>0.000151</v>
-      </c>
-      <c r="S42" s="2">
-        <f>IF(COUNT('Turns'!D96)=1,SUM('Turns'!D96),"Unknown")</f>
-        <v>31.0</v>
-      </c>
-      <c r="T42" s="2">
-        <f>IF(COUNT('Turns'!E96)=1,SUM('Turns'!E96),"Unknown")</f>
-        <v>3.260022e-05</v>
-      </c>
-      <c r="U42" s="2">
-        <f>IF(COUNT('Turns'!F96)=1,SUM('Turns'!F96),"Unknown")</f>
-        <v>3.72e-05</v>
-      </c>
-      <c r="V42" s="2">
-        <f>IF(COUNT('Turns'!D95)=1,SUM('Turns'!D95),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="W42" s="2">
-        <f>IF(COUNT('Turns'!E95)=1,SUM('Turns'!E95),"Unknown")</f>
-        <v>7.36134e-06</v>
-      </c>
-      <c r="X42" s="2">
-        <f>IF(COUNT('Turns'!F95)=1,SUM('Turns'!F95),"Unknown")</f>
-        <v>8.4e-06</v>
-      </c>
-      <c r="Y42" s="2">
-        <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
-        <v>0.00020944765</v>
-      </c>
-      <c r="Z42" s="2">
-        <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
-        <v>0.000239</v>
-      </c>
-      <c r="AA42" s="5">
-        <f>IF(ISNUMBER(Y42),ROUND(Y42*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="AB42" s="5">
-        <f>IF(ISNUMBER(Z42),ROUND(Z42*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
+        <v>190</v>
       </c>
       <c r="AD42" s="1">
-        <v>1686.641</v>
+        <v>0.34</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31" ht="54" customHeight="1">
-      <c r="A43" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B43" s="1">
-        <v>2</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F43" s="1">
-        <v>2697</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="H43" t="s">
-        <v>149</v>
-      </c>
-      <c r="I43" t="s">
-        <v>217</v>
-      </c>
-      <c r="J43" s="2">
-        <f>IF(COUNT('Turns'!D90)=1,SUM('Turns'!D90),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K43" s="2">
-        <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L43" s="2">
-        <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M43" s="2">
-        <f>IF(COUNT('Turns'!D89)=1,SUM('Turns'!D89),"Unknown")</f>
-        <v>2090.0</v>
-      </c>
-      <c r="N43" s="2">
-        <f>IF(COUNT('Turns'!E89)=1,SUM('Turns'!E89),"Unknown")</f>
-        <v>3.663143e-05</v>
-      </c>
-      <c r="O43" s="2">
-        <f>IF(COUNT('Turns'!F89)=1,SUM('Turns'!F89),"Unknown")</f>
-        <v>4.18e-05</v>
-      </c>
-      <c r="P43" s="2">
-        <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
-        <v>604.0</v>
-      </c>
-      <c r="Q43" s="2">
-        <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
-        <v>0.00013232885</v>
-      </c>
-      <c r="R43" s="2">
-        <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
-        <v>0.000151</v>
-      </c>
-      <c r="S43" s="2">
-        <f>IF(COUNT('Turns'!D96)=1,SUM('Turns'!D96),"Unknown")</f>
-        <v>31.0</v>
-      </c>
-      <c r="T43" s="2">
-        <f>IF(COUNT('Turns'!E96)=1,SUM('Turns'!E96),"Unknown")</f>
-        <v>3.260022e-05</v>
-      </c>
-      <c r="U43" s="2">
-        <f>IF(COUNT('Turns'!F96)=1,SUM('Turns'!F96),"Unknown")</f>
-        <v>3.72e-05</v>
-      </c>
-      <c r="V43" s="2">
-        <f>IF(COUNT('Turns'!D95)=1,SUM('Turns'!D95),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="W43" s="2">
-        <f>IF(COUNT('Turns'!E95)=1,SUM('Turns'!E95),"Unknown")</f>
-        <v>7.36134e-06</v>
-      </c>
-      <c r="X43" s="2">
-        <f>IF(COUNT('Turns'!F95)=1,SUM('Turns'!F95),"Unknown")</f>
-        <v>8.4e-06</v>
-      </c>
-      <c r="Y43" s="2">
-        <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
-        <v>0.00020944765</v>
-      </c>
-      <c r="Z43" s="2">
-        <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
-        <v>0.000239</v>
-      </c>
-      <c r="AA43" s="5">
-        <f>IF(ISNUMBER(Y43),ROUND(Y43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="AB43" s="5">
-        <f>IF(ISNUMBER(Z43),ROUND(Z43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
-      </c>
-      <c r="AC43" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AD43" s="1">
-        <v>1685.019</v>
-      </c>
-      <c r="AE43" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31" ht="54" customHeight="1">
-      <c r="A44" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B44" s="1">
-        <v>1</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H44" t="s">
-        <v>218</v>
-      </c>
-      <c r="I44" t="s">
-        <v>213</v>
-      </c>
-      <c r="AD44" s="1">
-        <v>0.369</v>
-      </c>
-      <c r="AE44" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31" ht="54" customHeight="1">
-      <c r="A45" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B45" s="1">
-        <v>1</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H45" t="s">
-        <v>219</v>
-      </c>
-      <c r="I45" t="s">
-        <v>213</v>
-      </c>
-      <c r="AD45" s="1">
-        <v>3.645</v>
-      </c>
-      <c r="AE45" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="46" spans="1:31" ht="54" customHeight="1">
-      <c r="A46" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B46" s="1">
-        <v>2</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="H46" t="s">
-        <v>151</v>
-      </c>
-      <c r="I46" t="s">
-        <v>219</v>
-      </c>
-      <c r="AD46" s="1">
-        <v>0.671</v>
-      </c>
-      <c r="AE46" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="47" spans="1:31" ht="54" customHeight="1">
-      <c r="A47" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B47" s="1">
-        <v>1</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H47" t="s">
-        <v>220</v>
-      </c>
-      <c r="I47" t="s">
-        <v>213</v>
-      </c>
-      <c r="AD47" s="1">
-        <v>0.272</v>
-      </c>
-      <c r="AE47" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="48" spans="1:31" ht="54" customHeight="1">
-      <c r="A48" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B48" s="1">
-        <v>1</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="H48" t="s">
-        <v>221</v>
-      </c>
-      <c r="I48" t="s">
-        <v>213</v>
-      </c>
-      <c r="J48" s="2">
-        <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K48" s="2">
-        <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L48" s="2">
-        <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M48" s="2">
-        <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
-        <v>2694.0</v>
-      </c>
-      <c r="N48" s="2">
-        <f>IF(COUNT('Turns'!E105)=1,SUM('Turns'!E105),"Unknown")</f>
-        <v>4.7217738e-05</v>
-      </c>
-      <c r="O48" s="2">
-        <f>IF(COUNT('Turns'!F105)=1,SUM('Turns'!F105),"Unknown")</f>
-        <v>5.388e-05</v>
-      </c>
-      <c r="P48" s="2">
-        <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>148.0</v>
-      </c>
-      <c r="Q48" s="2">
-        <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>3.242495e-05</v>
-      </c>
-      <c r="R48" s="2">
-        <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>3.7e-05</v>
-      </c>
-      <c r="S48" s="2">
-        <f>IF(COUNT('Turns'!D112)=1,SUM('Turns'!D112),"Unknown")</f>
-        <v>102.0</v>
-      </c>
-      <c r="T48" s="2">
-        <f>IF(COUNT('Turns'!E112)=1,SUM('Turns'!E112),"Unknown")</f>
-        <v>0.00010726524</v>
-      </c>
-      <c r="U48" s="2">
-        <f>IF(COUNT('Turns'!F112)=1,SUM('Turns'!F112),"Unknown")</f>
-        <v>0.0001224</v>
-      </c>
-      <c r="V48" s="2">
-        <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
-        <v>850.0</v>
-      </c>
-      <c r="W48" s="2">
-        <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
-        <v>0.000893877</v>
-      </c>
-      <c r="X48" s="2">
-        <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
-        <v>0.00102</v>
-      </c>
-      <c r="Y48" s="2">
-        <f>IF(COUNT('Turns'!E116)=1,SUM('Turns'!E116),"Unknown")</f>
-        <v>0.001081310738</v>
-      </c>
-      <c r="Z48" s="2">
-        <f>IF(COUNT('Turns'!F116)=1,SUM('Turns'!F116),"Unknown")</f>
-        <v>0.00123388</v>
-      </c>
-      <c r="AA48" s="5">
-        <f>IF(ISNUMBER(Y48),ROUND(Y48*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>108.0</v>
-      </c>
-      <c r="AB48" s="5">
-        <f>IF(ISNUMBER(Z48),ROUND(Z48*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>123.0</v>
-      </c>
-      <c r="AD48" s="1">
-        <v>13570.259</v>
-      </c>
-      <c r="AE48" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="49" spans="1:31" ht="54" customHeight="1">
-      <c r="A49" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B49" s="1">
-        <v>2</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F49" s="1">
-        <v>2845</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="H49" t="s">
-        <v>154</v>
-      </c>
-      <c r="I49" t="s">
-        <v>221</v>
-      </c>
-      <c r="J49" s="2">
-        <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K49" s="2">
-        <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L49" s="2">
-        <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M49" s="2">
-        <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
-        <v>2694.0</v>
-      </c>
-      <c r="N49" s="2">
-        <f>IF(COUNT('Turns'!E105)=1,SUM('Turns'!E105),"Unknown")</f>
-        <v>4.7217738e-05</v>
-      </c>
-      <c r="O49" s="2">
-        <f>IF(COUNT('Turns'!F105)=1,SUM('Turns'!F105),"Unknown")</f>
-        <v>5.388e-05</v>
-      </c>
-      <c r="P49" s="2">
-        <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>148.0</v>
-      </c>
-      <c r="Q49" s="2">
-        <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>3.242495e-05</v>
-      </c>
-      <c r="R49" s="2">
-        <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>3.7e-05</v>
-      </c>
-      <c r="S49" s="2">
-        <f>IF(COUNT('Turns'!D112)=1,SUM('Turns'!D112),"Unknown")</f>
-        <v>102.0</v>
-      </c>
-      <c r="T49" s="2">
-        <f>IF(COUNT('Turns'!E112)=1,SUM('Turns'!E112),"Unknown")</f>
-        <v>0.00010726524</v>
-      </c>
-      <c r="U49" s="2">
-        <f>IF(COUNT('Turns'!F112)=1,SUM('Turns'!F112),"Unknown")</f>
-        <v>0.0001224</v>
-      </c>
-      <c r="V49" s="2">
-        <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
-        <v>850.0</v>
-      </c>
-      <c r="W49" s="2">
-        <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
-        <v>0.000893877</v>
-      </c>
-      <c r="X49" s="2">
-        <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
-        <v>0.00102</v>
-      </c>
-      <c r="Y49" s="2">
-        <f>IF(COUNT('Turns'!E116)=1,SUM('Turns'!E116),"Unknown")</f>
-        <v>0.001081310738</v>
-      </c>
-      <c r="Z49" s="2">
-        <f>IF(COUNT('Turns'!F116)=1,SUM('Turns'!F116),"Unknown")</f>
-        <v>0.00123388</v>
-      </c>
-      <c r="AA49" s="5">
-        <f>IF(ISNUMBER(Y49),ROUND(Y49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>108.0</v>
-      </c>
-      <c r="AB49" s="5">
-        <f>IF(ISNUMBER(Z49),ROUND(Z49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>123.0</v>
-      </c>
-      <c r="AC49" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AD49" s="1">
-        <v>13566.758</v>
-      </c>
-      <c r="AE49" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31" ht="54" customHeight="1">
-      <c r="A50" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B50" s="1">
-        <v>1</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H50" t="s">
-        <v>222</v>
-      </c>
-      <c r="I50" t="s">
-        <v>213</v>
-      </c>
-      <c r="AD50" s="1">
-        <v>0.639</v>
-      </c>
-      <c r="AE50" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="51" spans="1:31" ht="54" customHeight="1">
-      <c r="A51" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B51" s="1">
-        <v>0</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="H51" t="s">
-        <v>223</v>
-      </c>
-      <c r="J51" s="2">
-        <f>IF(COUNT('Turns'!D122,'Turns'!D138)=2,SUM('Turns'!D122,'Turns'!D138),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="K51" s="2">
-        <f>IF(COUNT('Turns'!E122,'Turns'!E138)=2,SUM('Turns'!E122,'Turns'!E138),"Unknown")</f>
-        <v>1.05162e-06</v>
-      </c>
-      <c r="L51" s="2">
-        <f>IF(COUNT('Turns'!F122,'Turns'!F138)=2,SUM('Turns'!F122,'Turns'!F138),"Unknown")</f>
-        <v>1.2e-06</v>
-      </c>
-      <c r="M51" s="2">
-        <f>IF(COUNT('Turns'!D121,'Turns'!D137)=2,SUM('Turns'!D121,'Turns'!D137),"Unknown")</f>
-        <v>6662.0</v>
-      </c>
-      <c r="N51" s="2">
-        <f>IF(COUNT('Turns'!E121,'Turns'!E137)=2,SUM('Turns'!E121,'Turns'!E137),"Unknown")</f>
-        <v>0.000116764874</v>
-      </c>
-      <c r="O51" s="2">
-        <f>IF(COUNT('Turns'!F121,'Turns'!F137)=2,SUM('Turns'!F121,'Turns'!F137),"Unknown")</f>
-        <v>0.00013324</v>
-      </c>
-      <c r="P51" s="2">
-        <f>IF(COUNT('Turns'!D124,'Turns'!D140)=2,SUM('Turns'!D124,'Turns'!D140),"Unknown")</f>
-        <v>1126.0</v>
-      </c>
-      <c r="Q51" s="2">
-        <f>IF(COUNT('Turns'!E124,'Turns'!E140)=2,SUM('Turns'!E124,'Turns'!E140),"Unknown")</f>
-        <v>0.000246692525</v>
-      </c>
-      <c r="R51" s="2">
-        <f>IF(COUNT('Turns'!F124,'Turns'!F140)=2,SUM('Turns'!F124,'Turns'!F140),"Unknown")</f>
-        <v>0.0002815</v>
-      </c>
-      <c r="S51" s="2">
-        <f>IF(COUNT('Turns'!D128,'Turns'!D143)=2,SUM('Turns'!D128,'Turns'!D143),"Unknown")</f>
-        <v>47.0</v>
-      </c>
-      <c r="T51" s="2">
-        <f>IF(COUNT('Turns'!E128,'Turns'!E143)=2,SUM('Turns'!E128,'Turns'!E143),"Unknown")</f>
-        <v>4.942614e-05</v>
-      </c>
-      <c r="U51" s="2">
-        <f>IF(COUNT('Turns'!F128,'Turns'!F143)=2,SUM('Turns'!F128,'Turns'!F143),"Unknown")</f>
-        <v>5.64e-05</v>
-      </c>
-      <c r="V51" s="2">
-        <f>IF(COUNT('Turns'!D127)=1,SUM('Turns'!D127),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="W51" s="2">
-        <f>IF(COUNT('Turns'!E127)=1,SUM('Turns'!E127),"Unknown")</f>
-        <v>7.36134e-06</v>
-      </c>
-      <c r="X51" s="2">
-        <f>IF(COUNT('Turns'!F127)=1,SUM('Turns'!F127),"Unknown")</f>
-        <v>8.4e-06</v>
-      </c>
-      <c r="Y51" s="2">
-        <f>IF(COUNT('Turns'!E132,'Turns'!E147)=2,SUM('Turns'!E132,'Turns'!E147),"Unknown")</f>
-        <v>0.000421296499</v>
-      </c>
-      <c r="Z51" s="2">
-        <f>IF(COUNT('Turns'!F132,'Turns'!F147)=2,SUM('Turns'!F132,'Turns'!F147),"Unknown")</f>
-        <v>0.00048074</v>
-      </c>
-      <c r="AA51" s="5">
-        <f>IF(ISNUMBER(Y51),ROUND(Y51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>42.0</v>
-      </c>
-      <c r="AB51" s="5">
-        <f>IF(ISNUMBER(Z51),ROUND(Z51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
-      </c>
-      <c r="AD51" s="1">
-        <v>3303.082</v>
-      </c>
-      <c r="AE51" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="52" spans="1:31" ht="54" customHeight="1">
-      <c r="A52" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B52" s="1">
-        <v>1</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H52" t="s">
-        <v>224</v>
-      </c>
-      <c r="I52" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD52" s="1">
-        <v>0.522</v>
-      </c>
-      <c r="AE52" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31" ht="54" customHeight="1">
-      <c r="A53" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B53" s="1">
-        <v>1</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H53" t="s">
-        <v>225</v>
-      </c>
-      <c r="I53" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD53" s="1">
-        <v>3.172</v>
-      </c>
-      <c r="AE53" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31" ht="54" customHeight="1">
-      <c r="A54" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B54" s="1">
-        <v>2</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="H54" t="s">
         <v>156</v>
       </c>
-      <c r="I54" t="s">
-        <v>225</v>
-      </c>
-      <c r="AD54" s="1">
-        <v>1.274</v>
-      </c>
-      <c r="AE54" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31" ht="54" customHeight="1">
-      <c r="A55" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B55" s="1">
-        <v>1</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H55" t="s">
-        <v>226</v>
-      </c>
-      <c r="I55" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD55" s="1">
-        <v>0.353</v>
-      </c>
-      <c r="AE55" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31" ht="54" customHeight="1">
-      <c r="A56" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B56" s="1">
-        <v>1</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="H56" t="s">
-        <v>227</v>
-      </c>
-      <c r="I56" t="s">
-        <v>223</v>
-      </c>
-      <c r="J56" s="2">
-        <f>IF(COUNT('Turns'!D122)=1,SUM('Turns'!D122),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K56" s="2">
-        <f>IF(COUNT('Turns'!E122)=1,SUM('Turns'!E122),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L56" s="2">
-        <f>IF(COUNT('Turns'!F122)=1,SUM('Turns'!F122),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M56" s="2">
-        <f>IF(COUNT('Turns'!D121)=1,SUM('Turns'!D121),"Unknown")</f>
-        <v>2842.0</v>
-      </c>
-      <c r="N56" s="2">
-        <f>IF(COUNT('Turns'!E121)=1,SUM('Turns'!E121),"Unknown")</f>
-        <v>4.9811734e-05</v>
-      </c>
-      <c r="O56" s="2">
-        <f>IF(COUNT('Turns'!F121)=1,SUM('Turns'!F121),"Unknown")</f>
-        <v>5.684e-05</v>
-      </c>
-      <c r="P56" s="2">
-        <f>IF(COUNT('Turns'!D124)=1,SUM('Turns'!D124),"Unknown")</f>
-        <v>978.0</v>
-      </c>
-      <c r="Q56" s="2">
-        <f>IF(COUNT('Turns'!E124)=1,SUM('Turns'!E124),"Unknown")</f>
-        <v>0.000214267575</v>
-      </c>
-      <c r="R56" s="2">
-        <f>IF(COUNT('Turns'!F124)=1,SUM('Turns'!F124),"Unknown")</f>
-        <v>0.0002445</v>
-      </c>
-      <c r="S56" s="2">
-        <f>IF(COUNT('Turns'!D128)=1,SUM('Turns'!D128),"Unknown")</f>
-        <v>31.0</v>
-      </c>
-      <c r="T56" s="2">
-        <f>IF(COUNT('Turns'!E128)=1,SUM('Turns'!E128),"Unknown")</f>
-        <v>3.260022e-05</v>
-      </c>
-      <c r="U56" s="2">
-        <f>IF(COUNT('Turns'!F128)=1,SUM('Turns'!F128),"Unknown")</f>
-        <v>3.72e-05</v>
-      </c>
-      <c r="V56" s="2">
-        <f>IF(COUNT('Turns'!D127)=1,SUM('Turns'!D127),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="W56" s="2">
-        <f>IF(COUNT('Turns'!E127)=1,SUM('Turns'!E127),"Unknown")</f>
-        <v>7.36134e-06</v>
-      </c>
-      <c r="X56" s="2">
-        <f>IF(COUNT('Turns'!F127)=1,SUM('Turns'!F127),"Unknown")</f>
-        <v>8.4e-06</v>
-      </c>
-      <c r="Y56" s="2">
-        <f>IF(COUNT('Turns'!E132)=1,SUM('Turns'!E132),"Unknown")</f>
-        <v>0.000304566679</v>
-      </c>
-      <c r="Z56" s="2">
-        <f>IF(COUNT('Turns'!F132)=1,SUM('Turns'!F132),"Unknown")</f>
-        <v>0.00034754</v>
-      </c>
-      <c r="AA56" s="5">
-        <f>IF(ISNUMBER(Y56),ROUND(Y56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>30.0</v>
-      </c>
-      <c r="AB56" s="5">
-        <f>IF(ISNUMBER(Z56),ROUND(Z56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
-      </c>
-      <c r="AD56" s="1">
-        <v>1942.237</v>
-      </c>
-      <c r="AE56" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="57" spans="1:31" ht="54" customHeight="1">
-      <c r="A57" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B57" s="1">
-        <v>2</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F57" s="1">
-        <v>3823</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="H57" t="s">
-        <v>159</v>
-      </c>
-      <c r="I57" t="s">
-        <v>227</v>
-      </c>
-      <c r="J57" s="2">
-        <f>IF(COUNT('Turns'!D122)=1,SUM('Turns'!D122),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K57" s="2">
-        <f>IF(COUNT('Turns'!E122)=1,SUM('Turns'!E122),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L57" s="2">
-        <f>IF(COUNT('Turns'!F122)=1,SUM('Turns'!F122),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M57" s="2">
-        <f>IF(COUNT('Turns'!D121)=1,SUM('Turns'!D121),"Unknown")</f>
-        <v>2842.0</v>
-      </c>
-      <c r="N57" s="2">
-        <f>IF(COUNT('Turns'!E121)=1,SUM('Turns'!E121),"Unknown")</f>
-        <v>4.9811734e-05</v>
-      </c>
-      <c r="O57" s="2">
-        <f>IF(COUNT('Turns'!F121)=1,SUM('Turns'!F121),"Unknown")</f>
-        <v>5.684e-05</v>
-      </c>
-      <c r="P57" s="2">
-        <f>IF(COUNT('Turns'!D124)=1,SUM('Turns'!D124),"Unknown")</f>
-        <v>978.0</v>
-      </c>
-      <c r="Q57" s="2">
-        <f>IF(COUNT('Turns'!E124)=1,SUM('Turns'!E124),"Unknown")</f>
-        <v>0.000214267575</v>
-      </c>
-      <c r="R57" s="2">
-        <f>IF(COUNT('Turns'!F124)=1,SUM('Turns'!F124),"Unknown")</f>
-        <v>0.0002445</v>
-      </c>
-      <c r="S57" s="2">
-        <f>IF(COUNT('Turns'!D128)=1,SUM('Turns'!D128),"Unknown")</f>
-        <v>31.0</v>
-      </c>
-      <c r="T57" s="2">
-        <f>IF(COUNT('Turns'!E128)=1,SUM('Turns'!E128),"Unknown")</f>
-        <v>3.260022e-05</v>
-      </c>
-      <c r="U57" s="2">
-        <f>IF(COUNT('Turns'!F128)=1,SUM('Turns'!F128),"Unknown")</f>
-        <v>3.72e-05</v>
-      </c>
-      <c r="V57" s="2">
-        <f>IF(COUNT('Turns'!D127)=1,SUM('Turns'!D127),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="W57" s="2">
-        <f>IF(COUNT('Turns'!E127)=1,SUM('Turns'!E127),"Unknown")</f>
-        <v>7.36134e-06</v>
-      </c>
-      <c r="X57" s="2">
-        <f>IF(COUNT('Turns'!F127)=1,SUM('Turns'!F127),"Unknown")</f>
-        <v>8.4e-06</v>
-      </c>
-      <c r="Y57" s="2">
-        <f>IF(COUNT('Turns'!E132)=1,SUM('Turns'!E132),"Unknown")</f>
-        <v>0.000304566679</v>
-      </c>
-      <c r="Z57" s="2">
-        <f>IF(COUNT('Turns'!F132)=1,SUM('Turns'!F132),"Unknown")</f>
-        <v>0.00034754</v>
-      </c>
-      <c r="AA57" s="5">
-        <f>IF(ISNUMBER(Y57),ROUND(Y57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>30.0</v>
-      </c>
-      <c r="AB57" s="5">
-        <f>IF(ISNUMBER(Z57),ROUND(Z57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>35.0</v>
-      </c>
-      <c r="AC57" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AD57" s="1">
-        <v>1939.813</v>
-      </c>
-      <c r="AE57" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="58" spans="1:31" ht="54" customHeight="1">
-      <c r="A58" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B58" s="1">
-        <v>1</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H58" t="s">
-        <v>228</v>
-      </c>
-      <c r="I58" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD58" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="AE58" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31" ht="54" customHeight="1">
-      <c r="A59" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B59" s="1">
-        <v>1</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H59" t="s">
-        <v>229</v>
-      </c>
-      <c r="I59" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD59" s="1">
-        <v>5.563</v>
-      </c>
-      <c r="AE59" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="60" spans="1:31" ht="54" customHeight="1">
-      <c r="A60" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B60" s="1">
-        <v>2</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="H60" t="s">
-        <v>161</v>
-      </c>
-      <c r="I60" t="s">
-        <v>229</v>
-      </c>
-      <c r="AD60" s="1">
-        <v>1.433</v>
-      </c>
-      <c r="AE60" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="61" spans="1:31" ht="54" customHeight="1">
-      <c r="A61" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B61" s="1">
-        <v>1</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H61" t="s">
-        <v>230</v>
-      </c>
-      <c r="I61" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD61" s="1">
-        <v>0.579</v>
-      </c>
-      <c r="AE61" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="62" spans="1:31" ht="54" customHeight="1">
-      <c r="A62" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="H62" t="s">
-        <v>231</v>
-      </c>
-      <c r="I62" t="s">
-        <v>223</v>
-      </c>
-      <c r="J62" s="2">
-        <f>IF(COUNT('Turns'!D138)=1,SUM('Turns'!D138),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K62" s="2">
-        <f>IF(COUNT('Turns'!E138)=1,SUM('Turns'!E138),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L62" s="2">
-        <f>IF(COUNT('Turns'!F138)=1,SUM('Turns'!F138),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M62" s="2">
-        <f>IF(COUNT('Turns'!D137)=1,SUM('Turns'!D137),"Unknown")</f>
-        <v>3820.0</v>
-      </c>
-      <c r="N62" s="2">
-        <f>IF(COUNT('Turns'!E137)=1,SUM('Turns'!E137),"Unknown")</f>
-        <v>6.695314e-05</v>
-      </c>
-      <c r="O62" s="2">
-        <f>IF(COUNT('Turns'!F137)=1,SUM('Turns'!F137),"Unknown")</f>
-        <v>7.64e-05</v>
-      </c>
-      <c r="P62" s="2">
-        <f>IF(COUNT('Turns'!D140)=1,SUM('Turns'!D140),"Unknown")</f>
-        <v>148.0</v>
-      </c>
-      <c r="Q62" s="2">
-        <f>IF(COUNT('Turns'!E140)=1,SUM('Turns'!E140),"Unknown")</f>
-        <v>3.242495e-05</v>
-      </c>
-      <c r="R62" s="2">
-        <f>IF(COUNT('Turns'!F140)=1,SUM('Turns'!F140),"Unknown")</f>
-        <v>3.7e-05</v>
-      </c>
-      <c r="S62" s="2">
-        <f>IF(COUNT('Turns'!D143)=1,SUM('Turns'!D143),"Unknown")</f>
-        <v>16.0</v>
-      </c>
-      <c r="T62" s="2">
-        <f>IF(COUNT('Turns'!E143)=1,SUM('Turns'!E143),"Unknown")</f>
-        <v>1.682592e-05</v>
-      </c>
-      <c r="U62" s="2">
-        <f>IF(COUNT('Turns'!F143)=1,SUM('Turns'!F143),"Unknown")</f>
-        <v>1.92e-05</v>
-      </c>
-      <c r="V62" s="2">
-        <v>0</v>
-      </c>
-      <c r="W62" s="2">
-        <v>0</v>
-      </c>
-      <c r="X62" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="2">
-        <f>IF(COUNT('Turns'!E147)=1,SUM('Turns'!E147),"Unknown")</f>
-        <v>0.00011672982</v>
-      </c>
-      <c r="Z62" s="2">
-        <f>IF(COUNT('Turns'!F147)=1,SUM('Turns'!F147),"Unknown")</f>
-        <v>0.0001332</v>
-      </c>
-      <c r="AA62" s="5">
-        <f>IF(ISNUMBER(Y62),ROUND(Y62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-      <c r="AB62" s="5">
-        <f>IF(ISNUMBER(Z62),ROUND(Z62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="AD62" s="1">
-        <v>1336.344</v>
-      </c>
-      <c r="AE62" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="63" spans="1:31" ht="54" customHeight="1">
-      <c r="A63" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F63" s="1">
-        <v>3971</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="H63" t="s">
-        <v>164</v>
-      </c>
-      <c r="I63" t="s">
-        <v>231</v>
-      </c>
-      <c r="J63" s="2">
-        <f>IF(COUNT('Turns'!D138)=1,SUM('Turns'!D138),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K63" s="2">
-        <f>IF(COUNT('Turns'!E138)=1,SUM('Turns'!E138),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L63" s="2">
-        <f>IF(COUNT('Turns'!F138)=1,SUM('Turns'!F138),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M63" s="2">
-        <f>IF(COUNT('Turns'!D137)=1,SUM('Turns'!D137),"Unknown")</f>
-        <v>3820.0</v>
-      </c>
-      <c r="N63" s="2">
-        <f>IF(COUNT('Turns'!E137)=1,SUM('Turns'!E137),"Unknown")</f>
-        <v>6.695314e-05</v>
-      </c>
-      <c r="O63" s="2">
-        <f>IF(COUNT('Turns'!F137)=1,SUM('Turns'!F137),"Unknown")</f>
-        <v>7.64e-05</v>
-      </c>
-      <c r="P63" s="2">
-        <f>IF(COUNT('Turns'!D140)=1,SUM('Turns'!D140),"Unknown")</f>
-        <v>148.0</v>
-      </c>
-      <c r="Q63" s="2">
-        <f>IF(COUNT('Turns'!E140)=1,SUM('Turns'!E140),"Unknown")</f>
-        <v>3.242495e-05</v>
-      </c>
-      <c r="R63" s="2">
-        <f>IF(COUNT('Turns'!F140)=1,SUM('Turns'!F140),"Unknown")</f>
-        <v>3.7e-05</v>
-      </c>
-      <c r="S63" s="2">
-        <f>IF(COUNT('Turns'!D143)=1,SUM('Turns'!D143),"Unknown")</f>
-        <v>16.0</v>
-      </c>
-      <c r="T63" s="2">
-        <f>IF(COUNT('Turns'!E143)=1,SUM('Turns'!E143),"Unknown")</f>
-        <v>1.682592e-05</v>
-      </c>
-      <c r="U63" s="2">
-        <f>IF(COUNT('Turns'!F143)=1,SUM('Turns'!F143),"Unknown")</f>
-        <v>1.92e-05</v>
-      </c>
-      <c r="V63" s="2">
-        <v>0</v>
-      </c>
-      <c r="W63" s="2">
-        <v>0</v>
-      </c>
-      <c r="X63" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y63" s="2">
-        <f>IF(COUNT('Turns'!E147)=1,SUM('Turns'!E147),"Unknown")</f>
-        <v>0.00011672982</v>
-      </c>
-      <c r="Z63" s="2">
-        <f>IF(COUNT('Turns'!F147)=1,SUM('Turns'!F147),"Unknown")</f>
-        <v>0.0001332</v>
-      </c>
-      <c r="AA63" s="5">
-        <f>IF(ISNUMBER(Y63),ROUND(Y63*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-      <c r="AB63" s="5">
-        <f>IF(ISNUMBER(Z63),ROUND(Z63*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="AC63" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="AD63" s="1">
-        <v>1333.261</v>
-      </c>
-      <c r="AE63" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="64" spans="1:31" ht="54" customHeight="1">
-      <c r="A64" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H64" t="s">
-        <v>232</v>
-      </c>
-      <c r="I64" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD64" s="1">
-        <v>0.781</v>
-      </c>
-      <c r="AE64" s="1" t="s">
-        <v>173</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE64">
+  <conditionalFormatting sqref="A2:AE42">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>
@@ -8035,7 +5667,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87635</v>
+        <v>0.87974</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>
